--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -5173,7 +5173,7 @@
     <row r="236" ht="22" customHeight="1">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Key: ✅ Arrive dam by 8:45am — reach Kebema bridge 10:30am · beats 45min photo queue by midday  |  ️ Swarovski: go if raining · skip if clear · 5min off A12 at Wattens · no booking needed  |   Achensee: if kids tired → skip boat · park Pertisau + Gaisalm promenade walk (free, same views)</t>
+          <t>Key: ✅ Arrive dam by 8:45am — reach Kebema bridge 10:30am · beats 45min photo queue by midday  |  ☀️ Plan A (sunny): Achensee — steamboat ~€22/adult OR free Gaisalm promenade walk if kids tired  |  ️ Plan B (rain/cloudy): Swarovski Crystal Worlds — 5min off A12 · ~€22/adult · no booking needed</t>
         </is>
       </c>
     </row>
@@ -5321,51 +5321,51 @@
         </is>
       </c>
     </row>
-    <row r="243" ht="30" customHeight="1">
-      <c r="A243" s="16" t="inlineStr"/>
-      <c r="B243" s="17" t="inlineStr">
+    <row r="243" ht="50" customHeight="1">
+      <c r="A243" s="6" t="inlineStr"/>
+      <c r="B243" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C243" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D243" s="17" t="inlineStr"/>
-      <c r="E243" s="18" t="inlineStr">
-        <is>
-          <t>⭐ Swarovski Crystal Worlds (Wattens) — ️ Weather-dependent: — ~€22/adult · allow 1.5–2hrs</t>
-        </is>
-      </c>
-      <c r="F243" s="19" t="inlineStr">
-        <is>
-          <t>€22 / 2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="30" customHeight="1">
-      <c r="A244" s="6" t="inlineStr"/>
-      <c r="B244" s="7" t="inlineStr">
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D243" s="7" t="inlineStr"/>
+      <c r="E243" s="9" t="inlineStr">
+        <is>
+          <t>☀️ Plan A — Sunny: Achensee — 50 min drive north from Schlegeis · park at Pertisau · Option 1: Achensee steamboat ~€22/adult · allow 1.5hrs · Option 2 (kids tired): Gaisalm promenade walk — free · same fjord-like views ·</t>
+        </is>
+      </c>
+      <c r="F243" s="10" t="inlineStr">
+        <is>
+          <t>50 min / €22 / 5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="50" customHeight="1">
+      <c r="A244" s="20" t="inlineStr"/>
+      <c r="B244" s="21" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C244" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D244" s="7" t="inlineStr"/>
-      <c r="E244" s="9" t="inlineStr">
-        <is>
-          <t>➕ Optional: Achensee steamboat (Pertisau) — 50 min drive north from Schlegeis · ~€22/adult</t>
-        </is>
-      </c>
-      <c r="F244" s="10" t="inlineStr">
-        <is>
-          <t>50 min / €22</t>
+      <c r="C244" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D244" s="21" t="inlineStr"/>
+      <c r="E244" s="23" t="inlineStr">
+        <is>
+          <t>️ Plan B — Rain/Cloudy: Swarovski Crystal Worlds — 5 min off A12 at Wattens · ~€22/adult · allow 1.5–2hrs · indoor immersive art installation · perfect rainy-day refuge after cold wet Olpererhütte hike · no booking neede</t>
+        </is>
+      </c>
+      <c r="F244" s="24" t="inlineStr">
+        <is>
+          <t>5 min / €22 / 2hr</t>
         </is>
       </c>
     </row>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F311"/>
+  <dimension ref="A1:F312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5514,18 +5514,18 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>Timeline: Tonight: ATM Ehrwald €60–80 cash ▸ 8:30am Bichlbach ▸ 8:45am Ehrwalder Almbahn €26 ▸ Zugspitze platform ▸ 9:15am Seebensee mirror (before 10:30am) ▸ 10:15am Drachensee climb ▸ 11:30am Coburger Hütte Kaiserschmarrn ▸ 1pm descent ▸ 2:30pm Bichlbach + pack ▸ 7:30pm Heiterwanger See sunset</t>
+          <t>Timeline: Tonight: ATM Ehrwald €60–80 ▸ 7:45am Bichlbach ▸ 8:00am Ehrwalder Almbahn (first car) ▸ 8:10am hike ▸ 9:45am Seebensee mirror ▸ 10:15am Drachensee climb ▸ 11:00am Coburger Hütte Kaiserschmarrn ▸ 12:45pm descent ▸ 2:45pm back at car ▸ 3pm Bichlbach ▸ 7:30pm Heiterwanger See sunset</t>
         </is>
       </c>
     </row>
     <row r="255" ht="22" customHeight="1">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>Key: ✅ ATM in Ehrwald tonight — €60–80 cash · Coburger Hütte cash only · no card reader  |   Seebensee mirror reflection before 10:30am — winds create ripples by midday · early start essential  |  ⚠️ Drachensee path slippery if rained Jul 2 — best-grip boots · 260m steep climb</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="40" customHeight="1">
+          <t>Key: ✅ ATM in Ehrwald tonight — €60–80 cash · Coburger Hütte cash only · no card reader  |  ✅ 7:45am departure — first cable car 8:00am · arrive Seebensee 9:45am · beats 10:30am winds  |  ⚠️ Seebensee mirror reflection before 10:30am — winds create ripples by midday · 9:45am arrival ✅  |  ⚠️ Drachensee path slippery if rained Jul 2 — best-grip boots · 217m steep climb · 30–45 min  |  ➕ E-bikes optional at valley station — cuts Seebensee hike from 1.5hrs to 25 min · saves legs for Drachensee</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="50" customHeight="1">
       <c r="A256" s="16" t="inlineStr"/>
       <c r="B256" s="17" t="inlineStr">
         <is>
@@ -5540,12 +5540,12 @@
       <c r="D256" s="17" t="inlineStr"/>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Tonight (Jul 2 evening): ATM in Ehrwald — withdraw €60–80 cash for the family · Coburger Hütte is cash only — no card reader on the mountain</t>
+          <t>Tonight (Jul 2 evening): ATM in Ehrwald — withdraw €60–80 cash for the family · Coburger Hütte is cash only — no card reader on the mountain · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
         </is>
       </c>
       <c r="F256" s="19" t="inlineStr">
         <is>
-          <t>€60</t>
+          <t>€60 / €12 / €14</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       <c r="D257" s="7" t="inlineStr"/>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>⏰ 8:30am — Depart Bichlbach — 5 min drive to the Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~8:35am</t>
+          <t>7:45am — Depart Bichlbach — 5 min drive to Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~7:55am</t>
         </is>
       </c>
       <c r="F257" s="10" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
     </row>
-    <row r="258" ht="32" customHeight="1">
+    <row r="258" ht="44" customHeight="1">
       <c r="A258" s="16" t="inlineStr"/>
       <c r="B258" s="17" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
       <c r="D258" s="17" t="inlineStr"/>
       <c r="E258" s="18" t="inlineStr">
         <is>
-          <t>⭐ 8:45am — Ehrwalder Almbahn — ~€26/adult · free parking · take 5 min at top for Zugspitze platform view</t>
+          <t>⭐ 8:00am — Ehrwalder Almbahn — first cable car of the day · ~€26/adult · free parking · 5 min at top for Zugspitze platform view · ⚠️ July high season: opens 8:00am</t>
         </is>
       </c>
       <c r="F258" s="19" t="inlineStr">
@@ -5597,180 +5597,191 @@
         </is>
       </c>
     </row>
-    <row r="259" ht="31" customHeight="1">
-      <c r="A259" s="6" t="inlineStr"/>
-      <c r="B259" s="7" t="inlineStr">
+    <row r="259" ht="50" customHeight="1">
+      <c r="A259" s="20" t="inlineStr"/>
+      <c r="B259" s="21" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C259" s="8" t="inlineStr">
+      <c r="C259" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D259" s="21" t="inlineStr"/>
+      <c r="E259" s="23" t="inlineStr">
+        <is>
+          <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am · ➕ E-bikes available at valley station — cuts hike to 25 min if family wants to save le</t>
+        </is>
+      </c>
+      <c r="F259" s="24" t="inlineStr">
+        <is>
+          <t>6km / 5hr / 25 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="50" customHeight="1">
+      <c r="A260" s="6" t="inlineStr"/>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C260" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D259" s="7" t="inlineStr"/>
-      <c r="E259" s="9" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 9:15am — Seebensee — 1.5km flat path · mirror reflection before 10:30am (winds pick up after)</t>
-        </is>
-      </c>
-      <c r="F259" s="10" t="inlineStr">
-        <is>
-          <t>5km</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="32" customHeight="1">
-      <c r="A260" s="20" t="inlineStr"/>
-      <c r="B260" s="21" t="inlineStr">
+      <c r="D260" s="7" t="inlineStr"/>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 9:45am — Seebensee mirror reflection — crystal-clear turquoise water · Zugspitze reflected · winds pick up after 10:30am — 9:45am arrival is perfectly timed · allow 30 min · benches along the southern shore</t>
+        </is>
+      </c>
+      <c r="F260" s="10" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="44" customHeight="1">
+      <c r="A261" s="20" t="inlineStr"/>
+      <c r="B261" s="21" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C260" s="22" t="inlineStr">
+      <c r="C261" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D260" s="21" t="inlineStr"/>
-      <c r="E260" s="23" t="inlineStr">
-        <is>
-          <t>10:15am — Drachensee ascent — 1km steep · 260m gain · ⚠️ slippery if rained Jul 2 · best-grip boots</t>
-        </is>
-      </c>
-      <c r="F260" s="24" t="inlineStr">
-        <is>
-          <t>1km</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="33" customHeight="1">
-      <c r="A261" s="16" t="inlineStr"/>
-      <c r="B261" s="17" t="inlineStr">
+      <c r="D261" s="21" t="inlineStr"/>
+      <c r="E261" s="23" t="inlineStr">
+        <is>
+          <t>10:15am — Drachensee ascent — 1.4km · 217m elevation gain · 30–45 min · ⚠️ slippery if rained Jul 2 · best-grip boots · steeper than Seebensee section but short</t>
+        </is>
+      </c>
+      <c r="F261" s="24" t="inlineStr">
+        <is>
+          <t>4km / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="46" customHeight="1">
+      <c r="A262" s="16" t="inlineStr"/>
+      <c r="B262" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C261" s="16" t="inlineStr">
+      <c r="C262" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D261" s="17" t="inlineStr"/>
-      <c r="E261" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 11:30am — Coburger Hütte (2,026m) — legendary Kaiserschmarrn — MUST · cash only — bring €60–80 family</t>
-        </is>
-      </c>
-      <c r="F261" s="19" t="inlineStr">
-        <is>
-          <t>€60</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="39" customHeight="1">
-      <c r="A262" s="6" t="inlineStr"/>
-      <c r="B262" s="7" t="inlineStr">
+      <c r="D262" s="17" t="inlineStr"/>
+      <c r="E262" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring €60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
+        </is>
+      </c>
+      <c r="F262" s="19" t="inlineStr">
+        <is>
+          <t>€60 / 1hr / 45min</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" s="20" t="inlineStr"/>
+      <c r="B263" s="21" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C262" s="8" t="inlineStr">
+      <c r="C263" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D263" s="21" t="inlineStr"/>
+      <c r="E263" s="23" t="inlineStr">
+        <is>
+          <t>12:45pm — Descent to cable car station — ~1.5hrs back down · same trail · arrive top station ~2:15pm · cable car down · back at car ~2:45pm</t>
+        </is>
+      </c>
+      <c r="F263" s="24" t="inlineStr">
+        <is>
+          <t>5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="39" customHeight="1">
+      <c r="A264" s="6" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C264" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D262" s="7" t="inlineStr"/>
-      <c r="E262" s="9" t="inlineStr">
-        <is>
-          <t>1:00pm — Descent to cable car station — back down the ridge · ~1.5hrs · back at Ehrwald valley station ~2:30pm · drive 5 min to Bichlbach</t>
-        </is>
-      </c>
-      <c r="F262" s="10" t="inlineStr">
-        <is>
-          <t>5hr / 5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="39" customHeight="1">
-      <c r="A263" s="6" t="inlineStr"/>
-      <c r="B263" s="7" t="inlineStr">
+      <c r="D264" s="7" t="inlineStr"/>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>3:00pm — Back at Landhaus Bichlbach — shower · rest legs · pack bags for tomorrow · checkout 8am — Neuschwanstein 9:30am · alarm 7:00am</t>
+        </is>
+      </c>
+      <c r="F264" s="10" t="inlineStr"/>
+    </row>
+    <row r="265" ht="46" customHeight="1">
+      <c r="A265" s="16" t="inlineStr"/>
+      <c r="B265" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C263" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D263" s="7" t="inlineStr"/>
-      <c r="E263" s="9" t="inlineStr">
-        <is>
-          <t>2:30pm — Back at Landhaus Bichlbach — relax · shower · pack bags for tomorrow · checkout is 8am — Neuschwanstein 9:30am · alarm 7:00am</t>
-        </is>
-      </c>
-      <c r="F263" s="10" t="inlineStr"/>
-    </row>
-    <row r="264" ht="29" customHeight="1">
-      <c r="A264" s="16" t="inlineStr"/>
-      <c r="B264" s="17" t="inlineStr">
+      <c r="C265" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D265" s="17" t="inlineStr"/>
+      <c r="E265" s="18" t="inlineStr">
+        <is>
+          <t>⭐ 7:30pm — Heiterwanger See sunset walk — 20 min walk from Landhaus along the Panoramaweg · flat · easy · clears the lactic acid · alpenglow after sunset on the higher path</t>
+        </is>
+      </c>
+      <c r="F265" s="19" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="39" customHeight="1">
+      <c r="A266" s="11" t="inlineStr"/>
+      <c r="B266" s="12" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C264" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D264" s="17" t="inlineStr"/>
-      <c r="E264" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 7:30pm — Heiterwanger See sunset walk — 20 min walk from Landhaus along the Panoramaweg</t>
-        </is>
-      </c>
-      <c r="F264" s="19" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="39" customHeight="1">
-      <c r="A265" s="11" t="inlineStr"/>
-      <c r="B265" s="12" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C265" s="13" t="inlineStr">
+      <c r="C266" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D265" s="12" t="inlineStr"/>
-      <c r="E265" s="14" t="inlineStr">
-        <is>
-          <t>Dinner — Gasthof Bichlbach or hotel restaurant · early dinner + early bed · alarm 7:00am tomorrow · Neuschwanstein 9:30am — last big day</t>
-        </is>
-      </c>
-      <c r="F265" s="15" t="inlineStr"/>
-    </row>
-    <row r="266" ht="33" customHeight="1">
-      <c r="A266" s="30" t="inlineStr"/>
-      <c r="B266" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C266" s="32" t="inlineStr">
-        <is>
-          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="34" customHeight="1">
+      <c r="D266" s="12" t="inlineStr"/>
+      <c r="E266" s="14" t="inlineStr">
+        <is>
+          <t>Dinner — Gasthof Bichlbach or hotel restaurant — early dinner + early bed · alarm 7:00am tomorrow · Neuschwanstein 9:30am — last big day</t>
+        </is>
+      </c>
+      <c r="F266" s="15" t="inlineStr"/>
+    </row>
+    <row r="267" ht="33" customHeight="1">
       <c r="A267" s="30" t="inlineStr"/>
       <c r="B267" s="31" t="inlineStr">
         <is>
@@ -5779,7 +5790,7 @@
       </c>
       <c r="C267" s="32" t="inlineStr">
         <is>
-          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
+          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5803,7 @@
       </c>
       <c r="C268" s="32" t="inlineStr">
         <is>
-          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
+          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
         </is>
       </c>
     </row>
@@ -5805,88 +5816,77 @@
       </c>
       <c r="C269" s="32" t="inlineStr">
         <is>
+          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="34" customHeight="1">
+      <c r="A270" s="30" t="inlineStr"/>
+      <c r="B270" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C270" s="32" t="inlineStr">
+        <is>
           <t>Panoramaweg for Heiterwanger See — take the higher Panoramaweg trail not the lakeside path · stays above the valley floor to catch alpenglow after sunset · 20 min from hotel · flat + easy</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="3" customHeight="1">
-      <c r="A270" s="33" t="n"/>
-      <c r="B270" s="33" t="n"/>
-      <c r="C270" s="33" t="n"/>
-      <c r="D270" s="33" t="n"/>
-      <c r="E270" s="33" t="n"/>
-      <c r="F270" s="33" t="n"/>
-    </row>
-    <row r="271" ht="20" customHeight="1">
-      <c r="A271" s="3" t="inlineStr">
+    <row r="271" ht="3" customHeight="1">
+      <c r="A271" s="33" t="n"/>
+      <c r="B271" s="33" t="n"/>
+      <c r="C271" s="33" t="n"/>
+      <c r="D271" s="33" t="n"/>
+      <c r="E271" s="33" t="n"/>
+      <c r="F271" s="33" t="n"/>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>DAY 15  |  Jul 4  |  The Fairy Tale Finale — Neuschwanstein · Ebenalp · Aescher → ZRH  |  ~280 km / 174 mi  ~3h 30m · Neuschwanstein → Ebenalp → ZRH</t>
         </is>
       </c>
     </row>
-    <row r="272" ht="15" customHeight="1">
-      <c r="A272" s="4" t="inlineStr">
+    <row r="273" ht="15" customHeight="1">
+      <c r="A273" s="4" t="inlineStr">
         <is>
           <t>Timeline: 7:30am Bichlbach checkout ▸ 8:15am P4 Neuschwanstein ▸ 8:30am Marienbrücke FIRST ▸ 9:20am castle gate ▸ 9:30am tour ▸ 11:30am drive Bregenz tunnel ▸ 1:15pm Wasserauen ▸ 1:30pm Ebenalp cable car ▸ 2pm Aescher (before Swing event 5pm) ▸ 4pm descent ▸ 6pm ZRH hotel + return car tonight ▸ 5am alarm tomorrow</t>
         </is>
       </c>
     </row>
-    <row r="273" ht="22" customHeight="1">
-      <c r="A273" s="5" t="inlineStr">
+    <row r="274" ht="22" customHeight="1">
+      <c r="A274" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Marienbrücke BEFORE the tour — go at 8:30am · virtually no queue · by 10am it's packed  |  ⚠️ Castle gate by 9:20am — NOT the ticket centre · guide will not wait for latecomers  |   Return car TONIGHT — drop bags at hotel · 5 min to Europcar ZRH · open until midnight · eliminates 5:30am stress</t>
         </is>
       </c>
     </row>
-    <row r="274" ht="34" customHeight="1">
-      <c r="A274" s="6" t="inlineStr"/>
-      <c r="B274" s="7" t="inlineStr">
+    <row r="275" ht="34" customHeight="1">
+      <c r="A275" s="6" t="inlineStr"/>
+      <c r="B275" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C274" s="8" t="inlineStr">
+      <c r="C275" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D274" s="7" t="inlineStr"/>
-      <c r="E274" s="9" t="inlineStr">
+      <c r="D275" s="7" t="inlineStr"/>
+      <c r="E275" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:30am — Checkout Landhaus Bichlbach + depart — 30 min earlier than original plan · 45 min drive to Schwangau</t>
         </is>
       </c>
-      <c r="F274" s="10" t="inlineStr">
+      <c r="F275" s="10" t="inlineStr">
         <is>
           <t>30 min / 45 min</t>
         </is>
       </c>
     </row>
-    <row r="275" ht="25" customHeight="1">
-      <c r="A275" s="16" t="inlineStr"/>
-      <c r="B275" s="17" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C275" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D275" s="17" t="inlineStr"/>
-      <c r="E275" s="18" t="inlineStr">
-        <is>
-          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
-        </is>
-      </c>
-      <c r="F275" s="19" t="inlineStr">
-        <is>
-          <t>CHF 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="31" customHeight="1">
+    <row r="276" ht="25" customHeight="1">
       <c r="A276" s="16" t="inlineStr"/>
       <c r="B276" s="17" t="inlineStr">
         <is>
@@ -5901,16 +5901,16 @@
       <c r="D276" s="17" t="inlineStr"/>
       <c r="E276" s="18" t="inlineStr">
         <is>
-          <t>8:15am — Park P4, Schwangau — €7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
+          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
         </is>
       </c>
       <c r="F276" s="19" t="inlineStr">
         <is>
-          <t>€7 / 10 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="35" customHeight="1">
+          <t>CHF 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="31" customHeight="1">
       <c r="A277" s="16" t="inlineStr"/>
       <c r="B277" s="17" t="inlineStr">
         <is>
@@ -5925,16 +5925,16 @@
       <c r="D277" s="17" t="inlineStr"/>
       <c r="E277" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
+          <t>8:15am — Park P4, Schwangau — €7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
         </is>
       </c>
       <c r="F277" s="19" t="inlineStr">
         <is>
-          <t>10 min / 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="29" customHeight="1">
+          <t>€7 / 10 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="35" customHeight="1">
       <c r="A278" s="16" t="inlineStr"/>
       <c r="B278" s="17" t="inlineStr">
         <is>
@@ -5949,12 +5949,16 @@
       <c r="D278" s="17" t="inlineStr"/>
       <c r="E278" s="18" t="inlineStr">
         <is>
-          <t>⚠️ 9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
-        </is>
-      </c>
-      <c r="F278" s="19" t="inlineStr"/>
-    </row>
-    <row r="279" ht="34" customHeight="1">
+          <t>⭐ ⭐ 8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
+        </is>
+      </c>
+      <c r="F278" s="19" t="inlineStr">
+        <is>
+          <t>10 min / 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="29" customHeight="1">
       <c r="A279" s="16" t="inlineStr"/>
       <c r="B279" s="17" t="inlineStr">
         <is>
@@ -5969,217 +5973,224 @@
       <c r="D279" s="17" t="inlineStr"/>
       <c r="E279" s="18" t="inlineStr">
         <is>
+          <t>⚠️ 9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
+        </is>
+      </c>
+      <c r="F279" s="19" t="inlineStr"/>
+    </row>
+    <row r="280" ht="34" customHeight="1">
+      <c r="A280" s="16" t="inlineStr"/>
+      <c r="B280" s="17" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C280" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D280" s="17" t="inlineStr"/>
+      <c r="E280" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
         </is>
       </c>
-      <c r="F279" s="19" t="inlineStr">
+      <c r="F280" s="19" t="inlineStr">
         <is>
           <t>40 min</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="37" customHeight="1">
-      <c r="A280" s="6" t="inlineStr"/>
-      <c r="B280" s="7" t="inlineStr">
+    <row r="281" ht="37" customHeight="1">
+      <c r="A281" s="6" t="inlineStr"/>
+      <c r="B281" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C280" s="8" t="inlineStr">
+      <c r="C281" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D280" s="7" t="inlineStr"/>
-      <c r="E280" s="9" t="inlineStr">
+      <c r="D281" s="7" t="inlineStr"/>
+      <c r="E281" s="9" t="inlineStr">
         <is>
           <t>11:30am — Depart Neuschwanstein → Wasserauen — 1hr 30min drive · ⚠️ Saturday = absolute peak crowds on all German/Swiss roads</t>
         </is>
       </c>
-      <c r="F280" s="10" t="inlineStr">
+      <c r="F281" s="10" t="inlineStr">
         <is>
           <t>1hr / 30min</t>
         </is>
       </c>
     </row>
-    <row r="281" ht="30" customHeight="1">
-      <c r="A281" s="16" t="inlineStr"/>
-      <c r="B281" s="17" t="inlineStr">
+    <row r="282" ht="30" customHeight="1">
+      <c r="A282" s="16" t="inlineStr"/>
+      <c r="B282" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C281" s="16" t="inlineStr">
+      <c r="C282" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D281" s="17" t="inlineStr"/>
-      <c r="E281" s="18" t="inlineStr">
+      <c r="D282" s="17" t="inlineStr"/>
+      <c r="E282" s="18" t="inlineStr">
         <is>
           <t>1:15pm — Park at Wasserauen cable car — CHF 36/adult return (2026 rate) · runs every 15 min</t>
         </is>
       </c>
-      <c r="F281" s="19" t="inlineStr">
+      <c r="F282" s="19" t="inlineStr">
         <is>
           <t>CHF 36 / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="282" ht="32" customHeight="1">
-      <c r="A282" s="20" t="inlineStr"/>
-      <c r="B282" s="21" t="inlineStr">
+    <row r="283" ht="32" customHeight="1">
+      <c r="A283" s="20" t="inlineStr"/>
+      <c r="B283" s="21" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C282" s="22" t="inlineStr">
+      <c r="C283" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D282" s="21" t="inlineStr"/>
-      <c r="E282" s="23" t="inlineStr">
+      <c r="D283" s="21" t="inlineStr"/>
+      <c r="E283" s="23" t="inlineStr">
         <is>
           <t>⭐ 1:30pm — Ebenalp cable car — CHF 36/adult · 6 min · last descent 6pm · ⚠️ caves 10°C — pack a layer</t>
         </is>
       </c>
-      <c r="F282" s="24" t="inlineStr">
+      <c r="F283" s="24" t="inlineStr">
         <is>
           <t>CHF 36 / 6 min</t>
         </is>
       </c>
     </row>
-    <row r="283" ht="35" customHeight="1">
-      <c r="A283" s="16" t="inlineStr"/>
-      <c r="B283" s="17" t="inlineStr">
+    <row r="284" ht="35" customHeight="1">
+      <c r="A284" s="16" t="inlineStr"/>
+      <c r="B284" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C283" s="16" t="inlineStr">
+      <c r="C284" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D283" s="17" t="inlineStr"/>
-      <c r="E283" s="18" t="inlineStr">
+      <c r="D284" s="17" t="inlineStr"/>
+      <c r="E284" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 2:00pm — Berggasthaus Aescher — arrive before 4pm ·  Swing event 5pm · Chäs-Chnöpfli or Rösti · Siedwurst if full</t>
         </is>
       </c>
-      <c r="F283" s="19" t="inlineStr"/>
-    </row>
-    <row r="284" ht="39" customHeight="1">
-      <c r="A284" s="6" t="inlineStr"/>
-      <c r="B284" s="7" t="inlineStr">
+      <c r="F284" s="19" t="inlineStr"/>
+    </row>
+    <row r="285" ht="39" customHeight="1">
+      <c r="A285" s="6" t="inlineStr"/>
+      <c r="B285" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C284" s="8" t="inlineStr">
+      <c r="C285" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D284" s="7" t="inlineStr"/>
-      <c r="E284" s="9" t="inlineStr">
+      <c r="D285" s="7" t="inlineStr"/>
+      <c r="E285" s="9" t="inlineStr">
         <is>
           <t>4:00pm — Cable car down + drive to ZRH — walk 25 min back up to Ebenalp top station · cable car down · ~2hr drive to Zurich Airport area</t>
         </is>
       </c>
-      <c r="F284" s="10" t="inlineStr">
+      <c r="F285" s="10" t="inlineStr">
         <is>
           <t>25 min / ~2hr</t>
         </is>
       </c>
     </row>
-    <row r="285" ht="33" customHeight="1">
-      <c r="A285" s="16" t="inlineStr"/>
-      <c r="B285" s="17" t="inlineStr">
+    <row r="286" ht="33" customHeight="1">
+      <c r="A286" s="16" t="inlineStr"/>
+      <c r="B286" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C285" s="16" t="inlineStr">
+      <c r="C286" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D285" s="17" t="inlineStr"/>
-      <c r="E285" s="18" t="inlineStr">
+      <c r="D286" s="17" t="inlineStr"/>
+      <c r="E286" s="18" t="inlineStr">
         <is>
           <t>❌ Rhine Falls — SKIP TODAY — adding 45 min detour north on a peak Saturday risks missing car return window</t>
         </is>
       </c>
-      <c r="F285" s="19" t="inlineStr">
+      <c r="F286" s="19" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="286" ht="50" customHeight="1">
-      <c r="A286" s="6" t="inlineStr"/>
-      <c r="B286" s="7" t="inlineStr">
+    <row r="287" ht="50" customHeight="1">
+      <c r="A287" s="6" t="inlineStr"/>
+      <c r="B287" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C286" s="8" t="inlineStr">
+      <c r="C287" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D286" s="7" t="inlineStr"/>
-      <c r="E286" s="9" t="inlineStr">
+      <c r="D287" s="7" t="inlineStr"/>
+      <c r="E287" s="9" t="inlineStr">
         <is>
           <t>Return Europcar ZRH tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH return · return by 11:30pm · Hilton shuttle back · check Booking.com email for return confirmation</t>
         </is>
       </c>
-      <c r="F286" s="10" t="inlineStr">
+      <c r="F287" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="28" customHeight="1">
-      <c r="A287" s="25" t="inlineStr"/>
-      <c r="B287" s="26" t="inlineStr">
+    <row r="288" ht="28" customHeight="1">
+      <c r="A288" s="25" t="inlineStr"/>
+      <c r="B288" s="26" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C287" s="27" t="inlineStr">
+      <c r="C288" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D287" s="26" t="inlineStr"/>
-      <c r="E287" s="28" t="inlineStr">
+      <c r="D288" s="26" t="inlineStr"/>
+      <c r="E288" s="28" t="inlineStr">
         <is>
           <t>⚠️ Tonight — final checks — check-in opens 5:30am · hotel is 5 min walk to terminal</t>
         </is>
       </c>
-      <c r="F287" s="29" t="inlineStr">
+      <c r="F288" s="29" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="288" ht="31" customHeight="1">
-      <c r="A288" s="30" t="inlineStr"/>
-      <c r="B288" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C288" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="34" customHeight="1">
+    <row r="289" ht="31" customHeight="1">
       <c r="A289" s="30" t="inlineStr"/>
       <c r="B289" s="31" t="inlineStr">
         <is>
@@ -6188,11 +6199,11 @@
       </c>
       <c r="C289" s="32" t="inlineStr">
         <is>
-          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" ht="30" customHeight="1">
+          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="34" customHeight="1">
       <c r="A290" s="30" t="inlineStr"/>
       <c r="B290" s="31" t="inlineStr">
         <is>
@@ -6201,11 +6212,11 @@
       </c>
       <c r="C290" s="32" t="inlineStr">
         <is>
-          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" ht="34" customHeight="1">
+          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="30" customHeight="1">
       <c r="A291" s="30" t="inlineStr"/>
       <c r="B291" s="31" t="inlineStr">
         <is>
@@ -6214,7 +6225,7 @@
       </c>
       <c r="C291" s="32" t="inlineStr">
         <is>
-          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
         </is>
       </c>
     </row>
@@ -6227,11 +6238,11 @@
       </c>
       <c r="C292" s="32" t="inlineStr">
         <is>
-          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="32" customHeight="1">
+          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="34" customHeight="1">
       <c r="A293" s="30" t="inlineStr"/>
       <c r="B293" s="31" t="inlineStr">
         <is>
@@ -6240,148 +6251,137 @@
       </c>
       <c r="C293" s="32" t="inlineStr">
         <is>
+          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="32" customHeight="1">
+      <c r="A294" s="30" t="inlineStr"/>
+      <c r="B294" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C294" s="32" t="inlineStr">
+        <is>
           <t>⚠️ 5:00am alarm Jul 5 — set two alarms · FI571 departs 7:55am · check-in opens 5:30am · hotel is 5 min walk to terminal · boarding passes on phone tonight</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="3" customHeight="1">
-      <c r="A294" s="33" t="n"/>
-      <c r="B294" s="33" t="n"/>
-      <c r="C294" s="33" t="n"/>
-      <c r="D294" s="33" t="n"/>
-      <c r="E294" s="33" t="n"/>
-      <c r="F294" s="33" t="n"/>
-    </row>
-    <row r="295" ht="20" customHeight="1">
-      <c r="A295" s="3" t="inlineStr">
+    <row r="295" ht="3" customHeight="1">
+      <c r="A295" s="33" t="n"/>
+      <c r="B295" s="33" t="n"/>
+      <c r="C295" s="33" t="n"/>
+      <c r="D295" s="33" t="n"/>
+      <c r="E295" s="33" t="n"/>
+      <c r="F295" s="33" t="n"/>
+    </row>
+    <row r="296" ht="20" customHeight="1">
+      <c r="A296" s="3" t="inlineStr">
         <is>
           <t>DAY 16  |  Jul 5  |  Homebound — ZRH → KEF → MCO · The Final Leg  |  —  —</t>
         </is>
       </c>
     </row>
-    <row r="296" ht="15" customHeight="1">
-      <c r="A296" s="4" t="inlineStr">
+    <row r="297" ht="15" customHeight="1">
+      <c r="A297" s="4" t="inlineStr">
         <is>
           <t>Timeline: Sat night: app check-in ▸ confirm shuttle ▸ 5am wake ▸ 5:30am Hilton shuttle (NOT walk) ▸ 5:45am Terminal 2 · Check-in Row 3 ▸ 6am security + E Gate Skymetro ▸ 7:55am FI571 ZRH→KEF ▸ KEF Pylsur layover ▸ 8:50pm MCO home</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="22" customHeight="1">
-      <c r="A297" s="5" t="inlineStr">
+    <row r="298" ht="22" customHeight="1">
+      <c r="A298" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Take hotel shuttle NOT walk — Hilton is 2km from terminal · not walkable with luggage · CHF 7/person  |  ✅ Icelandair app check-in Saturday night — digital boarding pass · fast bag drop at Check-in 2 Row 3  |  ✅ US Customs at MCO not KEF — do not leave transit area in Iceland</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="39" customHeight="1">
-      <c r="A298" s="34" t="inlineStr"/>
-      <c r="B298" s="35" t="inlineStr">
+    <row r="299" ht="39" customHeight="1">
+      <c r="A299" s="34" t="inlineStr"/>
+      <c r="B299" s="35" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C298" s="36" t="inlineStr">
+      <c r="C299" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D298" s="35" t="inlineStr"/>
-      <c r="E298" s="37" t="inlineStr">
+      <c r="D299" s="35" t="inlineStr"/>
+      <c r="E299" s="37" t="inlineStr">
         <is>
           <t>✅ Night before (Jul 4 Saturday evening) — final prep — (2) Check Europcar/Booking.com email — confirm car return was closed out correctly</t>
         </is>
       </c>
-      <c r="F298" s="38" t="inlineStr"/>
-    </row>
-    <row r="299" ht="40" customHeight="1">
-      <c r="A299" s="11" t="inlineStr"/>
-      <c r="B299" s="12" t="inlineStr">
+      <c r="F299" s="38" t="inlineStr"/>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" s="11" t="inlineStr"/>
+      <c r="B300" s="12" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C299" s="13" t="inlineStr">
+      <c r="C300" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D299" s="12" t="inlineStr"/>
-      <c r="E299" s="14" t="inlineStr">
+      <c r="D300" s="12" t="inlineStr"/>
+      <c r="E300" s="14" t="inlineStr">
         <is>
           <t>⏰ 5:00am — Wake up — perfect timing · do not wake earlier unless extra bags need special handling · hotel breakfast starts at 5:30am if needed</t>
         </is>
       </c>
-      <c r="F299" s="15" t="inlineStr"/>
-    </row>
-    <row r="300" ht="31" customHeight="1">
-      <c r="A300" s="16" t="inlineStr"/>
-      <c r="B300" s="17" t="inlineStr">
+      <c r="F300" s="15" t="inlineStr"/>
+    </row>
+    <row r="301" ht="31" customHeight="1">
+      <c r="A301" s="16" t="inlineStr"/>
+      <c r="B301" s="17" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C300" s="16" t="inlineStr">
+      <c r="C301" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D300" s="17" t="inlineStr"/>
-      <c r="E300" s="18" t="inlineStr">
+      <c r="D301" s="17" t="inlineStr"/>
+      <c r="E301" s="18" t="inlineStr">
         <is>
           <t>⚠️ 5:30am — Hilton shuttle — ❌ do NOT walk · 2km to terminal · CHF 7/person · confirm seat tonight</t>
         </is>
       </c>
-      <c r="F300" s="19" t="inlineStr">
+      <c r="F301" s="19" t="inlineStr">
         <is>
           <t>2km / CHF 7</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="31" customHeight="1">
-      <c r="A301" s="25" t="inlineStr"/>
-      <c r="B301" s="26" t="inlineStr">
+    <row r="302" ht="31" customHeight="1">
+      <c r="A302" s="25" t="inlineStr"/>
+      <c r="B302" s="26" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C301" s="27" t="inlineStr">
+      <c r="C302" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D301" s="26" t="inlineStr"/>
-      <c r="E301" s="28" t="inlineStr">
+      <c r="D302" s="26" t="inlineStr"/>
+      <c r="E302" s="28" t="inlineStr">
         <is>
           <t>✈️ 5:45am — Terminal 2, Check-in Row 3 — bag drop opens 5:25am · digital boarding pass on phone</t>
         </is>
       </c>
-      <c r="F301" s="29" t="inlineStr"/>
-    </row>
-    <row r="302" ht="30" customHeight="1">
-      <c r="A302" s="16" t="inlineStr"/>
-      <c r="B302" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C302" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D302" s="17" t="inlineStr"/>
-      <c r="E302" s="18" t="inlineStr">
-        <is>
-          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
-        </is>
-      </c>
-      <c r="F302" s="19" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="38" customHeight="1">
+      <c r="F302" s="29" t="inlineStr"/>
+    </row>
+    <row r="303" ht="30" customHeight="1">
       <c r="A303" s="16" t="inlineStr"/>
       <c r="B303" s="17" t="inlineStr">
         <is>
@@ -6396,56 +6396,56 @@
       <c r="D303" s="17" t="inlineStr"/>
       <c r="E303" s="18" t="inlineStr">
         <is>
+          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
+        </is>
+      </c>
+      <c r="F303" s="19" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="38" customHeight="1">
+      <c r="A304" s="16" t="inlineStr"/>
+      <c r="B304" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C304" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D304" s="17" t="inlineStr"/>
+      <c r="E304" s="18" t="inlineStr">
+        <is>
           <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
         </is>
       </c>
-      <c r="F303" s="19" t="inlineStr"/>
-    </row>
-    <row r="304" ht="19" customHeight="1">
-      <c r="A304" s="6" t="inlineStr"/>
-      <c r="B304" s="7" t="inlineStr">
+      <c r="F304" s="19" t="inlineStr"/>
+    </row>
+    <row r="305" ht="19" customHeight="1">
+      <c r="A305" s="6" t="inlineStr"/>
+      <c r="B305" s="7" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C304" s="8" t="inlineStr">
+      <c r="C305" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D304" s="7" t="inlineStr"/>
-      <c r="E304" s="9" t="inlineStr">
+      <c r="D305" s="7" t="inlineStr"/>
+      <c r="E305" s="9" t="inlineStr">
         <is>
           <t>✈️ 7:55am — FI571 departs ZRH → KEF</t>
         </is>
       </c>
-      <c r="F304" s="10" t="inlineStr"/>
-    </row>
-    <row r="305" ht="37" customHeight="1">
-      <c r="A305" s="16" t="inlineStr"/>
-      <c r="B305" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C305" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D305" s="17" t="inlineStr"/>
-      <c r="E305" s="18" t="inlineStr">
-        <is>
-          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
-        </is>
-      </c>
-      <c r="F305" s="19" t="inlineStr">
-        <is>
-          <t>2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="35" customHeight="1">
+      <c r="F305" s="10" t="inlineStr"/>
+    </row>
+    <row r="306" ht="37" customHeight="1">
       <c r="A306" s="16" t="inlineStr"/>
       <c r="B306" s="17" t="inlineStr">
         <is>
@@ -6460,25 +6460,36 @@
       <c r="D306" s="17" t="inlineStr"/>
       <c r="E306" s="18" t="inlineStr">
         <is>
+          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
+        </is>
+      </c>
+      <c r="F306" s="19" t="inlineStr">
+        <is>
+          <t>2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="35" customHeight="1">
+      <c r="A307" s="16" t="inlineStr"/>
+      <c r="B307" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C307" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D307" s="17" t="inlineStr"/>
+      <c r="E307" s="18" t="inlineStr">
+        <is>
           <t>8:50pm — Arrive Orlando MCO — clear US Customs + Immigration at MCO · allow 45–60 min for customs on Sunday evening</t>
         </is>
       </c>
-      <c r="F306" s="19" t="inlineStr">
+      <c r="F307" s="19" t="inlineStr">
         <is>
           <t>60 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="307" ht="34" customHeight="1">
-      <c r="A307" s="30" t="inlineStr"/>
-      <c r="B307" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C307" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6502,7 @@
       </c>
       <c r="C308" s="32" t="inlineStr">
         <is>
-          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
+          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
         </is>
       </c>
     </row>
@@ -6504,11 +6515,11 @@
       </c>
       <c r="C309" s="32" t="inlineStr">
         <is>
-          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="310" ht="31" customHeight="1">
+          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="34" customHeight="1">
       <c r="A310" s="30" t="inlineStr"/>
       <c r="B310" s="31" t="inlineStr">
         <is>
@@ -6517,17 +6528,30 @@
       </c>
       <c r="C310" s="32" t="inlineStr">
         <is>
+          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="31" customHeight="1">
+      <c r="A311" s="30" t="inlineStr"/>
+      <c r="B311" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C311" s="32" t="inlineStr">
+        <is>
           <t>KEF layover — 1.5–2hrs · Pylsur hot dog (best in the world) · Skyr yoghurt · duty-free is excellent · US customs at MCO not here · do not leave transit</t>
         </is>
       </c>
     </row>
-    <row r="311" ht="3" customHeight="1">
-      <c r="A311" s="33" t="n"/>
-      <c r="B311" s="33" t="n"/>
-      <c r="C311" s="33" t="n"/>
-      <c r="D311" s="33" t="n"/>
-      <c r="E311" s="33" t="n"/>
-      <c r="F311" s="33" t="n"/>
+    <row r="312" ht="3" customHeight="1">
+      <c r="A312" s="33" t="n"/>
+      <c r="B312" s="33" t="n"/>
+      <c r="C312" s="33" t="n"/>
+      <c r="D312" s="33" t="n"/>
+      <c r="E312" s="33" t="n"/>
+      <c r="F312" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="110">
@@ -6546,6 +6570,7 @@
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="C172:F172"/>
     <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A274:F274"/>
     <mergeCell ref="C73:F73"/>
     <mergeCell ref="C250:F250"/>
     <mergeCell ref="C231:F231"/>
@@ -6565,7 +6590,6 @@
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="C175:F175"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C288:F288"/>
     <mergeCell ref="A122:F122"/>
     <mergeCell ref="A215:F215"/>
     <mergeCell ref="C98:F98"/>
@@ -6597,9 +6621,9 @@
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A253:F253"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="C294:F294"/>
     <mergeCell ref="C97:F97"/>
     <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A295:F295"/>
     <mergeCell ref="C94:F94"/>
     <mergeCell ref="C152:F152"/>
     <mergeCell ref="A157:F157"/>
@@ -6610,7 +6634,6 @@
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C95:F95"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A271:F271"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A273:F273"/>
@@ -6621,11 +6644,10 @@
     <mergeCell ref="A235:F235"/>
     <mergeCell ref="C154:F154"/>
     <mergeCell ref="C267:F267"/>
-    <mergeCell ref="C307:F307"/>
     <mergeCell ref="C49:F49"/>
+    <mergeCell ref="A298:F298"/>
     <mergeCell ref="A194:F194"/>
     <mergeCell ref="A234:F234"/>
-    <mergeCell ref="C266:F266"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="C269:F269"/>
@@ -6636,8 +6658,10 @@
     <mergeCell ref="C117:F117"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="C230:F230"/>
+    <mergeCell ref="C270:F270"/>
     <mergeCell ref="C118:F118"/>
     <mergeCell ref="C75:F75"/>
+    <mergeCell ref="C311:F311"/>
     <mergeCell ref="A138:F138"/>
     <mergeCell ref="C232:F232"/>
     <mergeCell ref="A196:F196"/>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -310,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -433,7 +433,7 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -500,6 +500,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -939,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -990,7 +993,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DAY 1–2  |  Jun 20–21  |  Iceland Day 1 + 2 — South Coast · Glacier · Jökulsárlón  |  ~660 km / 410 mi  ~7.5h total over 2 days</t>
+          <t>DAY 1  |  Jun 20  |  Iceland Day 1 - South Coast Gateway  |  ~180 km  ~2.5h</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr"/>
@@ -1001,7 +1004,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>&gt; Day 1: 10:30am KEF  Selfoss  Geysir  Seljalandsfoss+Gljúfrabúi  Skógafoss  Reynisfjara  7:30pm Vík | Day 2: 7am  Dyrhólaey  Skaftafellsjökull glacier walk  Skaftafell lunch  Jökulsárlón shore  Diamond Beach  2pm drive  4pm Fjaðrárgljúfur Canyon  Vík dinner  8pm BergOne</t>
+          <t>&gt; Day 1: 10:30am KEF &gt; Selfoss &gt; Geysir &gt; Seljalandsfoss+Gljufrabui &gt; Skogafoss &gt; Reynisfjara &gt; 7:30pm Vik</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr"/>
@@ -1012,7 +1015,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>KEY: Urriðafoss + Kerð dropped Day 1 — relaxed pace for jet-lag day  |   Day 2: Skaftafellsjökull glacier walk — free · easy · kids touch the ice  |   Depart Diamond Beach by 3pm firm — BergOne 8pm · 5:15am alarm</t>
+          <t>KEY: Selfoss lunch+grocery first  |  Gljufrabui MUST - waterproofs  |  Reynisfjara 6pm golden light</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr"/>
@@ -1023,12 +1026,12 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -1046,12 +1049,12 @@
     <row r="7" ht="33" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -1069,12 +1072,12 @@
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -1092,12 +1095,12 @@
     <row r="9" ht="37" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -1115,12 +1118,12 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -1138,12 +1141,12 @@
     <row r="11" ht="37" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1161,12 +1164,12 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -1184,12 +1187,12 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -1207,12 +1210,12 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -1230,12 +1233,12 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 20</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -1250,176 +1253,100 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>7:00am — Depart Skeidflot — already 10km from Dyrhólaey · head west first</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="33" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr"/>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>7:15am — Dyrhólaey arch — clifftop viewpoint over black sand coast · puffins nesting on Lágey islet in June — lower area · 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr"/>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>10:00am — Skaftafellsjökull glacier walk — easy flat trail from Skaftafell visitor centre car park · 3mi / 4.8km RT · 1–1.5hrs · walk right up to the glacier edge · feel the cold air · kids can touch the ice · Game of Thrones + Interstellar filming location · free</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="37" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr"/>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>11:30am — Lunch at Skaftafell — food trucks in the car park (lobster soup is outstanding) · or visitor centre café · use the toilets here · allow 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>12:30pm — Jökulsárlón — shore walk — 45 min drive east · floating blue icebergs glowing electric blue · walk the shore · seals resting on the ice · free · allow 30 min ·  every angle is a photo</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr"/>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>1:15pm — Diamond Beach — cross the bridge · crystal ice blocks on jet-black volcanic sand ·  same sneaker wave warning · allow 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="33" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>2:00pm — Start the drive back west — ~5hrs to BergOne incl. canyon stop · Ring Road all the way · sun still up the entire drive</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="28" t="inlineStr"/>
+      <c r="B16" s="28" t="inlineStr"/>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr"/>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>Parka app — download before landing · pay parking at Seljalandsfoss, Skógafoss, Reynisfjara · ~1000 ISK / 7 per stop · cameras read your plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="28" t="inlineStr"/>
+      <c r="B17" s="28" t="inlineStr"/>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr"/>
+      <c r="E17" s="30" t="inlineStr">
+        <is>
+          <t>24-hour daylight — Jun 20 sunset 12:03am · Reynisfjara at 6pm = golden light + no tour buses · Seljalandsfoss rainbow in the spray at 3pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="28" t="inlineStr"/>
+      <c r="B18" s="28" t="inlineStr"/>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr"/>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>Sneaker waves at Reynisfjara — Iceland's most dangerous beach · never turn your back to the ocean · stay well behind the safety rope</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="3" customHeight="1">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>DAY 2  |  Jun 21  |  Iceland Day 2 - Glacier Walk + Jokulsarlon  |  ~480 km  ~5h</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>&gt; Day 2: 7am &gt; Dyrholaey &gt; Glacier walk &gt; Skaftafell &gt; Jokulsarlon &gt; Diamond Beach &gt; 2pm drive &gt; Canyon 4pm &gt; Vik &gt; BergOne 8pm</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>KEY: Glacier walk free - kids touch ice  |  2pm departure firm  |  Canyon on return at 4pm</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 21</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Jun 20–21</t>
+          <t>Jun 21</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1430,264 +1357,288 @@
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
+          <t>7:00am — Depart Skeidflot — already 10km from Dyrhólaey · head west first</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr"/>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>7:15am — Dyrhólaey arch — clifftop viewpoint over black sand coast · puffins nesting on Lágey islet in June — lower area · 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr"/>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>10:00am — Skaftafellsjökull glacier walk — easy flat trail from Skaftafell visitor centre car park · 3mi / 4.8km RT · 1–1.5hrs · walk right up to the glacier edge · feel the cold air · kids can touch the ice · Game of Thrones + Interstellar filming location · free</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="37" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>11:30am — Lunch at Skaftafell — food trucks in the car park (lobster soup is outstanding) · or visitor centre café · use the toilets here · allow 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>12:30pm — Jökulsárlón — shore walk — 45 min drive east · floating blue icebergs glowing electric blue · walk the shore · seals resting on the ice · free · allow 30 min ·  every angle is a photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr"/>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>1:15pm — Diamond Beach — cross the bridge · crystal ice blocks on jet-black volcanic sand ·  same sneaker wave warning · allow 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>2:00pm — Start the drive back west — ~5hrs to BergOne incl. canyon stop · Ring Road all the way · sun still up the entire drive</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
           <t>~4:00pm — Fjaðrárgljúfur Canyon — natural break on the return drive · Route 1 passes right by it · 100m deep serpentine moss-covered canyon · Game of Thrones Season 8 · 2km rim walk · fewer crowds than morning · ISK 1000 Parka · allow 45 min</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="33" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
+    <row r="31" ht="33" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>~5:45pm — Dinner in Vík — Smiðjan Brugghsús — best burgers in South Iceland · or Suður-Vík · breaks the drive perfectly · allow 1hr</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="39" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Jun 20–21</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+    <row r="32" ht="39" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>BergOne, Ytri-Njarðvík —  Night 2 ·  1 Bergás, 260 Ytri-Njarðvík, Iceland ·  Booking.com · check in ~8pm · $263.98 ·  alarm 5:15am Jun 22 — FI568 departs KEF 7:20am</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="28" t="inlineStr"/>
-      <c r="B26" s="28" t="inlineStr"/>
-      <c r="C26" s="29" t="inlineStr">
+    <row r="33" ht="31" customHeight="1">
+      <c r="A33" s="28" t="inlineStr"/>
+      <c r="B33" s="28" t="inlineStr"/>
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr"/>
-      <c r="E26" s="30" t="inlineStr">
-        <is>
-          <t>Parka app — download before landing · pay parking at Seljalandsfoss, Skógafoss, Reynisfjara · ~1000 ISK / 7 per stop · cameras read your plate</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="28" t="inlineStr"/>
-      <c r="B27" s="28" t="inlineStr"/>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr"/>
+      <c r="E33" s="30" t="inlineStr">
+        <is>
+          <t>Skaftafellsjökull glacier walk — flat easy trail from car park · kids can walk right up to the ice · free · 1–1.5hrs · bring a warm layer — temperature drops near the ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="28" t="inlineStr"/>
+      <c r="B34" s="28" t="inlineStr"/>
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr"/>
-      <c r="E27" s="30" t="inlineStr">
-        <is>
-          <t>24-hour daylight — Jun 20 sunset 12:03am · Reynisfjara at 6pm = golden light + no tour buses · Seljalandsfoss rainbow in the spray at 3pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="28" t="inlineStr"/>
-      <c r="B28" s="28" t="inlineStr"/>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="inlineStr"/>
-      <c r="E28" s="30" t="inlineStr">
-        <is>
-          <t>Sneaker waves at Reynisfjara — Iceland's most dangerous beach · never turn your back to the ocean · stay well behind the safety rope</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="31" customHeight="1">
-      <c r="A29" s="28" t="inlineStr"/>
-      <c r="B29" s="28" t="inlineStr"/>
-      <c r="C29" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr"/>
-      <c r="E29" s="30" t="inlineStr">
-        <is>
-          <t>Skaftafellsjökull glacier walk — flat easy trail from car park · kids can walk right up to the ice · free · 1–1.5hrs · bring a warm layer — temperature drops near the ice</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="28" t="inlineStr"/>
-      <c r="B30" s="28" t="inlineStr"/>
-      <c r="C30" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr"/>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr"/>
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>3pm departure from Diamond Beach is firm — BergOne by 8pm · 5:15am alarm next morning · don't linger at Jökulsárlón or you'll be driving past midnight</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="3" customHeight="1">
-      <c r="A31" s="31" t="n"/>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="35" ht="3" customHeight="1">
+      <c r="A35" s="31" t="n"/>
+      <c r="B35" s="31" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>DAY 3  |  Jun 22  |  Fly KEFZRH · Spiez · Lauterbrunnen — The Alpine Entry  |  ~144 km / 90 mi  ~1h 45m</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr"/>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>&gt; 5:45am KEF drop-off  7:20am FI568  1:05pm ZRH land  2:30pm Europcar pickup  4:15pm Spiez Castle  Coop Lauterbrunnen  5:45pm Camping Jungfrau  Staubbach Falls evening  Austrian vignette tonight</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr"/>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr"/>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>KEY: At Europcar: confirm vignette · confirm cross-border Italy+Austria · photograph licence plate  |   Spiez Castle gardens (free) — Route 6 lakeside road NOT the motorway tunnel  |   Coop Lauterbrunnen before 6:30pm · Staubbach Falls evening walk · Austrian vignette tonight</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr"/>
-      <c r="C34" s="7" t="inlineStr"/>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr"/>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>5:45am — KEF Airport — return Budget rental car at the airport lot · shuttle back to terminal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="23" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr"/>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>7:20am — FI568 KEF  ZRH — 3hr 45min · allow 60–90 min for car pickup</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="53" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr"/>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>1:30pm — Europcar ZRH pickup — Booking #738796923 · Volkswagen Tiguan 4x4 or similar · Europcar counter in Arrivals · 5 seats · 2 large bags · unlimited mileage ·  Confirm cross-border Italy+Austria · photograph licence plate for Austrian vignette</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr"/>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>Swiss motorway vignette — the 2026 sticker must be on the windscreen before driving on any Swiss motorway · Europcar should include it — if not, buy at any petrol station for CHF 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
+      <c r="B38" s="7" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr"/>
+      <c r="D38" s="7" t="inlineStr"/>
+      <c r="E38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="27" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
@@ -1706,80 +1657,80 @@
       <c r="D39" s="18" t="inlineStr"/>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>4:15pm — Spiez Castle &amp; Lake Thun — panoramic view: Lake Thun + Niesen pyramid mountain + Eiger on clear days · allow 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="29" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+          <t>5:45am — KEF Airport — return Budget rental car at the airport lot · shuttle back to terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="23" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr"/>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Grocery stop — Coop Supermarket, Lauterbrunnen village — this is your first Alpine dinner — make it good</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="23" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr"/>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>7:20am — FI568 KEF  ZRH — 3hr 45min · allow 60–90 min for car pickup</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="53" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="C41" s="25" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D41" s="26" t="inlineStr"/>
-      <c r="E41" s="27" t="inlineStr">
-        <is>
-          <t>5:45pm — Check-in: Camping Jungfrau, Lauterbrunnen — CHF 398 / $499</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="29" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>1:30pm — Europcar ZRH pickup — Booking #738796923 · Volkswagen Tiguan 4x4 or similar · Europcar counter in Arrivals · 5 seats · 2 large bags · unlimited mileage ·  Confirm cross-border Italy+Austria · photograph licence plate for Austrian vignette</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="C42" s="25" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D42" s="26" t="inlineStr"/>
-      <c r="E42" s="27" t="inlineStr">
-        <is>
-          <t>Staubbach Falls — evening walk — 5 min walk from Camping Jungfrau · walk to the base and feel the mist</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1">
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr"/>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Swiss motorway vignette — the 2026 sticker must be on the windscreen before driving on any Swiss motorway · Europcar should include it — if not, buy at any petrol station for CHF 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Jun 22</t>
@@ -1798,11 +1749,11 @@
       <c r="D43" s="18" t="inlineStr"/>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>Tonight: buy Austrian Digital Vignette — ~16.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
+          <t>4:15pm — Spiez Castle &amp; Lake Thun — panoramic view: Lake Thun + Niesen pyramid mountain + Eiger on clear days · allow 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="29" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Jun 22</t>
@@ -1821,295 +1772,295 @@
       <c r="D44" s="14" t="inlineStr"/>
       <c r="E44" s="15" t="inlineStr">
         <is>
+          <t>Grocery stop — Coop Supermarket, Lauterbrunnen village — this is your first Alpine dinner — make it good</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="23" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr"/>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>5:45pm — Check-in: Camping Jungfrau, Lauterbrunnen — CHF 398 / $499</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="29" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr"/>
+      <c r="E46" s="27" t="inlineStr">
+        <is>
+          <t>Staubbach Falls — evening walk — 5 min walk from Camping Jungfrau · walk to the base and feel the mist</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr"/>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Tonight: buy Austrian Digital Vignette — ~16.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr"/>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
           <t>Dinner — or Restaurant Jungfrau in the village (10 min walk)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="28" t="inlineStr"/>
-      <c r="B45" s="28" t="inlineStr"/>
-      <c r="C45" s="29" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="28" t="inlineStr"/>
+      <c r="B49" s="28" t="inlineStr"/>
+      <c r="C49" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D45" s="28" t="inlineStr"/>
-      <c r="E45" s="30" t="inlineStr">
+      <c r="D49" s="28" t="inlineStr"/>
+      <c r="E49" s="30" t="inlineStr">
         <is>
           <t>Swiss vignette (CHF 40) — must be on windscreen before driving on Swiss motorways · Europcar should include it — verify at counter · buy at petrol station if missing · fine = CHF 200</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="28" t="inlineStr"/>
-      <c r="B46" s="28" t="inlineStr"/>
-      <c r="C46" s="29" t="inlineStr">
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="28" t="inlineStr"/>
+      <c r="B50" s="28" t="inlineStr"/>
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D46" s="28" t="inlineStr"/>
-      <c r="E46" s="30" t="inlineStr">
+      <c r="D50" s="28" t="inlineStr"/>
+      <c r="E50" s="30" t="inlineStr">
         <is>
           <t>Take the lakeside road — from Interlaken to Lauterbrunnen use Route 6 along Lake Thun shore · far more scenic than motorway tunnels · adds only 5 min</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="27" customHeight="1">
-      <c r="A47" s="28" t="inlineStr"/>
-      <c r="B47" s="28" t="inlineStr"/>
-      <c r="C47" s="29" t="inlineStr">
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="28" t="inlineStr"/>
+      <c r="B51" s="28" t="inlineStr"/>
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D47" s="28" t="inlineStr"/>
-      <c r="E47" s="30" t="inlineStr">
+      <c r="D51" s="28" t="inlineStr"/>
+      <c r="E51" s="30" t="inlineStr">
         <is>
           <t>Austrian vignette tonight — asfinag.at · ~16.50 · need your licence plate number · cameras check automatically when you enter Austria Jun 26</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="28" t="inlineStr"/>
-      <c r="B48" s="28" t="inlineStr"/>
-      <c r="C48" s="29" t="inlineStr">
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="28" t="inlineStr"/>
+      <c r="B52" s="28" t="inlineStr"/>
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D48" s="28" t="inlineStr"/>
-      <c r="E48" s="30" t="inlineStr">
+      <c r="D52" s="28" t="inlineStr"/>
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>Grocery strategy — Coop Lauterbrunnen today (Swiss days) · BIG shop at Rewe/Aldi Berchtesgaden Jun 24 (German prices 35% cheaper) · Hofer Bad Goisern Jun 27 (Austria + Dolomites days)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="3" customHeight="1">
-      <c r="A49" s="31" t="n"/>
-      <c r="B49" s="31" t="n"/>
-      <c r="C49" s="31" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="53" ht="3" customHeight="1">
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="31" t="n"/>
+      <c r="C53" s="31" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="31" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>DAY 4  |  Jun 23  |  Oeschinensee Heuberg Ridge + Grindelwald First — Double Gondola Day  |  ~100 km / 62 mi  ~2h 30m incl. mountain roads</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>&gt; 7:30am Lauterbrunnen  8:15am Kandersteg park  8:30am Oeschinensee gondola  Heuberg Ridge Trail #8  10am viewpoint  11am lakeside picnic  12pm drive Grindelwald  1:45pm Firstbahn  Cliff Walk  Bachalpsee  4:30pm turn back  5pm First station  6:30pm Lauterbrunnen</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr"/>
-      <c r="C51" s="6" t="inlineStr"/>
-      <c r="D51" s="6" t="inlineStr"/>
-      <c r="E51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>KEY: Heuberg Ridge Trail #8 — follow signs Läger  Heuberg · bird's-eye lake view · NOT the direct path  |   Last gondola down from First is 6:00pm — leave Bachalpsee by 4:30pm latest  |   Packed picnic at Heuberg viewpoint — bread + Swiss cheese from Coop last night</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr"/>
-      <c r="C52" s="7" t="inlineStr"/>
-      <c r="D52" s="7" t="inlineStr"/>
-      <c r="E52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53" ht="27" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr"/>
+      <c r="C56" s="7" t="inlineStr"/>
+      <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57" ht="27" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr"/>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr"/>
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>7:30am — Depart Lauterbrunnen — 45 min scenic drive to Kandersteg via the Kandertal valley</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C58" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr"/>
-      <c r="E54" s="19" t="inlineStr">
+      <c r="D58" s="18" t="inlineStr"/>
+      <c r="E58" s="19" t="inlineStr">
         <is>
           <t>8:15am — Park at Oeschinen Talstation — parking ~CHF 8</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C55" s="17" t="inlineStr">
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr"/>
-      <c r="E55" s="19" t="inlineStr">
+      <c r="D59" s="18" t="inlineStr"/>
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>8:30am — Oeschinensee gondola —  Pre-booked · CHF 125</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C56" s="21" t="inlineStr">
+      <c r="C60" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D56" s="22" t="inlineStr"/>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="D60" s="22" t="inlineStr"/>
+      <c r="E60" s="23" t="inlineStr">
         <is>
           <t>Heuberg Ridge Hike — Trail #8 (Priority) —  Some steep drop-offs near the cliffs — if anyone has severe vertigo stick to lower Trail #1</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr"/>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>10:00am — Heuberg Panoramic Viewpoint — allow 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D58" s="22" t="inlineStr"/>
-      <c r="E58" s="23" t="inlineStr">
-        <is>
-          <t>11:00am — Descent to lakeside — allow 1hr total</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="37" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr"/>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>12:00pm — Depart Kandersteg  Grindelwald — cable car down first · 1hr 15min drive · park at Parkhaus Eiger+ or Sportzentrum — near Firstbahn · ~CHF 10–15</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="25" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D60" s="18" t="inlineStr"/>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>1:45pm — Grindelwald Firstbahn gondola —  Booking #238070 · ride to First (2,168m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="29" customHeight="1">
+    <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
           <t>Jun 23</t>
@@ -2128,11 +2079,11 @@
       <c r="D61" s="18" t="inlineStr"/>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>2:15pm — First Cliff Walk — Tissot-sponsored glass floor section — walk over 45m of air · allow 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1">
+          <t>10:00am — Heuberg Panoramic Viewpoint — allow 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19" customHeight="1">
       <c r="A62" s="20" t="inlineStr">
         <is>
           <t>Jun 23</t>
@@ -2151,34 +2102,34 @@
       <c r="D62" s="22" t="inlineStr"/>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>2:45pm — Bachalpsee hike — Trail from First station · 3km / 1.9mi one-way</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
+          <t>11:00am — Descent to lakeside — allow 1hr total</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="37" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="inlineStr"/>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>3:45pm — Bachalpsee "Blue Jewel" — allow 30–45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="31" customHeight="1">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr"/>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>12:00pm — Depart Kandersteg  Grindelwald — cable car down first · 1hr 15min drive · park at Parkhaus Eiger+ or Sportzentrum — near Firstbahn · ~CHF 10–15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="25" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
           <t>Jun 23</t>
@@ -2197,117 +2148,149 @@
       <c r="D64" s="18" t="inlineStr"/>
       <c r="E64" s="19" t="inlineStr">
         <is>
+          <t>1:45pm — Grindelwald Firstbahn gondola —  Booking #238070 · ride to First (2,168m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="29" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr"/>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>2:15pm — First Cliff Walk — Tissot-sponsored glass floor section — walk over 45m of air · allow 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="inlineStr"/>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>2:45pm — Bachalpsee hike — Trail from First station · 3km / 1.9mi one-way</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr"/>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>3:45pm — Bachalpsee "Blue Jewel" — allow 30–45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="31" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr"/>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
           <t>5:00pm — Back at First station — LAST gondola down is 6:00pm — do not miss it · allow 45 min walk back from Bachalpsee</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr"/>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr"/>
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>5:30pm — Gondola down  drive back — 20 min drive to Camping Jungfrau, Lauterbrunnen · arrive ~6:30pm</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr"/>
-      <c r="E66" s="15" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr"/>
+      <c r="E70" s="15" t="inlineStr">
         <is>
           <t>Dinner — campsite kitchen with Coop groceries · or Airtime Restaurant — in Lauterbrunnen village (10 min walk)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="28" t="inlineStr"/>
-      <c r="B67" s="28" t="inlineStr"/>
-      <c r="C67" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D67" s="28" t="inlineStr"/>
-      <c r="E67" s="30" t="inlineStr">
-        <is>
-          <t>Grindelwald Firstbahn #238070 · Jun 23 · 2 adults + 2 children</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="33" customHeight="1">
-      <c r="A68" s="28" t="inlineStr"/>
-      <c r="B68" s="28" t="inlineStr"/>
-      <c r="C68" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D68" s="28" t="inlineStr"/>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>Heuberg Trail #8 — steep drop-offs — moderate difficulty · if severe vertigo in the family, take lower Trail #1 to lake directly · Trail #8 has exposed cliff sections near the viewpoint</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="33" customHeight="1">
-      <c r="A69" s="28" t="inlineStr"/>
-      <c r="B69" s="28" t="inlineStr"/>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D69" s="28" t="inlineStr"/>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>Bachalpsee in late June — small snow patches still possible on the trail · hiking boots with grip essential · cows with cowbells in the meadows · bring layers — 2,168m = cold even in June</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="29" customHeight="1">
-      <c r="A70" s="28" t="inlineStr"/>
-      <c r="B70" s="28" t="inlineStr"/>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D70" s="28" t="inlineStr"/>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>Grindelwald parking 2026 — very busy · Parkhaus Eiger+ or Sportzentrum first · if full: Grindelwald Grund  short train/bus to Firstbahn · CHF 10–15 either way</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="31" customHeight="1">
+    <row r="71" ht="17" customHeight="1">
       <c r="A71" s="28" t="inlineStr"/>
       <c r="B71" s="28" t="inlineStr"/>
       <c r="C71" s="29" t="inlineStr">
@@ -2318,143 +2301,111 @@
       <c r="D71" s="28" t="inlineStr"/>
       <c r="E71" s="30" t="inlineStr">
         <is>
+          <t>Grindelwald Firstbahn #238070 · Jun 23 · 2 adults + 2 children</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="33" customHeight="1">
+      <c r="A72" s="28" t="inlineStr"/>
+      <c r="B72" s="28" t="inlineStr"/>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D72" s="28" t="inlineStr"/>
+      <c r="E72" s="30" t="inlineStr">
+        <is>
+          <t>Heuberg Trail #8 — steep drop-offs — moderate difficulty · if severe vertigo in the family, take lower Trail #1 to lake directly · Trail #8 has exposed cliff sections near the viewpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="33" customHeight="1">
+      <c r="A73" s="28" t="inlineStr"/>
+      <c r="B73" s="28" t="inlineStr"/>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="inlineStr"/>
+      <c r="E73" s="30" t="inlineStr">
+        <is>
+          <t>Bachalpsee in late June — small snow patches still possible on the trail · hiking boots with grip essential · cows with cowbells in the meadows · bring layers — 2,168m = cold even in June</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="29" customHeight="1">
+      <c r="A74" s="28" t="inlineStr"/>
+      <c r="B74" s="28" t="inlineStr"/>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D74" s="28" t="inlineStr"/>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>Grindelwald parking 2026 — very busy · Parkhaus Eiger+ or Sportzentrum first · if full: Grindelwald Grund  short train/bus to Firstbahn · CHF 10–15 either way</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="31" customHeight="1">
+      <c r="A75" s="28" t="inlineStr"/>
+      <c r="B75" s="28" t="inlineStr"/>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D75" s="28" t="inlineStr"/>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
           <t>Pack picnic tonight — Coop Lauterbrunnen · fresh bread + Swiss mountain cheese + fruit + water · eat at Heuberg viewpoint 10am · far better than any restaurant on the mountain</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="3" customHeight="1">
-      <c r="A72" s="31" t="n"/>
-      <c r="B72" s="31" t="n"/>
-      <c r="C72" s="31" t="n"/>
-      <c r="D72" s="31" t="n"/>
-      <c r="E72" s="31" t="n"/>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="76" ht="3" customHeight="1">
+      <c r="A76" s="31" t="n"/>
+      <c r="B76" s="31" t="n"/>
+      <c r="C76" s="31" t="n"/>
+      <c r="D76" s="31" t="n"/>
+      <c r="E76" s="31" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>DAY 5  |  Jun 24  |  Lauterbrunnen  Berchtesgaden — The Cross-Country Push  |  ~595 km / 370 mi  ~6h non-stop · longest drive day</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr"/>
-      <c r="C73" s="4" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr"/>
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>&gt; 8:30am Trümmelbach Falls  10am coffee  10:45am depart  12:30pm Vaduz/Liechtenstein lunch  Germany border  A8 Munich area  Chiemsee stop  Hintersee photo  5:30pm Berchtesgaden</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr"/>
-      <c r="C74" s="6" t="inlineStr"/>
-      <c r="D74" s="6" t="inlineStr"/>
-      <c r="E74" s="6" t="inlineStr"/>
-    </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr"/>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>KEY: Trümmelbach Falls first — opens 9am · 3 min from campsite · wear waterproofs · do not skip  |   Vaduz/Liechtenstein lunch stop — Country #3 · passport stamp CHF 3 · 45 min total  |   Check A8 before Munich — if 60+ min delay switch to B31/B12 Deutsche Alpenstraße</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr"/>
-      <c r="C75" s="7" t="inlineStr"/>
-      <c r="D75" s="7" t="inlineStr"/>
-      <c r="E75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76" ht="31" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr"/>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>8:30am — Checkout Camping Jungfrau — walk to Trümmelbach Falls first (3 min drive or 15 min walk from the campsite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="26" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D77" s="18" t="inlineStr"/>
-      <c r="E77" s="19" t="inlineStr">
-        <is>
-          <t>8:30am — Trümmelbach Falls — be first at the gate when it opens at 9:00am · ~12/adult</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="19" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr"/>
-      <c r="E78" s="19" t="inlineStr">
-        <is>
-          <t>Lauterbrunnen valley exit photo stop — 5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="35" customHeight="1">
-      <c r="A79" s="24" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="C79" s="25" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D79" s="26" t="inlineStr"/>
-      <c r="E79" s="27" t="inlineStr">
-        <is>
-          <t>10:00am — Final Lauterbrunnen coffee — quick espresso in the village before the motorway · Airtime Café or Camping Jungfrau café · allow 20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="21" customHeight="1">
+      <c r="B79" s="7" t="inlineStr"/>
+      <c r="C79" s="7" t="inlineStr"/>
+      <c r="D79" s="7" t="inlineStr"/>
+      <c r="E79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80" ht="31" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
           <t>Jun 24</t>
@@ -2473,11 +2424,11 @@
       <c r="D80" s="10" t="inlineStr"/>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>10:45am — Depart Lauterbrunnen  Berchtesgaden — ~595 km</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="34" customHeight="1">
+          <t>8:30am — Checkout Camping Jungfrau — walk to Trümmelbach Falls first (3 min drive or 15 min walk from the campsite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Jun 24</t>
@@ -2496,11 +2447,11 @@
       <c r="D81" s="18" t="inlineStr"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>Austrian Pfändertunnel near Bregenz — you clip a corner of Austria near Bregenz on the standard route · your Austrian Digital Vignette</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="21" customHeight="1">
+          <t>8:30am — Trümmelbach Falls — be first at the gate when it opens at 9:00am · ~12/adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="19" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Jun 24</t>
@@ -2519,80 +2470,80 @@
       <c r="D82" s="18" t="inlineStr"/>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>Fuel strategy — first opportunity: Bregenz area (Austria)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="33" customHeight="1">
-      <c r="A83" s="12" t="inlineStr">
+          <t>Lauterbrunnen valley exit photo stop — 5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="35" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B83" s="24" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D83" s="14" t="inlineStr"/>
-      <c r="E83" s="15" t="inlineStr">
-        <is>
-          <t>12:30pm — Lunch stop: Vaduz, Liechtenstein — 45 min "Country #3" stop · get your passport stamped at the tourist office for 3 CHF</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="54" customHeight="1">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D83" s="26" t="inlineStr"/>
+      <c r="E83" s="27" t="inlineStr">
+        <is>
+          <t>10:00am — Final Lauterbrunnen coffee — quick espresso in the village before the motorway · Airtime Café or Camping Jungfrau café · allow 20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="21" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="B84" s="16" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C84" s="17" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr"/>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>10:45am — Depart Lauterbrunnen  Berchtesgaden — ~595 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D84" s="18" t="inlineStr"/>
-      <c r="E84" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A8 Construction Warning 2026 — A8 between Ulm and Munich is under major renovation in 2026 · check Google Maps live before Munich · if showing 60+ min red delay: switch to the scenic B31/B12 southern route — slower but beautiful — avoids stop-and-go misery · Wednesday = moderate </t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="40" customHeight="1">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="C85" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr"/>
-      <c r="E85" s="15" t="inlineStr">
-        <is>
-          <t>Grocery stop — REWE or Lidl, Lindau or Berchtesgaden — cross into Germany at Lindau — first stop after Switzerland · or use REWE Berchtesgaden on arrival (Maximilianstr. 26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="25" customHeight="1">
+      <c r="D85" s="18" t="inlineStr"/>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>Austrian Pfändertunnel near Bregenz — you clip a corner of Austria near Bregenz on the standard route · your Austrian Digital Vignette</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="21" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Jun 24</t>
@@ -2611,57 +2562,57 @@
       <c r="D86" s="18" t="inlineStr"/>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>Chiemsee photo stop — Bernau Exit 106 — 2km to Felden lakeshore · allow 15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+          <t>Fuel strategy — first opportunity: Bregenz area (Austria)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="33" customHeight="1">
+      <c r="A87" s="12" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr"/>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>~5:00pm — Hintersee lake photo stop — 15 min drive from Berchtesgaden town · allow 20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="26" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr"/>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>12:30pm — Lunch stop: Vaduz, Liechtenstein — 45 min "Country #3" stop · get your passport stamped at the tourist office for 3 CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="54" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="B88" s="24" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C88" s="25" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D88" s="26" t="inlineStr"/>
-      <c r="E88" s="27" t="inlineStr">
-        <is>
-          <t>~5:30pm — Check-in: One-Bedroom Apartment, Berchtesgaden —  Booking.com message host</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="1">
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr"/>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A8 Construction Warning 2026 — A8 between Ulm and Munich is under major renovation in 2026 · check Google Maps live before Munich · if showing 60+ min red delay: switch to the scenic B31/B12 southern route — slower but beautiful — avoids stop-and-go misery · Wednesday = moderate </t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
       <c r="A89" s="12" t="inlineStr">
         <is>
           <t>Jun 24</t>
@@ -2680,71 +2631,103 @@
       <c r="D89" s="14" t="inlineStr"/>
       <c r="E89" s="15" t="inlineStr">
         <is>
+          <t>Grocery stop — REWE or Lidl, Lindau or Berchtesgaden — cross into Germany at Lindau — first stop after Switzerland · or use REWE Berchtesgaden on arrival (Maximilianstr. 26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="25" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr"/>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>Chiemsee photo stop — Bernau Exit 106 — 2km to Felden lakeshore · allow 15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr"/>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>~5:00pm — Hintersee lake photo stop — 15 min drive from Berchtesgaden town · allow 20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="C92" s="25" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D92" s="26" t="inlineStr"/>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>~5:30pm — Check-in: One-Bedroom Apartment, Berchtesgaden —  Booking.com message host</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr"/>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
           <t>Dinner — Berchtesgaden — Bräustüberl Berchtesgaden — allow 1hr</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="28" t="inlineStr"/>
-      <c r="B90" s="28" t="inlineStr"/>
-      <c r="C90" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D90" s="28" t="inlineStr"/>
-      <c r="E90" s="30" t="inlineStr">
-        <is>
-          <t>Austrian vignette at Pfändertunnel — cameras check automatically near Bregenz · no booth to stop at · instant fine if not purchased · should be bought at asfinag.at on Day 3 evening</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="29" customHeight="1">
-      <c r="A91" s="28" t="inlineStr"/>
-      <c r="B91" s="28" t="inlineStr"/>
-      <c r="C91" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D91" s="28" t="inlineStr"/>
-      <c r="E91" s="30" t="inlineStr">
-        <is>
-          <t>A8 2026 construction — major roadworks Ulm–Munich · check Google Maps before Munich · alternative: B31/B12 Deutsche Alpenstraße — beautiful but adds 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="A92" s="28" t="inlineStr"/>
-      <c r="B92" s="28" t="inlineStr"/>
-      <c r="C92" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D92" s="28" t="inlineStr"/>
-      <c r="E92" s="30" t="inlineStr">
-        <is>
-          <t>Fuel — fill in Austria (Bregenz area) or Germany · never in Switzerland · Rosenheim or Bad Reichenhall last cheap before Berchtesgaden</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="28" t="inlineStr"/>
-      <c r="B93" s="28" t="inlineStr"/>
-      <c r="C93" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D93" s="28" t="inlineStr"/>
-      <c r="E93" s="30" t="inlineStr">
-        <is>
-          <t>Liechtenstein passport stamp — tourist office in Vaduz · CHF 3 per passport · one of the rarest stamps in Europe · great for the kids</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="27" customHeight="1">
+    <row r="94" ht="32" customHeight="1">
       <c r="A94" s="28" t="inlineStr"/>
       <c r="B94" s="28" t="inlineStr"/>
       <c r="C94" s="29" t="inlineStr">
@@ -2755,166 +2738,134 @@
       <c r="D94" s="28" t="inlineStr"/>
       <c r="E94" s="30" t="inlineStr">
         <is>
+          <t>Austrian vignette at Pfändertunnel — cameras check automatically near Bregenz · no booth to stop at · instant fine if not purchased · should be bought at asfinag.at on Day 3 evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="29" customHeight="1">
+      <c r="A95" s="28" t="inlineStr"/>
+      <c r="B95" s="28" t="inlineStr"/>
+      <c r="C95" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D95" s="28" t="inlineStr"/>
+      <c r="E95" s="30" t="inlineStr">
+        <is>
+          <t>A8 2026 construction — major roadworks Ulm–Munich · check Google Maps before Munich · alternative: B31/B12 Deutsche Alpenstraße — beautiful but adds 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="28" t="inlineStr"/>
+      <c r="B96" s="28" t="inlineStr"/>
+      <c r="C96" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D96" s="28" t="inlineStr"/>
+      <c r="E96" s="30" t="inlineStr">
+        <is>
+          <t>Fuel — fill in Austria (Bregenz area) or Germany · never in Switzerland · Rosenheim or Bad Reichenhall last cheap before Berchtesgaden</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="A97" s="28" t="inlineStr"/>
+      <c r="B97" s="28" t="inlineStr"/>
+      <c r="C97" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D97" s="28" t="inlineStr"/>
+      <c r="E97" s="30" t="inlineStr">
+        <is>
+          <t>Liechtenstein passport stamp — tourist office in Vaduz · CHF 3 per passport · one of the rarest stamps in Europe · great for the kids</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="27" customHeight="1">
+      <c r="A98" s="28" t="inlineStr"/>
+      <c r="B98" s="28" t="inlineStr"/>
+      <c r="C98" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D98" s="28" t="inlineStr"/>
+      <c r="E98" s="30" t="inlineStr">
+        <is>
           <t>Grocery — REWE Berchtesgaden (Maximilianstr. 26) · open until 8pm · German prices 30–40% cheaper than Swiss · stock up for 2 nights here</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="3" customHeight="1">
-      <c r="A95" s="31" t="n"/>
-      <c r="B95" s="31" t="n"/>
-      <c r="C95" s="31" t="n"/>
-      <c r="D95" s="31" t="n"/>
-      <c r="E95" s="31" t="n"/>
-    </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="99" ht="3" customHeight="1">
+      <c r="A99" s="31" t="n"/>
+      <c r="B99" s="31" t="n"/>
+      <c r="C99" s="31" t="n"/>
+      <c r="D99" s="31" t="n"/>
+      <c r="E99" s="31" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>DAY 6  |  Jun 25  |  Königssee · Eagle's Nest · Hintersee — Lakes, Legends &amp; Luxury  |  ~80 km / 50 mi  ~2h total · short loops around Berchtesgaden</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr"/>
-      <c r="C96" s="4" t="inlineStr"/>
-      <c r="D96" s="4" t="inlineStr"/>
-      <c r="E96" s="4" t="inlineStr"/>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr"/>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>&gt; 8:15am Königssee park  8:30am boat to Salet  Obersee + Röthbachfall 9:45am  St. Bartholomä lunch 12pm  1:30pm Eagle's Nest Kehlsteinbus  4pm Rossfeld Road  4:45pm Hintersee/Zauberwald  6:30pm Berchtesgaden dinner</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr"/>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="D97" s="6" t="inlineStr"/>
-      <c r="E97" s="6" t="inlineStr"/>
-    </row>
-    <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr"/>
+      <c r="C101" s="6" t="inlineStr"/>
+      <c r="D101" s="6" t="inlineStr"/>
+      <c r="E101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>KEY: Go to Salet (final stop) NOT St. Bartholomä — Obersee + Röthbachfall is the highlight  |   Eagle's Nest: register return bus time at counter BEFORE taking elevator — fills fast  |   Rossfeld Road after Eagle's Nest — same area · 9 · straddle the D/A border stone  |   Eagle's Nest if clear · Salt Mine if foggy — both at 1:30pm · same area · book Salt Mine online at salzbergwerk.de</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr"/>
-      <c r="C98" s="7" t="inlineStr"/>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="7" t="inlineStr"/>
-    </row>
-    <row r="99" ht="39" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr"/>
+      <c r="C102" s="7" t="inlineStr"/>
+      <c r="D102" s="7" t="inlineStr"/>
+      <c r="E102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103" ht="39" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr"/>
-      <c r="E99" s="11" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr"/>
+      <c r="E103" s="11" t="inlineStr">
         <is>
           <t>8:15am — Königssee Seelände car park — only 10 min drive from Berchtesgaden apartment · car park is huge but the dock is a 10 min walk from the lot — factor this in</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="43" customHeight="1">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D100" s="18" t="inlineStr"/>
-      <c r="E100" s="19" t="inlineStr">
-        <is>
-          <t>8:30am — Königssee electric boat — completely silent electric boats — only powered vessels allowed on this lake ·  Go all the way to Salet — 55 min to Salet · ~28–30 return to Salet per adult</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="A101" s="16" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C101" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D101" s="18" t="inlineStr"/>
-      <c r="E101" s="19" t="inlineStr">
-        <is>
-          <t>The mountain echo tradition — midway the captain stops and plays a trumpet · have 1–2 ready to tip</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="54" customHeight="1">
-      <c r="A102" s="16" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D102" s="18" t="inlineStr"/>
-      <c r="E102" s="19" t="inlineStr">
-        <is>
-          <t>9:45am — Obersee &amp; Röthbachfall — flat 15 min walk from Salet dock · mirror-like glacial lake · iconic half-submerged wooden boathouse · walk all the way to Fischunkelalm hut on the far side · look straight up the valley walls — Röthbachfall = Germany's highest waterfall crashing</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="12" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C103" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr"/>
-      <c r="E103" s="15" t="inlineStr">
-        <is>
-          <t>12:00pm — St. Bartholomä lunch stop — allow 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="28" customHeight="1">
+    <row r="104" ht="43" customHeight="1">
       <c r="A104" s="16" t="inlineStr">
         <is>
           <t>Jun 25</t>
@@ -2933,30 +2884,30 @@
       <c r="D104" s="18" t="inlineStr"/>
       <c r="E104" s="19" t="inlineStr">
         <is>
-          <t>12:45pm — Final boat back to Königssee Seelände — 35 min · arrive ~1:15pm · walk 10 min to car park</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="54" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+          <t>8:30am — Königssee electric boat — completely silent electric boats — only powered vessels allowed on this lake ·  Go all the way to Salet — 55 min to Salet · ~28–30 return to Salet per adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="16" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="16" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>1:30pm — Eagle's Nest (Kehlsteinhaus) — drive 10 min to Obersalzberg car park · Kehlsteinbus ~32 (bus + brass elevator) ·  Golden Rule: immediately book 4:00 or 4:15pm return slot at top counter · 360 Alpine panorama at 1,834m · allow 2hrs ·  If foggy/cloudy: swap for Berchtesgad</t>
+      <c r="C105" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="inlineStr"/>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>The mountain echo tradition — midway the captain stops and plays a trumpet · have 1–2 ready to tip</t>
         </is>
       </c>
     </row>
@@ -2971,46 +2922,42 @@
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C106" s="16" t="inlineStr">
+      <c r="C106" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D106" s="18" t="inlineStr">
-        <is>
-          <t>opt</t>
-        </is>
-      </c>
-      <c r="E106" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Optional: Berchtesgaden Salt Mine —  Weather backup for Eagle's Nest · Salzburger Str. 24 · open 9am–5pm · ~20/adult · ~12/child · miners' overalls + underground raft on salt lake + glittering crystals · constant 12C — bring a layer · 1.5–2hrs · book online at salzbergwerk.de to </t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="21" customHeight="1">
-      <c r="A107" s="16" t="inlineStr">
+      <c r="D106" s="18" t="inlineStr"/>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>9:45am — Obersee &amp; Röthbachfall — flat 15 min walk from Salet dock · mirror-like glacial lake · iconic half-submerged wooden boathouse · walk all the way to Fischunkelalm hut on the far side · look straight up the valley walls — Röthbachfall = Germany's highest waterfall crashing</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="12" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B107" s="16" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C107" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D107" s="18" t="inlineStr"/>
-      <c r="E107" s="19" t="inlineStr">
-        <is>
-          <t>Dokumentation Obersalzberg WWII Museum — 30 min · 10/adult</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="27" customHeight="1">
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr"/>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>12:00pm — St. Bartholomä lunch stop — allow 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
       <c r="A108" s="16" t="inlineStr">
         <is>
           <t>Jun 25</t>
@@ -3029,11 +2976,11 @@
       <c r="D108" s="18" t="inlineStr"/>
       <c r="E108" s="19" t="inlineStr">
         <is>
-          <t>~4:00pm — Rossfeld Panorama Road — 9 toll · Germany's highest panoramic toll road at 1,570m</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="31" customHeight="1">
+          <t>12:45pm — Final boat back to Königssee Seelände — 35 min · arrive ~1:15pm · walk 10 min to car park</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="54" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
           <t>Jun 25</t>
@@ -3052,303 +2999,307 @@
       <c r="D109" s="10" t="inlineStr"/>
       <c r="E109" s="11" t="inlineStr">
         <is>
+          <t>1:30pm — Eagle's Nest (Kehlsteinhaus) — drive 10 min to Obersalzberg car park · Kehlsteinbus ~32 (bus + brass elevator) ·  Golden Rule: immediately book 4:00 or 4:15pm return slot at top counter · 360 Alpine panorama at 1,834m · allow 2hrs ·  If foggy/cloudy: swap for Berchtesgad</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="54" customHeight="1">
+      <c r="A110" s="16" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D110" s="18" t="inlineStr">
+        <is>
+          <t>opt</t>
+        </is>
+      </c>
+      <c r="E110" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Optional: Berchtesgaden Salt Mine —  Weather backup for Eagle's Nest · Salzburger Str. 24 · open 9am–5pm · ~20/adult · ~12/child · miners' overalls + underground raft on salt lake + glittering crystals · constant 12C — bring a layer · 1.5–2hrs · book online at salzbergwerk.de to </t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="21" customHeight="1">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D111" s="18" t="inlineStr"/>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>Dokumentation Obersalzberg WWII Museum — 30 min · 10/adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="27" customHeight="1">
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr"/>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>~4:00pm — Rossfeld Panorama Road — 9 toll · Germany's highest panoramic toll road at 1,570m</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="31" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr"/>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
           <t>~4:45pm — Hintersee &amp; Zauberwald (Magic Forest) — 15 min drive toward Ramsau · follow the trail into the Zauberwald</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="30" customHeight="1">
-      <c r="A110" s="24" t="inlineStr">
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="24" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B110" s="24" t="inlineStr">
+      <c r="B114" s="24" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C110" s="25" t="inlineStr">
+      <c r="C114" s="25" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D110" s="26" t="inlineStr"/>
-      <c r="E110" s="27" t="inlineStr">
+      <c r="D114" s="26" t="inlineStr"/>
+      <c r="E114" s="27" t="inlineStr">
         <is>
           <t>Night 2 — Berchtesgaden Apartment —  Already checked in ·  Kälbersteinstraße 4, 83471 Berchtesgaden, Germany</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="12" t="inlineStr">
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="12" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C111" s="13" t="inlineStr">
+      <c r="C115" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D111" s="14" t="inlineStr"/>
-      <c r="E111" s="15" t="inlineStr">
+      <c r="D115" s="14" t="inlineStr"/>
+      <c r="E115" s="15" t="inlineStr">
         <is>
           <t>Dinner — Berchtesgaden — Bräustüberl Berchtesgaden (Bräuhausstraße 13) if not done Day 5 · or Gasthof Neuhaus</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="28" t="inlineStr"/>
-      <c r="B112" s="28" t="inlineStr"/>
-      <c r="C112" s="29" t="inlineStr">
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="28" t="inlineStr"/>
+      <c r="B116" s="28" t="inlineStr"/>
+      <c r="C116" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D112" s="28" t="inlineStr"/>
-      <c r="E112" s="30" t="inlineStr">
+      <c r="D116" s="28" t="inlineStr"/>
+      <c r="E116" s="30" t="inlineStr">
         <is>
           <t>Königssee boat tips — ~28–30 return to Salet per adult · book at seenschifffahrt.de 1 week before · dock is 10 min walk from car park · tip the captain 1–2 for the trumpet echo</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="28" customHeight="1">
-      <c r="A113" s="28" t="inlineStr"/>
-      <c r="B113" s="28" t="inlineStr"/>
-      <c r="C113" s="29" t="inlineStr">
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="28" t="inlineStr"/>
+      <c r="B117" s="28" t="inlineStr"/>
+      <c r="C117" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D113" s="28" t="inlineStr"/>
-      <c r="E113" s="30" t="inlineStr">
+      <c r="D117" s="28" t="inlineStr"/>
+      <c r="E117" s="30" t="inlineStr">
         <is>
           <t>Eagle's Nest return bus — book 4:00 or 4:15pm slot at the top counter IMMEDIATELY · slots fill fast in peak season · missing it = stranded at the top</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="21" customHeight="1">
-      <c r="A114" s="28" t="inlineStr"/>
-      <c r="B114" s="28" t="inlineStr"/>
-      <c r="C114" s="29" t="inlineStr">
+    <row r="118" ht="21" customHeight="1">
+      <c r="A118" s="28" t="inlineStr"/>
+      <c r="B118" s="28" t="inlineStr"/>
+      <c r="C118" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D114" s="28" t="inlineStr"/>
-      <c r="E114" s="30" t="inlineStr">
+      <c r="D118" s="28" t="inlineStr"/>
+      <c r="E118" s="30" t="inlineStr">
         <is>
           <t>Königssee booking — book at seenschifffahrt.de · reserve ~1 week before Jun 25 · non-refundable</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="3" customHeight="1">
-      <c r="A115" s="31" t="n"/>
-      <c r="B115" s="31" t="n"/>
-      <c r="C115" s="31" t="n"/>
-      <c r="D115" s="31" t="n"/>
-      <c r="E115" s="31" t="n"/>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
+    <row r="119" ht="3" customHeight="1">
+      <c r="A119" s="31" t="n"/>
+      <c r="B119" s="31" t="n"/>
+      <c r="C119" s="31" t="n"/>
+      <c r="D119" s="31" t="n"/>
+      <c r="E119" s="31" t="n"/>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>DAY 7  |  Jun 26  |  The Salzkammergut Sprint — Klamm · Salzburg · Wolfgangsee · Hallstatt  |  ~180 km / 112 mi  ~3h 30m incl. Salzburg parking</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr"/>
-      <c r="C116" s="4" t="inlineStr"/>
-      <c r="D116" s="4" t="inlineStr"/>
-      <c r="E116" s="4" t="inlineStr"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr"/>
+      <c r="C120" s="4" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>&gt; 8:15am depart Berchtesgaden  9:00am Liechtensteinklamm  11am drive Salzburg  12pm P+R South + Altstadt  Hohensalzburg Panorama Tour  3pm drive Wolfgangsee  4pm St. GilgenSt. Wolfgang ferry  5:30pm Hallstatt golden hour  7:30pm Kaiserblick Goisern</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr"/>
-      <c r="C117" s="6" t="inlineStr"/>
-      <c r="D117" s="6" t="inlineStr"/>
-      <c r="E117" s="6" t="inlineStr"/>
-    </row>
-    <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr"/>
+      <c r="C121" s="6" t="inlineStr"/>
+      <c r="D121" s="6" t="inlineStr"/>
+      <c r="E121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>KEY: Liechtensteinklamm 9:00am sharp — be first at the gate · 16/adult · wear sturdy shoes  |   Salzburg: P+R South (Alpenstraße) 15 family combo — do NOT park in city centre · 2026 restricted zone  |   Hallstatt tunnel signs: if "Full" — go straight to Goisern · park Obertraun + ferry instead</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr"/>
-      <c r="C118" s="7" t="inlineStr"/>
-      <c r="D118" s="7" t="inlineStr"/>
-      <c r="E118" s="7" t="inlineStr"/>
-    </row>
-    <row r="119" ht="41" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr"/>
+      <c r="C122" s="7" t="inlineStr"/>
+      <c r="D122" s="7" t="inlineStr"/>
+      <c r="E122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123" ht="41" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr"/>
-      <c r="E119" s="11" t="inlineStr">
+      <c r="D123" s="10" t="inlineStr"/>
+      <c r="E123" s="11" t="inlineStr">
         <is>
           <t>8:15am — Checkout Berchtesgaden + depart — drive 35 min south toward St. Johann im Pongau — Austrian motorway A10 ·  Austrian vignette must be active — you are on the A10 today</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="35" customHeight="1">
-      <c r="A120" s="16" t="inlineStr">
+    <row r="124" ht="35" customHeight="1">
+      <c r="A124" s="16" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B120" s="16" t="inlineStr">
+      <c r="B124" s="16" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C120" s="17" t="inlineStr">
+      <c r="C124" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D120" s="18" t="inlineStr"/>
-      <c r="E120" s="19" t="inlineStr">
+      <c r="D124" s="18" t="inlineStr"/>
+      <c r="E124" s="19" t="inlineStr">
         <is>
           <t>9:00am — Liechtensteinklamm Gorge — be there at opening (9:00am) — experience the helix staircase without crowds · thundering waterfalls + mist</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="54" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="125" ht="54" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C121" s="9" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr"/>
-      <c r="E121" s="11" t="inlineStr">
+      <c r="D125" s="10" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr">
         <is>
           <t>11:00am — Drive north to Salzburg — ~1hr on A10 · arrive ~12:00pm ·  Do NOT park in the city centre — 2026 restricted traffic zone + construction everywhere · use P+R South (Alpenstraße) — 15 combo-ticket covers parking + shuttle bus for the whole family</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="16" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B122" s="16" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D122" s="18" t="inlineStr"/>
-      <c r="E122" s="19" t="inlineStr">
-        <is>
-          <t>12:00pm — Salzburg old town</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="33" customHeight="1">
-      <c r="A123" s="16" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B123" s="16" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C123" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D123" s="18" t="inlineStr"/>
-      <c r="E123" s="19" t="inlineStr">
-        <is>
-          <t>12:30pm — Hohensalzburg Fortress — funicular up from Kapitelplatz · stick to the Panorama Tour —  Interior: 16/adult · allow 1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="30" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D124" s="10" t="inlineStr"/>
-      <c r="E124" s="11" t="inlineStr">
-        <is>
-          <t>3:00pm — Drive east to Wolfgangsee — 45 min to St. Gilgen · arrive ~3:45pm · park in St. Gilgen village car park</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="34" customHeight="1">
-      <c r="A125" s="16" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C125" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D125" s="18" t="inlineStr"/>
-      <c r="E125" s="19" t="inlineStr">
-        <is>
-          <t>4:00pm — Wolfgangsee ferry: St. Gilgen  St. Wolfgang  back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="19" customHeight="1">
+    <row r="126" ht="18" customHeight="1">
       <c r="A126" s="16" t="inlineStr">
         <is>
           <t>Jun 26</t>
@@ -3367,7 +3318,7 @@
       <c r="D126" s="18" t="inlineStr"/>
       <c r="E126" s="19" t="inlineStr">
         <is>
-          <t>5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
+          <t>12:00pm — Salzburg old town</t>
         </is>
       </c>
     </row>
@@ -3390,11 +3341,11 @@
       <c r="D127" s="18" t="inlineStr"/>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t>Hallstatt 2026 camera parking system — alternative: park at Obertraun (5 min drive) + take the ferry to Hallstatt (4 · 10 min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="25" customHeight="1">
+          <t>12:30pm — Hohensalzburg Fortress — funicular up from Kapitelplatz · stick to the Panorama Tour —  Interior: 16/adult · allow 1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="30" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
         <is>
           <t>Jun 26</t>
@@ -3413,215 +3364,211 @@
       <c r="D128" s="10" t="inlineStr"/>
       <c r="E128" s="11" t="inlineStr">
         <is>
+          <t>3:00pm — Drive east to Wolfgangsee — 45 min to St. Gilgen · arrive ~3:45pm · park in St. Gilgen village car park</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="34" customHeight="1">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D129" s="18" t="inlineStr"/>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>4:00pm — Wolfgangsee ferry: St. Gilgen  St. Wolfgang  back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="19" customHeight="1">
+      <c r="A130" s="16" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D130" s="18" t="inlineStr"/>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="33" customHeight="1">
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D131" s="18" t="inlineStr"/>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>Hallstatt 2026 camera parking system — alternative: park at Obertraun (5 min drive) + take the ferry to Hallstatt (4 · 10 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="25" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr"/>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
           <t>7:30pm — Kaiserblick Goisern, Bad Goisern — 15 min drive from Hallstatt · $333</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="36" customHeight="1">
-      <c r="A129" s="28" t="inlineStr"/>
-      <c r="B129" s="28" t="inlineStr"/>
-      <c r="C129" s="29" t="inlineStr">
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="28" t="inlineStr"/>
+      <c r="B133" s="28" t="inlineStr"/>
+      <c r="C133" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D129" s="28" t="inlineStr"/>
-      <c r="E129" s="30" t="inlineStr">
+      <c r="D133" s="28" t="inlineStr"/>
+      <c r="E133" s="30" t="inlineStr">
         <is>
           <t>Salzburg parking 2026 — Old Town becoming restricted traffic zone · construction barriers everywhere · use P+R South (Alpenstraße) · 15 combo = parking + shuttle bus for whole family · much faster than city garage hunting</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="34" customHeight="1">
-      <c r="A130" s="28" t="inlineStr"/>
-      <c r="B130" s="28" t="inlineStr"/>
-      <c r="C130" s="29" t="inlineStr">
+    <row r="134" ht="34" customHeight="1">
+      <c r="A134" s="28" t="inlineStr"/>
+      <c r="B134" s="28" t="inlineStr"/>
+      <c r="C134" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D130" s="28" t="inlineStr"/>
-      <c r="E130" s="30" t="inlineStr">
+      <c r="D134" s="28" t="inlineStr"/>
+      <c r="E134" s="30" t="inlineStr">
         <is>
           <t>Hallstatt 2026 camera system — electronic signs at tunnel entrance · if "Full": do not enter · drive straight to Kaiserblick Goisern · return via ferry from Obertraun (4 · 10 min) or bus on Day 8</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="31" customHeight="1">
-      <c r="A131" s="28" t="inlineStr"/>
-      <c r="B131" s="28" t="inlineStr"/>
-      <c r="C131" s="29" t="inlineStr">
+    <row r="135" ht="31" customHeight="1">
+      <c r="A135" s="28" t="inlineStr"/>
+      <c r="B135" s="28" t="inlineStr"/>
+      <c r="C135" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D131" s="28" t="inlineStr"/>
-      <c r="E131" s="30" t="inlineStr">
+      <c r="D135" s="28" t="inlineStr"/>
+      <c r="E135" s="30" t="inlineStr">
         <is>
           <t>Hohensalzburg tip — stick to Panorama Tour only (courtyards + bastions) · skip the individual museums to stay on schedule · the view is the reason to go up · allow 1hr max</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="3" customHeight="1">
-      <c r="A132" s="31" t="n"/>
-      <c r="B132" s="31" t="n"/>
-      <c r="C132" s="31" t="n"/>
-      <c r="D132" s="31" t="n"/>
-      <c r="E132" s="31" t="n"/>
-    </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
+    <row r="136" ht="3" customHeight="1">
+      <c r="A136" s="31" t="n"/>
+      <c r="B136" s="31" t="n"/>
+      <c r="C136" s="31" t="n"/>
+      <c r="D136" s="31" t="n"/>
+      <c r="E136" s="31" t="n"/>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>DAY 8  |  Jun 27  |  Dachstein Krippenstein · Gosausee · Hallstatt Evening — The High-Alpine Day  |  ~40 km / 25 mi  ~1h total · very local day</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr"/>
-      <c r="C133" s="4" t="inlineStr"/>
-      <c r="D133" s="4" t="inlineStr"/>
-      <c r="E133" s="4" t="inlineStr"/>
-    </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr"/>
+      <c r="C137" s="4" t="inlineStr"/>
+      <c r="D137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr"/>
+    </row>
+    <row r="138" ht="15" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>&gt; 8:15am depart Bad Goisern  8:45am Krippenstein cable car  9:30am 5 Fingers viewpoint  Ice Cave optional  1:30pm Gosausee Mirror Lake  2:00pm Gosaukammbahn  4:30pm Hallstatt golden hour + dinner  Beinhaus  ~7pm Kaiserblick Goisern</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr"/>
-      <c r="C134" s="6" t="inlineStr"/>
-      <c r="D134" s="6" t="inlineStr"/>
-      <c r="E134" s="6" t="inlineStr"/>
-    </row>
-    <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr"/>
+      <c r="C138" s="6" t="inlineStr"/>
+      <c r="D138" s="6" t="inlineStr"/>
+      <c r="E138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139" ht="24" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>KEY: Salt Mine + Skywalk CLOSED Jun 27 — reopens Jun 30 · do not book these  |   Dachstein Krippenstein 8:45am  5 Fingers  Gosausee 1:30pm  Gosaukammbahn  Hallstatt 4:30pm  |   Saturday = busy Hallstatt · check digital signs · if Full  park Obertraun + NAVIA ferry 4</t>
         </is>
       </c>
-      <c r="B135" s="7" t="inlineStr"/>
-      <c r="C135" s="7" t="inlineStr"/>
-      <c r="D135" s="7" t="inlineStr"/>
-      <c r="E135" s="7" t="inlineStr"/>
-    </row>
-    <row r="136" ht="54" customHeight="1">
-      <c r="A136" s="33" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr"/>
+      <c r="C139" s="7" t="inlineStr"/>
+      <c r="D139" s="7" t="inlineStr"/>
+      <c r="E139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140" ht="54" customHeight="1">
+      <c r="A140" s="33" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="B136" s="33" t="inlineStr">
+      <c r="B140" s="33" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C136" s="34" t="inlineStr">
+      <c r="C140" s="34" t="inlineStr">
         <is>
           <t>ALERT</t>
         </is>
       </c>
-      <c r="D136" s="35" t="inlineStr"/>
-      <c r="E136" s="36" t="inlineStr">
+      <c r="D140" s="35" t="inlineStr"/>
+      <c r="E140" s="36" t="inlineStr">
         <is>
           <t>2026 Alert: Hallstatt Salt Mine + Skywalk CLOSED Jun 27 — major renovation underway · scheduled to reopen June 30, 2026 · do not attempt to book these for today · alternative: Salzwelten Altaussee — (25 min from Bad Goisern) — active mine · only if you really want a salt mine</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="36" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>8:15am — Depart Bad Goisern — 20 min drive to Obertraun · arrive by 8:40am · park at the Dachstein Krippenstein cable car base station in Obertraun</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="26" customHeight="1">
-      <c r="A138" s="16" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="B138" s="16" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C138" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D138" s="18" t="inlineStr"/>
-      <c r="E138" s="19" t="inlineStr">
-        <is>
-          <t>8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · 44.90/adult</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="28" customHeight="1">
-      <c r="A139" s="16" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="B139" s="16" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C139" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D139" s="18" t="inlineStr"/>
-      <c r="E139" s="19" t="inlineStr">
-        <is>
-          <t>9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="28" customHeight="1">
-      <c r="A140" s="16" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D140" s="18" t="inlineStr">
-        <is>
-          <t>opt</t>
-        </is>
-      </c>
-      <c r="E140" s="32" t="inlineStr">
-        <is>
-          <t>Optional: Giant Ice Cave (Section 1) — accessible from Section 1 midstation · extra cost ~10/adult</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="26" customHeight="1">
+    <row r="141" ht="36" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Jun 27</t>
@@ -3640,11 +3587,11 @@
       <c r="D141" s="10" t="inlineStr"/>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>1:30pm — Vorderer Gosausee — the Mirror Lake — 25 min drive from Obertraun · allow 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="29" customHeight="1">
+          <t>8:15am — Depart Bad Goisern — 20 min drive to Obertraun · arrive by 8:40am · park at the Dachstein Krippenstein cable car base station in Obertraun</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="26" customHeight="1">
       <c r="A142" s="16" t="inlineStr">
         <is>
           <t>Jun 27</t>
@@ -3663,11 +3610,11 @@
       <c r="D142" s="18" t="inlineStr"/>
       <c r="E142" s="19" t="inlineStr">
         <is>
-          <t>2:00pm — Gosaukammbahn cable car — ~28 return/adult · panoramic view of the Dachstein glacier from above</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="27" customHeight="1">
+          <t>8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · 44.90/adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
       <c r="A143" s="16" t="inlineStr">
         <is>
           <t>Jun 27</t>
@@ -3686,295 +3633,299 @@
       <c r="D143" s="18" t="inlineStr"/>
       <c r="E143" s="19" t="inlineStr">
         <is>
+          <t>9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="16" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C144" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>opt</t>
+        </is>
+      </c>
+      <c r="E144" s="32" t="inlineStr">
+        <is>
+          <t>Optional: Giant Ice Cave (Section 1) — accessible from Section 1 midstation · extra cost ~10/adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="26" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr"/>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>1:30pm — Vorderer Gosausee — the Mirror Lake — 25 min drive from Obertraun · allow 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="29" customHeight="1">
+      <c r="A146" s="16" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D146" s="18" t="inlineStr"/>
+      <c r="E146" s="19" t="inlineStr">
+        <is>
+          <t>2:00pm — Gosaukammbahn cable car — ~28 return/adult · panoramic view of the Dachstein glacier from above</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="27" customHeight="1">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D147" s="18" t="inlineStr"/>
+      <c r="E147" s="19" t="inlineStr">
+        <is>
           <t>4:30pm — Hallstatt village evening — mine renovation crowds have gone by now · allow 1.5hrs</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="33" customHeight="1">
-      <c r="A144" s="16" t="inlineStr">
+    <row r="148" ht="33" customHeight="1">
+      <c r="A148" s="16" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="B144" s="16" t="inlineStr">
+      <c r="B148" s="16" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C144" s="17" t="inlineStr">
+      <c r="C148" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D144" s="18" t="inlineStr"/>
-      <c r="E144" s="19" t="inlineStr">
+      <c r="D148" s="18" t="inlineStr"/>
+      <c r="E148" s="19" t="inlineStr">
         <is>
           <t>Saturday parking warning — if P1/P2 show "Full": park in Obertraun (5 min drive) + take the ferry across · NAVIA ferry: 4 cash</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="19" customHeight="1">
-      <c r="A145" s="16" t="inlineStr">
+    <row r="149" ht="19" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="B145" s="16" t="inlineStr">
+      <c r="B149" s="16" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C145" s="17" t="inlineStr">
+      <c r="C149" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D145" s="18" t="inlineStr"/>
-      <c r="E145" s="19" t="inlineStr">
+      <c r="D149" s="18" t="inlineStr"/>
+      <c r="E149" s="19" t="inlineStr">
         <is>
           <t>Beinhaus (Bone Chapel) — 1.50/adult · 10 min</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="32" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="150" ht="32" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="C150" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr"/>
-      <c r="E146" s="11" t="inlineStr">
+      <c r="D150" s="10" t="inlineStr"/>
+      <c r="E150" s="11" t="inlineStr">
         <is>
           <t>Night 2 — Kaiserblick Goisern —  Already checked in ·  38 Unterjoch, 4822 Bad Goisern, Austria · 15 min drive from Hallstatt</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="31" customHeight="1">
-      <c r="A147" s="28" t="inlineStr"/>
-      <c r="B147" s="28" t="inlineStr"/>
-      <c r="C147" s="29" t="inlineStr">
+    <row r="151" ht="31" customHeight="1">
+      <c r="A151" s="28" t="inlineStr"/>
+      <c r="B151" s="28" t="inlineStr"/>
+      <c r="C151" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D147" s="28" t="inlineStr"/>
-      <c r="E147" s="30" t="inlineStr">
+      <c r="D151" s="28" t="inlineStr"/>
+      <c r="E151" s="30" t="inlineStr">
         <is>
           <t>Salt Mine + Skywalk CLOSED Jun 27 — major renovation · reopens Jun 30, 2026 · alternative: Salzwelten Altaussee (25 min from Bad Goisern) · active mine · most authentic</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="36" customHeight="1">
-      <c r="A148" s="28" t="inlineStr"/>
-      <c r="B148" s="28" t="inlineStr"/>
-      <c r="C148" s="29" t="inlineStr">
+    <row r="152" ht="36" customHeight="1">
+      <c r="A152" s="28" t="inlineStr"/>
+      <c r="B152" s="28" t="inlineStr"/>
+      <c r="C152" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D148" s="28" t="inlineStr"/>
-      <c r="E148" s="30" t="inlineStr">
+      <c r="D152" s="28" t="inlineStr"/>
+      <c r="E152" s="30" t="inlineStr">
         <is>
           <t>5 Fingers vs Skywalk — 5 Fingers on Krippenstein is higher, more dramatic, free with cable car ticket · direct aerial view down into Hallstatt village · Skywalk is closed anyway — 5 Fingers is the better experience</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="28" t="inlineStr"/>
-      <c r="B149" s="28" t="inlineStr"/>
-      <c r="C149" s="29" t="inlineStr">
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="28" t="inlineStr"/>
+      <c r="B153" s="28" t="inlineStr"/>
+      <c r="C153" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D149" s="28" t="inlineStr"/>
-      <c r="E149" s="30" t="inlineStr">
+      <c r="D153" s="28" t="inlineStr"/>
+      <c r="E153" s="30" t="inlineStr">
         <is>
           <t>Gosausee afternoon tip — best photos happen when the sun hits the Dachstein glacier face-on in the afternoon · go at 3pm not morning for the mirror reflection shot</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="33" customHeight="1">
-      <c r="A150" s="28" t="inlineStr"/>
-      <c r="B150" s="28" t="inlineStr"/>
-      <c r="C150" s="29" t="inlineStr">
+    <row r="154" ht="33" customHeight="1">
+      <c r="A154" s="28" t="inlineStr"/>
+      <c r="B154" s="28" t="inlineStr"/>
+      <c r="C154" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D150" s="28" t="inlineStr"/>
-      <c r="E150" s="30" t="inlineStr">
+      <c r="D154" s="28" t="inlineStr"/>
+      <c r="E154" s="30" t="inlineStr">
         <is>
           <t>Hofer (Aldi) Bad Goisern — stock up this morning or evening · discount prices · buy for Jun 27–Jul 1: Grossglockner · Sillian · Dolomites 3 nights · Hofrat-Renner-Weg 1 · open Tue 7:15am</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="3" customHeight="1">
-      <c r="A151" s="31" t="n"/>
-      <c r="B151" s="31" t="n"/>
-      <c r="C151" s="31" t="n"/>
-      <c r="D151" s="31" t="n"/>
-      <c r="E151" s="31" t="n"/>
-    </row>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="3" t="inlineStr">
+    <row r="155" ht="3" customHeight="1">
+      <c r="A155" s="31" t="n"/>
+      <c r="B155" s="31" t="n"/>
+      <c r="C155" s="31" t="n"/>
+      <c r="D155" s="31" t="n"/>
+      <c r="E155" s="31" t="n"/>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>DAY 9  |  Jun 28  |  The Roof of Austria — Grossglockner High Alpine Road  Sillian  |  ~280 km / 174 mi  ~4h 30m incl. Grossglockner slow drive</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr"/>
-      <c r="C152" s="4" t="inlineStr"/>
-      <c r="D152" s="4" t="inlineStr"/>
-      <c r="E152" s="4" t="inlineStr"/>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="B156" s="4" t="inlineStr"/>
+      <c r="C156" s="4" t="inlineStr"/>
+      <c r="D156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr"/>
+    </row>
+    <row r="157" ht="15" customHeight="1">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>&gt; 8:00am checkout  9:30am Ferleiten toll 46.50  10:15am Edelweiß-Spitze  11:30am Hochtor tunnel  12:15pm KFJ-Höhe + marmots  1:30pm glacier lunch  3:30pm Heiligenblut church photo  5:30pm Sillian  alarm 5am</t>
         </is>
       </c>
-      <c r="B153" s="6" t="inlineStr"/>
-      <c r="C153" s="6" t="inlineStr"/>
-      <c r="D153" s="6" t="inlineStr"/>
-      <c r="E153" s="6" t="inlineStr"/>
-    </row>
-    <row r="154" ht="24" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
+      <c r="B157" s="6" t="inlineStr"/>
+      <c r="C157" s="6" t="inlineStr"/>
+      <c r="D157" s="6" t="inlineStr"/>
+      <c r="E157" s="6" t="inlineStr"/>
+    </row>
+    <row r="158" ht="24" customHeight="1">
+      <c r="A158" s="7" t="inlineStr">
         <is>
           <t>KEY: Edelweiß-Spitze FIRST — go before motorcycles arrive · dead-end road congests by afternoon  |   Gamsgrubenweg 10 min from KFJ-Höhe — best marmot spotting on the road · kids will love it  |   Descent: engine brake in low gear · do NOT ride the brakes · they will overheat</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr"/>
-      <c r="C154" s="7" t="inlineStr"/>
-      <c r="D154" s="7" t="inlineStr"/>
-      <c r="E154" s="7" t="inlineStr"/>
-    </row>
-    <row r="155" ht="38" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
+      <c r="B158" s="7" t="inlineStr"/>
+      <c r="C158" s="7" t="inlineStr"/>
+      <c r="D158" s="7" t="inlineStr"/>
+      <c r="E158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159" ht="38" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C155" s="9" t="inlineStr">
+      <c r="C159" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D155" s="10" t="inlineStr"/>
-      <c r="E155" s="11" t="inlineStr">
+      <c r="D159" s="10" t="inlineStr"/>
+      <c r="E159" s="11" t="inlineStr">
         <is>
           <t>8:00am — Checkout Kaiserblick Goisern — 1.5hr drive to the Ferleiten toll gate via the B311 · download offline maps for the Dolomites tonight if not done yet</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="39" customHeight="1">
-      <c r="A156" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C156" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D156" s="18" t="inlineStr"/>
-      <c r="E156" s="19" t="inlineStr">
-        <is>
-          <t>Grossglockner High Alpine Road — 48km of switchbacks across the highest surfaced alpine pass in Austria · road open from 5:30am — last entry 45 min before 9pm closing</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="33" customHeight="1">
-      <c r="A157" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B157" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C157" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D157" s="18" t="inlineStr"/>
-      <c r="E157" s="19" t="inlineStr">
-        <is>
-          <t>9:30am — Ferleiten Toll Gate — 2026 rate: 46.50/car — first stop: Edelweiß-Spitze — go there FIRST before the motorcycles arrive</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="30" customHeight="1">
-      <c r="A158" s="20" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B158" s="20" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C158" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D158" s="22" t="inlineStr"/>
-      <c r="E158" s="23" t="inlineStr">
-        <is>
-          <t>Haus Alpine Naturschau — natural history museum — 15 min · great context for the kids before reaching the summit</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="28" customHeight="1">
-      <c r="A159" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B159" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C159" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D159" s="18" t="inlineStr"/>
-      <c r="E159" s="19" t="inlineStr">
-        <is>
-          <t>10:15am — Edelweiß-Spitze (2,571m) — MUST STOP · dead-end cobblestone branch road — go here FIRST</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="19" customHeight="1">
+    <row r="160" ht="39" customHeight="1">
       <c r="A160" s="16" t="inlineStr">
         <is>
           <t>Jun 28</t>
@@ -3993,149 +3944,149 @@
       <c r="D160" s="18" t="inlineStr"/>
       <c r="E160" s="19" t="inlineStr">
         <is>
+          <t>Grossglockner High Alpine Road — 48km of switchbacks across the highest surfaced alpine pass in Austria · road open from 5:30am — last entry 45 min before 9pm closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="33" customHeight="1">
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D161" s="18" t="inlineStr"/>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>9:30am — Ferleiten Toll Gate — 2026 rate: 46.50/car — first stop: Edelweiß-Spitze — go there FIRST before the motorcycles arrive</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B162" s="20" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C162" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="inlineStr"/>
+      <c r="E162" s="23" t="inlineStr">
+        <is>
+          <t>Haus Alpine Naturschau — natural history museum — 15 min · great context for the kids before reaching the summit</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="28" customHeight="1">
+      <c r="A163" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C163" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D163" s="18" t="inlineStr"/>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>10:15am — Edelweiß-Spitze (2,571m) — MUST STOP · dead-end cobblestone branch road — go here FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="19" customHeight="1">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C164" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D164" s="18" t="inlineStr"/>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
           <t>11:30am — Hochtor Tunnel (2,504m) — 10 min stop</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="50" customHeight="1">
-      <c r="A161" s="20" t="inlineStr">
+    <row r="165" ht="50" customHeight="1">
+      <c r="A165" s="20" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="B161" s="20" t="inlineStr">
+      <c r="B165" s="20" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C161" s="21" t="inlineStr">
+      <c r="C165" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D161" s="22" t="inlineStr"/>
-      <c r="E161" s="23" t="inlineStr">
+      <c r="D165" s="22" t="inlineStr"/>
+      <c r="E165" s="23" t="inlineStr">
         <is>
           <t>12:15pm — Kaiser-Franz-Josefs-Höhe (2,369m) — Austria's longest glacier (8km) stretching toward the Grossglockner ·  2026: glacier has receded significantly — to touch the ice take the Gletscherbahn funicular down + hike 30–45 min</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="31" customHeight="1">
-      <c r="A162" s="16" t="inlineStr">
+    <row r="166" ht="31" customHeight="1">
+      <c r="A166" s="16" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="B162" s="16" t="inlineStr">
+      <c r="B166" s="16" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C162" s="17" t="inlineStr">
+      <c r="C166" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D162" s="18" t="inlineStr"/>
-      <c r="E162" s="19" t="inlineStr">
+      <c r="D166" s="18" t="inlineStr"/>
+      <c r="E166" s="19" t="inlineStr">
         <is>
           <t>Marmot &amp; ibex spotting — Gamsgrubenweg — from Kaiser-Franz-Josefs-Höhe: follow the Gamsgrubenweg tunnel path for 10 min</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="27" customHeight="1">
-      <c r="A163" s="12" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B163" s="12" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C163" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D163" s="14" t="inlineStr"/>
-      <c r="E163" s="15" t="inlineStr">
-        <is>
-          <t>1:30pm — Lunch at Kaiser-Franz-Josefs-Höhe — panoramic terrace facing the glacier · allow 1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="19" customHeight="1">
-      <c r="A164" s="20" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B164" s="20" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C164" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D164" s="22" t="inlineStr"/>
-      <c r="E164" s="23" t="inlineStr">
-        <is>
-          <t>Descent toward Heiligenblut — brake warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="19" customHeight="1">
-      <c r="A165" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B165" s="16" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C165" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D165" s="18" t="inlineStr"/>
-      <c r="E165" s="19" t="inlineStr">
-        <is>
-          <t>3:30pm — Heiligenblut village — allow 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="21" customHeight="1">
-      <c r="A166" s="24" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="B166" s="24" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C166" s="25" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D166" s="26" t="inlineStr"/>
-      <c r="E166" s="27" t="inlineStr">
-        <is>
-          <t>5:30pm — Hotel Schwarzer Adler, Sillian — $115 / 99.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="35" customHeight="1">
+    <row r="167" ht="27" customHeight="1">
       <c r="A167" s="12" t="inlineStr">
         <is>
           <t>Jun 28</t>
@@ -4154,71 +4105,103 @@
       <c r="D167" s="14" t="inlineStr"/>
       <c r="E167" s="15" t="inlineStr">
         <is>
+          <t>1:30pm — Lunch at Kaiser-Franz-Josefs-Höhe — panoramic terrace facing the glacier · allow 1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="19" customHeight="1">
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B168" s="20" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C168" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D168" s="22" t="inlineStr"/>
+      <c r="E168" s="23" t="inlineStr">
+        <is>
+          <t>Descent toward Heiligenblut — brake warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="19" customHeight="1">
+      <c r="A169" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D169" s="18" t="inlineStr"/>
+      <c r="E169" s="19" t="inlineStr">
+        <is>
+          <t>3:30pm — Heiligenblut village — allow 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="21" customHeight="1">
+      <c r="A170" s="24" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B170" s="24" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C170" s="25" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D170" s="26" t="inlineStr"/>
+      <c r="E170" s="27" t="inlineStr">
+        <is>
+          <t>5:30pm — Hotel Schwarzer Adler, Sillian — $115 / 99.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="35" customHeight="1">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C171" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D171" s="14" t="inlineStr"/>
+      <c r="E171" s="15" t="inlineStr">
+        <is>
           <t>Dinner in Sillian —  Download offline Dolomites maps tonight (Maps.me or Google Maps) · check Rifugio Auronzo parking booking confirmation</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="35" customHeight="1">
-      <c r="A168" s="28" t="inlineStr"/>
-      <c r="B168" s="28" t="inlineStr"/>
-      <c r="C168" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D168" s="28" t="inlineStr"/>
-      <c r="E168" s="30" t="inlineStr">
-        <is>
-          <t>Grossglockner toll 2026: 46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="32" customHeight="1">
-      <c r="A169" s="28" t="inlineStr"/>
-      <c r="B169" s="28" t="inlineStr"/>
-      <c r="C169" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D169" s="28" t="inlineStr"/>
-      <c r="E169" s="30" t="inlineStr">
-        <is>
-          <t>Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="28" t="inlineStr"/>
-      <c r="B170" s="28" t="inlineStr"/>
-      <c r="C170" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D170" s="28" t="inlineStr"/>
-      <c r="E170" s="30" t="inlineStr">
-        <is>
-          <t>Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="31" customHeight="1">
-      <c r="A171" s="28" t="inlineStr"/>
-      <c r="B171" s="28" t="inlineStr"/>
-      <c r="C171" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D171" s="28" t="inlineStr"/>
-      <c r="E171" s="30" t="inlineStr">
-        <is>
-          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="33" customHeight="1">
+    <row r="172" ht="35" customHeight="1">
       <c r="A172" s="28" t="inlineStr"/>
       <c r="B172" s="28" t="inlineStr"/>
       <c r="C172" s="29" t="inlineStr">
@@ -4229,212 +4212,180 @@
       <c r="D172" s="28" t="inlineStr"/>
       <c r="E172" s="30" t="inlineStr">
         <is>
+          <t>Grossglockner toll 2026: 46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="32" customHeight="1">
+      <c r="A173" s="28" t="inlineStr"/>
+      <c r="B173" s="28" t="inlineStr"/>
+      <c r="C173" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D173" s="28" t="inlineStr"/>
+      <c r="E173" s="30" t="inlineStr">
+        <is>
+          <t>Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="28" t="inlineStr"/>
+      <c r="B174" s="28" t="inlineStr"/>
+      <c r="C174" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D174" s="28" t="inlineStr"/>
+      <c r="E174" s="30" t="inlineStr">
+        <is>
+          <t>Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="31" customHeight="1">
+      <c r="A175" s="28" t="inlineStr"/>
+      <c r="B175" s="28" t="inlineStr"/>
+      <c r="C175" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D175" s="28" t="inlineStr"/>
+      <c r="E175" s="30" t="inlineStr">
+        <is>
+          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="33" customHeight="1">
+      <c r="A176" s="28" t="inlineStr"/>
+      <c r="B176" s="28" t="inlineStr"/>
+      <c r="C176" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D176" s="28" t="inlineStr"/>
+      <c r="E176" s="30" t="inlineStr">
+        <is>
           <t>Tonight: prep for Dolomites — download offline maps (Google Maps or Maps.me) for the Dolomites · confirm Rifugio Auronzo parking booking · 5am alarm tomorrow · Braies gate opens 7:30am</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="3" customHeight="1">
-      <c r="A173" s="31" t="n"/>
-      <c r="B173" s="31" t="n"/>
-      <c r="C173" s="31" t="n"/>
-      <c r="D173" s="31" t="n"/>
-      <c r="E173" s="31" t="n"/>
-    </row>
-    <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="3" t="inlineStr">
+    <row r="177" ht="3" customHeight="1">
+      <c r="A177" s="31" t="n"/>
+      <c r="B177" s="31" t="n"/>
+      <c r="C177" s="31" t="n"/>
+      <c r="D177" s="31" t="n"/>
+      <c r="E177" s="31" t="n"/>
+    </row>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>DAY 10  |  Jun 29  |  The Iconic Dolomites — Braies Sunrise · Tre Cime · Prato Piazza · Gardena  |  ~200 km / 124 mi  ~5h total driving · many short hops</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr"/>
-      <c r="C174" s="4" t="inlineStr"/>
-      <c r="D174" s="4" t="inlineStr"/>
-      <c r="E174" s="4" t="inlineStr"/>
-    </row>
-    <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="5" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr"/>
+      <c r="C178" s="4" t="inlineStr"/>
+      <c r="D178" s="4" t="inlineStr"/>
+      <c r="E178" s="4" t="inlineStr"/>
+    </row>
+    <row r="179" ht="15" customHeight="1">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>&gt; 8am Sillian  8:45am Braies P3  10:15am depart  Misurina coffee  11:15am Auronzo gate  11:45am Cadini Trail 117  1:30pm lunch  2:30pm Tre Cime walk  3:45pm Gardena Pass  5pm Collalbo</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr"/>
-      <c r="C175" s="6" t="inlineStr"/>
-      <c r="D175" s="6" t="inlineStr"/>
-      <c r="E175" s="6" t="inlineStr"/>
-    </row>
-    <row r="176" ht="24" customHeight="1">
-      <c r="A176" s="7" t="inlineStr">
+      <c r="B179" s="6" t="inlineStr"/>
+      <c r="C179" s="6" t="inlineStr"/>
+      <c r="D179" s="6" t="inlineStr"/>
+      <c r="E179" s="6" t="inlineStr"/>
+    </row>
+    <row r="180" ht="24" customHeight="1">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>KEY: 8am departure — relaxed start · Braies 8:45am · still beautiful · P3 no reservation  |   Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |   Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |   Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |   Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr"/>
-      <c r="C176" s="7" t="inlineStr"/>
-      <c r="D176" s="7" t="inlineStr"/>
-      <c r="E176" s="7" t="inlineStr"/>
-    </row>
-    <row r="177" ht="42" customHeight="1">
-      <c r="A177" s="8" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr"/>
+      <c r="C180" s="7" t="inlineStr"/>
+      <c r="D180" s="7" t="inlineStr"/>
+      <c r="E180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181" ht="42" customHeight="1">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="C181" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D177" s="10" t="inlineStr"/>
-      <c r="E177" s="11" t="inlineStr">
+      <c r="D181" s="10" t="inlineStr"/>
+      <c r="E181" s="11" t="inlineStr">
         <is>
           <t>8:00am — Depart Sillian — 45 min straight across the Italian border · download offline Dolomites maps tonight if not done · update Auronzo plate at pass.auronzo.info tonight (Jun 28)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="42" customHeight="1">
-      <c r="A178" s="16" t="inlineStr">
+    <row r="182" ht="42" customHeight="1">
+      <c r="A182" s="16" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B178" s="16" t="inlineStr">
+      <c r="B182" s="16" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C178" s="17" t="inlineStr">
+      <c r="C182" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D178" s="18" t="inlineStr"/>
-      <c r="E178" s="19" t="inlineStr">
+      <c r="D182" s="18" t="inlineStr"/>
+      <c r="E182" s="19" t="inlineStr">
         <is>
           <t>8:45am — Lago di Braies — park P3 ~12 · no reservation needed · walk the best half of the lakeside circuit · famous stilt boathouse · morning views · allow 1.5hrs · leave by 10:15am</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="39" customHeight="1">
-      <c r="A179" s="8" t="inlineStr">
+    <row r="183" ht="39" customHeight="1">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D179" s="10" t="inlineStr"/>
-      <c r="E179" s="11" t="inlineStr">
+      <c r="D183" s="10" t="inlineStr"/>
+      <c r="E183" s="11" t="inlineStr">
         <is>
           <t>10:15am — Drive via Lago di Misurina — 1hr drive down the valley · stop at Rifugio Misurina café · 15 min coffee + mirror-reflection photo of Tre Cime in the lake</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="39" customHeight="1">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C180" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D180" s="10" t="inlineStr"/>
-      <c r="E180" s="11" t="inlineStr">
-        <is>
-          <t>11:15am — Auronzo gate —  Pre-booked · PASS3CIME_26017885 · Ticket P26134547 · 9am–8:59pm slot · plate reads automatically · drive straight up · 40 paid · no queue</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="51" customHeight="1">
-      <c r="A181" s="20" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="B181" s="20" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C181" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D181" s="22" t="inlineStr"/>
-      <c r="E181" s="23" t="inlineStr">
-        <is>
-          <t>11:45am — Cadini di Misurina Trail 117 — hike out to the iconic jagged peak viewpoint · 45 min RT at normal pace ·  final 50m is a narrow ridge · secondary viewpoint 20m back is 95% as good · allow 1hr 45min total for photos + kids pace</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="26" customHeight="1">
-      <c r="A182" s="12" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="B182" s="12" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C182" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D182" s="14" t="inlineStr"/>
-      <c r="E182" s="15" t="inlineStr">
-        <is>
-          <t>1:30pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="35" customHeight="1">
-      <c r="A183" s="12" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="B183" s="12" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C183" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D183" s="14" t="inlineStr"/>
-      <c r="E183" s="15" t="inlineStr">
-        <is>
-          <t>2:30pm — Tre Cime Highlights Walk — flat path to Rifugio Lavaredo (20 min each way) · see the towering north faces up close · allow 1hr 15min</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="43" customHeight="1">
+    <row r="184" ht="39" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
         <is>
           <t>Jun 29</t>
@@ -4453,1378 +4404,1378 @@
       <c r="D184" s="10" t="inlineStr"/>
       <c r="E184" s="11" t="inlineStr">
         <is>
+          <t>11:15am — Auronzo gate —  Pre-booked · PASS3CIME_26017885 · Ticket P26134547 · 9am–8:59pm slot · plate reads automatically · drive straight up · 40 paid · no queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="51" customHeight="1">
+      <c r="A185" s="20" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="B185" s="20" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C185" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D185" s="22" t="inlineStr"/>
+      <c r="E185" s="23" t="inlineStr">
+        <is>
+          <t>11:45am — Cadini di Misurina Trail 117 — hike out to the iconic jagged peak viewpoint · 45 min RT at normal pace ·  final 50m is a narrow ridge · secondary viewpoint 20m back is 95% as good · allow 1hr 45min total for photos + kids pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="26" customHeight="1">
+      <c r="A186" s="12" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="B186" s="12" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C186" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D186" s="14" t="inlineStr"/>
+      <c r="E186" s="15" t="inlineStr">
+        <is>
+          <t>1:30pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="35" customHeight="1">
+      <c r="A187" s="12" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C187" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D187" s="14" t="inlineStr"/>
+      <c r="E187" s="15" t="inlineStr">
+        <is>
+          <t>2:30pm — Tre Cime Highlights Walk — flat path to Rifugio Lavaredo (20 min each way) · see the towering north faces up close · allow 1hr 15min</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="43" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="inlineStr"/>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
           <t>3:45pm — Passo Gardena scenic drive — drive back down toll road · SS243 Gardena Pass (2,121m) · hairpin turns · low gear descent ·  Lagazuoi cable car optional if energy · ~1hr 15min drive</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="37" customHeight="1">
-      <c r="A185" s="24" t="inlineStr">
+    <row r="189" ht="37" customHeight="1">
+      <c r="A189" s="24" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="B185" s="24" t="inlineStr">
+      <c r="B189" s="24" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C185" s="25" t="inlineStr">
+      <c r="C189" s="25" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D185" s="26" t="inlineStr"/>
-      <c r="E185" s="27" t="inlineStr">
+      <c r="D189" s="26" t="inlineStr"/>
+      <c r="E189" s="27" t="inlineStr">
         <is>
           <t>5:00pm — Kaiserau 1907, Collalbo —  Check in · Via Peter Mayr 65, 39054 Collalbo · check-in 15:00–22:00 · unpack · rest · open a bottle of Italian wine</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="30" customHeight="1">
-      <c r="A186" s="28" t="inlineStr"/>
-      <c r="B186" s="28" t="inlineStr"/>
-      <c r="C186" s="29" t="inlineStr">
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="28" t="inlineStr"/>
+      <c r="B190" s="28" t="inlineStr"/>
+      <c r="C190" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D186" s="28" t="inlineStr"/>
-      <c r="E186" s="30" t="inlineStr">
+      <c r="D190" s="28" t="inlineStr"/>
+      <c r="E190" s="30" t="inlineStr">
         <is>
           <t>Braies 2026 access — road blocked 9am–4pm in peak season · arrive by 5:30am · P3 no reservation before 8am · 12 · leave before 8:30am · pivot to Prato Piazza if cloudy</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="32" customHeight="1">
-      <c r="A187" s="28" t="inlineStr"/>
-      <c r="B187" s="28" t="inlineStr"/>
-      <c r="C187" s="29" t="inlineStr">
+    <row r="191" ht="32" customHeight="1">
+      <c r="A191" s="28" t="inlineStr"/>
+      <c r="B191" s="28" t="inlineStr"/>
+      <c r="C191" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D187" s="28" t="inlineStr"/>
-      <c r="E187" s="30" t="inlineStr">
+      <c r="D191" s="28" t="inlineStr"/>
+      <c r="E191" s="30" t="inlineStr">
         <is>
           <t>Auronzo toll road 2026 — book at pass.auronzo.info · 40/car · 12-hour slot · book May 30 (exactly 30 days before) · rental plate: leave blank · update night before at Sillian hotel</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="35" customHeight="1">
-      <c r="A188" s="28" t="inlineStr"/>
-      <c r="B188" s="28" t="inlineStr"/>
-      <c r="C188" s="29" t="inlineStr">
+    <row r="192" ht="35" customHeight="1">
+      <c r="A192" s="28" t="inlineStr"/>
+      <c r="B192" s="28" t="inlineStr"/>
+      <c r="C192" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D188" s="28" t="inlineStr"/>
-      <c r="E188" s="30" t="inlineStr">
+      <c r="D192" s="28" t="inlineStr"/>
+      <c r="E192" s="30" t="inlineStr">
         <is>
           <t>Cadini viewpoint tip — final 50m is a narrow ridge · secondary viewpoint 20m before the narrow section · 95% as good · go early — very crowded by midday · most dramatic jagged peak view in the Dolomites</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="3" customHeight="1">
-      <c r="A189" s="31" t="n"/>
-      <c r="B189" s="31" t="n"/>
-      <c r="C189" s="31" t="n"/>
-      <c r="D189" s="31" t="n"/>
-      <c r="E189" s="31" t="n"/>
-    </row>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="3" t="inlineStr">
+    <row r="193" ht="3" customHeight="1">
+      <c r="A193" s="31" t="n"/>
+      <c r="B193" s="31" t="n"/>
+      <c r="C193" s="31" t="n"/>
+      <c r="D193" s="31" t="n"/>
+      <c r="E193" s="31" t="n"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="3" t="inlineStr">
         <is>
           <t>DAY 11  |  Jun 30  |  The Razor-Edge Peaks — Seceda · Val di Funes · Adolf Munkel Trail  |  ~80 km / 50 mi  ~2h total · Collalbo loop day</t>
         </is>
       </c>
-      <c r="B190" s="4" t="inlineStr"/>
-      <c r="C190" s="4" t="inlineStr"/>
-      <c r="D190" s="4" t="inlineStr"/>
-      <c r="E190" s="4" t="inlineStr"/>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="5" t="inlineStr">
+      <c r="B194" s="4" t="inlineStr"/>
+      <c r="C194" s="4" t="inlineStr"/>
+      <c r="D194" s="4" t="inlineStr"/>
+      <c r="E194" s="4" t="inlineStr"/>
+    </row>
+    <row r="195" ht="15" customHeight="1">
+      <c r="A195" s="5" t="inlineStr">
         <is>
           <t>&gt; 8am Collalbo  8:45am Seceda cable car  Trail 1 ridge + Rifugio Firenze lunch  1pm drive Val di Funes  Santa Maddalena barrier + Panorama Trail  St. Johann Ranui  Zans traffic light  1:30pm Adolf Munkel Trail 35  Rifugio Odle lounge chairs  5:30pm descent  7pm Collalbo</t>
         </is>
       </c>
-      <c r="B191" s="6" t="inlineStr"/>
-      <c r="C191" s="6" t="inlineStr"/>
-      <c r="D191" s="6" t="inlineStr"/>
-      <c r="E191" s="6" t="inlineStr"/>
-    </row>
-    <row r="192" ht="24" customHeight="1">
-      <c r="A192" s="7" t="inlineStr">
+      <c r="B195" s="6" t="inlineStr"/>
+      <c r="C195" s="6" t="inlineStr"/>
+      <c r="D195" s="6" t="inlineStr"/>
+      <c r="E195" s="6" t="inlineStr"/>
+    </row>
+    <row r="196" ht="24" customHeight="1">
+      <c r="A196" s="7" t="inlineStr">
         <is>
           <t>KEY: Seceda 8:45am — pre-booked · photos best 9–10:30am before clouds form · razor ridge Trail 1  |   Santa Maddalena 2026 barrier — park at Filler/Putzen lot · walk 25min Panorama Trail · cannot drive up  |   Zans traffic light Red  don't wait · park Ranui immediately + Bus 330 · saves hiking time</t>
         </is>
       </c>
-      <c r="B192" s="7" t="inlineStr"/>
-      <c r="C192" s="7" t="inlineStr"/>
-      <c r="D192" s="7" t="inlineStr"/>
-      <c r="E192" s="7" t="inlineStr"/>
-    </row>
-    <row r="193" ht="48" customHeight="1">
-      <c r="A193" s="16" t="inlineStr">
+      <c r="B196" s="7" t="inlineStr"/>
+      <c r="C196" s="7" t="inlineStr"/>
+      <c r="D196" s="7" t="inlineStr"/>
+      <c r="E196" s="7" t="inlineStr"/>
+    </row>
+    <row r="197" ht="48" customHeight="1">
+      <c r="A197" s="16" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B193" s="16" t="inlineStr">
+      <c r="B197" s="16" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C193" s="17" t="inlineStr">
+      <c r="C197" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D193" s="18" t="inlineStr"/>
-      <c r="E193" s="19" t="inlineStr">
+      <c r="D197" s="18" t="inlineStr"/>
+      <c r="E197" s="19" t="inlineStr">
         <is>
           <t>Parking at Seceda valley station — no booking needed · 2.80/hr · 250+ spaces · arrive before 9am (your 8:45am slot guarantees this) · if full: Garage Central Ortisei 19.80/day · 10 min walk via La Curta escalator tunnel</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="42" customHeight="1">
-      <c r="A194" s="8" t="inlineStr">
+    <row r="198" ht="42" customHeight="1">
+      <c r="A198" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C194" s="9" t="inlineStr">
+      <c r="C198" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D194" s="10" t="inlineStr"/>
-      <c r="E194" s="11" t="inlineStr">
+      <c r="D198" s="10" t="inlineStr"/>
+      <c r="E198" s="11" t="inlineStr">
         <is>
           <t>8:45am — Seceda 360 cable car —  Booked · Receipt 1161/678/554260 · 255 total · 2 adults 84.50 + 2 juniors 43 · print tickets before departure · best photos 9–10:30am before clouds</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="32" customHeight="1">
-      <c r="A195" s="20" t="inlineStr">
+    <row r="199" ht="32" customHeight="1">
+      <c r="A199" s="20" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B195" s="20" t="inlineStr">
+      <c r="B199" s="20" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C195" s="21" t="inlineStr">
+      <c r="C199" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D195" s="22" t="inlineStr"/>
-      <c r="E195" s="23" t="inlineStr">
+      <c r="D199" s="22" t="inlineStr"/>
+      <c r="E199" s="23" t="inlineStr">
         <is>
           <t>Trail 1 — Razor Edge ridge walk — from the cable car top follow Trail 1 to the summit cross · allow 1.5hrs for the ridge walk</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="20" customHeight="1">
-      <c r="A196" s="12" t="inlineStr">
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B196" s="12" t="inlineStr">
+      <c r="B200" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C196" s="13" t="inlineStr">
+      <c r="C200" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D196" s="14" t="inlineStr"/>
-      <c r="E196" s="15" t="inlineStr">
+      <c r="D200" s="14" t="inlineStr"/>
+      <c r="E200" s="15" t="inlineStr">
         <is>
           <t>Lunch at Rifugio Firenze (2,039m) — allow 45 min</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="33" customHeight="1">
-      <c r="A197" s="8" t="inlineStr">
+    <row r="201" ht="33" customHeight="1">
+      <c r="A201" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C197" s="9" t="inlineStr">
+      <c r="C201" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D197" s="10" t="inlineStr"/>
-      <c r="E197" s="11" t="inlineStr">
+      <c r="D201" s="10" t="inlineStr"/>
+      <c r="E201" s="11" t="inlineStr">
         <is>
           <t>1:00pm — Val di Funes (Santa Maddalena) —  2026 barrier — park Filler/Putzen lots · walk 25 min Panorama Trail · cannot drive up</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="24" customHeight="1">
-      <c r="A198" s="16" t="inlineStr">
+    <row r="202" ht="24" customHeight="1">
+      <c r="A202" s="16" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B198" s="16" t="inlineStr">
+      <c r="B202" s="16" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C198" s="17" t="inlineStr">
+      <c r="C202" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D198" s="18" t="inlineStr"/>
-      <c r="E198" s="19" t="inlineStr">
+      <c r="D202" s="18" t="inlineStr"/>
+      <c r="E202" s="19" t="inlineStr">
         <is>
           <t>St. Johann in Ranui — 4 turnstile for meadow access · card only · 15 min</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="27" customHeight="1">
-      <c r="A199" s="16" t="inlineStr">
+    <row r="203" ht="27" customHeight="1">
+      <c r="A203" s="16" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B199" s="16" t="inlineStr">
+      <c r="B203" s="16" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C199" s="17" t="inlineStr">
+      <c r="C203" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D199" s="18" t="inlineStr"/>
-      <c r="E199" s="19" t="inlineStr">
+      <c r="D203" s="18" t="inlineStr"/>
+      <c r="E203" s="19" t="inlineStr">
         <is>
           <t>Santa Maddalena viewpoint — most photographed scene in South Tyrol · best light: late afternoon</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="25" customHeight="1">
-      <c r="A200" s="8" t="inlineStr">
+    <row r="204" ht="25" customHeight="1">
+      <c r="A204" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C200" s="9" t="inlineStr">
+      <c r="C204" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D200" s="10" t="inlineStr"/>
-      <c r="E200" s="11" t="inlineStr">
+      <c r="D204" s="10" t="inlineStr"/>
+      <c r="E204" s="11" t="inlineStr">
         <is>
           <t>Zans traffic light —  Green = drive up ·  Red = park Ranui + Bus 330 · don't wait</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="29" customHeight="1">
-      <c r="A201" s="20" t="inlineStr">
+    <row r="205" ht="29" customHeight="1">
+      <c r="A205" s="20" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B201" s="20" t="inlineStr">
+      <c r="B205" s="20" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C201" s="21" t="inlineStr">
+      <c r="C205" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D201" s="22" t="inlineStr"/>
-      <c r="E201" s="23" t="inlineStr">
+      <c r="D205" s="22" t="inlineStr"/>
+      <c r="E205" s="23" t="inlineStr">
         <is>
           <t>1:30pm — Adolf Munkel Trail 35 — from Parkplatz Zanser Alm (Zannes) trailhead · Trail 35 (Via delle Odle)</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="33" customHeight="1">
-      <c r="A202" s="12" t="inlineStr">
+    <row r="206" ht="33" customHeight="1">
+      <c r="A206" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B202" s="12" t="inlineStr">
+      <c r="B206" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C202" s="13" t="inlineStr">
+      <c r="C206" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D202" s="14" t="inlineStr"/>
-      <c r="E202" s="15" t="inlineStr">
+      <c r="D206" s="14" t="inlineStr"/>
+      <c r="E206" s="15" t="inlineStr">
         <is>
           <t>Rifugio Odle / Geisler Alm (1,986m) — the Cinema of the Odle — the best seats in the Dolomites · cash is faster but cards accepted</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="32" customHeight="1">
-      <c r="A203" s="8" t="inlineStr">
+    <row r="207" ht="32" customHeight="1">
+      <c r="A207" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B203" s="8" t="inlineStr">
+      <c r="B207" s="8" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C203" s="9" t="inlineStr">
+      <c r="C207" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D203" s="10" t="inlineStr"/>
-      <c r="E203" s="11" t="inlineStr">
+      <c r="D207" s="10" t="inlineStr"/>
+      <c r="E207" s="11" t="inlineStr">
         <is>
           <t>5:30pm — Descent to Zannes car park — ~1hr back down · same trail · arrive Zannes ~6:30pm · drive 50 min back to Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="25" customHeight="1">
-      <c r="A204" s="24" t="inlineStr">
+    <row r="208" ht="25" customHeight="1">
+      <c r="A208" s="24" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B204" s="24" t="inlineStr">
+      <c r="B208" s="24" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C204" s="25" t="inlineStr">
+      <c r="C208" s="25" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D204" s="26" t="inlineStr"/>
-      <c r="E204" s="27" t="inlineStr">
+      <c r="D208" s="26" t="inlineStr"/>
+      <c r="E208" s="27" t="inlineStr">
         <is>
           <t>Renon Earth Pyramids — evening walk —  Optional if energy allows · 5 min from hotel</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="18" customHeight="1">
-      <c r="A205" s="24" t="inlineStr">
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="24" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="B205" s="24" t="inlineStr">
+      <c r="B209" s="24" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C205" s="25" t="inlineStr">
+      <c r="C209" s="25" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D205" s="26" t="inlineStr"/>
-      <c r="E205" s="27" t="inlineStr">
+      <c r="D209" s="26" t="inlineStr"/>
+      <c r="E209" s="27" t="inlineStr">
         <is>
           <t>Night 2 — Kaiserau 1907, Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="36" customHeight="1">
-      <c r="A206" s="28" t="inlineStr"/>
-      <c r="B206" s="28" t="inlineStr"/>
-      <c r="C206" s="29" t="inlineStr">
+    <row r="210" ht="36" customHeight="1">
+      <c r="A210" s="28" t="inlineStr"/>
+      <c r="B210" s="28" t="inlineStr"/>
+      <c r="C210" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D206" s="28" t="inlineStr"/>
-      <c r="E206" s="30" t="inlineStr">
+      <c r="D210" s="28" t="inlineStr"/>
+      <c r="E210" s="30" t="inlineStr">
         <is>
           <t>Santa Maddalena 2026 barrier — physical barrier blocks non-resident cars since May 2026 · park Filler or Putzen lots in village · follow Panorama Trail signs · 25 min uphill walk to the viewpoint · you can no longer drive to the famous photo spot</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="28" customHeight="1">
-      <c r="A207" s="28" t="inlineStr"/>
-      <c r="B207" s="28" t="inlineStr"/>
-      <c r="C207" s="29" t="inlineStr">
+    <row r="211" ht="28" customHeight="1">
+      <c r="A211" s="28" t="inlineStr"/>
+      <c r="B211" s="28" t="inlineStr"/>
+      <c r="C211" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D207" s="28" t="inlineStr"/>
-      <c r="E207" s="30" t="inlineStr">
+      <c r="D211" s="28" t="inlineStr"/>
+      <c r="E211" s="30" t="inlineStr">
         <is>
           <t>Zans traffic light 2026 — Green = drive up · Red = park at Ranui immediately + Bus 330 every 30–60 min · do not wait at the gate — bus is faster</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="35" customHeight="1">
-      <c r="A208" s="28" t="inlineStr"/>
-      <c r="B208" s="28" t="inlineStr"/>
-      <c r="C208" s="29" t="inlineStr">
+    <row r="212" ht="35" customHeight="1">
+      <c r="A212" s="28" t="inlineStr"/>
+      <c r="B212" s="28" t="inlineStr"/>
+      <c r="C212" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D208" s="28" t="inlineStr"/>
-      <c r="E208" s="30" t="inlineStr">
+      <c r="D212" s="28" t="inlineStr"/>
+      <c r="E212" s="30" t="inlineStr">
         <is>
           <t>Photography windows — Seceda ridge: 9:00–10:30am before clouds form · Santa Maddalena viewpoint: late afternoon — sun behind you · Odle peaks lit directly · morning light hits the wrong side of the peaks</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="3" customHeight="1">
-      <c r="A209" s="31" t="n"/>
-      <c r="B209" s="31" t="n"/>
-      <c r="C209" s="31" t="n"/>
-      <c r="D209" s="31" t="n"/>
-      <c r="E209" s="31" t="n"/>
-    </row>
-    <row r="210" ht="22" customHeight="1">
-      <c r="A210" s="3" t="inlineStr">
+    <row r="213" ht="3" customHeight="1">
+      <c r="A213" s="31" t="n"/>
+      <c r="B213" s="31" t="n"/>
+      <c r="C213" s="31" t="n"/>
+      <c r="D213" s="31" t="n"/>
+      <c r="E213" s="31" t="n"/>
+    </row>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="3" t="inlineStr">
         <is>
           <t>DAY 12  |  Jul 1  |  Alpe di Siusi + Brenner Pass  Finkenberg — The Plateau &amp; The Pass  |  ~120 km / 75 mi  ~1h 45m · Collalbo  Finkenberg via Brenner</t>
         </is>
       </c>
-      <c r="B210" s="4" t="inlineStr"/>
-      <c r="C210" s="4" t="inlineStr"/>
-      <c r="D210" s="4" t="inlineStr"/>
-      <c r="E210" s="4" t="inlineStr"/>
-    </row>
-    <row r="211" ht="15" customHeight="1">
-      <c r="A211" s="5" t="inlineStr">
+      <c r="B214" s="4" t="inlineStr"/>
+      <c r="C214" s="4" t="inlineStr"/>
+      <c r="D214" s="4" t="inlineStr"/>
+      <c r="E214" s="4" t="inlineStr"/>
+    </row>
+    <row r="215" ht="15" customHeight="1">
+      <c r="A215" s="5" t="inlineStr">
         <is>
           <t>&gt; 7:45am Collalbo  8:30am St. Valentin gate (must be before 9am)  8:45am P2 Compatsch  9:15am Bullaccia loop  Hexenbänke viewpoint  12pm Tschötsch Alm lunch  1:30pm depart  Brenner construction  M-Preis Mayrhofen  4:30pm Keyone Rooms Finkenberg</t>
         </is>
       </c>
-      <c r="B211" s="6" t="inlineStr"/>
-      <c r="C211" s="6" t="inlineStr"/>
-      <c r="D211" s="6" t="inlineStr"/>
-      <c r="E211" s="6" t="inlineStr"/>
-    </row>
-    <row r="212" ht="24" customHeight="1">
-      <c r="A212" s="7" t="inlineStr">
+      <c r="B215" s="6" t="inlineStr"/>
+      <c r="C215" s="6" t="inlineStr"/>
+      <c r="D215" s="6" t="inlineStr"/>
+      <c r="E215" s="6" t="inlineStr"/>
+    </row>
+    <row r="216" ht="24" customHeight="1">
+      <c r="A216" s="7" t="inlineStr">
         <is>
           <t>KEY: Plan A: P2 Compatsch — keep checking seiseralm.it for cancellations · must arrive before 9am · 30  |   Plan B: Seis cable car  Compatsch — park in Seis · ~30/adult RT · no booking · no 9am rule · same trailhead  |   St. Valentin gate closes 9:00am SHARP — leave Collalbo 7:45am · arrive 8:30am · no exceptions  |   Skip Rifugio Zallinger — 4hr RT or 2 extra lifts · impractical · eat at Tschötsch Alm instead  |   Brenner Lueg Bridge construction 2026 — 30–45 min delay · Digital Flex toll essential</t>
         </is>
       </c>
-      <c r="B212" s="7" t="inlineStr"/>
-      <c r="C212" s="7" t="inlineStr"/>
-      <c r="D212" s="7" t="inlineStr"/>
-      <c r="E212" s="7" t="inlineStr"/>
-    </row>
-    <row r="213" ht="35" customHeight="1">
-      <c r="A213" s="8" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr"/>
+      <c r="C216" s="7" t="inlineStr"/>
+      <c r="D216" s="7" t="inlineStr"/>
+      <c r="E216" s="7" t="inlineStr"/>
+    </row>
+    <row r="217" ht="35" customHeight="1">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B213" s="8" t="inlineStr">
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C213" s="9" t="inlineStr">
+      <c r="C217" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D213" s="10" t="inlineStr"/>
-      <c r="E213" s="11" t="inlineStr">
+      <c r="D217" s="10" t="inlineStr"/>
+      <c r="E217" s="11" t="inlineStr">
         <is>
           <t>7:45am — Depart Collalbo — 40 min drive to the Alpe di Siusi St. Valentin gate · checkout Kaiserau 1907 before leaving · luggage in the car</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="27" customHeight="1">
-      <c r="A214" s="33" t="inlineStr">
+    <row r="218" ht="27" customHeight="1">
+      <c r="A218" s="33" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B214" s="33" t="inlineStr">
+      <c r="B218" s="33" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C214" s="34" t="inlineStr">
+      <c r="C218" s="34" t="inlineStr">
         <is>
           <t>ALERT</t>
         </is>
       </c>
-      <c r="D214" s="35" t="inlineStr"/>
-      <c r="E214" s="36" t="inlineStr">
+      <c r="D218" s="35" t="inlineStr"/>
+      <c r="E218" s="36" t="inlineStr">
         <is>
           <t>CRITICAL: St. Valentin Gate — before 9:00am — 9:01am = turned back · 120+ cable car alternative</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="54" customHeight="1">
-      <c r="A215" s="20" t="inlineStr">
+    <row r="219" ht="54" customHeight="1">
+      <c r="A219" s="20" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B215" s="20" t="inlineStr">
+      <c r="B219" s="20" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C215" s="21" t="inlineStr">
+      <c r="C219" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D215" s="22" t="inlineStr"/>
-      <c r="E215" s="23" t="inlineStr">
+      <c r="D219" s="22" t="inlineStr"/>
+      <c r="E219" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">P2 Compatsch parking —  Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · 30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch cable car — park in Seis village · gondola up to Compatsch (same </t>
         </is>
       </c>
     </row>
-    <row r="216" ht="30" customHeight="1">
-      <c r="A216" s="20" t="inlineStr">
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="20" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B216" s="20" t="inlineStr">
+      <c r="B220" s="20" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C216" s="21" t="inlineStr">
+      <c r="C220" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D216" s="22" t="inlineStr"/>
-      <c r="E216" s="23" t="inlineStr">
+      <c r="D220" s="22" t="inlineStr"/>
+      <c r="E220" s="23" t="inlineStr">
         <is>
           <t>9:15am — Bullaccia (Puflatsch) Loop — take the Telemix lift up from Compatsch · Trail PU (Puflatschumrundung)</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="20" customHeight="1">
-      <c r="A217" s="20" t="inlineStr">
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="20" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B217" s="20" t="inlineStr">
+      <c r="B221" s="20" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C217" s="21" t="inlineStr">
+      <c r="C221" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D217" s="22" t="inlineStr"/>
-      <c r="E217" s="23" t="inlineStr">
+      <c r="D221" s="22" t="inlineStr"/>
+      <c r="E221" s="23" t="inlineStr">
         <is>
           <t>Hexenbänke — Witches' Benches — signed from the trail</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="27" customHeight="1">
-      <c r="A218" s="12" t="inlineStr">
+    <row r="222" ht="27" customHeight="1">
+      <c r="A222" s="12" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B218" s="12" t="inlineStr">
+      <c r="B222" s="12" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C218" s="13" t="inlineStr">
+      <c r="C222" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D218" s="14" t="inlineStr"/>
-      <c r="E218" s="15" t="inlineStr">
+      <c r="D222" s="14" t="inlineStr"/>
+      <c r="E222" s="15" t="inlineStr">
         <is>
           <t>12:00pm — Lunch: Tschötsch Alm or Arnika Hütte —  Do NOT go to Rifugio Zallinger — allow 1hr</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="24" customHeight="1">
-      <c r="A219" s="8" t="inlineStr">
+    <row r="223" ht="24" customHeight="1">
+      <c r="A223" s="8" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B219" s="8" t="inlineStr">
+      <c r="B223" s="8" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C219" s="9" t="inlineStr">
+      <c r="C223" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D219" s="10" t="inlineStr"/>
-      <c r="E219" s="11" t="inlineStr">
+      <c r="D223" s="10" t="inlineStr"/>
+      <c r="E223" s="11" t="inlineStr">
         <is>
           <t>1:30pm — Depart Alpe di Siusi — unrestricted descent · head north to Brenner</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="28" customHeight="1">
-      <c r="A220" s="16" t="inlineStr">
+    <row r="224" ht="28" customHeight="1">
+      <c r="A224" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B220" s="16" t="inlineStr">
+      <c r="B224" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C220" s="17" t="inlineStr">
+      <c r="C224" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D220" s="18" t="inlineStr"/>
-      <c r="E220" s="19" t="inlineStr">
+      <c r="D224" s="18" t="inlineStr"/>
+      <c r="E224" s="19" t="inlineStr">
         <is>
           <t>Brenner Pass — Lueg Bridge construction — 30–45 min delay · Digital Flex toll green lanes · 11.50</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="18" customHeight="1">
-      <c r="A221" s="16" t="inlineStr">
+    <row r="225" ht="18" customHeight="1">
+      <c r="A225" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B221" s="16" t="inlineStr">
+      <c r="B225" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C221" s="17" t="inlineStr">
+      <c r="C225" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D221" s="18" t="inlineStr"/>
-      <c r="E221" s="19" t="inlineStr">
+      <c r="D225" s="18" t="inlineStr"/>
+      <c r="E225" s="19" t="inlineStr">
         <is>
           <t>Austrian vignette still valid?</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="31" customHeight="1">
-      <c r="A222" s="16" t="inlineStr">
+    <row r="226" ht="31" customHeight="1">
+      <c r="A226" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B222" s="16" t="inlineStr">
+      <c r="B226" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C222" s="17" t="inlineStr">
+      <c r="C226" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D222" s="18" t="inlineStr"/>
-      <c r="E222" s="19" t="inlineStr">
+      <c r="D226" s="18" t="inlineStr"/>
+      <c r="E226" s="19" t="inlineStr">
         <is>
           <t>M-Preis Supermarket, Mayrhofen — Finkenberg is up a winding road — nothing open nearby in the evening · allow 20 min</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="29" customHeight="1">
-      <c r="A223" s="16" t="inlineStr">
+    <row r="227" ht="29" customHeight="1">
+      <c r="A227" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B223" s="16" t="inlineStr">
+      <c r="B227" s="16" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C223" s="17" t="inlineStr">
+      <c r="C227" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D223" s="18" t="inlineStr"/>
-      <c r="E223" s="19" t="inlineStr">
+      <c r="D227" s="18" t="inlineStr"/>
+      <c r="E227" s="19" t="inlineStr">
         <is>
           <t>4:30pm — Keyone Rooms, Finkenberg — $176 / 152.92 ·  Driveway can be steep — take it slowly on the approach</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="26" customHeight="1">
-      <c r="A224" s="8" t="inlineStr">
+    <row r="228" ht="26" customHeight="1">
+      <c r="A228" s="8" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="B224" s="8" t="inlineStr">
+      <c r="B228" s="8" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C224" s="9" t="inlineStr">
+      <c r="C228" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D224" s="10" t="inlineStr"/>
-      <c r="E224" s="11" t="inlineStr">
+      <c r="D228" s="10" t="inlineStr"/>
+      <c r="E228" s="11" t="inlineStr">
         <is>
           <t>Dinner in Finkenberg or Mayrhofen — or drive 5 min down to Mayrhofen for more options</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="33" customHeight="1">
-      <c r="A225" s="28" t="inlineStr"/>
-      <c r="B225" s="28" t="inlineStr"/>
-      <c r="C225" s="29" t="inlineStr">
+    <row r="229" ht="33" customHeight="1">
+      <c r="A229" s="28" t="inlineStr"/>
+      <c r="B229" s="28" t="inlineStr"/>
+      <c r="C229" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D225" s="28" t="inlineStr"/>
-      <c r="E225" s="30" t="inlineStr">
+      <c r="D229" s="28" t="inlineStr"/>
+      <c r="E229" s="30" t="inlineStr">
         <is>
           <t>9:00am St. Valentin gate — non-negotiable — electronic barrier closes to private cars at exactly 9am · 9:01am = turned back · 120+ family cable car alternative · leave Collalbo by 7:45am</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="32" customHeight="1">
-      <c r="A226" s="28" t="inlineStr"/>
-      <c r="B226" s="28" t="inlineStr"/>
-      <c r="C226" s="29" t="inlineStr">
+    <row r="230" ht="32" customHeight="1">
+      <c r="A230" s="28" t="inlineStr"/>
+      <c r="B230" s="28" t="inlineStr"/>
+      <c r="C230" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D226" s="28" t="inlineStr"/>
-      <c r="E226" s="30" t="inlineStr">
+      <c r="D230" s="28" t="inlineStr"/>
+      <c r="E230" s="30" t="inlineStr">
         <is>
           <t>Brenner Lueg Bridge 2026 — single-lane renovation · 30–45 min delay expected · Digital Flex toll at autobrennero.it · 11.50 · green Video Toll lanes · saves 1hr vs manual queue</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="32" customHeight="1">
-      <c r="A227" s="28" t="inlineStr"/>
-      <c r="B227" s="28" t="inlineStr"/>
-      <c r="C227" s="29" t="inlineStr">
+    <row r="231" ht="32" customHeight="1">
+      <c r="A231" s="28" t="inlineStr"/>
+      <c r="B231" s="28" t="inlineStr"/>
+      <c r="C231" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D227" s="28" t="inlineStr"/>
-      <c r="E227" s="30" t="inlineStr">
+      <c r="D231" s="28" t="inlineStr"/>
+      <c r="E231" s="30" t="inlineStr">
         <is>
           <t>Hexenbänke — Witches' Benches — giant stone formations on the Bullaccia ridge · highest point of the plateau · best 360 photo spot · signed from the trail · kids love the legend</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="29" customHeight="1">
-      <c r="A228" s="28" t="inlineStr"/>
-      <c r="B228" s="28" t="inlineStr"/>
-      <c r="C228" s="29" t="inlineStr">
+    <row r="232" ht="29" customHeight="1">
+      <c r="A232" s="28" t="inlineStr"/>
+      <c r="B232" s="28" t="inlineStr"/>
+      <c r="C232" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D228" s="28" t="inlineStr"/>
-      <c r="E228" s="30" t="inlineStr">
+      <c r="D232" s="28" t="inlineStr"/>
+      <c r="E232" s="30" t="inlineStr">
         <is>
           <t>M-Preis Mayrhofen — stop before Finkenberg · buy breakfast for Day 13 · nothing open near Keyone in evenings · steep winding road to Finkenberg — take slowly</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="3" customHeight="1">
-      <c r="A229" s="31" t="n"/>
-      <c r="B229" s="31" t="n"/>
-      <c r="C229" s="31" t="n"/>
-      <c r="D229" s="31" t="n"/>
-      <c r="E229" s="31" t="n"/>
-    </row>
-    <row r="230" ht="22" customHeight="1">
-      <c r="A230" s="3" t="inlineStr">
+    <row r="233" ht="3" customHeight="1">
+      <c r="A233" s="31" t="n"/>
+      <c r="B233" s="31" t="n"/>
+      <c r="C233" s="31" t="n"/>
+      <c r="D233" s="31" t="n"/>
+      <c r="E233" s="31" t="n"/>
+    </row>
+    <row r="234" ht="22" customHeight="1">
+      <c r="A234" s="3" t="inlineStr">
         <is>
           <t>DAY 13  |  Jul 2  |  High Bridges &amp; Deep Lakes — Olpererhütte · Achensee · Swarovski  Bichlbach  |  ~150 km / 93 mi  ~2h 30m incl. Achensee + Swarovski stops</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr"/>
-      <c r="C230" s="4" t="inlineStr"/>
-      <c r="D230" s="4" t="inlineStr"/>
-      <c r="E230" s="4" t="inlineStr"/>
-    </row>
-    <row r="231" ht="15" customHeight="1">
-      <c r="A231" s="5" t="inlineStr">
+      <c r="B234" s="4" t="inlineStr"/>
+      <c r="C234" s="4" t="inlineStr"/>
+      <c r="D234" s="4" t="inlineStr"/>
+      <c r="E234" s="4" t="inlineStr"/>
+    </row>
+    <row r="235" ht="15" customHeight="1">
+      <c r="A235" s="5" t="inlineStr">
         <is>
           <t>&gt; 8am Finkenberg  8:30am Schlegeis toll 17  9am Olpererhütte hike  10:30am Kebema bridge  11am lunch  1:30pm descent  Swarovski (if rain)  Achensee optional  Fern Pass  7:30pm Bichlbach  Heiterwanger See sunset</t>
         </is>
       </c>
-      <c r="B231" s="6" t="inlineStr"/>
-      <c r="C231" s="6" t="inlineStr"/>
-      <c r="D231" s="6" t="inlineStr"/>
-      <c r="E231" s="6" t="inlineStr"/>
-    </row>
-    <row r="232" ht="24" customHeight="1">
-      <c r="A232" s="7" t="inlineStr">
+      <c r="B235" s="6" t="inlineStr"/>
+      <c r="C235" s="6" t="inlineStr"/>
+      <c r="D235" s="6" t="inlineStr"/>
+      <c r="E235" s="6" t="inlineStr"/>
+    </row>
+    <row r="236" ht="24" customHeight="1">
+      <c r="A236" s="7" t="inlineStr">
         <is>
           <t>KEY: Arrive dam by 8:45am — reach Kebema bridge 10:30am · beats 45min photo queue by midday  |   Plan A (sunny): Achensee — steamboat ~22/adult OR free Gaisalm promenade walk if kids tired  |   Plan B (rain/cloudy): Swarovski Crystal Worlds — 5min off A12 · ~22/adult · no booking needed</t>
         </is>
       </c>
-      <c r="B232" s="7" t="inlineStr"/>
-      <c r="C232" s="7" t="inlineStr"/>
-      <c r="D232" s="7" t="inlineStr"/>
-      <c r="E232" s="7" t="inlineStr"/>
-    </row>
-    <row r="233" ht="27" customHeight="1">
-      <c r="A233" s="8" t="inlineStr">
+      <c r="B236" s="7" t="inlineStr"/>
+      <c r="C236" s="7" t="inlineStr"/>
+      <c r="D236" s="7" t="inlineStr"/>
+      <c r="E236" s="7" t="inlineStr"/>
+    </row>
+    <row r="237" ht="27" customHeight="1">
+      <c r="A237" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B233" s="8" t="inlineStr">
+      <c r="B237" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C233" s="9" t="inlineStr">
+      <c r="C237" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D233" s="10" t="inlineStr"/>
-      <c r="E233" s="11" t="inlineStr">
+      <c r="D237" s="10" t="inlineStr"/>
+      <c r="E237" s="11" t="inlineStr">
         <is>
           <t>8:00am — Depart Finkenberg — 20 min to Schlegeis ·  tunnel traffic lights = up to 15 min wait</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="24" customHeight="1">
-      <c r="A234" s="16" t="inlineStr">
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="16" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B234" s="16" t="inlineStr">
+      <c r="B238" s="16" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C234" s="17" t="inlineStr">
+      <c r="C238" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D234" s="18" t="inlineStr"/>
-      <c r="E234" s="19" t="inlineStr">
+      <c r="D238" s="18" t="inlineStr"/>
+      <c r="E238" s="19" t="inlineStr">
         <is>
           <t>8:30am — Schlegeis Alpine Road toll — 17 · pay at the gate (cash or card)</t>
         </is>
       </c>
     </row>
-    <row r="235" ht="26" customHeight="1">
-      <c r="A235" s="20" t="inlineStr">
+    <row r="239" ht="26" customHeight="1">
+      <c r="A239" s="20" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B235" s="20" t="inlineStr">
+      <c r="B239" s="20" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C235" s="21" t="inlineStr">
+      <c r="C239" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D235" s="22" t="inlineStr"/>
-      <c r="E235" s="23" t="inlineStr">
+      <c r="D239" s="22" t="inlineStr"/>
+      <c r="E239" s="23" t="inlineStr">
         <is>
           <t>9:00am — Olpererhütte Hike (Trail 502) — 3km / 1.9mi each way · well-maintained trail</t>
         </is>
       </c>
     </row>
-    <row r="236" ht="35" customHeight="1">
-      <c r="A236" s="16" t="inlineStr">
+    <row r="240" ht="35" customHeight="1">
+      <c r="A240" s="16" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B236" s="16" t="inlineStr">
+      <c r="B240" s="16" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C236" s="17" t="inlineStr">
+      <c r="C240" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D236" s="18" t="inlineStr"/>
-      <c r="E236" s="19" t="inlineStr">
+      <c r="D240" s="18" t="inlineStr"/>
+      <c r="E240" s="19" t="inlineStr">
         <is>
           <t>10:30am — Kebema Suspension Bridge (Olperer Panoramabrücke) — 3–4 min past the hut · floats in mid-air above the turquoise reservoir 600m below</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="31" customHeight="1">
-      <c r="A237" s="12" t="inlineStr">
+    <row r="241" ht="31" customHeight="1">
+      <c r="A241" s="12" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B237" s="12" t="inlineStr">
+      <c r="B241" s="12" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C237" s="13" t="inlineStr">
+      <c r="C241" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D237" s="14" t="inlineStr"/>
-      <c r="E237" s="15" t="inlineStr">
+      <c r="D241" s="14" t="inlineStr"/>
+      <c r="E241" s="15" t="inlineStr">
         <is>
           <t>11:00am — Lunch at Olpererhütte — cash preferred (but Wi-Fi available — check your Neuschwanstein booking!) · allow 1hr</t>
         </is>
       </c>
     </row>
-    <row r="238" ht="30" customHeight="1">
-      <c r="A238" s="20" t="inlineStr">
+    <row r="242" ht="30" customHeight="1">
+      <c r="A242" s="20" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B238" s="20" t="inlineStr">
+      <c r="B242" s="20" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C238" s="21" t="inlineStr">
+      <c r="C242" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D238" s="22" t="inlineStr"/>
-      <c r="E238" s="23" t="inlineStr">
+      <c r="D242" s="22" t="inlineStr"/>
+      <c r="E242" s="23" t="inlineStr">
         <is>
           <t>1:30pm — Descent to the dam — ~1hr back down same trail · easier on the knees than going up · back at car ~2:30pm</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="54" customHeight="1">
-      <c r="A239" s="8" t="inlineStr">
+    <row r="243" ht="54" customHeight="1">
+      <c r="A243" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B239" s="8" t="inlineStr">
+      <c r="B243" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C239" s="9" t="inlineStr">
+      <c r="C243" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D239" s="10" t="inlineStr"/>
-      <c r="E239" s="11" t="inlineStr">
+      <c r="D243" s="10" t="inlineStr"/>
+      <c r="E243" s="11" t="inlineStr">
         <is>
           <t>Plan A — Sunny: Achensee — 50 min drive north from Schlegeis · park at Pertisau · Option 1: Achensee steamboat ~22/adult · allow 1.5hrs · Option 2 (kids tired): Gaisalm promenade walk — free · same fjord-like views · no schedule pressure · just walk and enjoy</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="48" customHeight="1">
-      <c r="A240" s="20" t="inlineStr">
+    <row r="244" ht="48" customHeight="1">
+      <c r="A244" s="20" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B240" s="20" t="inlineStr">
+      <c r="B244" s="20" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C240" s="21" t="inlineStr">
+      <c r="C244" s="21" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D240" s="22" t="inlineStr"/>
-      <c r="E240" s="23" t="inlineStr">
+      <c r="D244" s="22" t="inlineStr"/>
+      <c r="E244" s="23" t="inlineStr">
         <is>
           <t>Plan B — Rain/Cloudy: Swarovski Crystal Worlds — 5 min off A12 at Wattens · ~22/adult · allow 1.5–2hrs · indoor immersive art installation · perfect rainy-day refuge after cold wet Olpererhütte hike · no booking needed</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="26" customHeight="1">
-      <c r="A241" s="8" t="inlineStr">
+    <row r="245" ht="26" customHeight="1">
+      <c r="A245" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B241" s="8" t="inlineStr">
+      <c r="B245" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C241" s="9" t="inlineStr">
+      <c r="C245" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D241" s="10" t="inlineStr"/>
-      <c r="E241" s="11" t="inlineStr">
+      <c r="D245" s="10" t="inlineStr"/>
+      <c r="E245" s="11" t="inlineStr">
         <is>
           <t>Fern Pass warning on drive to Bichlbach — village Gasthäuser are relaxed about timing</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="29" customHeight="1">
-      <c r="A242" s="24" t="inlineStr">
+    <row r="246" ht="29" customHeight="1">
+      <c r="A246" s="24" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B242" s="24" t="inlineStr">
+      <c r="B246" s="24" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C242" s="25" t="inlineStr">
+      <c r="C246" s="25" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D242" s="26" t="inlineStr"/>
-      <c r="E242" s="27" t="inlineStr">
+      <c r="D246" s="26" t="inlineStr"/>
+      <c r="E246" s="27" t="inlineStr">
         <is>
           <t>~7:30pm — Landhaus Bichlbach — $467 / 405 · Heiterwanger See lake is a 20 min evening walk from the hotel</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="25" customHeight="1">
-      <c r="A243" s="16" t="inlineStr">
+    <row r="247" ht="25" customHeight="1">
+      <c r="A247" s="16" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B243" s="16" t="inlineStr">
+      <c r="B247" s="16" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C243" s="17" t="inlineStr">
+      <c r="C247" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D243" s="18" t="inlineStr"/>
-      <c r="E243" s="19" t="inlineStr">
+      <c r="D247" s="18" t="inlineStr"/>
+      <c r="E247" s="19" t="inlineStr">
         <is>
           <t>Heiterwanger See sunset walk — easy 20 min walk from Landhaus along Panoramaweg</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="22" customHeight="1">
-      <c r="A244" s="8" t="inlineStr">
+    <row r="248" ht="22" customHeight="1">
+      <c r="A248" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="B244" s="8" t="inlineStr">
+      <c r="B248" s="8" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C244" s="9" t="inlineStr">
+      <c r="C248" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D244" s="10" t="inlineStr"/>
-      <c r="E244" s="11" t="inlineStr">
+      <c r="D248" s="10" t="inlineStr"/>
+      <c r="E248" s="11" t="inlineStr">
         <is>
           <t>Dinner + pack bags — Gasthof Bichlbach · checkout 8am · alarm 7am</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="29" customHeight="1">
-      <c r="A245" s="28" t="inlineStr"/>
-      <c r="B245" s="28" t="inlineStr"/>
-      <c r="C245" s="29" t="inlineStr">
+    <row r="249" ht="29" customHeight="1">
+      <c r="A249" s="28" t="inlineStr"/>
+      <c r="B249" s="28" t="inlineStr"/>
+      <c r="C249" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D245" s="28" t="inlineStr"/>
-      <c r="E245" s="30" t="inlineStr">
+      <c r="D249" s="28" t="inlineStr"/>
+      <c r="E249" s="30" t="inlineStr">
         <is>
           <t>Schlegeis tunnel traffic lights — one-way sections · red light = up to 15 min wait · factor into morning timing · aim to be at the dam car park by 8:45am</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="31" customHeight="1">
-      <c r="A246" s="28" t="inlineStr"/>
-      <c r="B246" s="28" t="inlineStr"/>
-      <c r="C246" s="29" t="inlineStr">
+    <row r="250" ht="31" customHeight="1">
+      <c r="A250" s="28" t="inlineStr"/>
+      <c r="B250" s="28" t="inlineStr"/>
+      <c r="C250" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D246" s="28" t="inlineStr"/>
-      <c r="E246" s="30" t="inlineStr">
+      <c r="D250" s="28" t="inlineStr"/>
+      <c r="E250" s="30" t="inlineStr">
         <is>
           <t>Fern Pass congestion 2026 — slow trucks · one of the most congested alpine roads · flexible dinner only — no reservations · Bichlbach Gasthäuser are relaxed about timing</t>
         </is>
       </c>
     </row>
-    <row r="247" ht="30" customHeight="1">
-      <c r="A247" s="28" t="inlineStr"/>
-      <c r="B247" s="28" t="inlineStr"/>
-      <c r="C247" s="29" t="inlineStr">
+    <row r="251" ht="30" customHeight="1">
+      <c r="A251" s="28" t="inlineStr"/>
+      <c r="B251" s="28" t="inlineStr"/>
+      <c r="C251" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D247" s="28" t="inlineStr"/>
-      <c r="E247" s="30" t="inlineStr">
+      <c r="D251" s="28" t="inlineStr"/>
+      <c r="E251" s="30" t="inlineStr">
         <is>
           <t>At Olpererhütte: check Neuschwanstein booking — the hut has excellent Wi-Fi · confirm your 9:30am slot for tomorrow · cash preferred for food but cards accepted</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="3" customHeight="1">
-      <c r="A248" s="31" t="n"/>
-      <c r="B248" s="31" t="n"/>
-      <c r="C248" s="31" t="n"/>
-      <c r="D248" s="31" t="n"/>
-      <c r="E248" s="31" t="n"/>
-    </row>
-    <row r="249" ht="22" customHeight="1">
-      <c r="A249" s="3" t="inlineStr">
+    <row r="252" ht="3" customHeight="1">
+      <c r="A252" s="31" t="n"/>
+      <c r="B252" s="31" t="n"/>
+      <c r="C252" s="31" t="n"/>
+      <c r="D252" s="31" t="n"/>
+      <c r="E252" s="31" t="n"/>
+    </row>
+    <row r="253" ht="22" customHeight="1">
+      <c r="A253" s="3" t="inlineStr">
         <is>
           <t>DAY 14  |  Jul 3  |  The Lakes of the Dragon — Seebensee · Drachensee · Coburger Hütte  |  ~20 km / 12 mi  ~30m · just Bichlbach  Ehrwald</t>
         </is>
       </c>
-      <c r="B249" s="4" t="inlineStr"/>
-      <c r="C249" s="4" t="inlineStr"/>
-      <c r="D249" s="4" t="inlineStr"/>
-      <c r="E249" s="4" t="inlineStr"/>
-    </row>
-    <row r="250" ht="15" customHeight="1">
-      <c r="A250" s="5" t="inlineStr">
+      <c r="B253" s="4" t="inlineStr"/>
+      <c r="C253" s="4" t="inlineStr"/>
+      <c r="D253" s="4" t="inlineStr"/>
+      <c r="E253" s="4" t="inlineStr"/>
+    </row>
+    <row r="254" ht="15" customHeight="1">
+      <c r="A254" s="5" t="inlineStr">
         <is>
           <t>&gt; Tonight: ATM Ehrwald 60–80  7:45am Bichlbach  8:00am Ehrwalder Almbahn (first car)  8:10am hike  9:45am Seebensee mirror  10:15am Drachensee climb  11:00am Coburger Hütte Kaiserschmarrn  12:45pm descent  2:45pm back at car  3pm Bichlbach  7:30pm Heiterwanger See sunset</t>
         </is>
       </c>
-      <c r="B250" s="6" t="inlineStr"/>
-      <c r="C250" s="6" t="inlineStr"/>
-      <c r="D250" s="6" t="inlineStr"/>
-      <c r="E250" s="6" t="inlineStr"/>
-    </row>
-    <row r="251" ht="24" customHeight="1">
-      <c r="A251" s="7" t="inlineStr">
+      <c r="B254" s="6" t="inlineStr"/>
+      <c r="C254" s="6" t="inlineStr"/>
+      <c r="D254" s="6" t="inlineStr"/>
+      <c r="E254" s="6" t="inlineStr"/>
+    </row>
+    <row r="255" ht="24" customHeight="1">
+      <c r="A255" s="7" t="inlineStr">
         <is>
           <t>KEY: ATM in Ehrwald tonight — 60–80 cash · Coburger Hütte cash only · no card reader  |   7:45am departure — first cable car 8:00am · arrive Seebensee 9:45am · beats 10:30am winds  |   Seebensee mirror reflection before 10:30am — winds create ripples by midday · 9:45am arrival   |   Drachensee path slippery if rained Jul 2 — best-grip boots · 217m steep climb · 30–45 min  |   E-bikes optional at valley station — cuts Seebensee hike from 1.5hrs to 25 min · saves legs for Drachensee</t>
         </is>
       </c>
-      <c r="B251" s="7" t="inlineStr"/>
-      <c r="C251" s="7" t="inlineStr"/>
-      <c r="D251" s="7" t="inlineStr"/>
-      <c r="E251" s="7" t="inlineStr"/>
-    </row>
-    <row r="252" ht="46" customHeight="1">
-      <c r="A252" s="16" t="inlineStr">
+      <c r="B255" s="7" t="inlineStr"/>
+      <c r="C255" s="7" t="inlineStr"/>
+      <c r="D255" s="7" t="inlineStr"/>
+      <c r="E255" s="7" t="inlineStr"/>
+    </row>
+    <row r="256" ht="46" customHeight="1">
+      <c r="A256" s="16" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="B252" s="16" t="inlineStr">
+      <c r="B256" s="16" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C252" s="17" t="inlineStr">
+      <c r="C256" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D252" s="18" t="inlineStr"/>
-      <c r="E252" s="19" t="inlineStr">
+      <c r="D256" s="18" t="inlineStr"/>
+      <c r="E256" s="19" t="inlineStr">
         <is>
           <t>Tonight (Jul 2 evening): ATM in Ehrwald — withdraw 60–80 cash for the family · Coburger Hütte is cash only — no card reader on the mountain · budget: Kaiserschmarrn ~12 · Tiroler Gröstl ~14 · drinks ~4–6 each</t>
         </is>
       </c>
     </row>
-    <row r="253" ht="33" customHeight="1">
-      <c r="A253" s="8" t="inlineStr">
+    <row r="257" ht="33" customHeight="1">
+      <c r="A257" s="8" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="B253" s="8" t="inlineStr">
+      <c r="B257" s="8" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C253" s="9" t="inlineStr">
+      <c r="C257" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D253" s="10" t="inlineStr"/>
-      <c r="E253" s="11" t="inlineStr">
+      <c r="D257" s="10" t="inlineStr"/>
+      <c r="E257" s="11" t="inlineStr">
         <is>
           <t>7:45am — Depart Bichlbach — 5 min drive to Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~7:55am</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="38" customHeight="1">
-      <c r="A254" s="16" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="B254" s="16" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C254" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D254" s="18" t="inlineStr"/>
-      <c r="E254" s="19" t="inlineStr">
-        <is>
-          <t>8:00am — Ehrwalder Almbahn — first cable car of the day · ~26/adult · free parking · 5 min at top for Zugspitze platform view ·  July high season: opens 8:00am</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="48" customHeight="1">
-      <c r="A255" s="20" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="B255" s="20" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C255" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D255" s="22" t="inlineStr"/>
-      <c r="E255" s="23" t="inlineStr">
-        <is>
-          <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am ·  E-bikes available at valley station — cuts hike to 25 min if family wants to save legs</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="46" customHeight="1">
-      <c r="A256" s="8" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="B256" s="8" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C256" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D256" s="10" t="inlineStr"/>
-      <c r="E256" s="11" t="inlineStr">
-        <is>
-          <t>9:45am — Seebensee mirror reflection — crystal-clear turquoise water · Zugspitze reflected · winds pick up after 10:30am — 9:45am arrival is perfectly timed · allow 30 min · benches along the southern shore</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="38" customHeight="1">
-      <c r="A257" s="20" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="B257" s="20" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C257" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D257" s="22" t="inlineStr"/>
-      <c r="E257" s="23" t="inlineStr">
-        <is>
-          <t>10:15am — Drachensee ascent — 1.4km · 217m elevation gain · 30–45 min ·  slippery if rained Jul 2 · best-grip boots · steeper than Seebensee section but short</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="40" customHeight="1">
+    <row r="258" ht="38" customHeight="1">
       <c r="A258" s="16" t="inlineStr">
         <is>
           <t>Jul 3</t>
@@ -5843,11 +5794,11 @@
       <c r="D258" s="18" t="inlineStr"/>
       <c r="E258" s="19" t="inlineStr">
         <is>
-          <t>11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring 60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="35" customHeight="1">
+          <t>8:00am — Ehrwalder Almbahn — first cable car of the day · ~26/adult · free parking · 5 min at top for Zugspitze platform view ·  July high season: opens 8:00am</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="48" customHeight="1">
       <c r="A259" s="20" t="inlineStr">
         <is>
           <t>Jul 3</t>
@@ -5866,11 +5817,11 @@
       <c r="D259" s="22" t="inlineStr"/>
       <c r="E259" s="23" t="inlineStr">
         <is>
-          <t>12:45pm — Descent to cable car station — ~1.5hrs back down · same trail · arrive top station ~2:15pm · cable car down · back at car ~2:45pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="34" customHeight="1">
+          <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am ·  E-bikes available at valley station — cuts hike to 25 min if family wants to save legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="46" customHeight="1">
       <c r="A260" s="8" t="inlineStr">
         <is>
           <t>Jul 3</t>
@@ -5889,272 +5840,272 @@
       <c r="D260" s="10" t="inlineStr"/>
       <c r="E260" s="11" t="inlineStr">
         <is>
+          <t>9:45am — Seebensee mirror reflection — crystal-clear turquoise water · Zugspitze reflected · winds pick up after 10:30am — 9:45am arrival is perfectly timed · allow 30 min · benches along the southern shore</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="38" customHeight="1">
+      <c r="A261" s="20" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="B261" s="20" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C261" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D261" s="22" t="inlineStr"/>
+      <c r="E261" s="23" t="inlineStr">
+        <is>
+          <t>10:15am — Drachensee ascent — 1.4km · 217m elevation gain · 30–45 min ·  slippery if rained Jul 2 · best-grip boots · steeper than Seebensee section but short</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" s="16" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="B262" s="16" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C262" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D262" s="18" t="inlineStr"/>
+      <c r="E262" s="19" t="inlineStr">
+        <is>
+          <t>11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring 60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="35" customHeight="1">
+      <c r="A263" s="20" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="B263" s="20" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C263" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D263" s="22" t="inlineStr"/>
+      <c r="E263" s="23" t="inlineStr">
+        <is>
+          <t>12:45pm — Descent to cable car station — ~1.5hrs back down · same trail · arrive top station ~2:15pm · cable car down · back at car ~2:45pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="34" customHeight="1">
+      <c r="A264" s="8" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="B264" s="8" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D264" s="10" t="inlineStr"/>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
           <t>3:00pm — Back at Landhaus Bichlbach — shower · rest legs · pack bags for tomorrow · checkout 8am — Neuschwanstein 9:30am · alarm 7:00am</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="40" customHeight="1">
-      <c r="A261" s="16" t="inlineStr">
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" s="16" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="B261" s="16" t="inlineStr">
+      <c r="B265" s="16" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C261" s="17" t="inlineStr">
+      <c r="C265" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D261" s="18" t="inlineStr"/>
-      <c r="E261" s="19" t="inlineStr">
+      <c r="D265" s="18" t="inlineStr"/>
+      <c r="E265" s="19" t="inlineStr">
         <is>
           <t>7:30pm — Heiterwanger See sunset walk — 20 min walk from Landhaus along the Panoramaweg · flat · easy · clears the lactic acid · alpenglow after sunset on the higher path</t>
         </is>
       </c>
     </row>
-    <row r="262" ht="34" customHeight="1">
-      <c r="A262" s="12" t="inlineStr">
+    <row r="266" ht="34" customHeight="1">
+      <c r="A266" s="12" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="B262" s="12" t="inlineStr">
+      <c r="B266" s="12" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C262" s="13" t="inlineStr">
+      <c r="C266" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D262" s="14" t="inlineStr"/>
-      <c r="E262" s="15" t="inlineStr">
+      <c r="D266" s="14" t="inlineStr"/>
+      <c r="E266" s="15" t="inlineStr">
         <is>
           <t>Dinner — Gasthof Bichlbach or hotel restaurant — early dinner + early bed · alarm 7:00am tomorrow · Neuschwanstein 9:30am — last big day</t>
         </is>
       </c>
     </row>
-    <row r="263" ht="29" customHeight="1">
-      <c r="A263" s="28" t="inlineStr"/>
-      <c r="B263" s="28" t="inlineStr"/>
-      <c r="C263" s="29" t="inlineStr">
+    <row r="267" ht="29" customHeight="1">
+      <c r="A267" s="28" t="inlineStr"/>
+      <c r="B267" s="28" t="inlineStr"/>
+      <c r="C267" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D263" s="28" t="inlineStr"/>
-      <c r="E263" s="30" t="inlineStr">
+      <c r="D267" s="28" t="inlineStr"/>
+      <c r="E267" s="30" t="inlineStr">
         <is>
           <t>Coburger Hütte cash only — withdraw 60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~12 · Tiroler Gröstl ~14 · drinks ~4–6 each</t>
         </is>
       </c>
     </row>
-    <row r="264" ht="31" customHeight="1">
-      <c r="A264" s="28" t="inlineStr"/>
-      <c r="B264" s="28" t="inlineStr"/>
-      <c r="C264" s="29" t="inlineStr">
+    <row r="268" ht="31" customHeight="1">
+      <c r="A268" s="28" t="inlineStr"/>
+      <c r="B268" s="28" t="inlineStr"/>
+      <c r="C268" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D264" s="28" t="inlineStr"/>
-      <c r="E264" s="30" t="inlineStr">
+      <c r="D268" s="28" t="inlineStr"/>
+      <c r="E268" s="30" t="inlineStr">
         <is>
           <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="34" customHeight="1">
-      <c r="A265" s="28" t="inlineStr"/>
-      <c r="B265" s="28" t="inlineStr"/>
-      <c r="C265" s="29" t="inlineStr">
+    <row r="269" ht="34" customHeight="1">
+      <c r="A269" s="28" t="inlineStr"/>
+      <c r="B269" s="28" t="inlineStr"/>
+      <c r="C269" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D265" s="28" t="inlineStr"/>
-      <c r="E265" s="30" t="inlineStr">
+      <c r="D269" s="28" t="inlineStr"/>
+      <c r="E269" s="30" t="inlineStr">
         <is>
           <t>Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="33" customHeight="1">
-      <c r="A266" s="28" t="inlineStr"/>
-      <c r="B266" s="28" t="inlineStr"/>
-      <c r="C266" s="29" t="inlineStr">
+    <row r="270" ht="33" customHeight="1">
+      <c r="A270" s="28" t="inlineStr"/>
+      <c r="B270" s="28" t="inlineStr"/>
+      <c r="C270" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D266" s="28" t="inlineStr"/>
-      <c r="E266" s="30" t="inlineStr">
+      <c r="D270" s="28" t="inlineStr"/>
+      <c r="E270" s="30" t="inlineStr">
         <is>
           <t>Panoramaweg for Heiterwanger See — take the higher Panoramaweg trail not the lakeside path · stays above the valley floor to catch alpenglow after sunset · 20 min from hotel · flat + easy</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="3" customHeight="1">
-      <c r="A267" s="31" t="n"/>
-      <c r="B267" s="31" t="n"/>
-      <c r="C267" s="31" t="n"/>
-      <c r="D267" s="31" t="n"/>
-      <c r="E267" s="31" t="n"/>
-    </row>
-    <row r="268" ht="22" customHeight="1">
-      <c r="A268" s="3" t="inlineStr">
+    <row r="271" ht="3" customHeight="1">
+      <c r="A271" s="31" t="n"/>
+      <c r="B271" s="31" t="n"/>
+      <c r="C271" s="31" t="n"/>
+      <c r="D271" s="31" t="n"/>
+      <c r="E271" s="31" t="n"/>
+    </row>
+    <row r="272" ht="22" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>DAY 15  |  Jul 4  |  The Fairy Tale Finale — Neuschwanstein · Ebenalp · Aescher  ZRH  |  ~280 km / 174 mi  ~3h 30m · Neuschwanstein  Ebenalp  ZRH</t>
         </is>
       </c>
-      <c r="B268" s="4" t="inlineStr"/>
-      <c r="C268" s="4" t="inlineStr"/>
-      <c r="D268" s="4" t="inlineStr"/>
-      <c r="E268" s="4" t="inlineStr"/>
-    </row>
-    <row r="269" ht="15" customHeight="1">
-      <c r="A269" s="5" t="inlineStr">
+      <c r="B272" s="4" t="inlineStr"/>
+      <c r="C272" s="4" t="inlineStr"/>
+      <c r="D272" s="4" t="inlineStr"/>
+      <c r="E272" s="4" t="inlineStr"/>
+    </row>
+    <row r="273" ht="15" customHeight="1">
+      <c r="A273" s="5" t="inlineStr">
         <is>
           <t>&gt; 7:30am Bichlbach checkout  8:15am P4 Neuschwanstein  8:30am Marienbrücke FIRST  9:20am castle gate  9:30am tour  11:30am drive Bregenz tunnel  1:15pm Wasserauen  1:30pm Ebenalp cable car  2pm Aescher (before Swing event 5pm)  4pm descent  6pm ZRH hotel + return car tonight  5am alarm tomorrow</t>
         </is>
       </c>
-      <c r="B269" s="6" t="inlineStr"/>
-      <c r="C269" s="6" t="inlineStr"/>
-      <c r="D269" s="6" t="inlineStr"/>
-      <c r="E269" s="6" t="inlineStr"/>
-    </row>
-    <row r="270" ht="24" customHeight="1">
-      <c r="A270" s="7" t="inlineStr">
+      <c r="B273" s="6" t="inlineStr"/>
+      <c r="C273" s="6" t="inlineStr"/>
+      <c r="D273" s="6" t="inlineStr"/>
+      <c r="E273" s="6" t="inlineStr"/>
+    </row>
+    <row r="274" ht="24" customHeight="1">
+      <c r="A274" s="7" t="inlineStr">
         <is>
           <t>KEY: Marienbrücke BEFORE the tour — go at 8:30am · virtually no queue · by 10am it's packed  |   Castle gate by 9:20am — NOT the ticket centre · guide will not wait for latecomers  |   Return car TONIGHT — drop bags at hotel · 5 min to Europcar ZRH · open until midnight · eliminates 5:30am stress</t>
         </is>
       </c>
-      <c r="B270" s="7" t="inlineStr"/>
-      <c r="C270" s="7" t="inlineStr"/>
-      <c r="D270" s="7" t="inlineStr"/>
-      <c r="E270" s="7" t="inlineStr"/>
-    </row>
-    <row r="271" ht="30" customHeight="1">
-      <c r="A271" s="8" t="inlineStr">
+      <c r="B274" s="7" t="inlineStr"/>
+      <c r="C274" s="7" t="inlineStr"/>
+      <c r="D274" s="7" t="inlineStr"/>
+      <c r="E274" s="7" t="inlineStr"/>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="8" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="B271" s="8" t="inlineStr">
+      <c r="B275" s="8" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C271" s="9" t="inlineStr">
+      <c r="C275" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D271" s="10" t="inlineStr"/>
-      <c r="E271" s="11" t="inlineStr">
+      <c r="D275" s="10" t="inlineStr"/>
+      <c r="E275" s="11" t="inlineStr">
         <is>
           <t>7:30am — Checkout Landhaus Bichlbach + depart — 30 min earlier than original plan · 45 min drive to Schwangau</t>
         </is>
       </c>
     </row>
-    <row r="272" ht="22" customHeight="1">
-      <c r="A272" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="B272" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C272" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D272" s="18" t="inlineStr"/>
-      <c r="E272" s="19" t="inlineStr">
-        <is>
-          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="27" customHeight="1">
-      <c r="A273" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="B273" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C273" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D273" s="18" t="inlineStr"/>
-      <c r="E273" s="19" t="inlineStr">
-        <is>
-          <t>8:15am — Park P4, Schwangau — 7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="30" customHeight="1">
-      <c r="A274" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="B274" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C274" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D274" s="18" t="inlineStr"/>
-      <c r="E274" s="19" t="inlineStr">
-        <is>
-          <t>8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="26" customHeight="1">
-      <c r="A275" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="B275" s="16" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C275" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D275" s="18" t="inlineStr"/>
-      <c r="E275" s="19" t="inlineStr">
-        <is>
-          <t>9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="30" customHeight="1">
+    <row r="276" ht="22" customHeight="1">
       <c r="A276" s="16" t="inlineStr">
         <is>
           <t>Jul 4</t>
@@ -6173,34 +6124,34 @@
       <c r="D276" s="18" t="inlineStr"/>
       <c r="E276" s="19" t="inlineStr">
         <is>
-          <t>9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="32" customHeight="1">
-      <c r="A277" s="8" t="inlineStr">
+          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="27" customHeight="1">
+      <c r="A277" s="16" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="B277" s="8" t="inlineStr">
+      <c r="B277" s="16" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D277" s="10" t="inlineStr"/>
-      <c r="E277" s="11" t="inlineStr">
-        <is>
-          <t>11:30am — Depart Neuschwanstein  Wasserauen — 1hr 30min drive ·  Saturday = absolute peak crowds on all German/Swiss roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="27" customHeight="1">
+      <c r="C277" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D277" s="18" t="inlineStr"/>
+      <c r="E277" s="19" t="inlineStr">
+        <is>
+          <t>8:15am — Park P4, Schwangau — 7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="30" customHeight="1">
       <c r="A278" s="16" t="inlineStr">
         <is>
           <t>Jul 4</t>
@@ -6219,30 +6170,30 @@
       <c r="D278" s="18" t="inlineStr"/>
       <c r="E278" s="19" t="inlineStr">
         <is>
-          <t>1:15pm — Park at Wasserauen cable car — CHF 36/adult return (2026 rate) · runs every 15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="279" ht="28" customHeight="1">
-      <c r="A279" s="20" t="inlineStr">
+          <t>8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="26" customHeight="1">
+      <c r="A279" s="16" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="B279" s="20" t="inlineStr">
+      <c r="B279" s="16" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C279" s="21" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D279" s="22" t="inlineStr"/>
-      <c r="E279" s="23" t="inlineStr">
-        <is>
-          <t>1:30pm — Ebenalp cable car — CHF 36/adult · 6 min · last descent 6pm ·  caves 10C — pack a layer</t>
+      <c r="C279" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D279" s="18" t="inlineStr"/>
+      <c r="E279" s="19" t="inlineStr">
+        <is>
+          <t>9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
         </is>
       </c>
     </row>
@@ -6265,11 +6216,11 @@
       <c r="D280" s="18" t="inlineStr"/>
       <c r="E280" s="19" t="inlineStr">
         <is>
-          <t>2:00pm — Berggasthaus Aescher — arrive before 4pm ·  Swing event 5pm · Chäs-Chnöpfli or Rösti · Siedwurst if full</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="34" customHeight="1">
+          <t>9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="32" customHeight="1">
       <c r="A281" s="8" t="inlineStr">
         <is>
           <t>Jul 4</t>
@@ -6288,11 +6239,11 @@
       <c r="D281" s="10" t="inlineStr"/>
       <c r="E281" s="11" t="inlineStr">
         <is>
-          <t>4:00pm — Cable car down + drive to ZRH — walk 25 min back up to Ebenalp top station · cable car down · ~2hr drive to Zurich Airport area</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="29" customHeight="1">
+          <t>11:30am — Depart Neuschwanstein  Wasserauen — 1hr 30min drive ·  Saturday = absolute peak crowds on all German/Swiss roads</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="27" customHeight="1">
       <c r="A282" s="16" t="inlineStr">
         <is>
           <t>Jul 4</t>
@@ -6311,117 +6262,149 @@
       <c r="D282" s="18" t="inlineStr"/>
       <c r="E282" s="19" t="inlineStr">
         <is>
+          <t>1:15pm — Park at Wasserauen cable car — CHF 36/adult return (2026 rate) · runs every 15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="28" customHeight="1">
+      <c r="A283" s="20" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="B283" s="20" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C283" s="21" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D283" s="22" t="inlineStr"/>
+      <c r="E283" s="23" t="inlineStr">
+        <is>
+          <t>1:30pm — Ebenalp cable car — CHF 36/adult · 6 min · last descent 6pm ·  caves 10C — pack a layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="30" customHeight="1">
+      <c r="A284" s="16" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="B284" s="16" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C284" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D284" s="18" t="inlineStr"/>
+      <c r="E284" s="19" t="inlineStr">
+        <is>
+          <t>2:00pm — Berggasthaus Aescher — arrive before 4pm ·  Swing event 5pm · Chäs-Chnöpfli or Rösti · Siedwurst if full</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="34" customHeight="1">
+      <c r="A285" s="8" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D285" s="10" t="inlineStr"/>
+      <c r="E285" s="11" t="inlineStr">
+        <is>
+          <t>4:00pm — Cable car down + drive to ZRH — walk 25 min back up to Ebenalp top station · cable car down · ~2hr drive to Zurich Airport area</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="29" customHeight="1">
+      <c r="A286" s="16" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="B286" s="16" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C286" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D286" s="18" t="inlineStr"/>
+      <c r="E286" s="19" t="inlineStr">
+        <is>
           <t>Rhine Falls — SKIP TODAY — adding 45 min detour north on a peak Saturday risks missing car return window</t>
         </is>
       </c>
     </row>
-    <row r="283" ht="44" customHeight="1">
-      <c r="A283" s="8" t="inlineStr">
+    <row r="287" ht="44" customHeight="1">
+      <c r="A287" s="8" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="B283" s="8" t="inlineStr">
+      <c r="B287" s="8" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C283" s="9" t="inlineStr">
+      <c r="C287" s="9" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D283" s="10" t="inlineStr"/>
-      <c r="E283" s="11" t="inlineStr">
+      <c r="D287" s="10" t="inlineStr"/>
+      <c r="E287" s="11" t="inlineStr">
         <is>
           <t>Return Europcar ZRH tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH return · return by 11:30pm · Hilton shuttle back · check Booking.com email for return confirmation</t>
         </is>
       </c>
     </row>
-    <row r="284" ht="25" customHeight="1">
-      <c r="A284" s="24" t="inlineStr">
+    <row r="288" ht="25" customHeight="1">
+      <c r="A288" s="24" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="B284" s="24" t="inlineStr">
+      <c r="B288" s="24" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C284" s="25" t="inlineStr">
+      <c r="C288" s="25" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D284" s="26" t="inlineStr"/>
-      <c r="E284" s="27" t="inlineStr">
+      <c r="D288" s="26" t="inlineStr"/>
+      <c r="E288" s="27" t="inlineStr">
         <is>
           <t>Tonight — final checks — check-in opens 5:30am · hotel is 5 min walk to terminal</t>
         </is>
       </c>
     </row>
-    <row r="285" ht="28" customHeight="1">
-      <c r="A285" s="28" t="inlineStr"/>
-      <c r="B285" s="28" t="inlineStr"/>
-      <c r="C285" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D285" s="28" t="inlineStr"/>
-      <c r="E285" s="30" t="inlineStr">
-        <is>
-          <t>Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · 17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="36" customHeight="1">
-      <c r="A286" s="28" t="inlineStr"/>
-      <c r="B286" s="28" t="inlineStr"/>
-      <c r="C286" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D286" s="28" t="inlineStr"/>
-      <c r="E286" s="30" t="inlineStr">
-        <is>
-          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
-        </is>
-      </c>
-    </row>
-    <row r="287" ht="28" customHeight="1">
-      <c r="A287" s="28" t="inlineStr"/>
-      <c r="B287" s="28" t="inlineStr"/>
-      <c r="C287" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D287" s="28" t="inlineStr"/>
-      <c r="E287" s="30" t="inlineStr">
-        <is>
-          <t>Wildkirchli caves — 30C outside · 10C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="33" customHeight="1">
-      <c r="A288" s="28" t="inlineStr"/>
-      <c r="B288" s="28" t="inlineStr"/>
-      <c r="C288" s="29" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="D288" s="28" t="inlineStr"/>
-      <c r="E288" s="30" t="inlineStr">
-        <is>
-          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="31" customHeight="1">
+    <row r="289" ht="28" customHeight="1">
       <c r="A289" s="28" t="inlineStr"/>
       <c r="B289" s="28" t="inlineStr"/>
       <c r="C289" s="29" t="inlineStr">
@@ -6432,11 +6415,11 @@
       <c r="D289" s="28" t="inlineStr"/>
       <c r="E289" s="30" t="inlineStr">
         <is>
-          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" ht="28" customHeight="1">
+          <t>Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · 17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="36" customHeight="1">
       <c r="A290" s="28" t="inlineStr"/>
       <c r="B290" s="28" t="inlineStr"/>
       <c r="C290" s="29" t="inlineStr">
@@ -6447,235 +6430,203 @@
       <c r="D290" s="28" t="inlineStr"/>
       <c r="E290" s="30" t="inlineStr">
         <is>
+          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="28" customHeight="1">
+      <c r="A291" s="28" t="inlineStr"/>
+      <c r="B291" s="28" t="inlineStr"/>
+      <c r="C291" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D291" s="28" t="inlineStr"/>
+      <c r="E291" s="30" t="inlineStr">
+        <is>
+          <t>Wildkirchli caves — 30C outside · 10C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="33" customHeight="1">
+      <c r="A292" s="28" t="inlineStr"/>
+      <c r="B292" s="28" t="inlineStr"/>
+      <c r="C292" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D292" s="28" t="inlineStr"/>
+      <c r="E292" s="30" t="inlineStr">
+        <is>
+          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="31" customHeight="1">
+      <c r="A293" s="28" t="inlineStr"/>
+      <c r="B293" s="28" t="inlineStr"/>
+      <c r="C293" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D293" s="28" t="inlineStr"/>
+      <c r="E293" s="30" t="inlineStr">
+        <is>
+          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="28" customHeight="1">
+      <c r="A294" s="28" t="inlineStr"/>
+      <c r="B294" s="28" t="inlineStr"/>
+      <c r="C294" s="29" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="D294" s="28" t="inlineStr"/>
+      <c r="E294" s="30" t="inlineStr">
+        <is>
           <t>5:00am alarm Jul 5 — set two alarms · FI571 departs 7:55am · check-in opens 5:30am · hotel is 5 min walk to terminal · boarding passes on phone tonight</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="3" customHeight="1">
-      <c r="A291" s="31" t="n"/>
-      <c r="B291" s="31" t="n"/>
-      <c r="C291" s="31" t="n"/>
-      <c r="D291" s="31" t="n"/>
-      <c r="E291" s="31" t="n"/>
-    </row>
-    <row r="292" ht="22" customHeight="1">
-      <c r="A292" s="3" t="inlineStr">
+    <row r="295" ht="3" customHeight="1">
+      <c r="A295" s="31" t="n"/>
+      <c r="B295" s="31" t="n"/>
+      <c r="C295" s="31" t="n"/>
+      <c r="D295" s="31" t="n"/>
+      <c r="E295" s="31" t="n"/>
+    </row>
+    <row r="296" ht="22" customHeight="1">
+      <c r="A296" s="3" t="inlineStr">
         <is>
           <t>DAY 16  |  Jul 5  |  Homebound — ZRH  KEF  MCO · The Final Leg  |  —  —</t>
         </is>
       </c>
-      <c r="B292" s="4" t="inlineStr"/>
-      <c r="C292" s="4" t="inlineStr"/>
-      <c r="D292" s="4" t="inlineStr"/>
-      <c r="E292" s="4" t="inlineStr"/>
-    </row>
-    <row r="293" ht="15" customHeight="1">
-      <c r="A293" s="5" t="inlineStr">
+      <c r="B296" s="4" t="inlineStr"/>
+      <c r="C296" s="4" t="inlineStr"/>
+      <c r="D296" s="4" t="inlineStr"/>
+      <c r="E296" s="4" t="inlineStr"/>
+    </row>
+    <row r="297" ht="15" customHeight="1">
+      <c r="A297" s="5" t="inlineStr">
         <is>
           <t>&gt; Sat night: app check-in  confirm shuttle  5am wake  5:30am Hilton shuttle (NOT walk)  5:45am Terminal 2 · Check-in Row 3  6am security + E Gate Skymetro  7:55am FI571 ZRHKEF  KEF Pylsur layover  8:50pm MCO home</t>
         </is>
       </c>
-      <c r="B293" s="6" t="inlineStr"/>
-      <c r="C293" s="6" t="inlineStr"/>
-      <c r="D293" s="6" t="inlineStr"/>
-      <c r="E293" s="6" t="inlineStr"/>
-    </row>
-    <row r="294" ht="24" customHeight="1">
-      <c r="A294" s="7" t="inlineStr">
+      <c r="B297" s="6" t="inlineStr"/>
+      <c r="C297" s="6" t="inlineStr"/>
+      <c r="D297" s="6" t="inlineStr"/>
+      <c r="E297" s="6" t="inlineStr"/>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="7" t="inlineStr">
         <is>
           <t>KEY: Take hotel shuttle NOT walk — Hilton is 2km from terminal · not walkable with luggage · CHF 7/person  |   Icelandair app check-in Saturday night — digital boarding pass · fast bag drop at Check-in 2 Row 3  |   US Customs at MCO not KEF — do not leave transit area in Iceland</t>
         </is>
       </c>
-      <c r="B294" s="7" t="inlineStr"/>
-      <c r="C294" s="7" t="inlineStr"/>
-      <c r="D294" s="7" t="inlineStr"/>
-      <c r="E294" s="7" t="inlineStr"/>
-    </row>
-    <row r="295" ht="34" customHeight="1">
-      <c r="A295" s="33" t="inlineStr">
+      <c r="B298" s="7" t="inlineStr"/>
+      <c r="C298" s="7" t="inlineStr"/>
+      <c r="D298" s="7" t="inlineStr"/>
+      <c r="E298" s="7" t="inlineStr"/>
+    </row>
+    <row r="299" ht="34" customHeight="1">
+      <c r="A299" s="33" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="B295" s="33" t="inlineStr">
+      <c r="B299" s="33" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C295" s="34" t="inlineStr">
+      <c r="C299" s="34" t="inlineStr">
         <is>
           <t>ALERT</t>
         </is>
       </c>
-      <c r="D295" s="35" t="inlineStr"/>
-      <c r="E295" s="36" t="inlineStr">
+      <c r="D299" s="35" t="inlineStr"/>
+      <c r="E299" s="36" t="inlineStr">
         <is>
           <t>Night before (Jul 4 Saturday evening) — final prep — (2) Check Europcar/Booking.com email — confirm car return was closed out correctly</t>
         </is>
       </c>
     </row>
-    <row r="296" ht="35" customHeight="1">
-      <c r="A296" s="12" t="inlineStr">
+    <row r="300" ht="35" customHeight="1">
+      <c r="A300" s="12" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="B296" s="12" t="inlineStr">
+      <c r="B300" s="12" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C296" s="13" t="inlineStr">
+      <c r="C300" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D296" s="14" t="inlineStr"/>
-      <c r="E296" s="15" t="inlineStr">
+      <c r="D300" s="14" t="inlineStr"/>
+      <c r="E300" s="15" t="inlineStr">
         <is>
           <t>5:00am — Wake up — perfect timing · do not wake earlier unless extra bags need special handling · hotel breakfast starts at 5:30am if needed</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="27" customHeight="1">
-      <c r="A297" s="16" t="inlineStr">
+    <row r="301" ht="27" customHeight="1">
+      <c r="A301" s="16" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="B297" s="16" t="inlineStr">
+      <c r="B301" s="16" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C297" s="17" t="inlineStr">
+      <c r="C301" s="17" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D297" s="18" t="inlineStr"/>
-      <c r="E297" s="19" t="inlineStr">
+      <c r="D301" s="18" t="inlineStr"/>
+      <c r="E301" s="19" t="inlineStr">
         <is>
           <t>5:30am — Hilton shuttle —  do NOT walk · 2km to terminal · CHF 7/person · confirm seat tonight</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="27" customHeight="1">
-      <c r="A298" s="24" t="inlineStr">
+    <row r="302" ht="27" customHeight="1">
+      <c r="A302" s="24" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="B298" s="24" t="inlineStr">
+      <c r="B302" s="24" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C298" s="25" t="inlineStr">
+      <c r="C302" s="25" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D298" s="26" t="inlineStr"/>
-      <c r="E298" s="27" t="inlineStr">
+      <c r="D302" s="26" t="inlineStr"/>
+      <c r="E302" s="27" t="inlineStr">
         <is>
           <t>5:45am — Terminal 2, Check-in Row 3 — bag drop opens 5:25am · digital boarding pass on phone</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="27" customHeight="1">
-      <c r="A299" s="16" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="B299" s="16" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C299" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D299" s="18" t="inlineStr"/>
-      <c r="E299" s="19" t="inlineStr">
-        <is>
-          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="33" customHeight="1">
-      <c r="A300" s="16" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="B300" s="16" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C300" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D300" s="18" t="inlineStr"/>
-      <c r="E300" s="19" t="inlineStr">
-        <is>
-          <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
-        </is>
-      </c>
-    </row>
-    <row r="301" ht="18" customHeight="1">
-      <c r="A301" s="8" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="B301" s="8" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C301" s="9" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D301" s="10" t="inlineStr"/>
-      <c r="E301" s="11" t="inlineStr">
-        <is>
-          <t>7:55am — FI571 departs ZRH  KEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="32" customHeight="1">
-      <c r="A302" s="16" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="B302" s="16" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C302" s="17" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D302" s="18" t="inlineStr"/>
-      <c r="E302" s="19" t="inlineStr">
-        <is>
-          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="31" customHeight="1">
+    <row r="303" ht="27" customHeight="1">
       <c r="A303" s="16" t="inlineStr">
         <is>
           <t>Jul 5</t>
@@ -6694,76 +6645,168 @@
       <c r="D303" s="18" t="inlineStr"/>
       <c r="E303" s="19" t="inlineStr">
         <is>
+          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="33" customHeight="1">
+      <c r="A304" s="16" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="B304" s="16" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C304" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D304" s="18" t="inlineStr"/>
+      <c r="E304" s="19" t="inlineStr">
+        <is>
+          <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="18" customHeight="1">
+      <c r="A305" s="8" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D305" s="10" t="inlineStr"/>
+      <c r="E305" s="11" t="inlineStr">
+        <is>
+          <t>7:55am — FI571 departs ZRH  KEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="32" customHeight="1">
+      <c r="A306" s="16" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="B306" s="16" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C306" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D306" s="18" t="inlineStr"/>
+      <c r="E306" s="19" t="inlineStr">
+        <is>
+          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="31" customHeight="1">
+      <c r="A307" s="16" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="B307" s="16" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C307" s="17" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D307" s="18" t="inlineStr"/>
+      <c r="E307" s="19" t="inlineStr">
+        <is>
           <t>8:50pm — Arrive Orlando MCO — clear US Customs + Immigration at MCO · allow 45–60 min for customs on Sunday evening</t>
         </is>
       </c>
     </row>
-    <row r="304" ht="32" customHeight="1">
-      <c r="A304" s="28" t="inlineStr"/>
-      <c r="B304" s="28" t="inlineStr"/>
-      <c r="C304" s="29" t="inlineStr">
+    <row r="308" ht="32" customHeight="1">
+      <c r="A308" s="28" t="inlineStr"/>
+      <c r="B308" s="28" t="inlineStr"/>
+      <c r="C308" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D304" s="28" t="inlineStr"/>
-      <c r="E304" s="30" t="inlineStr">
+      <c r="D308" s="28" t="inlineStr"/>
+      <c r="E308" s="30" t="inlineStr">
         <is>
           <t>Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
         </is>
       </c>
     </row>
-    <row r="305" ht="34" customHeight="1">
-      <c r="A305" s="28" t="inlineStr"/>
-      <c r="B305" s="28" t="inlineStr"/>
-      <c r="C305" s="29" t="inlineStr">
+    <row r="309" ht="34" customHeight="1">
+      <c r="A309" s="28" t="inlineStr"/>
+      <c r="B309" s="28" t="inlineStr"/>
+      <c r="C309" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D305" s="28" t="inlineStr"/>
-      <c r="E305" s="30" t="inlineStr">
+      <c r="D309" s="28" t="inlineStr"/>
+      <c r="E309" s="30" t="inlineStr">
         <is>
           <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
         </is>
       </c>
     </row>
-    <row r="306" ht="36" customHeight="1">
-      <c r="A306" s="28" t="inlineStr"/>
-      <c r="B306" s="28" t="inlineStr"/>
-      <c r="C306" s="29" t="inlineStr">
+    <row r="310" ht="36" customHeight="1">
+      <c r="A310" s="28" t="inlineStr"/>
+      <c r="B310" s="28" t="inlineStr"/>
+      <c r="C310" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D306" s="28" t="inlineStr"/>
-      <c r="E306" s="30" t="inlineStr">
+      <c r="D310" s="28" t="inlineStr"/>
+      <c r="E310" s="30" t="inlineStr">
         <is>
           <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
         </is>
       </c>
     </row>
-    <row r="307" ht="28" customHeight="1">
-      <c r="A307" s="28" t="inlineStr"/>
-      <c r="B307" s="28" t="inlineStr"/>
-      <c r="C307" s="29" t="inlineStr">
+    <row r="311" ht="28" customHeight="1">
+      <c r="A311" s="28" t="inlineStr"/>
+      <c r="B311" s="28" t="inlineStr"/>
+      <c r="C311" s="29" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D307" s="28" t="inlineStr"/>
-      <c r="E307" s="30" t="inlineStr">
+      <c r="D311" s="28" t="inlineStr"/>
+      <c r="E311" s="30" t="inlineStr">
         <is>
           <t>KEF layover — 1.5–2hrs · Pylsur hot dog (best in the world) · Skyr yoghurt · duty-free is excellent · US customs at MCO not here · do not leave transit</t>
         </is>
       </c>
     </row>
-    <row r="308" ht="3" customHeight="1">
-      <c r="A308" s="31" t="n"/>
-      <c r="B308" s="31" t="n"/>
-      <c r="C308" s="31" t="n"/>
-      <c r="D308" s="31" t="n"/>
-      <c r="E308" s="31" t="n"/>
+    <row r="312" ht="3" customHeight="1">
+      <c r="A312" s="31" t="n"/>
+      <c r="B312" s="31" t="n"/>
+      <c r="C312" s="31" t="n"/>
+      <c r="D312" s="31" t="n"/>
+      <c r="E312" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6869,7 +6912,11 @@
           <t>~180 km  ~2.5h</t>
         </is>
       </c>
-      <c r="G3" s="42" t="inlineStr"/>
+      <c r="G3" s="42" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="38" t="inlineStr">
@@ -6902,7 +6949,11 @@
           <t>~480 km  ~5h</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr"/>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="43" t="inlineStr">
@@ -7416,36 +7467,38 @@
           <t>— —</t>
         </is>
       </c>
-      <c r="G18" s="42" t="inlineStr"/>
+      <c r="G18" s="65" t="inlineStr"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>Colours: Blue=Iceland  Green=Switzerland  Yellow=Germany  Red=Austria  Pink=Italy  |  Map: tap to open Google Maps</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr"/>
-      <c r="C20" s="65" t="inlineStr"/>
-      <c r="D20" s="65" t="inlineStr"/>
-      <c r="E20" s="65" t="inlineStr"/>
-      <c r="F20" s="65" t="inlineStr"/>
-      <c r="G20" s="65" t="inlineStr"/>
+      <c r="B20" s="66" t="inlineStr"/>
+      <c r="C20" s="66" t="inlineStr"/>
+      <c r="D20" s="66" t="inlineStr"/>
+      <c r="E20" s="66" t="inlineStr"/>
+      <c r="F20" s="66" t="inlineStr"/>
+      <c r="G20" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7506,7 +7559,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="66" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7522,14 +7575,14 @@
         </is>
       </c>
       <c r="D3" s="45" t="inlineStr"/>
-      <c r="E3" s="67" t="inlineStr">
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7545,14 +7598,14 @@
         </is>
       </c>
       <c r="D4" s="45" t="inlineStr"/>
-      <c r="E4" s="67" t="inlineStr">
+      <c r="E4" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7568,14 +7621,14 @@
         </is>
       </c>
       <c r="D5" s="45" t="inlineStr"/>
-      <c r="E5" s="67" t="inlineStr">
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7591,14 +7644,14 @@
         </is>
       </c>
       <c r="D6" s="45" t="inlineStr"/>
-      <c r="E6" s="67" t="inlineStr">
+      <c r="E6" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7614,14 +7667,14 @@
         </is>
       </c>
       <c r="D7" s="45" t="inlineStr"/>
-      <c r="E7" s="67" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7637,14 +7690,14 @@
         </is>
       </c>
       <c r="D8" s="45" t="inlineStr"/>
-      <c r="E8" s="67" t="inlineStr">
+      <c r="E8" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>URGENT</t>
         </is>
@@ -7664,10 +7717,10 @@
           <t>Book NOW — July sells out weeks ahead</t>
         </is>
       </c>
-      <c r="E9" s="69" t="inlineStr"/>
+      <c r="E9" s="70" t="inlineStr"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7687,14 +7740,14 @@
           <t>Booked  — print tickets before departure</t>
         </is>
       </c>
-      <c r="E10" s="67" t="inlineStr">
+      <c r="E10" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>URGENT</t>
         </is>
@@ -7710,10 +7763,10 @@
           <t>Buy on Jun 22 at asfinag.at after picking up Europcar car · need licence plate · ~16.50 · 10-day pass</t>
         </is>
       </c>
-      <c r="E11" s="69" t="inlineStr"/>
+      <c r="E11" s="70" t="inlineStr"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="66" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7729,14 +7782,14 @@
         </is>
       </c>
       <c r="D12" s="45" t="inlineStr"/>
-      <c r="E12" s="67" t="inlineStr">
+      <c r="E12" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7752,10 +7805,10 @@
           <t>Book 1–2 weeks before Jun 25 (non-refundable · pick time you are confident about) · seenschifffahrt.de</t>
         </is>
       </c>
-      <c r="E13" s="71" t="inlineStr"/>
+      <c r="E13" s="72" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="70" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7775,10 +7828,10 @@
           <t>Book soon — Jun 27 Saturday peak season</t>
         </is>
       </c>
-      <c r="E14" s="71" t="inlineStr"/>
+      <c r="E14" s="72" t="inlineStr"/>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="66" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7798,14 +7851,14 @@
           <t>N/A — closed during our visit</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="70" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7825,10 +7878,10 @@
           <t>Book before departure</t>
         </is>
       </c>
-      <c r="E16" s="71" t="inlineStr"/>
+      <c r="E16" s="72" t="inlineStr"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="70" t="inlineStr">
+      <c r="A17" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7844,10 +7897,10 @@
           <t>Day-of or day-before fine · large boats · no timed slots · achensee.com</t>
         </is>
       </c>
-      <c r="E17" s="71" t="inlineStr"/>
+      <c r="E17" s="72" t="inlineStr"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="70" t="inlineStr">
+      <c r="A18" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7867,10 +7920,10 @@
           <t>Buy on day — no pre-booking needed</t>
         </is>
       </c>
-      <c r="E18" s="71" t="inlineStr"/>
+      <c r="E18" s="72" t="inlineStr"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="70" t="inlineStr">
+      <c r="A19" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7886,10 +7939,10 @@
           <t>Before departure</t>
         </is>
       </c>
-      <c r="E19" s="71" t="inlineStr"/>
+      <c r="E19" s="72" t="inlineStr"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="70" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7909,10 +7962,10 @@
           <t>Keep checking daily — cancellations appear · Plan B = Seis–Compatsch cable car (no booking needed)</t>
         </is>
       </c>
-      <c r="E20" s="71" t="inlineStr"/>
+      <c r="E20" s="72" t="inlineStr"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="70" t="inlineStr">
+      <c r="A21" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7932,10 +7985,10 @@
           <t>Buy before Jun 30</t>
         </is>
       </c>
-      <c r="E21" s="71" t="inlineStr"/>
+      <c r="E21" s="72" t="inlineStr"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="66" t="inlineStr">
+      <c r="A22" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7955,14 +8008,14 @@
           <t>Booked  · update licence plate night before (Jun 28 in Sillian)</t>
         </is>
       </c>
-      <c r="E22" s="67" t="inlineStr">
+      <c r="E22" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="66" t="inlineStr">
+      <c r="A23" s="67" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7982,7 +8035,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E23" s="67" t="inlineStr">
+      <c r="E23" s="68" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -8048,270 +8101,270 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="73" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="73" t="inlineStr">
+      <c r="B3" s="74" t="inlineStr">
         <is>
           <t>Jun 20–21</t>
         </is>
       </c>
-      <c r="C3" s="73" t="inlineStr">
+      <c r="C3" s="74" t="inlineStr">
         <is>
           <t>Farmhouse Lodge, Vík</t>
         </is>
       </c>
-      <c r="D3" s="74" t="inlineStr">
+      <c r="D3" s="75" t="inlineStr">
         <is>
           <t>871 Vík, Iceland</t>
         </is>
       </c>
-      <c r="E3" s="74" t="inlineStr">
+      <c r="E3" s="75" t="inlineStr">
         <is>
           <t>+354 xxx xxxx · Airbnb message host</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="75" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="76" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>Jun 21–22</t>
         </is>
       </c>
-      <c r="C4" s="76" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>BergOne</t>
         </is>
       </c>
-      <c r="D4" s="77" t="inlineStr">
+      <c r="D4" s="78" t="inlineStr">
         <is>
           <t>1 Bergás, 260 Ytri-Njarðvík, Iceland</t>
         </is>
       </c>
-      <c r="E4" s="77" t="inlineStr">
+      <c r="E4" s="78" t="inlineStr">
         <is>
           <t>+354 xxx xxxx · Booking.com message host</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="73" t="inlineStr">
         <is>
           <t>3–4</t>
         </is>
       </c>
-      <c r="B5" s="73" t="inlineStr">
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>Jun 22–24</t>
         </is>
       </c>
-      <c r="C5" s="73" t="inlineStr">
+      <c r="C5" s="74" t="inlineStr">
         <is>
           <t>Camping Jungfrau</t>
         </is>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="75" t="inlineStr">
         <is>
           <t>Weid 406, 3822 Lauterbrunnen, Switzerland</t>
         </is>
       </c>
-      <c r="E5" s="74" t="inlineStr">
+      <c r="E5" s="75" t="inlineStr">
         <is>
           <t>+41 33 856 20 10 · reception@camping-jungfrau.ch</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>5–6</t>
         </is>
       </c>
-      <c r="B6" s="76" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>Jun 24–26</t>
         </is>
       </c>
-      <c r="C6" s="76" t="inlineStr">
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>One-Bedroom Apartment, Berchtesgaden</t>
         </is>
       </c>
-      <c r="D6" s="77" t="inlineStr">
+      <c r="D6" s="78" t="inlineStr">
         <is>
           <t>Kälbersteinstraße 4, 83471 Berchtesgaden, Germany</t>
         </is>
       </c>
-      <c r="E6" s="77" t="inlineStr">
+      <c r="E6" s="78" t="inlineStr">
         <is>
           <t>+49 8652 xxx · Booking.com message host</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="72" t="inlineStr">
+      <c r="A7" s="73" t="inlineStr">
         <is>
           <t>7–8</t>
         </is>
       </c>
-      <c r="B7" s="73" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>Jun 26–28</t>
         </is>
       </c>
-      <c r="C7" s="73" t="inlineStr">
+      <c r="C7" s="74" t="inlineStr">
         <is>
           <t>Kaiserblick Goisern</t>
         </is>
       </c>
-      <c r="D7" s="74" t="inlineStr">
+      <c r="D7" s="75" t="inlineStr">
         <is>
           <t>38 Unterjoch, 4822 Bad Goisern, Austria</t>
         </is>
       </c>
-      <c r="E7" s="74" t="inlineStr">
+      <c r="E7" s="75" t="inlineStr">
         <is>
           <t>+43 xxx · Airbnb message host · key box on arrival</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B8" s="76" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>Jun 28–29</t>
         </is>
       </c>
-      <c r="C8" s="76" t="inlineStr">
+      <c r="C8" s="77" t="inlineStr">
         <is>
           <t>Hotel Schwarzer Adler Sillian</t>
         </is>
       </c>
-      <c r="D8" s="77" t="inlineStr">
+      <c r="D8" s="78" t="inlineStr">
         <is>
           <t>Sillian 12, 9920 Sillian, Austria</t>
         </is>
       </c>
-      <c r="E8" s="77" t="inlineStr">
+      <c r="E8" s="78" t="inlineStr">
         <is>
           <t>+43 4842 6214 · info@schwarzeradler-sillian.at</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="73" t="inlineStr">
         <is>
           <t>10–11</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>Jun 29–Jul 1</t>
         </is>
       </c>
-      <c r="C9" s="73" t="inlineStr">
+      <c r="C9" s="74" t="inlineStr">
         <is>
           <t>Kaiserau 1907, Collalbo</t>
         </is>
       </c>
-      <c r="D9" s="74" t="inlineStr">
+      <c r="D9" s="75" t="inlineStr">
         <is>
           <t>Via Peter Mayr, 65, 39054 Collalbo (Renon), Italy</t>
         </is>
       </c>
-      <c r="E9" s="74" t="inlineStr">
+      <c r="E9" s="75" t="inlineStr">
         <is>
           <t>+39 0471 356 xxx · Booking.com · check-in 15:00–22:00</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="75" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>Jul 1–2</t>
         </is>
       </c>
-      <c r="C10" s="76" t="inlineStr">
+      <c r="C10" s="77" t="inlineStr">
         <is>
           <t>Keyone Rooms Finkenberg</t>
         </is>
       </c>
-      <c r="D10" s="77" t="inlineStr">
+      <c r="D10" s="78" t="inlineStr">
         <is>
           <t>Dorf 131, 6292 Finkenberg, Austria</t>
         </is>
       </c>
-      <c r="E10" s="77" t="inlineStr">
+      <c r="E10" s="78" t="inlineStr">
         <is>
           <t>+43 5285 xxx · Booking.com · check-in from 16:00</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="73" t="inlineStr">
         <is>
           <t>13-14-15</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>Jul 2–4</t>
         </is>
       </c>
-      <c r="C11" s="73" t="inlineStr">
+      <c r="C11" s="74" t="inlineStr">
         <is>
           <t>Landhaus Bichlbach</t>
         </is>
       </c>
-      <c r="D11" s="74" t="inlineStr">
+      <c r="D11" s="75" t="inlineStr">
         <is>
           <t>159 Siedlung, 6621 Bichlbach, Austria</t>
         </is>
       </c>
-      <c r="E11" s="74" t="inlineStr">
+      <c r="E11" s="75" t="inlineStr">
         <is>
           <t>+43 5674 xxx · Booking.com · check-in 15:00–18:00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B12" s="76" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>Jul 4–5</t>
         </is>
       </c>
-      <c r="C12" s="76" t="inlineStr">
+      <c r="C12" s="77" t="inlineStr">
         <is>
           <t>Airport Hotel Zurich</t>
         </is>
       </c>
-      <c r="D12" s="77" t="inlineStr">
+      <c r="D12" s="78" t="inlineStr">
         <is>
           <t>Lindbergh-Platz 1, 8152 Glattbrugg, Switzerland</t>
         </is>
       </c>
-      <c r="E12" s="77" t="inlineStr">
+      <c r="E12" s="78" t="inlineStr">
         <is>
           <t>+41 44 808 00 00 · Lindbergh-Platz 1, Glattbrugg</t>
         </is>
@@ -8370,66 +8423,66 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="73" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>Flights x4 (confirmed)</t>
         </is>
       </c>
-      <c r="B3" s="78" t="inlineStr">
+      <c r="B3" s="79" t="inlineStr">
         <is>
           <t>$4,088</t>
         </is>
       </c>
-      <c r="C3" s="79" t="inlineStr">
+      <c r="C3" s="80" t="inlineStr">
         <is>
           <t>$4,088</t>
         </is>
       </c>
-      <c r="D3" s="74" t="inlineStr">
+      <c r="D3" s="75" t="inlineStr">
         <is>
           <t>Icelandair A77762</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="73" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Accommodation 15 nights (confirmed)</t>
         </is>
       </c>
-      <c r="B4" s="78" t="inlineStr">
+      <c r="B4" s="79" t="inlineStr">
         <is>
           <t>$3,032</t>
         </is>
       </c>
-      <c r="C4" s="79" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>$3,032</t>
         </is>
       </c>
-      <c r="D4" s="74" t="inlineStr">
+      <c r="D4" s="75" t="inlineStr">
         <is>
           <t>All 10 properties</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="73" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>Car Rental ZRH + KEF (confirmed)</t>
         </is>
       </c>
-      <c r="B5" s="78" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>$1,182</t>
         </is>
       </c>
-      <c r="C5" s="79" t="inlineStr">
+      <c r="C5" s="80" t="inlineStr">
         <is>
           <t>$1,182</t>
         </is>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="75" t="inlineStr">
         <is>
           <t>Europcar 738796923 + Budget #42334482US1</t>
         </is>
@@ -8441,31 +8494,31 @@
           <t>Food &amp; Drinks</t>
         </is>
       </c>
-      <c r="B6" s="80" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>$1,850</t>
         </is>
       </c>
-      <c r="C6" s="81" t="inlineStr"/>
-      <c r="D6" s="77" t="inlineStr">
+      <c r="C6" s="82" t="inlineStr"/>
+      <c r="D6" s="78" t="inlineStr">
         <is>
           <t>Update daily</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>Activities &amp; Entry Fees</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>$1,100</t>
         </is>
       </c>
-      <c r="C7" s="84" t="inlineStr"/>
-      <c r="D7" s="85" t="inlineStr">
+      <c r="C7" s="85" t="inlineStr"/>
+      <c r="D7" s="86" t="inlineStr">
         <is>
           <t>Cable cars, castle entries</t>
         </is>
@@ -8477,45 +8530,45 @@
           <t>Fuel &amp; Tolls</t>
         </is>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>$1,000</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr"/>
-      <c r="D8" s="77" t="inlineStr">
+      <c r="C8" s="82" t="inlineStr"/>
+      <c r="D8" s="78" t="inlineStr">
         <is>
           <t>Grossglockner 46.50 EUR, Schlegeis 17 EUR, Auronzo 40 EUR</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>Shopping &amp; Misc</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="84" t="inlineStr">
         <is>
           <t>$400</t>
         </is>
       </c>
-      <c r="C9" s="84" t="inlineStr"/>
-      <c r="D9" s="85" t="inlineStr"/>
+      <c r="C9" s="85" t="inlineStr"/>
+      <c r="D9" s="86" t="inlineStr"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="86" t="inlineStr">
+      <c r="A10" s="87" t="inlineStr">
         <is>
           <t>TOTAL CONFIRMED</t>
         </is>
       </c>
-      <c r="B10" s="87" t="inlineStr">
+      <c r="B10" s="88" t="inlineStr">
         <is>
           <t>$8,302</t>
         </is>
       </c>
-      <c r="C10" s="87" t="inlineStr"/>
-      <c r="D10" s="88" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr"/>
+      <c r="D10" s="89" t="inlineStr">
         <is>
           <t>vs est. ~$11,600-$12,900</t>
         </is>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:F316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2869,103 +2869,103 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="11" t="inlineStr"/>
-      <c r="B107" s="12" t="inlineStr">
+    <row r="107" ht="50" customHeight="1">
+      <c r="A107" s="16" t="inlineStr"/>
+      <c r="B107" s="17" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C107" s="13" t="inlineStr">
+      <c r="C107" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr"/>
+      <c r="E107" s="18" t="inlineStr">
+        <is>
+          <t>Malerwinkel — Painter's Corner viewpoint — on the walk back from Obersee toward St. Bartholomä · wooden bench overlook · most famous postcard view of the lake · red onion domes of St. Bartholomä perfectly reflected · mos</t>
+        </is>
+      </c>
+      <c r="F107" s="19" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="11" t="inlineStr"/>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C108" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D107" s="12" t="inlineStr"/>
-      <c r="E107" s="14" t="inlineStr">
+      <c r="D108" s="12" t="inlineStr"/>
+      <c r="E108" s="14" t="inlineStr">
         <is>
           <t>12:00pm — St. Bartholomä lunch stop — allow 45 min</t>
         </is>
       </c>
-      <c r="F107" s="15" t="inlineStr">
+      <c r="F108" s="15" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="16" t="inlineStr"/>
-      <c r="B108" s="17" t="inlineStr">
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="16" t="inlineStr"/>
+      <c r="B109" s="17" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C108" s="16" t="inlineStr">
+      <c r="C109" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D108" s="17" t="inlineStr"/>
-      <c r="E108" s="18" t="inlineStr">
+      <c r="D109" s="17" t="inlineStr"/>
+      <c r="E109" s="18" t="inlineStr">
         <is>
           <t>⛵ 12:45pm — Final boat back to Königssee Seelände — 35 min · arrive ~1:15pm · walk 10 min to car park</t>
         </is>
       </c>
-      <c r="F108" s="19" t="inlineStr">
+      <c r="F109" s="19" t="inlineStr">
         <is>
           <t>35 min / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="50" customHeight="1">
-      <c r="A109" s="6" t="inlineStr"/>
-      <c r="B109" s="7" t="inlineStr">
+    <row r="110" ht="50" customHeight="1">
+      <c r="A110" s="6" t="inlineStr"/>
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr"/>
+      <c r="E110" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 1:30pm — Eagle's Nest (Kehlsteinhaus) — drive 10 min to Obersalzberg car park · Kehlsteinbus ~€32 (bus + brass elevator) ·  Golden Rule: immediately book 4:00 or 4:15pm return slot at top counter · 360° Alpine panora</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr">
         <is>
           <t>10 min / €32 / 2hr</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="50" customHeight="1">
-      <c r="A110" s="16" t="inlineStr"/>
-      <c r="B110" s="17" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D110" s="17" t="inlineStr"/>
-      <c r="E110" s="18" t="inlineStr">
-        <is>
-          <t>➕ Optional: Berchtesgaden Salt Mine — ☁️ Weather backup for Eagle's Nest · Salzburger Str. 24 · open 9am–5pm · ~€20/adult · ~€12/child · miners' overalls + underground raft on salt lake + glittering crystals · constant 1</t>
-        </is>
-      </c>
-      <c r="F110" s="19" t="inlineStr">
-        <is>
-          <t>€20 / €12 / 2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="24" customHeight="1">
+    <row r="111" ht="50" customHeight="1">
       <c r="A111" s="16" t="inlineStr"/>
       <c r="B111" s="17" t="inlineStr">
         <is>
@@ -2980,16 +2980,16 @@
       <c r="D111" s="17" t="inlineStr"/>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>Dokumentation Obersalzberg WWII Museum — 30 min · €10/adult</t>
+          <t>➕ Optional: Berchtesgaden Salt Mine — ☁️ Weather backup for Eagle's Nest · Salzburger Str. 24 · open 9am–5pm · ~€20/adult · ~€12/child · miners' overalls + underground raft on salt lake + glittering crystals · constant 1</t>
         </is>
       </c>
       <c r="F111" s="19" t="inlineStr">
         <is>
-          <t>30 min / €10</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="30" customHeight="1">
+          <t>€20 / €12 / 2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="24" customHeight="1">
       <c r="A112" s="16" t="inlineStr"/>
       <c r="B112" s="17" t="inlineStr">
         <is>
@@ -3004,93 +3004,104 @@
       <c r="D112" s="17" t="inlineStr"/>
       <c r="E112" s="18" t="inlineStr">
         <is>
+          <t>Dokumentation Obersalzberg WWII Museum — 30 min · €10/adult</t>
+        </is>
+      </c>
+      <c r="F112" s="19" t="inlineStr">
+        <is>
+          <t>30 min / €10</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="16" t="inlineStr"/>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr"/>
+      <c r="E113" s="18" t="inlineStr">
+        <is>
           <t>⭐ ~4:00pm — Rossfeld Panorama Road — €9 toll · Germany's highest panoramic toll road at 1,570m</t>
         </is>
       </c>
-      <c r="F112" s="19" t="inlineStr">
+      <c r="F113" s="19" t="inlineStr">
         <is>
           <t>€9</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="35" customHeight="1">
-      <c r="A113" s="6" t="inlineStr"/>
-      <c r="B113" s="7" t="inlineStr">
+    <row r="114" ht="35" customHeight="1">
+      <c r="A114" s="6" t="inlineStr"/>
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr"/>
+      <c r="E114" s="9" t="inlineStr">
         <is>
           <t>~4:45pm — Hintersee &amp; Zauberwald (Magic Forest) — 15 min drive toward Ramsau · follow the trail into the Zauberwald</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F114" s="10" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="34" customHeight="1">
-      <c r="A114" s="25" t="inlineStr"/>
-      <c r="B114" s="26" t="inlineStr">
+    <row r="115" ht="34" customHeight="1">
+      <c r="A115" s="25" t="inlineStr"/>
+      <c r="B115" s="26" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C114" s="27" t="inlineStr">
+      <c r="C115" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D114" s="26" t="inlineStr"/>
-      <c r="E114" s="28" t="inlineStr">
+      <c r="D115" s="26" t="inlineStr"/>
+      <c r="E115" s="28" t="inlineStr">
         <is>
           <t>Night 2 — Berchtesgaden Apartment — ✅ Already checked in ·  Kälbersteinstraße 4, 83471 Berchtesgaden, Germany</t>
         </is>
       </c>
-      <c r="F114" s="29" t="inlineStr"/>
-    </row>
-    <row r="115" ht="34" customHeight="1">
-      <c r="A115" s="11" t="inlineStr"/>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="F115" s="29" t="inlineStr"/>
+    </row>
+    <row r="116" ht="34" customHeight="1">
+      <c r="A116" s="11" t="inlineStr"/>
+      <c r="B116" s="12" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C115" s="13" t="inlineStr">
+      <c r="C116" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D115" s="12" t="inlineStr"/>
-      <c r="E115" s="14" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr"/>
+      <c r="E116" s="14" t="inlineStr">
         <is>
           <t>Dinner — Berchtesgaden — Bräustüberl Berchtesgaden (Bräuhausstraße 13) if not done Day 5 · or Gasthof Neuhaus</t>
         </is>
       </c>
-      <c r="F115" s="15" t="inlineStr"/>
-    </row>
-    <row r="116" ht="34" customHeight="1">
-      <c r="A116" s="30" t="inlineStr"/>
-      <c r="B116" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C116" s="32" t="inlineStr">
-        <is>
-          <t>⛵ Königssee boat tips — ~€28–30 return to Salet per adult · book at seenschifffahrt.de 1 week before · dock is 10 min walk from car park · tip the captain €1–2 for the trumpet echo</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="31" customHeight="1">
+      <c r="F116" s="15" t="inlineStr"/>
+    </row>
+    <row r="117" ht="34" customHeight="1">
       <c r="A117" s="30" t="inlineStr"/>
       <c r="B117" s="31" t="inlineStr">
         <is>
@@ -3099,11 +3110,11 @@
       </c>
       <c r="C117" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Eagle's Nest return bus — book 4:00 or 4:15pm slot at the top counter IMMEDIATELY · slots fill fast in peak season · missing it = stranded at the top</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="23" customHeight="1">
+          <t>⛵ Königssee boat tips — ~€28–30 return to Salet per adult · book at seenschifffahrt.de 1 week before · dock is 10 min walk from car park · tip the captain €1–2 for the trumpet echo</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="31" customHeight="1">
       <c r="A118" s="30" t="inlineStr"/>
       <c r="B118" s="31" t="inlineStr">
         <is>
@@ -3112,132 +3123,110 @@
       </c>
       <c r="C118" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Eagle's Nest return bus — book 4:00 or 4:15pm slot at the top counter IMMEDIATELY · slots fill fast in peak season · missing it = stranded at the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="23" customHeight="1">
+      <c r="A119" s="30" t="inlineStr"/>
+      <c r="B119" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C119" s="32" t="inlineStr">
+        <is>
           <t>⛵ Königssee booking — book at seenschifffahrt.de · reserve ~1 week before Jun 25 · non-refundable</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="3" customHeight="1">
-      <c r="A119" s="33" t="n"/>
-      <c r="B119" s="33" t="n"/>
-      <c r="C119" s="33" t="n"/>
-      <c r="D119" s="33" t="n"/>
-      <c r="E119" s="33" t="n"/>
-      <c r="F119" s="33" t="n"/>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
+    <row r="120" ht="34" customHeight="1">
+      <c r="A120" s="30" t="inlineStr"/>
+      <c r="B120" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C120" s="32" t="inlineStr">
+        <is>
+          <t>Ramsau village — 10 min from Berchtesgaden — stone bridge over the fast-moving turquoise Ramsauer Ache river · Reiteralpe massif behind it · one of the most photographed spots in Bavaria · zero crowds at 7am · drive through on the way to Kö</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="3" customHeight="1">
+      <c r="A121" s="33" t="n"/>
+      <c r="B121" s="33" t="n"/>
+      <c r="C121" s="33" t="n"/>
+      <c r="D121" s="33" t="n"/>
+      <c r="E121" s="33" t="n"/>
+      <c r="F121" s="33" t="n"/>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>DAY 7  |  Jun 26  |  The Salzkammergut Sprint — Klamm · Salzburg · Wolfgangsee · Hallstatt  |  ~180 km / 112 mi  ~3h 30m incl. Salzburg parking</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:15am depart Berchtesgaden ▸ 9:00am Liechtensteinklamm ▸ 11am drive Salzburg ▸ 12pm P+R South + Altstadt ▸ Hohensalzburg Panorama Tour ▸ 3pm drive Wolfgangsee ▸ 4pm St. Gilgen→St. Wolfgang ferry ▸ 5:30pm Hallstatt golden hour ▸ 7:30pm Kaiserblick Goisern</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Liechtensteinklamm 9:00am sharp — be first at the gate · €16/adult · wear sturdy shoes  |  ✅ Salzburg: P+R South (Alpenstraße) €15 family combo — do NOT park in city centre · 2026 restricted zone  |  ⚠️ Hallstatt tunnel signs: if "Full" — go straight to Goisern · park Obertraun + ferry instead</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="47" customHeight="1">
-      <c r="A123" s="6" t="inlineStr"/>
-      <c r="B123" s="7" t="inlineStr">
+    <row r="125" ht="47" customHeight="1">
+      <c r="A125" s="6" t="inlineStr"/>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr"/>
-      <c r="E123" s="9" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr"/>
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:15am — Checkout Berchtesgaden + depart — drive 35 min south toward St. Johann im Pongau — Austrian motorway A10 · ✅ Austrian vignette must be active — you are on the A10 today</t>
         </is>
       </c>
-      <c r="F123" s="10" t="inlineStr">
+      <c r="F125" s="10" t="inlineStr">
         <is>
           <t>35 min</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="41" customHeight="1">
-      <c r="A124" s="16" t="inlineStr"/>
-      <c r="B124" s="17" t="inlineStr">
+    <row r="126" ht="41" customHeight="1">
+      <c r="A126" s="16" t="inlineStr"/>
+      <c r="B126" s="17" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C124" s="16" t="inlineStr">
+      <c r="C126" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D124" s="17" t="inlineStr"/>
-      <c r="E124" s="18" t="inlineStr">
+      <c r="D126" s="17" t="inlineStr"/>
+      <c r="E126" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 9:00am — Liechtensteinklamm Gorge — be there at opening (9:00am) — experience the helix staircase without crowds · thundering waterfalls + mist</t>
         </is>
       </c>
-      <c r="F124" s="19" t="inlineStr"/>
-    </row>
-    <row r="125" ht="50" customHeight="1">
-      <c r="A125" s="16" t="inlineStr"/>
-      <c r="B125" s="17" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D125" s="17" t="inlineStr"/>
-      <c r="E125" s="18" t="inlineStr">
-        <is>
-          <t>⭐ Sound of Music meadow — Gschwandtanger, Werfen — just off the B159 near Liechtensteinklamm · the exact meadow where the Do-Re-Mi picnic scene was filmed · jaw-dropping views of Hohenwerfen Castle + mountains · no crowd</t>
-        </is>
-      </c>
-      <c r="F125" s="19" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="50" customHeight="1">
-      <c r="A126" s="6" t="inlineStr"/>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr"/>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>11:00am — Drive north to Salzburg — ~1hr on A10 · arrive ~12:00pm · ⚠️ Do NOT park in the city centre — 2026 restricted traffic zone + construction everywhere · use P+R South (Alpenstraße) — €15 combo-ticket covers parki</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t>~1hr / €15</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
+      <c r="F126" s="19" t="inlineStr"/>
+    </row>
+    <row r="127" ht="50" customHeight="1">
       <c r="A127" s="16" t="inlineStr"/>
       <c r="B127" s="17" t="inlineStr">
         <is>
@@ -3252,60 +3241,60 @@
       <c r="D127" s="17" t="inlineStr"/>
       <c r="E127" s="18" t="inlineStr">
         <is>
+          <t>⭐ Sound of Music meadow — Gschwandtanger, Werfen — just off the B159 near Liechtensteinklamm · the exact meadow where the Do-Re-Mi picnic scene was filmed · jaw-dropping views of Hohenwerfen Castle + mountains · no crowd</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="50" customHeight="1">
+      <c r="A128" s="6" t="inlineStr"/>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr"/>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>11:00am — Drive north to Salzburg — ~1hr on A10 · arrive ~12:00pm · ⚠️ Do NOT park in the city centre — 2026 restricted traffic zone + construction everywhere · use P+R South (Alpenstraße) — €15 combo-ticket covers parki</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>~1hr / €15</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="16" t="inlineStr"/>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C129" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr"/>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
           <t>⭐ 12:00pm — Salzburg old town</t>
         </is>
       </c>
-      <c r="F127" s="19" t="inlineStr"/>
-    </row>
-    <row r="128" ht="38" customHeight="1">
-      <c r="A128" s="16" t="inlineStr"/>
-      <c r="B128" s="17" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C128" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D128" s="17" t="inlineStr"/>
-      <c r="E128" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 12:30pm — Hohensalzburg Fortress — funicular up from Kapitelplatz · stick to the Panorama Tour — ➕ Interior: €16/adult · allow 1hr</t>
-        </is>
-      </c>
-      <c r="F128" s="19" t="inlineStr">
-        <is>
-          <t>€16 / 1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="34" customHeight="1">
-      <c r="A129" s="6" t="inlineStr"/>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr"/>
-      <c r="E129" s="9" t="inlineStr">
-        <is>
-          <t>3:00pm — Drive east to Wolfgangsee — 45 min to St. Gilgen · arrive ~3:45pm · park in St. Gilgen village car park</t>
-        </is>
-      </c>
-      <c r="F129" s="10" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="39" customHeight="1">
+      <c r="F129" s="19" t="inlineStr"/>
+    </row>
+    <row r="130" ht="38" customHeight="1">
       <c r="A130" s="16" t="inlineStr"/>
       <c r="B130" s="17" t="inlineStr">
         <is>
@@ -3320,40 +3309,40 @@
       <c r="D130" s="17" t="inlineStr"/>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>⭐ 4:00pm — Wolfgangsee ferry: St. Gilgen → St. Wolfgang → back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
+          <t>⭐ 12:30pm — Hohensalzburg Fortress — funicular up from Kapitelplatz · stick to the Panorama Tour — ➕ Interior: €16/adult · allow 1hr</t>
         </is>
       </c>
       <c r="F130" s="19" t="inlineStr">
         <is>
-          <t>~20 min / 90 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="16" t="inlineStr"/>
-      <c r="B131" s="17" t="inlineStr">
+          <t>€16 / 1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="34" customHeight="1">
+      <c r="A131" s="6" t="inlineStr"/>
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D131" s="17" t="inlineStr"/>
-      <c r="E131" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
-        </is>
-      </c>
-      <c r="F131" s="19" t="inlineStr">
-        <is>
-          <t>2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="38" customHeight="1">
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr"/>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>3:00pm — Drive east to Wolfgangsee — 45 min to St. Gilgen · arrive ~3:45pm · park in St. Gilgen village car park</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="39" customHeight="1">
       <c r="A132" s="16" t="inlineStr"/>
       <c r="B132" s="17" t="inlineStr">
         <is>
@@ -3368,62 +3357,84 @@
       <c r="D132" s="17" t="inlineStr"/>
       <c r="E132" s="18" t="inlineStr">
         <is>
+          <t>⭐ 4:00pm — Wolfgangsee ferry: St. Gilgen → St. Wolfgang → back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
+        </is>
+      </c>
+      <c r="F132" s="19" t="inlineStr">
+        <is>
+          <t>~20 min / 90 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="16" t="inlineStr"/>
+      <c r="B133" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C133" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D133" s="17" t="inlineStr"/>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
+        </is>
+      </c>
+      <c r="F133" s="19" t="inlineStr">
+        <is>
+          <t>2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="38" customHeight="1">
+      <c r="A134" s="16" t="inlineStr"/>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C134" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr"/>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
           <t>⚠️ Hallstatt 2026 camera parking system — alternative: park at Obertraun (5 min drive) + take the ferry to Hallstatt (€4 · 10 min)</t>
         </is>
       </c>
-      <c r="F132" s="19" t="inlineStr">
+      <c r="F134" s="19" t="inlineStr">
         <is>
           <t>5 min / €4 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="6" t="inlineStr"/>
-      <c r="B133" s="7" t="inlineStr">
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="6" t="inlineStr"/>
+      <c r="B135" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="C135" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr"/>
-      <c r="E133" s="9" t="inlineStr">
+      <c r="D135" s="7" t="inlineStr"/>
+      <c r="E135" s="9" t="inlineStr">
         <is>
           <t>7:30pm — Kaiserblick Goisern, Bad Goisern — 15 min drive from Hallstatt · $333</t>
         </is>
       </c>
-      <c r="F133" s="10" t="inlineStr">
+      <c r="F135" s="10" t="inlineStr">
         <is>
           <t>15 min / $333</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="34" customHeight="1">
-      <c r="A134" s="30" t="inlineStr"/>
-      <c r="B134" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C134" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Salzburg parking 2026 — Old Town becoming restricted traffic zone · construction barriers everywhere · use P+R South (Alpenstraße) · €15 combo = parking + shuttle bus for whole family · much faster than city garage hunting</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="34" customHeight="1">
-      <c r="A135" s="30" t="inlineStr"/>
-      <c r="B135" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C135" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Hallstatt 2026 camera system — electronic signs at tunnel entrance · if "Full": do not enter · drive straight to Kaiserblick Goisern · return via ferry from Obertraun (€4 · 10 min) or bus on Day 8</t>
         </is>
       </c>
     </row>
@@ -3436,136 +3447,114 @@
       </c>
       <c r="C136" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Salzburg parking 2026 — Old Town becoming restricted traffic zone · construction barriers everywhere · use P+R South (Alpenstraße) · €15 combo = parking + shuttle bus for whole family · much faster than city garage hunting</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="34" customHeight="1">
+      <c r="A137" s="30" t="inlineStr"/>
+      <c r="B137" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C137" s="32" t="inlineStr">
+        <is>
+          <t>⚠️ Hallstatt 2026 camera system — electronic signs at tunnel entrance · if "Full": do not enter · drive straight to Kaiserblick Goisern · return via ferry from Obertraun (€4 · 10 min) or bus on Day 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="34" customHeight="1">
+      <c r="A138" s="30" t="inlineStr"/>
+      <c r="B138" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C138" s="32" t="inlineStr">
+        <is>
           <t>☕ Hohensalzburg tip — stick to Panorama Tour only (courtyards + bastions) · skip the individual museums to stay on schedule · the view is the reason to go up · allow 1hr max</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="3" customHeight="1">
-      <c r="A137" s="33" t="n"/>
-      <c r="B137" s="33" t="n"/>
-      <c r="C137" s="33" t="n"/>
-      <c r="D137" s="33" t="n"/>
-      <c r="E137" s="33" t="n"/>
-      <c r="F137" s="33" t="n"/>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="3" t="inlineStr">
+    <row r="139" ht="3" customHeight="1">
+      <c r="A139" s="33" t="n"/>
+      <c r="B139" s="33" t="n"/>
+      <c r="C139" s="33" t="n"/>
+      <c r="D139" s="33" t="n"/>
+      <c r="E139" s="33" t="n"/>
+      <c r="F139" s="33" t="n"/>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>DAY 8  |  Jun 27  |  Dachstein Krippenstein · Gosausee · Hallstatt Evening — The High-Alpine Day  |  ~40 km / 25 mi  ~1h total · very local day</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:15am depart Bad Goisern ▸ 8:45am Krippenstein cable car ▸ 9:30am 5 Fingers viewpoint ▸ Ice Cave optional ▸ 1:30pm Gosausee Mirror Lake ▸ 2:00pm Gosaukammbahn ▸ 4:30pm Hallstatt golden hour + dinner ▸ Beinhaus ▸ ~7pm Kaiserblick Goisern</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Key: Salt Mine + Skywalk CLOSED Jun 27 — reopens Jun 30 · do not book these  |  ✅ Dachstein Krippenstein 8:45am → 5 Fingers → Gosausee 1:30pm → Gosaukammbahn → Hallstatt 4:30pm  |  ⚠️ Saturday = busy Hallstatt · check digital signs · if Full → park Obertraun + NAVIA ferry €4</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="50" customHeight="1">
-      <c r="A141" s="34" t="inlineStr"/>
-      <c r="B141" s="35" t="inlineStr">
+    <row r="143" ht="50" customHeight="1">
+      <c r="A143" s="34" t="inlineStr"/>
+      <c r="B143" s="35" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C141" s="36" t="inlineStr">
+      <c r="C143" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D141" s="35" t="inlineStr"/>
-      <c r="E141" s="37" t="inlineStr">
+      <c r="D143" s="35" t="inlineStr"/>
+      <c r="E143" s="37" t="inlineStr">
         <is>
           <t>2026 Alert: Hallstatt Salt Mine + Skywalk CLOSED Jun 27 — major renovation underway · scheduled to reopen June 30, 2026 · do not attempt to book these for today · alternative: Salzwelten Altaussee — (25 min from Bad Gois</t>
         </is>
       </c>
-      <c r="F141" s="38" t="inlineStr">
+      <c r="F143" s="38" t="inlineStr">
         <is>
           <t>25 min</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="41" customHeight="1">
-      <c r="A142" s="6" t="inlineStr"/>
-      <c r="B142" s="7" t="inlineStr">
+    <row r="144" ht="41" customHeight="1">
+      <c r="A144" s="6" t="inlineStr"/>
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C142" s="8" t="inlineStr">
+      <c r="C144" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr"/>
-      <c r="E142" s="9" t="inlineStr">
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:15am — Depart Bad Goisern — 20 min drive to Obertraun · arrive by 8:40am · park at the Dachstein Krippenstein cable car base station in Obertraun</t>
         </is>
       </c>
-      <c r="F142" s="10" t="inlineStr">
+      <c r="F144" s="10" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="30" customHeight="1">
-      <c r="A143" s="16" t="inlineStr"/>
-      <c r="B143" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C143" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D143" s="17" t="inlineStr"/>
-      <c r="E143" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · €44.90/adult</t>
-        </is>
-      </c>
-      <c r="F143" s="19" t="inlineStr">
-        <is>
-          <t>€44.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="16" t="inlineStr"/>
-      <c r="B144" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C144" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D144" s="17" t="inlineStr"/>
-      <c r="E144" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
-        </is>
-      </c>
-      <c r="F144" s="19" t="inlineStr">
-        <is>
-          <t>20 min / 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="32" customHeight="1">
+    <row r="145" ht="30" customHeight="1">
       <c r="A145" s="16" t="inlineStr"/>
       <c r="B145" s="17" t="inlineStr">
         <is>
@@ -3580,40 +3569,40 @@
       <c r="D145" s="17" t="inlineStr"/>
       <c r="E145" s="18" t="inlineStr">
         <is>
-          <t>➕ Optional: Giant Ice Cave (Section 1) — accessible from Section 1 midstation · extra cost ~€10/adult</t>
+          <t>⭐ ⭐ 8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · €44.90/adult</t>
         </is>
       </c>
       <c r="F145" s="19" t="inlineStr">
         <is>
-          <t>€10</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="30" customHeight="1">
-      <c r="A146" s="6" t="inlineStr"/>
-      <c r="B146" s="7" t="inlineStr">
+          <t>€44.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="32" customHeight="1">
+      <c r="A146" s="16" t="inlineStr"/>
+      <c r="B146" s="17" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D146" s="7" t="inlineStr"/>
-      <c r="E146" s="9" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 1:30pm — Vorderer Gosausee — the Mirror Lake — 25 min drive from Obertraun · allow 30 min</t>
-        </is>
-      </c>
-      <c r="F146" s="10" t="inlineStr">
-        <is>
-          <t>25 min / 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="33" customHeight="1">
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr"/>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
+        </is>
+      </c>
+      <c r="F146" s="19" t="inlineStr">
+        <is>
+          <t>20 min / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="32" customHeight="1">
       <c r="A147" s="16" t="inlineStr"/>
       <c r="B147" s="17" t="inlineStr">
         <is>
@@ -3628,40 +3617,40 @@
       <c r="D147" s="17" t="inlineStr"/>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>⭐ 2:00pm — Gosaukammbahn cable car — ~€28 return/adult · panoramic view of the Dachstein glacier from above</t>
+          <t>➕ Optional: Giant Ice Cave (Section 1) — accessible from Section 1 midstation · extra cost ~€10/adult</t>
         </is>
       </c>
       <c r="F147" s="19" t="inlineStr">
         <is>
-          <t>€28</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="31" customHeight="1">
-      <c r="A148" s="16" t="inlineStr"/>
-      <c r="B148" s="17" t="inlineStr">
+          <t>€10</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="6" t="inlineStr"/>
+      <c r="B148" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C148" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D148" s="17" t="inlineStr"/>
-      <c r="E148" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 4:30pm — Hallstatt village evening — mine renovation crowds have gone by now · allow 1.5hrs</t>
-        </is>
-      </c>
-      <c r="F148" s="19" t="inlineStr">
-        <is>
-          <t>5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="38" customHeight="1">
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr"/>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 1:30pm — Vorderer Gosausee — the Mirror Lake — 25 min drive from Obertraun · allow 30 min</t>
+        </is>
+      </c>
+      <c r="F148" s="10" t="inlineStr">
+        <is>
+          <t>25 min / 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="33" customHeight="1">
       <c r="A149" s="16" t="inlineStr"/>
       <c r="B149" s="17" t="inlineStr">
         <is>
@@ -3676,16 +3665,16 @@
       <c r="D149" s="17" t="inlineStr"/>
       <c r="E149" s="18" t="inlineStr">
         <is>
-          <t>⚠️ Saturday parking warning — if P1/P2 show "Full": park in Obertraun (5 min drive) + take the ferry across · NAVIA ferry: €4 cash</t>
+          <t>⭐ 2:00pm — Gosaukammbahn cable car — ~€28 return/adult · panoramic view of the Dachstein glacier from above</t>
         </is>
       </c>
       <c r="F149" s="19" t="inlineStr">
         <is>
-          <t>5 min / €4</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="21" customHeight="1">
+          <t>€28</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="31" customHeight="1">
       <c r="A150" s="16" t="inlineStr"/>
       <c r="B150" s="17" t="inlineStr">
         <is>
@@ -3700,66 +3689,88 @@
       <c r="D150" s="17" t="inlineStr"/>
       <c r="E150" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 4:30pm — Hallstatt village evening — mine renovation crowds have gone by now · allow 1.5hrs</t>
+        </is>
+      </c>
+      <c r="F150" s="19" t="inlineStr">
+        <is>
+          <t>5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="38" customHeight="1">
+      <c r="A151" s="16" t="inlineStr"/>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr"/>
+      <c r="E151" s="18" t="inlineStr">
+        <is>
+          <t>⚠️ Saturday parking warning — if P1/P2 show "Full": park in Obertraun (5 min drive) + take the ferry across · NAVIA ferry: €4 cash</t>
+        </is>
+      </c>
+      <c r="F151" s="19" t="inlineStr">
+        <is>
+          <t>5 min / €4</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="21" customHeight="1">
+      <c r="A152" s="16" t="inlineStr"/>
+      <c r="B152" s="17" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D152" s="17" t="inlineStr"/>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
           <t>⭐ Beinhaus (Bone Chapel) — €1.50/adult · 10 min</t>
         </is>
       </c>
-      <c r="F150" s="19" t="inlineStr">
+      <c r="F152" s="19" t="inlineStr">
         <is>
           <t>€1.50 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="37" customHeight="1">
-      <c r="A151" s="6" t="inlineStr"/>
-      <c r="B151" s="7" t="inlineStr">
+    <row r="153" ht="37" customHeight="1">
+      <c r="A153" s="6" t="inlineStr"/>
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C151" s="8" t="inlineStr">
+      <c r="C153" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D151" s="7" t="inlineStr"/>
-      <c r="E151" s="9" t="inlineStr">
+      <c r="D153" s="7" t="inlineStr"/>
+      <c r="E153" s="9" t="inlineStr">
         <is>
           <t>Night 2 — Kaiserblick Goisern — ✅ Already checked in ·  38 Unterjoch, 4822 Bad Goisern, Austria · 15 min drive from Hallstatt</t>
         </is>
       </c>
-      <c r="F151" s="10" t="inlineStr">
+      <c r="F153" s="10" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="34" customHeight="1">
-      <c r="A152" s="30" t="inlineStr"/>
-      <c r="B152" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C152" s="32" t="inlineStr">
-        <is>
-          <t>Salt Mine + Skywalk CLOSED Jun 27 — major renovation · reopens Jun 30, 2026 · alternative: Salzwelten Altaussee (25 min from Bad Goisern) · active mine · most authentic</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="34" customHeight="1">
-      <c r="A153" s="30" t="inlineStr"/>
-      <c r="B153" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C153" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ 5 Fingers vs Skywalk — 5 Fingers on Krippenstein is higher, more dramatic, free with cable car ticket · direct aerial view down into Hallstatt village · Skywalk is closed anyway — 5 Fingers is the better experience</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="33" customHeight="1">
+    <row r="154" ht="34" customHeight="1">
       <c r="A154" s="30" t="inlineStr"/>
       <c r="B154" s="31" t="inlineStr">
         <is>
@@ -3768,7 +3779,7 @@
       </c>
       <c r="C154" s="32" t="inlineStr">
         <is>
-          <t>Gosausee afternoon tip — best photos happen when the sun hits the Dachstein glacier face-on in the afternoon · go at 3pm not morning for the mirror reflection shot</t>
+          <t>Salt Mine + Skywalk CLOSED Jun 27 — major renovation · reopens Jun 30, 2026 · alternative: Salzwelten Altaussee (25 min from Bad Goisern) · active mine · most authentic</t>
         </is>
       </c>
     </row>
@@ -3781,136 +3792,114 @@
       </c>
       <c r="C155" s="32" t="inlineStr">
         <is>
+          <t>⚠️ 5 Fingers vs Skywalk — 5 Fingers on Krippenstein is higher, more dramatic, free with cable car ticket · direct aerial view down into Hallstatt village · Skywalk is closed anyway — 5 Fingers is the better experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="33" customHeight="1">
+      <c r="A156" s="30" t="inlineStr"/>
+      <c r="B156" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C156" s="32" t="inlineStr">
+        <is>
+          <t>Gosausee afternoon tip — best photos happen when the sun hits the Dachstein glacier face-on in the afternoon · go at 3pm not morning for the mirror reflection shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="34" customHeight="1">
+      <c r="A157" s="30" t="inlineStr"/>
+      <c r="B157" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C157" s="32" t="inlineStr">
+        <is>
           <t>Hofer (Aldi) Bad Goisern — stock up this morning or evening · discount prices · buy for Jun 27–Jul 1: Grossglockner · Sillian · Dolomites 3 nights · Hofrat-Renner-Weg 1 · open Tue 7:15am</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="3" customHeight="1">
-      <c r="A156" s="33" t="n"/>
-      <c r="B156" s="33" t="n"/>
-      <c r="C156" s="33" t="n"/>
-      <c r="D156" s="33" t="n"/>
-      <c r="E156" s="33" t="n"/>
-      <c r="F156" s="33" t="n"/>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="3" t="inlineStr">
+    <row r="158" ht="3" customHeight="1">
+      <c r="A158" s="33" t="n"/>
+      <c r="B158" s="33" t="n"/>
+      <c r="C158" s="33" t="n"/>
+      <c r="D158" s="33" t="n"/>
+      <c r="E158" s="33" t="n"/>
+      <c r="F158" s="33" t="n"/>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>DAY 9  |  Jun 28  |  The Roof of Austria — Grossglockner High Alpine Road → Sillian  |  ~280 km / 174 mi  ~4h 30m incl. Grossglockner slow drive</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
+    <row r="160" ht="15" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:00am checkout ▸ 9:30am Ferleiten toll €46.50 ▸ 10:15am Edelweiß-Spitze ▸ 11:30am Hochtor tunnel ▸ 12:15pm KFJ-Höhe + marmots ▸ 1:30pm glacier lunch ▸ 3:30pm Heiligenblut church photo ▸ 5:30pm Sillian ▸ alarm 5am</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Edelweiß-Spitze FIRST — go before motorcycles arrive · dead-end road congests by afternoon  |  ✅ Gamsgrubenweg 10 min from KFJ-Höhe — best marmot spotting on the road · kids will love it  |  ⚠️ Descent: engine brake in low gear · do NOT ride the brakes · they will overheat</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="43" customHeight="1">
-      <c r="A160" s="6" t="inlineStr"/>
-      <c r="B160" s="7" t="inlineStr">
+    <row r="162" ht="43" customHeight="1">
+      <c r="A162" s="6" t="inlineStr"/>
+      <c r="B162" s="7" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C160" s="8" t="inlineStr">
+      <c r="C162" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D160" s="7" t="inlineStr"/>
-      <c r="E160" s="9" t="inlineStr">
+      <c r="D162" s="7" t="inlineStr"/>
+      <c r="E162" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:00am — Checkout Kaiserblick Goisern — 1.5hr drive to the Ferleiten toll gate via the B311 · download offline maps for the Dolomites tonight if not done yet</t>
         </is>
       </c>
-      <c r="F160" s="10" t="inlineStr">
+      <c r="F162" s="10" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="46" customHeight="1">
-      <c r="A161" s="16" t="inlineStr"/>
-      <c r="B161" s="17" t="inlineStr">
+    <row r="163" ht="46" customHeight="1">
+      <c r="A163" s="16" t="inlineStr"/>
+      <c r="B163" s="17" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C161" s="16" t="inlineStr">
+      <c r="C163" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D161" s="17" t="inlineStr"/>
-      <c r="E161" s="18" t="inlineStr">
+      <c r="D163" s="17" t="inlineStr"/>
+      <c r="E163" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ Grossglockner High Alpine Road — 48km of switchbacks across the highest surfaced alpine pass in Austria · road open from 5:30am — last entry 45 min before 9pm closing</t>
         </is>
       </c>
-      <c r="F161" s="19" t="inlineStr">
+      <c r="F163" s="19" t="inlineStr">
         <is>
           <t>48km / 45 min</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="38" customHeight="1">
-      <c r="A162" s="16" t="inlineStr"/>
-      <c r="B162" s="17" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C162" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D162" s="17" t="inlineStr"/>
-      <c r="E162" s="18" t="inlineStr">
-        <is>
-          <t>9:30am — Ferleiten Toll Gate — 2026 rate: €46.50/car — first stop: Edelweiß-Spitze — go there FIRST before the motorcycles arrive</t>
-        </is>
-      </c>
-      <c r="F162" s="19" t="inlineStr">
-        <is>
-          <t>€46.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="34" customHeight="1">
-      <c r="A163" s="20" t="inlineStr"/>
-      <c r="B163" s="21" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C163" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D163" s="21" t="inlineStr"/>
-      <c r="E163" s="23" t="inlineStr">
-        <is>
-          <t>Haus Alpine Naturschau — natural history museum — 15 min · great context for the kids before reaching the summit</t>
-        </is>
-      </c>
-      <c r="F163" s="24" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="32" customHeight="1">
+    <row r="164" ht="38" customHeight="1">
       <c r="A164" s="16" t="inlineStr"/>
       <c r="B164" s="17" t="inlineStr">
         <is>
@@ -3925,60 +3914,60 @@
       <c r="D164" s="17" t="inlineStr"/>
       <c r="E164" s="18" t="inlineStr">
         <is>
+          <t>9:30am — Ferleiten Toll Gate — 2026 rate: €46.50/car — first stop: Edelweiß-Spitze — go there FIRST before the motorcycles arrive</t>
+        </is>
+      </c>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>€46.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="34" customHeight="1">
+      <c r="A165" s="20" t="inlineStr"/>
+      <c r="B165" s="21" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C165" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D165" s="21" t="inlineStr"/>
+      <c r="E165" s="23" t="inlineStr">
+        <is>
+          <t>Haus Alpine Naturschau — natural history museum — 15 min · great context for the kids before reaching the summit</t>
+        </is>
+      </c>
+      <c r="F165" s="24" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="16" t="inlineStr"/>
+      <c r="B166" s="17" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D166" s="17" t="inlineStr"/>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 10:15am — Edelweiß-Spitze (2,571m) — MUST STOP · dead-end cobblestone branch road — go here FIRST</t>
         </is>
       </c>
-      <c r="F164" s="19" t="inlineStr"/>
-    </row>
-    <row r="165" ht="21" customHeight="1">
-      <c r="A165" s="16" t="inlineStr"/>
-      <c r="B165" s="17" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D165" s="17" t="inlineStr"/>
-      <c r="E165" s="18" t="inlineStr">
-        <is>
-          <t>11:30am — Hochtor Tunnel (2,504m) — 10 min stop</t>
-        </is>
-      </c>
-      <c r="F165" s="19" t="inlineStr">
-        <is>
-          <t>10 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="50" customHeight="1">
-      <c r="A166" s="20" t="inlineStr"/>
-      <c r="B166" s="21" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C166" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D166" s="21" t="inlineStr"/>
-      <c r="E166" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⭐ ⭐ 12:15pm — Kaiser-Franz-Josefs-Höhe (2,369m) — Austria's longest glacier (8km) stretching toward the Grossglockner · ⚠️ 2026: glacier has receded significantly — to touch the ice take the Gletscherbahn funicular down </t>
-        </is>
-      </c>
-      <c r="F166" s="24" t="inlineStr">
-        <is>
-          <t>8km / 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="36" customHeight="1">
+      <c r="F166" s="19" t="inlineStr"/>
+    </row>
+    <row r="167" ht="21" customHeight="1">
       <c r="A167" s="16" t="inlineStr"/>
       <c r="B167" s="17" t="inlineStr">
         <is>
@@ -3993,178 +3982,200 @@
       <c r="D167" s="17" t="inlineStr"/>
       <c r="E167" s="18" t="inlineStr">
         <is>
+          <t>11:30am — Hochtor Tunnel (2,504m) — 10 min stop</t>
+        </is>
+      </c>
+      <c r="F167" s="19" t="inlineStr">
+        <is>
+          <t>10 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="50" customHeight="1">
+      <c r="A168" s="20" t="inlineStr"/>
+      <c r="B168" s="21" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C168" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D168" s="21" t="inlineStr"/>
+      <c r="E168" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⭐ ⭐ 12:15pm — Kaiser-Franz-Josefs-Höhe (2,369m) — Austria's longest glacier (8km) stretching toward the Grossglockner · ⚠️ 2026: glacier has receded significantly — to touch the ice take the Gletscherbahn funicular down </t>
+        </is>
+      </c>
+      <c r="F168" s="24" t="inlineStr">
+        <is>
+          <t>8km / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="36" customHeight="1">
+      <c r="A169" s="16" t="inlineStr"/>
+      <c r="B169" s="17" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D169" s="17" t="inlineStr"/>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
           <t>Marmot &amp; ibex spotting — Gamsgrubenweg — from Kaiser-Franz-Josefs-Höhe: follow the Gamsgrubenweg tunnel path for 10 min</t>
         </is>
       </c>
-      <c r="F167" s="19" t="inlineStr">
+      <c r="F169" s="19" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="31" customHeight="1">
-      <c r="A168" s="11" t="inlineStr"/>
-      <c r="B168" s="12" t="inlineStr">
+    <row r="170" ht="31" customHeight="1">
+      <c r="A170" s="11" t="inlineStr"/>
+      <c r="B170" s="12" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C168" s="13" t="inlineStr">
+      <c r="C170" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D168" s="12" t="inlineStr"/>
-      <c r="E168" s="14" t="inlineStr">
+      <c r="D170" s="12" t="inlineStr"/>
+      <c r="E170" s="14" t="inlineStr">
         <is>
           <t>1:30pm — Lunch at Kaiser-Franz-Josefs-Höhe — panoramic terrace facing the glacier · allow 1hr</t>
         </is>
       </c>
-      <c r="F168" s="15" t="inlineStr">
+      <c r="F170" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="21" customHeight="1">
-      <c r="A169" s="20" t="inlineStr"/>
-      <c r="B169" s="21" t="inlineStr">
+    <row r="171" ht="21" customHeight="1">
+      <c r="A171" s="20" t="inlineStr"/>
+      <c r="B171" s="21" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C169" s="22" t="inlineStr">
+      <c r="C171" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D169" s="21" t="inlineStr"/>
-      <c r="E169" s="23" t="inlineStr">
+      <c r="D171" s="21" t="inlineStr"/>
+      <c r="E171" s="23" t="inlineStr">
         <is>
           <t>⚠️ Descent toward Heiligenblut — brake warning</t>
         </is>
       </c>
-      <c r="F169" s="24" t="inlineStr"/>
-    </row>
-    <row r="170" ht="21" customHeight="1">
-      <c r="A170" s="16" t="inlineStr"/>
-      <c r="B170" s="17" t="inlineStr">
+      <c r="F171" s="24" t="inlineStr"/>
+    </row>
+    <row r="172" ht="21" customHeight="1">
+      <c r="A172" s="16" t="inlineStr"/>
+      <c r="B172" s="17" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C170" s="16" t="inlineStr">
+      <c r="C172" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D170" s="17" t="inlineStr"/>
-      <c r="E170" s="18" t="inlineStr">
+      <c r="D172" s="17" t="inlineStr"/>
+      <c r="E172" s="18" t="inlineStr">
         <is>
           <t>⭐ 3:30pm — Heiligenblut village — allow 30 min</t>
         </is>
       </c>
-      <c r="F170" s="19" t="inlineStr">
+      <c r="F172" s="19" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="50" customHeight="1">
-      <c r="A171" s="16" t="inlineStr"/>
-      <c r="B171" s="17" t="inlineStr">
+    <row r="173" ht="50" customHeight="1">
+      <c r="A173" s="16" t="inlineStr"/>
+      <c r="B173" s="17" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C171" s="16" t="inlineStr">
+      <c r="C173" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D171" s="17" t="inlineStr"/>
-      <c r="E171" s="18" t="inlineStr">
+      <c r="D173" s="17" t="inlineStr"/>
+      <c r="E173" s="18" t="inlineStr">
         <is>
           <t>Gößnitzfall waterfall — Heiligenblut — right outside the village · easy 20 min walk through shaded forest to dramatic wooden viewing platform · thunderous alpine waterfall · stroller-friendly · free · perfect for shaking</t>
         </is>
       </c>
-      <c r="F171" s="19" t="inlineStr">
+      <c r="F173" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="23" customHeight="1">
-      <c r="A172" s="25" t="inlineStr"/>
-      <c r="B172" s="26" t="inlineStr">
+    <row r="174" ht="23" customHeight="1">
+      <c r="A174" s="25" t="inlineStr"/>
+      <c r="B174" s="26" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C172" s="27" t="inlineStr">
+      <c r="C174" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D172" s="26" t="inlineStr"/>
-      <c r="E172" s="28" t="inlineStr">
+      <c r="D174" s="26" t="inlineStr"/>
+      <c r="E174" s="28" t="inlineStr">
         <is>
           <t>5:30pm — Hotel Schwarzer Adler, Sillian — $115 / €99.40</t>
         </is>
       </c>
-      <c r="F172" s="29" t="inlineStr">
+      <c r="F174" s="29" t="inlineStr">
         <is>
           <t>$115 / €99.40</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="40" customHeight="1">
-      <c r="A173" s="11" t="inlineStr"/>
-      <c r="B173" s="12" t="inlineStr">
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="11" t="inlineStr"/>
+      <c r="B175" s="12" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C173" s="13" t="inlineStr">
+      <c r="C175" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D173" s="12" t="inlineStr"/>
-      <c r="E173" s="14" t="inlineStr">
+      <c r="D175" s="12" t="inlineStr"/>
+      <c r="E175" s="14" t="inlineStr">
         <is>
           <t>Dinner in Sillian —  Download offline Dolomites maps tonight (Maps.me or Google Maps) · check Rifugio Auronzo parking booking confirmation</t>
         </is>
       </c>
-      <c r="F173" s="15" t="inlineStr"/>
-    </row>
-    <row r="174" ht="34" customHeight="1">
-      <c r="A174" s="30" t="inlineStr"/>
-      <c r="B174" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C174" s="32" t="inlineStr">
-        <is>
-          <t>Grossglockner toll 2026: €46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="34" customHeight="1">
-      <c r="A175" s="30" t="inlineStr"/>
-      <c r="B175" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C175" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="33" customHeight="1">
+      <c r="F175" s="15" t="inlineStr"/>
+    </row>
+    <row r="176" ht="34" customHeight="1">
       <c r="A176" s="30" t="inlineStr"/>
       <c r="B176" s="31" t="inlineStr">
         <is>
@@ -4173,7 +4184,7 @@
       </c>
       <c r="C176" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
+          <t>Grossglockner toll 2026: €46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
         </is>
       </c>
     </row>
@@ -4186,11 +4197,11 @@
       </c>
       <c r="C177" s="32" t="inlineStr">
         <is>
-          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="34" customHeight="1">
+          <t>⚠️ Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="33" customHeight="1">
       <c r="A178" s="30" t="inlineStr"/>
       <c r="B178" s="31" t="inlineStr">
         <is>
@@ -4199,88 +4210,66 @@
       </c>
       <c r="C178" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="34" customHeight="1">
+      <c r="A179" s="30" t="inlineStr"/>
+      <c r="B179" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C179" s="32" t="inlineStr">
+        <is>
+          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="34" customHeight="1">
+      <c r="A180" s="30" t="inlineStr"/>
+      <c r="B180" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C180" s="32" t="inlineStr">
+        <is>
           <t>Tonight: prep for Dolomites — download offline maps (Google Maps or Maps.me) for the Dolomites · confirm Rifugio Auronzo parking booking · 5am alarm tomorrow · Braies gate opens 7:30am</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="3" customHeight="1">
-      <c r="A179" s="33" t="n"/>
-      <c r="B179" s="33" t="n"/>
-      <c r="C179" s="33" t="n"/>
-      <c r="D179" s="33" t="n"/>
-      <c r="E179" s="33" t="n"/>
-      <c r="F179" s="33" t="n"/>
-    </row>
-    <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="3" t="inlineStr">
+    <row r="181" ht="3" customHeight="1">
+      <c r="A181" s="33" t="n"/>
+      <c r="B181" s="33" t="n"/>
+      <c r="C181" s="33" t="n"/>
+      <c r="D181" s="33" t="n"/>
+      <c r="E181" s="33" t="n"/>
+      <c r="F181" s="33" t="n"/>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>DAY 10  |  Jun 29  |  The Iconic Dolomites — Braies Sunrise · Tre Cime · Prato Piazza · Gardena  |  ~200 km / 124 mi  ~5h total driving · many short hops</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="183" ht="15" customHeight="1">
+      <c r="A183" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Sillian ▸ 8:45am Braies P3 ▸ 10:15am depart ▸ Misurina coffee ▸ 11:15am Auronzo gate ▸ 11:45am Cadini Trail 117 ▸ 1:30pm lunch ▸ 2:30pm Tre Cime walk ▸ 3:45pm Gardena Pass ▸ 5pm Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="5" t="inlineStr">
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ 8am departure — relaxed start · Braies 8:45am · still beautiful · P3 no reservation  |  ❌ Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |  ✅ Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |  ⚠️ Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |  ⚠️ Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="48" customHeight="1">
-      <c r="A183" s="6" t="inlineStr"/>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C183" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D183" s="7" t="inlineStr"/>
-      <c r="E183" s="9" t="inlineStr">
-        <is>
-          <t>8:00am — Depart Sillian — 45 min straight across the Italian border · download offline Dolomites maps tonight if not done · update Auronzo plate at pass.auronzo.info tonight (Jun 28)</t>
-        </is>
-      </c>
-      <c r="F183" s="10" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="49" customHeight="1">
-      <c r="A184" s="16" t="inlineStr"/>
-      <c r="B184" s="17" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C184" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D184" s="17" t="inlineStr"/>
-      <c r="E184" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 · no reservation needed · walk the best half of the lakeside circuit · famous stilt boathouse · morning views · allow 1.5hrs · leave by 10:15am</t>
-        </is>
-      </c>
-      <c r="F184" s="19" t="inlineStr">
-        <is>
-          <t>€12 / 5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="44" customHeight="1">
+    <row r="185" ht="48" customHeight="1">
       <c r="A185" s="6" t="inlineStr"/>
       <c r="B185" s="7" t="inlineStr">
         <is>
@@ -4295,180 +4284,202 @@
       <c r="D185" s="7" t="inlineStr"/>
       <c r="E185" s="9" t="inlineStr">
         <is>
+          <t>8:00am — Depart Sillian — 45 min straight across the Italian border · download offline Dolomites maps tonight if not done · update Auronzo plate at pass.auronzo.info tonight (Jun 28)</t>
+        </is>
+      </c>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="49" customHeight="1">
+      <c r="A186" s="16" t="inlineStr"/>
+      <c r="B186" s="17" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C186" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D186" s="17" t="inlineStr"/>
+      <c r="E186" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 · no reservation needed · walk the best half of the lakeside circuit · famous stilt boathouse · morning views · allow 1.5hrs · leave by 10:15am</t>
+        </is>
+      </c>
+      <c r="F186" s="19" t="inlineStr">
+        <is>
+          <t>€12 / 5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="44" customHeight="1">
+      <c r="A187" s="6" t="inlineStr"/>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr"/>
+      <c r="E187" s="9" t="inlineStr">
+        <is>
           <t>☕ 10:15am — Drive via Lago di Misurina — 1hr drive down the valley · stop at Rifugio Misurina café · 15 min coffee + mirror-reflection photo of Tre Cime in the lake</t>
         </is>
       </c>
-      <c r="F185" s="10" t="inlineStr">
+      <c r="F187" s="10" t="inlineStr">
         <is>
           <t>1hr / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="45" customHeight="1">
-      <c r="A186" s="6" t="inlineStr"/>
-      <c r="B186" s="7" t="inlineStr">
+    <row r="188" ht="45" customHeight="1">
+      <c r="A188" s="6" t="inlineStr"/>
+      <c r="B188" s="7" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C186" s="8" t="inlineStr">
+      <c r="C188" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D186" s="7" t="inlineStr"/>
-      <c r="E186" s="9" t="inlineStr">
+      <c r="D188" s="7" t="inlineStr"/>
+      <c r="E188" s="9" t="inlineStr">
         <is>
           <t>⚠️ 11:15am — Auronzo gate — ✅ Pre-booked · PASS3CIME_26017885 · Ticket P26134547 · 9am–8:59pm slot · plate reads automatically · drive straight up · €40 paid · no queue</t>
         </is>
       </c>
-      <c r="F186" s="10" t="inlineStr">
+      <c r="F188" s="10" t="inlineStr">
         <is>
           <t>€40</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="50" customHeight="1">
-      <c r="A187" s="20" t="inlineStr"/>
-      <c r="B187" s="21" t="inlineStr">
+    <row r="189" ht="50" customHeight="1">
+      <c r="A189" s="20" t="inlineStr"/>
+      <c r="B189" s="21" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C187" s="22" t="inlineStr">
+      <c r="C189" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D187" s="21" t="inlineStr"/>
-      <c r="E187" s="23" t="inlineStr">
+      <c r="D189" s="21" t="inlineStr"/>
+      <c r="E189" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⭐ ⭐ 11:45am — Cadini di Misurina Trail 117 — hike out to the iconic jagged peak viewpoint · 45 min RT at normal pace · ⚠️ final 50m is a narrow ridge · secondary viewpoint 20m back is 95% as good · allow 1hr 45min total </t>
         </is>
       </c>
-      <c r="F187" s="24" t="inlineStr">
+      <c r="F189" s="24" t="inlineStr">
         <is>
           <t>45 min / 1hr / 45min</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="29" customHeight="1">
-      <c r="A188" s="11" t="inlineStr"/>
-      <c r="B188" s="12" t="inlineStr">
+    <row r="190" ht="29" customHeight="1">
+      <c r="A190" s="11" t="inlineStr"/>
+      <c r="B190" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C188" s="13" t="inlineStr">
+      <c r="C190" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D188" s="12" t="inlineStr"/>
-      <c r="E188" s="14" t="inlineStr">
+      <c r="D190" s="12" t="inlineStr"/>
+      <c r="E190" s="14" t="inlineStr">
         <is>
           <t>1:30pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr</t>
         </is>
       </c>
-      <c r="F188" s="15" t="inlineStr">
+      <c r="F190" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="40" customHeight="1">
-      <c r="A189" s="11" t="inlineStr"/>
-      <c r="B189" s="12" t="inlineStr">
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" s="11" t="inlineStr"/>
+      <c r="B191" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C189" s="13" t="inlineStr">
+      <c r="C191" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D189" s="12" t="inlineStr"/>
-      <c r="E189" s="14" t="inlineStr">
+      <c r="D191" s="12" t="inlineStr"/>
+      <c r="E191" s="14" t="inlineStr">
         <is>
           <t>2:30pm — Tre Cime Highlights Walk — flat path to Rifugio Lavaredo (20 min each way) · see the towering north faces up close · allow 1hr 15min</t>
         </is>
       </c>
-      <c r="F189" s="15" t="inlineStr">
+      <c r="F191" s="15" t="inlineStr">
         <is>
           <t>20 min / 1hr / 15min</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="50" customHeight="1">
-      <c r="A190" s="6" t="inlineStr"/>
-      <c r="B190" s="7" t="inlineStr">
+    <row r="192" ht="50" customHeight="1">
+      <c r="A192" s="6" t="inlineStr"/>
+      <c r="B192" s="7" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr">
+      <c r="C192" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D190" s="7" t="inlineStr"/>
-      <c r="E190" s="9" t="inlineStr">
+      <c r="D192" s="7" t="inlineStr"/>
+      <c r="E192" s="9" t="inlineStr">
         <is>
           <t>3:45pm — Passo Gardena scenic drive — drive back down toll road · SS243 Gardena Pass (2,121m) · hairpin turns · low gear descent · ➕ Lagazuoi cable car optional if energy · ~1hr 15min drive</t>
         </is>
       </c>
-      <c r="F190" s="10" t="inlineStr">
+      <c r="F192" s="10" t="inlineStr">
         <is>
           <t>~1hr / 15min</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="43" customHeight="1">
-      <c r="A191" s="25" t="inlineStr"/>
-      <c r="B191" s="26" t="inlineStr">
+    <row r="193" ht="43" customHeight="1">
+      <c r="A193" s="25" t="inlineStr"/>
+      <c r="B193" s="26" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C191" s="27" t="inlineStr">
+      <c r="C193" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D191" s="26" t="inlineStr"/>
-      <c r="E191" s="28" t="inlineStr">
+      <c r="D193" s="26" t="inlineStr"/>
+      <c r="E193" s="28" t="inlineStr">
         <is>
           <t>5:00pm — Kaiserau 1907, Collalbo — ✅ Check in · Via Peter Mayr 65, 39054 Collalbo · check-in 15:00–22:00 · unpack · rest · open a bottle of Italian wine</t>
         </is>
       </c>
-      <c r="F191" s="29" t="inlineStr"/>
-    </row>
-    <row r="192" ht="34" customHeight="1">
-      <c r="A192" s="30" t="inlineStr"/>
-      <c r="B192" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C192" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Braies 2026 access — road blocked 9am–4pm in peak season · arrive by 5:30am · P3 no reservation before 8am · €12 · leave before 8:30am · pivot to Prato Piazza if cloudy</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="34" customHeight="1">
-      <c r="A193" s="30" t="inlineStr"/>
-      <c r="B193" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C193" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Auronzo toll road 2026 — book at pass.auronzo.info · €40/car · 12-hour slot · book May 30 (exactly 30 days before) · rental plate: leave blank · update night before at Sillian hotel</t>
-        </is>
-      </c>
+      <c r="F193" s="29" t="inlineStr"/>
     </row>
     <row r="194" ht="34" customHeight="1">
       <c r="A194" s="30" t="inlineStr"/>
@@ -4479,356 +4490,356 @@
       </c>
       <c r="C194" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Braies 2026 access — road blocked 9am–4pm in peak season · arrive by 5:30am · P3 no reservation before 8am · €12 · leave before 8:30am · pivot to Prato Piazza if cloudy</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="34" customHeight="1">
+      <c r="A195" s="30" t="inlineStr"/>
+      <c r="B195" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C195" s="32" t="inlineStr">
+        <is>
+          <t>⚠️ Auronzo toll road 2026 — book at pass.auronzo.info · €40/car · 12-hour slot · book May 30 (exactly 30 days before) · rental plate: leave blank · update night before at Sillian hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="34" customHeight="1">
+      <c r="A196" s="30" t="inlineStr"/>
+      <c r="B196" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C196" s="32" t="inlineStr">
+        <is>
           <t>Cadini viewpoint tip — final 50m is a narrow ridge · secondary viewpoint 20m before the narrow section · 95% as good · go early — very crowded by midday · most dramatic jagged peak view in the Dolomites</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="3" customHeight="1">
-      <c r="A195" s="33" t="n"/>
-      <c r="B195" s="33" t="n"/>
-      <c r="C195" s="33" t="n"/>
-      <c r="D195" s="33" t="n"/>
-      <c r="E195" s="33" t="n"/>
-      <c r="F195" s="33" t="n"/>
-    </row>
-    <row r="196" ht="20" customHeight="1">
-      <c r="A196" s="3" t="inlineStr">
+    <row r="197" ht="3" customHeight="1">
+      <c r="A197" s="33" t="n"/>
+      <c r="B197" s="33" t="n"/>
+      <c r="C197" s="33" t="n"/>
+      <c r="D197" s="33" t="n"/>
+      <c r="E197" s="33" t="n"/>
+      <c r="F197" s="33" t="n"/>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>DAY 11  |  Jun 30  |  The Razor-Edge Peaks — Seceda · Val di Funes · Adolf Munkel Trail  |  ~80 km / 50 mi  ~2h total · Collalbo loop day</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="15" customHeight="1">
-      <c r="A197" s="4" t="inlineStr">
+    <row r="199" ht="15" customHeight="1">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Collalbo ▸ 8:45am Seceda cable car ▸ Trail 1 ridge + Rifugio Firenze lunch ▸ 1pm drive Val di Funes ▸ Santa Maddalena barrier + Panorama Trail ▸ St. Johann Ranui ▸ Zans traffic light ▸ 1:30pm Adolf Munkel Trail 35 ▸ Rifugio Odle lounge chairs ▸ 5:30pm descent ▸ 7pm Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="5" t="inlineStr">
+    <row r="200" ht="22" customHeight="1">
+      <c r="A200" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Seceda 8:45am — pre-booked · photos best 9–10:30am before clouds form · razor ridge Trail 1  |   Santa Maddalena 2026 barrier — park at Filler/Putzen lot · walk 25min Panorama Trail · cannot drive up  |   Zans traffic light Red → don't wait · park Ranui immediately + Bus 330 · saves hiking time</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="50" customHeight="1">
-      <c r="A199" s="16" t="inlineStr"/>
-      <c r="B199" s="17" t="inlineStr">
+    <row r="201" ht="50" customHeight="1">
+      <c r="A201" s="16" t="inlineStr"/>
+      <c r="B201" s="17" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C199" s="16" t="inlineStr">
+      <c r="C201" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D199" s="17" t="inlineStr"/>
-      <c r="E199" s="18" t="inlineStr">
+      <c r="D201" s="17" t="inlineStr"/>
+      <c r="E201" s="18" t="inlineStr">
         <is>
           <t>️ Parking at Seceda valley station — no booking needed · €2.80/hr · 250+ spaces · arrive before 9am (your 8:45am slot guarantees this) · if full: Garage Central Ortisei €19.80/day · 10 min walk via La Curta escalator tun</t>
         </is>
       </c>
-      <c r="F199" s="19" t="inlineStr">
+      <c r="F201" s="19" t="inlineStr">
         <is>
           <t>€2.80 / €19.80 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="49" customHeight="1">
-      <c r="A200" s="6" t="inlineStr"/>
-      <c r="B200" s="7" t="inlineStr">
+    <row r="202" ht="49" customHeight="1">
+      <c r="A202" s="6" t="inlineStr"/>
+      <c r="B202" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr">
+      <c r="C202" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D200" s="7" t="inlineStr"/>
-      <c r="E200" s="9" t="inlineStr">
+      <c r="D202" s="7" t="inlineStr"/>
+      <c r="E202" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 8:45am — Seceda 360 cable car — ✅ Booked · Receipt 1161/678/554260 · €255 total · 2 adults €84.50 + 2 juniors €43 · print tickets before departure · best photos 9–10:30am before clouds</t>
         </is>
       </c>
-      <c r="F200" s="10" t="inlineStr">
+      <c r="F202" s="10" t="inlineStr">
         <is>
           <t>€255 / €84.50 / €43</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="37" customHeight="1">
-      <c r="A201" s="20" t="inlineStr"/>
-      <c r="B201" s="21" t="inlineStr">
+    <row r="203" ht="37" customHeight="1">
+      <c r="A203" s="20" t="inlineStr"/>
+      <c r="B203" s="21" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C201" s="22" t="inlineStr">
+      <c r="C203" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D201" s="21" t="inlineStr"/>
-      <c r="E201" s="23" t="inlineStr">
+      <c r="D203" s="21" t="inlineStr"/>
+      <c r="E203" s="23" t="inlineStr">
         <is>
           <t>Trail 1 — Razor Edge ridge walk — from the cable car top follow Trail 1 to the summit cross · allow 1.5hrs for the ridge walk</t>
         </is>
       </c>
-      <c r="F201" s="24" t="inlineStr">
+      <c r="F203" s="24" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="11" t="inlineStr"/>
-      <c r="B202" s="12" t="inlineStr">
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="11" t="inlineStr"/>
+      <c r="B204" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C202" s="13" t="inlineStr">
+      <c r="C204" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D202" s="12" t="inlineStr"/>
-      <c r="E202" s="14" t="inlineStr">
+      <c r="D204" s="12" t="inlineStr"/>
+      <c r="E204" s="14" t="inlineStr">
         <is>
           <t>Lunch at Rifugio Firenze (2,039m) — allow 45 min</t>
         </is>
       </c>
-      <c r="F202" s="15" t="inlineStr">
+      <c r="F204" s="15" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="38" customHeight="1">
-      <c r="A203" s="6" t="inlineStr"/>
-      <c r="B203" s="7" t="inlineStr">
+    <row r="205" ht="38" customHeight="1">
+      <c r="A205" s="6" t="inlineStr"/>
+      <c r="B205" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C203" s="8" t="inlineStr">
+      <c r="C205" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D203" s="7" t="inlineStr"/>
-      <c r="E203" s="9" t="inlineStr">
+      <c r="D205" s="7" t="inlineStr"/>
+      <c r="E205" s="9" t="inlineStr">
         <is>
           <t>1:00pm — Val di Funes (Santa Maddalena) —  2026 barrier — park Filler/Putzen lots · walk 25 min Panorama Trail · cannot drive up</t>
         </is>
       </c>
-      <c r="F203" s="10" t="inlineStr">
+      <c r="F205" s="10" t="inlineStr">
         <is>
           <t>25 min</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="27" customHeight="1">
-      <c r="A204" s="16" t="inlineStr"/>
-      <c r="B204" s="17" t="inlineStr">
+    <row r="206" ht="27" customHeight="1">
+      <c r="A206" s="16" t="inlineStr"/>
+      <c r="B206" s="17" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C204" s="16" t="inlineStr">
+      <c r="C206" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D204" s="17" t="inlineStr"/>
-      <c r="E204" s="18" t="inlineStr">
+      <c r="D206" s="17" t="inlineStr"/>
+      <c r="E206" s="18" t="inlineStr">
         <is>
           <t>⭐ St. Johann in Ranui — €4 turnstile for meadow access · card only · 15 min</t>
         </is>
       </c>
-      <c r="F204" s="19" t="inlineStr">
+      <c r="F206" s="19" t="inlineStr">
         <is>
           <t>€4 / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="31" customHeight="1">
-      <c r="A205" s="16" t="inlineStr"/>
-      <c r="B205" s="17" t="inlineStr">
+    <row r="207" ht="31" customHeight="1">
+      <c r="A207" s="16" t="inlineStr"/>
+      <c r="B207" s="17" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C205" s="16" t="inlineStr">
+      <c r="C207" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D205" s="17" t="inlineStr"/>
-      <c r="E205" s="18" t="inlineStr">
+      <c r="D207" s="17" t="inlineStr"/>
+      <c r="E207" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ Santa Maddalena viewpoint — most photographed scene in South Tyrol · best light: late afternoon</t>
         </is>
       </c>
-      <c r="F205" s="19" t="inlineStr"/>
-    </row>
-    <row r="206" ht="29" customHeight="1">
-      <c r="A206" s="6" t="inlineStr"/>
-      <c r="B206" s="7" t="inlineStr">
+      <c r="F207" s="19" t="inlineStr"/>
+    </row>
+    <row r="208" ht="29" customHeight="1">
+      <c r="A208" s="6" t="inlineStr"/>
+      <c r="B208" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C206" s="8" t="inlineStr">
+      <c r="C208" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D206" s="7" t="inlineStr"/>
-      <c r="E206" s="9" t="inlineStr">
+      <c r="D208" s="7" t="inlineStr"/>
+      <c r="E208" s="9" t="inlineStr">
         <is>
           <t>⚠️ Zans traffic light —  Green = drive up ·  Red = park Ranui + Bus 330 · don't wait</t>
         </is>
       </c>
-      <c r="F206" s="10" t="inlineStr"/>
-    </row>
-    <row r="207" ht="33" customHeight="1">
-      <c r="A207" s="20" t="inlineStr"/>
-      <c r="B207" s="21" t="inlineStr">
+      <c r="F208" s="10" t="inlineStr"/>
+    </row>
+    <row r="209" ht="33" customHeight="1">
+      <c r="A209" s="20" t="inlineStr"/>
+      <c r="B209" s="21" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C207" s="22" t="inlineStr">
+      <c r="C209" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D207" s="21" t="inlineStr"/>
-      <c r="E207" s="23" t="inlineStr">
+      <c r="D209" s="21" t="inlineStr"/>
+      <c r="E209" s="23" t="inlineStr">
         <is>
           <t>1:30pm — Adolf Munkel Trail 35 — from Parkplatz Zanser Alm (Zannes) trailhead · Trail 35 (Via delle Odle)</t>
         </is>
       </c>
-      <c r="F207" s="24" t="inlineStr"/>
-    </row>
-    <row r="208" ht="38" customHeight="1">
-      <c r="A208" s="11" t="inlineStr"/>
-      <c r="B208" s="12" t="inlineStr">
+      <c r="F209" s="24" t="inlineStr"/>
+    </row>
+    <row r="210" ht="38" customHeight="1">
+      <c r="A210" s="11" t="inlineStr"/>
+      <c r="B210" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C208" s="13" t="inlineStr">
+      <c r="C210" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D208" s="12" t="inlineStr"/>
-      <c r="E208" s="14" t="inlineStr">
+      <c r="D210" s="12" t="inlineStr"/>
+      <c r="E210" s="14" t="inlineStr">
         <is>
           <t>⭐ ⭐ Rifugio Odle / Geisler Alm (1,986m) — the Cinema of the Odle — the best seats in the Dolomites · cash is faster but cards accepted</t>
         </is>
       </c>
-      <c r="F208" s="15" t="inlineStr"/>
-    </row>
-    <row r="209" ht="36" customHeight="1">
-      <c r="A209" s="6" t="inlineStr"/>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="F210" s="15" t="inlineStr"/>
+    </row>
+    <row r="211" ht="36" customHeight="1">
+      <c r="A211" s="6" t="inlineStr"/>
+      <c r="B211" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C209" s="8" t="inlineStr">
+      <c r="C211" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D209" s="7" t="inlineStr"/>
-      <c r="E209" s="9" t="inlineStr">
+      <c r="D211" s="7" t="inlineStr"/>
+      <c r="E211" s="9" t="inlineStr">
         <is>
           <t>5:30pm — Descent to Zannes car park — ~1hr back down · same trail · arrive Zannes ~6:30pm · drive 50 min back to Collalbo</t>
         </is>
       </c>
-      <c r="F209" s="10" t="inlineStr">
+      <c r="F211" s="10" t="inlineStr">
         <is>
           <t>~1hr / 50 min</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="29" customHeight="1">
-      <c r="A210" s="25" t="inlineStr"/>
-      <c r="B210" s="26" t="inlineStr">
+    <row r="212" ht="29" customHeight="1">
+      <c r="A212" s="25" t="inlineStr"/>
+      <c r="B212" s="26" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C210" s="27" t="inlineStr">
+      <c r="C212" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D210" s="26" t="inlineStr"/>
-      <c r="E210" s="28" t="inlineStr">
+      <c r="D212" s="26" t="inlineStr"/>
+      <c r="E212" s="28" t="inlineStr">
         <is>
           <t>⭐ Renon Earth Pyramids — evening walk — ➕ Optional if energy allows · 5 min from hotel</t>
         </is>
       </c>
-      <c r="F210" s="29" t="inlineStr">
+      <c r="F212" s="29" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="19" customHeight="1">
-      <c r="A211" s="25" t="inlineStr"/>
-      <c r="B211" s="26" t="inlineStr">
+    <row r="213" ht="19" customHeight="1">
+      <c r="A213" s="25" t="inlineStr"/>
+      <c r="B213" s="26" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C211" s="27" t="inlineStr">
+      <c r="C213" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D211" s="26" t="inlineStr"/>
-      <c r="E211" s="28" t="inlineStr">
+      <c r="D213" s="26" t="inlineStr"/>
+      <c r="E213" s="28" t="inlineStr">
         <is>
           <t>Night 2 — Kaiserau 1907, Collalbo</t>
         </is>
       </c>
-      <c r="F211" s="29" t="inlineStr"/>
-    </row>
-    <row r="212" ht="34" customHeight="1">
-      <c r="A212" s="30" t="inlineStr"/>
-      <c r="B212" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C212" s="32" t="inlineStr">
-        <is>
-          <t>Santa Maddalena 2026 barrier — physical barrier blocks non-resident cars since May 2026 · park Filler or Putzen lots in village · follow Panorama Trail signs · 25 min uphill walk to the viewpoint · you can no longer drive to the famous phot</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="30" customHeight="1">
-      <c r="A213" s="30" t="inlineStr"/>
-      <c r="B213" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C213" s="32" t="inlineStr">
-        <is>
-          <t>Zans traffic light 2026 — Green = drive up · Red = park at Ranui immediately + Bus 330 every 30–60 min · do not wait at the gate — bus is faster</t>
-        </is>
-      </c>
+      <c r="F213" s="29" t="inlineStr"/>
     </row>
     <row r="214" ht="34" customHeight="1">
       <c r="A214" s="30" t="inlineStr"/>
@@ -4839,132 +4850,114 @@
       </c>
       <c r="C214" s="32" t="inlineStr">
         <is>
+          <t>Santa Maddalena 2026 barrier — physical barrier blocks non-resident cars since May 2026 · park Filler or Putzen lots in village · follow Panorama Trail signs · 25 min uphill walk to the viewpoint · you can no longer drive to the famous phot</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="30" customHeight="1">
+      <c r="A215" s="30" t="inlineStr"/>
+      <c r="B215" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C215" s="32" t="inlineStr">
+        <is>
+          <t>Zans traffic light 2026 — Green = drive up · Red = park at Ranui immediately + Bus 330 every 30–60 min · do not wait at the gate — bus is faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="34" customHeight="1">
+      <c r="A216" s="30" t="inlineStr"/>
+      <c r="B216" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C216" s="32" t="inlineStr">
+        <is>
           <t>Photography windows — Seceda ridge: 9:00–10:30am before clouds form · Santa Maddalena viewpoint: late afternoon — sun behind you · Odle peaks lit directly · morning light hits the wrong side of the peaks</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="3" customHeight="1">
-      <c r="A215" s="33" t="n"/>
-      <c r="B215" s="33" t="n"/>
-      <c r="C215" s="33" t="n"/>
-      <c r="D215" s="33" t="n"/>
-      <c r="E215" s="33" t="n"/>
-      <c r="F215" s="33" t="n"/>
-    </row>
-    <row r="216" ht="20" customHeight="1">
-      <c r="A216" s="3" t="inlineStr">
+    <row r="217" ht="3" customHeight="1">
+      <c r="A217" s="33" t="n"/>
+      <c r="B217" s="33" t="n"/>
+      <c r="C217" s="33" t="n"/>
+      <c r="D217" s="33" t="n"/>
+      <c r="E217" s="33" t="n"/>
+      <c r="F217" s="33" t="n"/>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="3" t="inlineStr">
         <is>
           <t>DAY 12  |  Jul 1  |  Alpe di Siusi + Brenner Pass → Finkenberg — The Plateau &amp; The Pass  |  ~120 km / 75 mi  ~1h 45m · Collalbo → Finkenberg via Brenner</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="15" customHeight="1">
-      <c r="A217" s="4" t="inlineStr">
+    <row r="219" ht="15" customHeight="1">
+      <c r="A219" s="4" t="inlineStr">
         <is>
           <t>Timeline: 7:45am Collalbo ▸ 8:30am St. Valentin gate (must be before 9am) ▸ 8:45am P2 Compatsch ▸ 9:15am Bullaccia loop ▸ Hexenbänke viewpoint ▸ 12pm Tschötsch Alm lunch ▸ 1:30pm depart ▸ Brenner construction ▸ M-Preis Mayrhofen ▸ 4:30pm Keyone Rooms Finkenberg</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="22" customHeight="1">
-      <c r="A218" s="5" t="inlineStr">
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="5" t="inlineStr">
         <is>
           <t>Key: ️ Plan A: P2 Compatsch — keep checking seiseralm.it for cancellations · must arrive before 9am · €30  |   Plan B: Seis cable car → Compatsch — park in Seis · ~€30/adult RT · no booking · no 9am rule · same trailhead  |   St. Valentin gate closes 9:00am SHARP — leave Collalbo 7:45am · arrive 8:30am · no exceptions  |  ❌ Skip Rifugio Zallinger — 4hr RT or 2 extra lifts · impractical · eat at Tschötsch Alm instead  |  ⚠️ Brenner Lueg Bridge construction 2026 — 30–45 min delay · Digital Flex toll essential</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="40" customHeight="1">
-      <c r="A219" s="6" t="inlineStr"/>
-      <c r="B219" s="7" t="inlineStr">
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" s="6" t="inlineStr"/>
+      <c r="B221" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C219" s="8" t="inlineStr">
+      <c r="C221" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D219" s="7" t="inlineStr"/>
-      <c r="E219" s="9" t="inlineStr">
+      <c r="D221" s="7" t="inlineStr"/>
+      <c r="E221" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:45am — Depart Collalbo — 40 min drive to the Alpe di Siusi St. Valentin gate · checkout Kaiserau 1907 before leaving · luggage in the car</t>
         </is>
       </c>
-      <c r="F219" s="10" t="inlineStr">
+      <c r="F221" s="10" t="inlineStr">
         <is>
           <t>40 min</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="31" customHeight="1">
-      <c r="A220" s="34" t="inlineStr"/>
-      <c r="B220" s="35" t="inlineStr">
+    <row r="222" ht="31" customHeight="1">
+      <c r="A222" s="34" t="inlineStr"/>
+      <c r="B222" s="35" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C220" s="36" t="inlineStr">
+      <c r="C222" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D220" s="35" t="inlineStr"/>
-      <c r="E220" s="37" t="inlineStr">
+      <c r="D222" s="35" t="inlineStr"/>
+      <c r="E222" s="37" t="inlineStr">
         <is>
           <t>⚠️ CRITICAL: St. Valentin Gate — before 9:00am — 9:01am = turned back · €120+ cable car alternative</t>
         </is>
       </c>
-      <c r="F220" s="38" t="inlineStr">
+      <c r="F222" s="38" t="inlineStr">
         <is>
           <t>€120</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="50" customHeight="1">
-      <c r="A221" s="20" t="inlineStr"/>
-      <c r="B221" s="21" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C221" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D221" s="21" t="inlineStr"/>
-      <c r="E221" s="23" t="inlineStr">
-        <is>
-          <t>P2 Compatsch parking — ⚠️ Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · €30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch ca</t>
-        </is>
-      </c>
-      <c r="F221" s="24" t="inlineStr">
-        <is>
-          <t>€30 / €30 / €65</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="34" customHeight="1">
-      <c r="A222" s="20" t="inlineStr"/>
-      <c r="B222" s="21" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C222" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D222" s="21" t="inlineStr"/>
-      <c r="E222" s="23" t="inlineStr">
-        <is>
-          <t>9:15am — Bullaccia (Puflatsch) Loop — take the Telemix lift up from Compatsch · Trail PU (Puflatschumrundung)</t>
-        </is>
-      </c>
-      <c r="F222" s="24" t="inlineStr"/>
-    </row>
-    <row r="223" ht="23" customHeight="1">
+    <row r="223" ht="50" customHeight="1">
       <c r="A223" s="20" t="inlineStr"/>
       <c r="B223" s="21" t="inlineStr">
         <is>
@@ -4979,124 +4972,124 @@
       <c r="D223" s="21" t="inlineStr"/>
       <c r="E223" s="23" t="inlineStr">
         <is>
+          <t>P2 Compatsch parking — ⚠️ Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · €30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch ca</t>
+        </is>
+      </c>
+      <c r="F223" s="24" t="inlineStr">
+        <is>
+          <t>€30 / €30 / €65</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="34" customHeight="1">
+      <c r="A224" s="20" t="inlineStr"/>
+      <c r="B224" s="21" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C224" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D224" s="21" t="inlineStr"/>
+      <c r="E224" s="23" t="inlineStr">
+        <is>
+          <t>9:15am — Bullaccia (Puflatsch) Loop — take the Telemix lift up from Compatsch · Trail PU (Puflatschumrundung)</t>
+        </is>
+      </c>
+      <c r="F224" s="24" t="inlineStr"/>
+    </row>
+    <row r="225" ht="23" customHeight="1">
+      <c r="A225" s="20" t="inlineStr"/>
+      <c r="B225" s="21" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C225" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D225" s="21" t="inlineStr"/>
+      <c r="E225" s="23" t="inlineStr">
+        <is>
           <t>⭐ Hexenbänke — Witches' Benches — signed from the trail</t>
         </is>
       </c>
-      <c r="F223" s="24" t="inlineStr"/>
-    </row>
-    <row r="224" ht="31" customHeight="1">
-      <c r="A224" s="11" t="inlineStr"/>
-      <c r="B224" s="12" t="inlineStr">
+      <c r="F225" s="24" t="inlineStr"/>
+    </row>
+    <row r="226" ht="31" customHeight="1">
+      <c r="A226" s="11" t="inlineStr"/>
+      <c r="B226" s="12" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C224" s="13" t="inlineStr">
+      <c r="C226" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D224" s="12" t="inlineStr"/>
-      <c r="E224" s="14" t="inlineStr">
+      <c r="D226" s="12" t="inlineStr"/>
+      <c r="E226" s="14" t="inlineStr">
         <is>
           <t>️ 12:00pm — Lunch: Tschötsch Alm or Arnika Hütte — ⚠️ Do NOT go to Rifugio Zallinger — allow 1hr</t>
         </is>
       </c>
-      <c r="F224" s="15" t="inlineStr">
+      <c r="F226" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="27" customHeight="1">
-      <c r="A225" s="6" t="inlineStr"/>
-      <c r="B225" s="7" t="inlineStr">
+    <row r="227" ht="27" customHeight="1">
+      <c r="A227" s="6" t="inlineStr"/>
+      <c r="B227" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C225" s="8" t="inlineStr">
+      <c r="C227" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D225" s="7" t="inlineStr"/>
-      <c r="E225" s="9" t="inlineStr">
+      <c r="D227" s="7" t="inlineStr"/>
+      <c r="E227" s="9" t="inlineStr">
         <is>
           <t>1:30pm — Depart Alpe di Siusi — unrestricted descent · head north to Brenner</t>
         </is>
       </c>
-      <c r="F225" s="10" t="inlineStr"/>
-    </row>
-    <row r="226" ht="50" customHeight="1">
-      <c r="A226" s="16" t="inlineStr"/>
-      <c r="B226" s="17" t="inlineStr">
+      <c r="F227" s="10" t="inlineStr"/>
+    </row>
+    <row r="228" ht="50" customHeight="1">
+      <c r="A228" s="16" t="inlineStr"/>
+      <c r="B228" s="17" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C226" s="16" t="inlineStr">
+      <c r="C228" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D226" s="17" t="inlineStr"/>
-      <c r="E226" s="18" t="inlineStr">
+      <c r="D228" s="17" t="inlineStr"/>
+      <c r="E228" s="18" t="inlineStr">
         <is>
           <t>⚠️ Brenner Pass — Lueg Bridge construction — 30–45 min delay expected · Digital Flex toll green lanes · €11.50 · ➡️ If standstill at A22/A13 toll plaza: take B182 Brenner Route Nationale — free state road running paralle</t>
         </is>
       </c>
-      <c r="F226" s="19" t="inlineStr">
+      <c r="F228" s="19" t="inlineStr">
         <is>
           <t>45 min / €11.50</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="18" customHeight="1">
-      <c r="A227" s="16" t="inlineStr"/>
-      <c r="B227" s="17" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C227" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D227" s="17" t="inlineStr"/>
-      <c r="E227" s="18" t="inlineStr">
-        <is>
-          <t>Austrian vignette still valid?</t>
-        </is>
-      </c>
-      <c r="F227" s="19" t="inlineStr"/>
-    </row>
-    <row r="228" ht="35" customHeight="1">
-      <c r="A228" s="11" t="inlineStr"/>
-      <c r="B228" s="12" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C228" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D228" s="12" t="inlineStr"/>
-      <c r="E228" s="14" t="inlineStr">
-        <is>
-          <t>M-Preis Supermarket, Mayrhofen — Finkenberg is up a winding road — nothing open nearby in the evening · allow 20 min</t>
-        </is>
-      </c>
-      <c r="F228" s="15" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="34" customHeight="1">
+    <row r="229" ht="18" customHeight="1">
       <c r="A229" s="16" t="inlineStr"/>
       <c r="B229" s="17" t="inlineStr">
         <is>
@@ -5111,62 +5104,80 @@
       <c r="D229" s="17" t="inlineStr"/>
       <c r="E229" s="18" t="inlineStr">
         <is>
+          <t>Austrian vignette still valid?</t>
+        </is>
+      </c>
+      <c r="F229" s="19" t="inlineStr"/>
+    </row>
+    <row r="230" ht="35" customHeight="1">
+      <c r="A230" s="11" t="inlineStr"/>
+      <c r="B230" s="12" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C230" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D230" s="12" t="inlineStr"/>
+      <c r="E230" s="14" t="inlineStr">
+        <is>
+          <t>M-Preis Supermarket, Mayrhofen — Finkenberg is up a winding road — nothing open nearby in the evening · allow 20 min</t>
+        </is>
+      </c>
+      <c r="F230" s="15" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="34" customHeight="1">
+      <c r="A231" s="16" t="inlineStr"/>
+      <c r="B231" s="17" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C231" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D231" s="17" t="inlineStr"/>
+      <c r="E231" s="18" t="inlineStr">
+        <is>
           <t>4:30pm — Keyone Rooms, Finkenberg — $176 / €152.92 · ⚠️ Driveway can be steep — take it slowly on the approach</t>
         </is>
       </c>
-      <c r="F229" s="19" t="inlineStr">
+      <c r="F231" s="19" t="inlineStr">
         <is>
           <t>$176 / €152.92</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="29" customHeight="1">
-      <c r="A230" s="6" t="inlineStr"/>
-      <c r="B230" s="7" t="inlineStr">
+    <row r="232" ht="29" customHeight="1">
+      <c r="A232" s="6" t="inlineStr"/>
+      <c r="B232" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C230" s="8" t="inlineStr">
+      <c r="C232" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D230" s="7" t="inlineStr"/>
-      <c r="E230" s="9" t="inlineStr">
+      <c r="D232" s="7" t="inlineStr"/>
+      <c r="E232" s="9" t="inlineStr">
         <is>
           <t>Dinner in Finkenberg or Mayrhofen — or drive 5 min down to Mayrhofen for more options</t>
         </is>
       </c>
-      <c r="F230" s="10" t="inlineStr">
+      <c r="F232" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="34" customHeight="1">
-      <c r="A231" s="30" t="inlineStr"/>
-      <c r="B231" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C231" s="32" t="inlineStr">
-        <is>
-          <t>9:00am St. Valentin gate — non-negotiable — electronic barrier closes to private cars at exactly 9am · 9:01am = turned back · €120+ family cable car alternative · leave Collalbo by 7:45am</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="34" customHeight="1">
-      <c r="A232" s="30" t="inlineStr"/>
-      <c r="B232" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C232" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Brenner Lueg Bridge 2026 — single-lane renovation · 30–45 min delay expected · Digital Flex toll at autobrennero.it · €11.50 · green Video Toll lanes · saves 1hr vs manual queue</t>
         </is>
       </c>
     </row>
@@ -5179,11 +5190,11 @@
       </c>
       <c r="C233" s="32" t="inlineStr">
         <is>
-          <t>Hexenbänke — Witches' Benches — giant stone formations on the Bullaccia ridge · highest point of the plateau · best 360° photo spot · signed from the trail · kids love the legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="32" customHeight="1">
+          <t>9:00am St. Valentin gate — non-negotiable — electronic barrier closes to private cars at exactly 9am · 9:01am = turned back · €120+ family cable car alternative · leave Collalbo by 7:45am</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="34" customHeight="1">
       <c r="A234" s="30" t="inlineStr"/>
       <c r="B234" s="31" t="inlineStr">
         <is>
@@ -5192,112 +5203,90 @@
       </c>
       <c r="C234" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Brenner Lueg Bridge 2026 — single-lane renovation · 30–45 min delay expected · Digital Flex toll at autobrennero.it · €11.50 · green Video Toll lanes · saves 1hr vs manual queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="34" customHeight="1">
+      <c r="A235" s="30" t="inlineStr"/>
+      <c r="B235" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C235" s="32" t="inlineStr">
+        <is>
+          <t>Hexenbänke — Witches' Benches — giant stone formations on the Bullaccia ridge · highest point of the plateau · best 360° photo spot · signed from the trail · kids love the legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="32" customHeight="1">
+      <c r="A236" s="30" t="inlineStr"/>
+      <c r="B236" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C236" s="32" t="inlineStr">
+        <is>
           <t>M-Preis Mayrhofen — stop before Finkenberg · buy breakfast for Day 13 · nothing open near Keyone in evenings · steep winding road to Finkenberg — take slowly</t>
         </is>
       </c>
     </row>
-    <row r="235" ht="3" customHeight="1">
-      <c r="A235" s="33" t="n"/>
-      <c r="B235" s="33" t="n"/>
-      <c r="C235" s="33" t="n"/>
-      <c r="D235" s="33" t="n"/>
-      <c r="E235" s="33" t="n"/>
-      <c r="F235" s="33" t="n"/>
-    </row>
-    <row r="236" ht="20" customHeight="1">
-      <c r="A236" s="3" t="inlineStr">
+    <row r="237" ht="3" customHeight="1">
+      <c r="A237" s="33" t="n"/>
+      <c r="B237" s="33" t="n"/>
+      <c r="C237" s="33" t="n"/>
+      <c r="D237" s="33" t="n"/>
+      <c r="E237" s="33" t="n"/>
+      <c r="F237" s="33" t="n"/>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="3" t="inlineStr">
         <is>
           <t>DAY 13  |  Jul 2  |  High Bridges &amp; Deep Lakes — Olpererhütte · Achensee · Swarovski → Bichlbach  |  ~150 km / 93 mi  ~2h 30m incl. Achensee + Swarovski stops</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="15" customHeight="1">
-      <c r="A237" s="4" t="inlineStr">
+    <row r="239" ht="15" customHeight="1">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Finkenberg ▸ 8:30am Schlegeis toll €17 ▸ 9am Olpererhütte hike ▸ 10:30am Kebema bridge ▸ 11am lunch ▸ 1:30pm descent ▸ Swarovski (if rain) ▸ Achensee optional ▸ Fern Pass ▸ 7:30pm Bichlbach ▸ Heiterwanger See sunset</t>
         </is>
       </c>
     </row>
-    <row r="238" ht="22" customHeight="1">
-      <c r="A238" s="5" t="inlineStr">
+    <row r="240" ht="22" customHeight="1">
+      <c r="A240" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Arrive dam by 8:45am — reach Kebema bridge 10:30am · beats 45min photo queue by midday  |  ☀️ Plan A (sunny): Achensee — steamboat ~€22/adult OR free Gaisalm promenade walk if kids tired  |  ️ Plan B (rain/cloudy): Swarovski Crystal Worlds — 5min off A12 · ~€22/adult · no booking needed</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="31" customHeight="1">
-      <c r="A239" s="6" t="inlineStr"/>
-      <c r="B239" s="7" t="inlineStr">
+    <row r="241" ht="31" customHeight="1">
+      <c r="A241" s="6" t="inlineStr"/>
+      <c r="B241" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C239" s="8" t="inlineStr">
+      <c r="C241" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D239" s="7" t="inlineStr"/>
-      <c r="E239" s="9" t="inlineStr">
+      <c r="D241" s="7" t="inlineStr"/>
+      <c r="E241" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:00am — Depart Finkenberg — 20 min to Schlegeis · ⚠️ tunnel traffic lights = up to 15 min wait</t>
         </is>
       </c>
-      <c r="F239" s="10" t="inlineStr">
+      <c r="F241" s="10" t="inlineStr">
         <is>
           <t>20 min / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="27" customHeight="1">
-      <c r="A240" s="16" t="inlineStr"/>
-      <c r="B240" s="17" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C240" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D240" s="17" t="inlineStr"/>
-      <c r="E240" s="18" t="inlineStr">
-        <is>
-          <t>8:30am — Schlegeis Alpine Road toll — €17 · pay at the gate (cash or card)</t>
-        </is>
-      </c>
-      <c r="F240" s="19" t="inlineStr">
-        <is>
-          <t>€17</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="29" customHeight="1">
-      <c r="A241" s="20" t="inlineStr"/>
-      <c r="B241" s="21" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C241" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D241" s="21" t="inlineStr"/>
-      <c r="E241" s="23" t="inlineStr">
-        <is>
-          <t>9:00am — Olpererhütte Hike (Trail 502) — 3km / 1.9mi each way · well-maintained trail</t>
-        </is>
-      </c>
-      <c r="F241" s="24" t="inlineStr">
-        <is>
-          <t>3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="41" customHeight="1">
+    <row r="242" ht="27" customHeight="1">
       <c r="A242" s="16" t="inlineStr"/>
       <c r="B242" s="17" t="inlineStr">
         <is>
@@ -5312,88 +5301,88 @@
       <c r="D242" s="17" t="inlineStr"/>
       <c r="E242" s="18" t="inlineStr">
         <is>
+          <t>8:30am — Schlegeis Alpine Road toll — €17 · pay at the gate (cash or card)</t>
+        </is>
+      </c>
+      <c r="F242" s="19" t="inlineStr">
+        <is>
+          <t>€17</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="29" customHeight="1">
+      <c r="A243" s="20" t="inlineStr"/>
+      <c r="B243" s="21" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C243" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D243" s="21" t="inlineStr"/>
+      <c r="E243" s="23" t="inlineStr">
+        <is>
+          <t>9:00am — Olpererhütte Hike (Trail 502) — 3km / 1.9mi each way · well-maintained trail</t>
+        </is>
+      </c>
+      <c r="F243" s="24" t="inlineStr">
+        <is>
+          <t>3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="41" customHeight="1">
+      <c r="A244" s="16" t="inlineStr"/>
+      <c r="B244" s="17" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C244" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D244" s="17" t="inlineStr"/>
+      <c r="E244" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 10:30am — Kebema Suspension Bridge (Olperer Panoramabrücke) — 3–4 min past the hut · floats in mid-air above the turquoise reservoir 600m below</t>
         </is>
       </c>
-      <c r="F242" s="19" t="inlineStr">
+      <c r="F244" s="19" t="inlineStr">
         <is>
           <t>4 min</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="36" customHeight="1">
-      <c r="A243" s="11" t="inlineStr"/>
-      <c r="B243" s="12" t="inlineStr">
+    <row r="245" ht="36" customHeight="1">
+      <c r="A245" s="11" t="inlineStr"/>
+      <c r="B245" s="12" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C243" s="13" t="inlineStr">
+      <c r="C245" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D243" s="12" t="inlineStr"/>
-      <c r="E243" s="14" t="inlineStr">
+      <c r="D245" s="12" t="inlineStr"/>
+      <c r="E245" s="14" t="inlineStr">
         <is>
           <t>️ 11:00am — Lunch at Olpererhütte — cash preferred (but Wi-Fi available — check your Neuschwanstein booking!) · allow 1hr</t>
         </is>
       </c>
-      <c r="F243" s="15" t="inlineStr">
+      <c r="F245" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="35" customHeight="1">
-      <c r="A244" s="20" t="inlineStr"/>
-      <c r="B244" s="21" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C244" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D244" s="21" t="inlineStr"/>
-      <c r="E244" s="23" t="inlineStr">
-        <is>
-          <t>1:30pm — Descent to the dam — ~1hr back down same trail · easier on the knees than going up · back at car ~2:30pm</t>
-        </is>
-      </c>
-      <c r="F244" s="24" t="inlineStr">
-        <is>
-          <t>~1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="50" customHeight="1">
-      <c r="A245" s="6" t="inlineStr"/>
-      <c r="B245" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C245" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D245" s="7" t="inlineStr"/>
-      <c r="E245" s="9" t="inlineStr">
-        <is>
-          <t>☀️ Plan A — Sunny: Achensee — 50 min drive north from Schlegeis · park at Pertisau · Option 1: Achensee steamboat ~€22/adult · allow 1.5hrs · Option 2 (kids tired): Gaisalm promenade walk — free · same fjord-like views ·</t>
-        </is>
-      </c>
-      <c r="F245" s="10" t="inlineStr">
-        <is>
-          <t>50 min / €22 / 5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="50" customHeight="1">
+    <row r="246" ht="35" customHeight="1">
       <c r="A246" s="20" t="inlineStr"/>
       <c r="B246" s="21" t="inlineStr">
         <is>
@@ -5408,16 +5397,16 @@
       <c r="D246" s="21" t="inlineStr"/>
       <c r="E246" s="23" t="inlineStr">
         <is>
-          <t>️ Plan B — Rain/Cloudy: Swarovski Crystal Worlds — 5 min off A12 at Wattens · ~€22/adult · allow 1.5–2hrs · indoor immersive art installation · perfect rainy-day refuge after cold wet Olpererhütte hike · no booking neede</t>
+          <t>1:30pm — Descent to the dam — ~1hr back down same trail · easier on the knees than going up · back at car ~2:30pm</t>
         </is>
       </c>
       <c r="F246" s="24" t="inlineStr">
         <is>
-          <t>5 min / €22 / 2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="29" customHeight="1">
+          <t>~1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="50" customHeight="1">
       <c r="A247" s="6" t="inlineStr"/>
       <c r="B247" s="7" t="inlineStr">
         <is>
@@ -5432,104 +5421,126 @@
       <c r="D247" s="7" t="inlineStr"/>
       <c r="E247" s="9" t="inlineStr">
         <is>
+          <t>☀️ Plan A — Sunny: Achensee — 50 min drive north from Schlegeis · park at Pertisau · Option 1: Achensee steamboat ~€22/adult · allow 1.5hrs · Option 2 (kids tired): Gaisalm promenade walk — free · same fjord-like views ·</t>
+        </is>
+      </c>
+      <c r="F247" s="10" t="inlineStr">
+        <is>
+          <t>50 min / €22 / 5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="50" customHeight="1">
+      <c r="A248" s="20" t="inlineStr"/>
+      <c r="B248" s="21" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C248" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D248" s="21" t="inlineStr"/>
+      <c r="E248" s="23" t="inlineStr">
+        <is>
+          <t>️ Plan B — Rain/Cloudy: Swarovski Crystal Worlds — 5 min off A12 at Wattens · ~€22/adult · allow 1.5–2hrs · indoor immersive art installation · perfect rainy-day refuge after cold wet Olpererhütte hike · no booking neede</t>
+        </is>
+      </c>
+      <c r="F248" s="24" t="inlineStr">
+        <is>
+          <t>5 min / €22 / 2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="29" customHeight="1">
+      <c r="A249" s="6" t="inlineStr"/>
+      <c r="B249" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D249" s="7" t="inlineStr"/>
+      <c r="E249" s="9" t="inlineStr">
+        <is>
           <t>⚠️ Fern Pass warning on drive to Bichlbach — village Gasthäuser are relaxed about timing</t>
         </is>
       </c>
-      <c r="F247" s="10" t="inlineStr"/>
-    </row>
-    <row r="248" ht="33" customHeight="1">
-      <c r="A248" s="25" t="inlineStr"/>
-      <c r="B248" s="26" t="inlineStr">
+      <c r="F249" s="10" t="inlineStr"/>
+    </row>
+    <row r="250" ht="33" customHeight="1">
+      <c r="A250" s="25" t="inlineStr"/>
+      <c r="B250" s="26" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C248" s="27" t="inlineStr">
+      <c r="C250" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D248" s="26" t="inlineStr"/>
-      <c r="E248" s="28" t="inlineStr">
+      <c r="D250" s="26" t="inlineStr"/>
+      <c r="E250" s="28" t="inlineStr">
         <is>
           <t>~7:30pm — Landhaus Bichlbach — $467 / €405 · Heiterwanger See lake is a 20 min evening walk from the hotel</t>
         </is>
       </c>
-      <c r="F248" s="29" t="inlineStr">
+      <c r="F250" s="29" t="inlineStr">
         <is>
           <t>$467 / €405 / 20 min</t>
         </is>
       </c>
     </row>
-    <row r="249" ht="28" customHeight="1">
-      <c r="A249" s="16" t="inlineStr"/>
-      <c r="B249" s="17" t="inlineStr">
+    <row r="251" ht="28" customHeight="1">
+      <c r="A251" s="16" t="inlineStr"/>
+      <c r="B251" s="17" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C249" s="16" t="inlineStr">
+      <c r="C251" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D249" s="17" t="inlineStr"/>
-      <c r="E249" s="18" t="inlineStr">
+      <c r="D251" s="17" t="inlineStr"/>
+      <c r="E251" s="18" t="inlineStr">
         <is>
           <t>⭐ Heiterwanger See sunset walk — easy 20 min walk from Landhaus along Panoramaweg</t>
         </is>
       </c>
-      <c r="F249" s="19" t="inlineStr">
+      <c r="F251" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="25" customHeight="1">
-      <c r="A250" s="6" t="inlineStr"/>
-      <c r="B250" s="7" t="inlineStr">
+    <row r="252" ht="25" customHeight="1">
+      <c r="A252" s="6" t="inlineStr"/>
+      <c r="B252" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C250" s="8" t="inlineStr">
+      <c r="C252" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D250" s="7" t="inlineStr"/>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="D252" s="7" t="inlineStr"/>
+      <c r="E252" s="9" t="inlineStr">
         <is>
           <t>Dinner + pack bags — Gasthof Bichlbach · checkout 8am · alarm 7am</t>
         </is>
       </c>
-      <c r="F250" s="10" t="inlineStr"/>
-    </row>
-    <row r="251" ht="32" customHeight="1">
-      <c r="A251" s="30" t="inlineStr"/>
-      <c r="B251" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C251" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Schlegeis tunnel traffic lights — one-way sections · red light = up to 15 min wait · factor into morning timing · aim to be at the dam car park by 8:45am</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="34" customHeight="1">
-      <c r="A252" s="30" t="inlineStr"/>
-      <c r="B252" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C252" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Fern Pass congestion 2026 — slow trucks · one of the most congested alpine roads · flexible dinner only — no reservations · Bichlbach Gasthäuser are relaxed about timing</t>
-        </is>
-      </c>
+      <c r="F252" s="10" t="inlineStr"/>
     </row>
     <row r="253" ht="32" customHeight="1">
       <c r="A253" s="30" t="inlineStr"/>
@@ -5540,88 +5551,66 @@
       </c>
       <c r="C253" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Schlegeis tunnel traffic lights — one-way sections · red light = up to 15 min wait · factor into morning timing · aim to be at the dam car park by 8:45am</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="34" customHeight="1">
+      <c r="A254" s="30" t="inlineStr"/>
+      <c r="B254" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C254" s="32" t="inlineStr">
+        <is>
+          <t>⚠️ Fern Pass congestion 2026 — slow trucks · one of the most congested alpine roads · flexible dinner only — no reservations · Bichlbach Gasthäuser are relaxed about timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="32" customHeight="1">
+      <c r="A255" s="30" t="inlineStr"/>
+      <c r="B255" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C255" s="32" t="inlineStr">
+        <is>
           <t>At Olpererhütte: check Neuschwanstein booking — the hut has excellent Wi-Fi · confirm your 9:30am slot for tomorrow · cash preferred for food but cards accepted</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="3" customHeight="1">
-      <c r="A254" s="33" t="n"/>
-      <c r="B254" s="33" t="n"/>
-      <c r="C254" s="33" t="n"/>
-      <c r="D254" s="33" t="n"/>
-      <c r="E254" s="33" t="n"/>
-      <c r="F254" s="33" t="n"/>
-    </row>
-    <row r="255" ht="20" customHeight="1">
-      <c r="A255" s="3" t="inlineStr">
+    <row r="256" ht="3" customHeight="1">
+      <c r="A256" s="33" t="n"/>
+      <c r="B256" s="33" t="n"/>
+      <c r="C256" s="33" t="n"/>
+      <c r="D256" s="33" t="n"/>
+      <c r="E256" s="33" t="n"/>
+      <c r="F256" s="33" t="n"/>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="3" t="inlineStr">
         <is>
           <t>DAY 14  |  Jul 3  |  The Lakes of the Dragon — Seebensee · Drachensee · Coburger Hütte  |  ~20 km / 12 mi  ~30m · just Bichlbach ↔ Ehrwald</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="4" t="inlineStr">
+    <row r="258" ht="15" customHeight="1">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>Timeline: Tonight: ATM Ehrwald €60–80 ▸ 7:45am Bichlbach ▸ 8:00am Ehrwalder Almbahn (first car) ▸ 8:10am hike ▸ 9:45am Seebensee mirror ▸ 10:15am Drachensee climb ▸ 11:00am Coburger Hütte Kaiserschmarrn ▸ 12:45pm descent ▸ 2:45pm back at car ▸ 3pm Bichlbach ▸ 7:30pm Heiterwanger See sunset</t>
         </is>
       </c>
     </row>
-    <row r="257" ht="22" customHeight="1">
-      <c r="A257" s="5" t="inlineStr">
+    <row r="259" ht="22" customHeight="1">
+      <c r="A259" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ ATM in Ehrwald tonight — €60–80 cash · Coburger Hütte cash only · no card reader  |  ✅ 7:45am departure — first cable car 8:00am · arrive Seebensee 9:45am · beats 10:30am winds  |  ⚠️ Seebensee mirror reflection before 10:30am — winds create ripples by midday · 9:45am arrival ✅  |  ⚠️ Drachensee path slippery if rained Jul 2 — best-grip boots · 217m steep climb · 30–45 min  |  ➕ E-bikes optional at valley station — cuts Seebensee hike from 1.5hrs to 25 min · saves legs for Drachensee</t>
         </is>
       </c>
     </row>
-    <row r="258" ht="50" customHeight="1">
-      <c r="A258" s="16" t="inlineStr"/>
-      <c r="B258" s="17" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C258" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D258" s="17" t="inlineStr"/>
-      <c r="E258" s="18" t="inlineStr">
-        <is>
-          <t>Tonight (Jul 2 evening): ATM in Ehrwald — withdraw €60–80 cash for the family · Coburger Hütte is cash only — no card reader on the mountain · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
-        </is>
-      </c>
-      <c r="F258" s="19" t="inlineStr">
-        <is>
-          <t>€60 / €12 / €14</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="38" customHeight="1">
-      <c r="A259" s="6" t="inlineStr"/>
-      <c r="B259" s="7" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C259" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D259" s="7" t="inlineStr"/>
-      <c r="E259" s="9" t="inlineStr">
-        <is>
-          <t>7:45am — Depart Bichlbach — 5 min drive to Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~7:55am</t>
-        </is>
-      </c>
-      <c r="F259" s="10" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="44" customHeight="1">
+    <row r="260" ht="50" customHeight="1">
       <c r="A260" s="16" t="inlineStr"/>
       <c r="B260" s="17" t="inlineStr">
         <is>
@@ -5636,64 +5625,64 @@
       <c r="D260" s="17" t="inlineStr"/>
       <c r="E260" s="18" t="inlineStr">
         <is>
+          <t>Tonight (Jul 2 evening): ATM in Ehrwald — withdraw €60–80 cash for the family · Coburger Hütte is cash only — no card reader on the mountain · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
+        </is>
+      </c>
+      <c r="F260" s="19" t="inlineStr">
+        <is>
+          <t>€60 / €12 / €14</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="38" customHeight="1">
+      <c r="A261" s="6" t="inlineStr"/>
+      <c r="B261" s="7" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D261" s="7" t="inlineStr"/>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>7:45am — Depart Bichlbach — 5 min drive to Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~7:55am</t>
+        </is>
+      </c>
+      <c r="F261" s="10" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="44" customHeight="1">
+      <c r="A262" s="16" t="inlineStr"/>
+      <c r="B262" s="17" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C262" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D262" s="17" t="inlineStr"/>
+      <c r="E262" s="18" t="inlineStr">
+        <is>
           <t>⭐ 8:00am — Ehrwalder Almbahn — first cable car of the day · ~€26/adult · free parking · 5 min at top for Zugspitze platform view · ⚠️ July high season: opens 8:00am</t>
         </is>
       </c>
-      <c r="F260" s="19" t="inlineStr">
+      <c r="F262" s="19" t="inlineStr">
         <is>
           <t>€26 / 5 min</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="50" customHeight="1">
-      <c r="A261" s="20" t="inlineStr"/>
-      <c r="B261" s="21" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C261" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D261" s="21" t="inlineStr"/>
-      <c r="E261" s="23" t="inlineStr">
-        <is>
-          <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am · ➕ E-bikes available at valley station — cuts hike to 25 min if family wants to save le</t>
-        </is>
-      </c>
-      <c r="F261" s="24" t="inlineStr">
-        <is>
-          <t>6km / 5hr / 25 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="50" customHeight="1">
-      <c r="A262" s="6" t="inlineStr"/>
-      <c r="B262" s="7" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C262" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D262" s="7" t="inlineStr"/>
-      <c r="E262" s="9" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 9:45am — Seebensee mirror reflection — crystal-clear turquoise water · Zugspitze reflected · winds pick up after 10:30am — 9:45am arrival is perfectly timed · allow 30 min · benches along the southern shore</t>
-        </is>
-      </c>
-      <c r="F262" s="10" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="44" customHeight="1">
+    <row r="263" ht="50" customHeight="1">
       <c r="A263" s="20" t="inlineStr"/>
       <c r="B263" s="21" t="inlineStr">
         <is>
@@ -5708,40 +5697,40 @@
       <c r="D263" s="21" t="inlineStr"/>
       <c r="E263" s="23" t="inlineStr">
         <is>
-          <t>10:15am — Drachensee ascent — 1.4km · 217m elevation gain · 30–45 min · ⚠️ slippery if rained Jul 2 · best-grip boots · steeper than Seebensee section but short</t>
+          <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am · ➕ E-bikes available at valley station — cuts hike to 25 min if family wants to save le</t>
         </is>
       </c>
       <c r="F263" s="24" t="inlineStr">
         <is>
-          <t>4km / 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="46" customHeight="1">
-      <c r="A264" s="16" t="inlineStr"/>
-      <c r="B264" s="17" t="inlineStr">
+          <t>6km / 5hr / 25 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="50" customHeight="1">
+      <c r="A264" s="6" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C264" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D264" s="17" t="inlineStr"/>
-      <c r="E264" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring €60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
-        </is>
-      </c>
-      <c r="F264" s="19" t="inlineStr">
-        <is>
-          <t>€60 / 1hr / 45min</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="40" customHeight="1">
+      <c r="C264" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="inlineStr"/>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 9:45am — Seebensee mirror reflection — crystal-clear turquoise water · Zugspitze reflected · winds pick up after 10:30am — 9:45am arrival is perfectly timed · allow 30 min · benches along the southern shore</t>
+        </is>
+      </c>
+      <c r="F264" s="10" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="44" customHeight="1">
       <c r="A265" s="20" t="inlineStr"/>
       <c r="B265" s="21" t="inlineStr">
         <is>
@@ -5756,106 +5745,128 @@
       <c r="D265" s="21" t="inlineStr"/>
       <c r="E265" s="23" t="inlineStr">
         <is>
+          <t>10:15am — Drachensee ascent — 1.4km · 217m elevation gain · 30–45 min · ⚠️ slippery if rained Jul 2 · best-grip boots · steeper than Seebensee section but short</t>
+        </is>
+      </c>
+      <c r="F265" s="24" t="inlineStr">
+        <is>
+          <t>4km / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="46" customHeight="1">
+      <c r="A266" s="16" t="inlineStr"/>
+      <c r="B266" s="17" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C266" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D266" s="17" t="inlineStr"/>
+      <c r="E266" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring €60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
+        </is>
+      </c>
+      <c r="F266" s="19" t="inlineStr">
+        <is>
+          <t>€60 / 1hr / 45min</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" s="20" t="inlineStr"/>
+      <c r="B267" s="21" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C267" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D267" s="21" t="inlineStr"/>
+      <c r="E267" s="23" t="inlineStr">
+        <is>
           <t>12:45pm — Descent to cable car station — ~1.5hrs back down · same trail · arrive top station ~2:15pm · cable car down · back at car ~2:45pm</t>
         </is>
       </c>
-      <c r="F265" s="24" t="inlineStr">
+      <c r="F267" s="24" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="39" customHeight="1">
-      <c r="A266" s="6" t="inlineStr"/>
-      <c r="B266" s="7" t="inlineStr">
+    <row r="268" ht="39" customHeight="1">
+      <c r="A268" s="6" t="inlineStr"/>
+      <c r="B268" s="7" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C266" s="8" t="inlineStr">
+      <c r="C268" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D266" s="7" t="inlineStr"/>
-      <c r="E266" s="9" t="inlineStr">
+      <c r="D268" s="7" t="inlineStr"/>
+      <c r="E268" s="9" t="inlineStr">
         <is>
           <t>3:00pm — Back at Landhaus Bichlbach — shower · rest legs · pack bags for tomorrow · checkout 8am — Neuschwanstein 9:30am · alarm 7:00am</t>
         </is>
       </c>
-      <c r="F266" s="10" t="inlineStr"/>
-    </row>
-    <row r="267" ht="46" customHeight="1">
-      <c r="A267" s="16" t="inlineStr"/>
-      <c r="B267" s="17" t="inlineStr">
+      <c r="F268" s="10" t="inlineStr"/>
+    </row>
+    <row r="269" ht="46" customHeight="1">
+      <c r="A269" s="16" t="inlineStr"/>
+      <c r="B269" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C267" s="16" t="inlineStr">
+      <c r="C269" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D267" s="17" t="inlineStr"/>
-      <c r="E267" s="18" t="inlineStr">
+      <c r="D269" s="17" t="inlineStr"/>
+      <c r="E269" s="18" t="inlineStr">
         <is>
           <t>⭐ 7:30pm — Heiterwanger See sunset walk — 20 min walk from Landhaus along the Panoramaweg · flat · easy · clears the lactic acid · alpenglow after sunset on the higher path</t>
         </is>
       </c>
-      <c r="F267" s="19" t="inlineStr">
+      <c r="F269" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="39" customHeight="1">
-      <c r="A268" s="11" t="inlineStr"/>
-      <c r="B268" s="12" t="inlineStr">
+    <row r="270" ht="39" customHeight="1">
+      <c r="A270" s="11" t="inlineStr"/>
+      <c r="B270" s="12" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C268" s="13" t="inlineStr">
+      <c r="C270" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D268" s="12" t="inlineStr"/>
-      <c r="E268" s="14" t="inlineStr">
+      <c r="D270" s="12" t="inlineStr"/>
+      <c r="E270" s="14" t="inlineStr">
         <is>
           <t>Dinner — Gasthof Bichlbach or hotel restaurant — early dinner + early bed · alarm 7:00am tomorrow · Neuschwanstein 9:30am — last big day</t>
         </is>
       </c>
-      <c r="F268" s="15" t="inlineStr"/>
-    </row>
-    <row r="269" ht="33" customHeight="1">
-      <c r="A269" s="30" t="inlineStr"/>
-      <c r="B269" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C269" s="32" t="inlineStr">
-        <is>
-          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
-        </is>
-      </c>
-    </row>
-    <row r="270" ht="34" customHeight="1">
-      <c r="A270" s="30" t="inlineStr"/>
-      <c r="B270" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C270" s="32" t="inlineStr">
-        <is>
-          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="34" customHeight="1">
+      <c r="F270" s="15" t="inlineStr"/>
+    </row>
+    <row r="271" ht="33" customHeight="1">
       <c r="A271" s="30" t="inlineStr"/>
       <c r="B271" s="31" t="inlineStr">
         <is>
@@ -5864,7 +5875,7 @@
       </c>
       <c r="C271" s="32" t="inlineStr">
         <is>
-          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
+          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
         </is>
       </c>
     </row>
@@ -5877,112 +5888,90 @@
       </c>
       <c r="C272" s="32" t="inlineStr">
         <is>
+          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="34" customHeight="1">
+      <c r="A273" s="30" t="inlineStr"/>
+      <c r="B273" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C273" s="32" t="inlineStr">
+        <is>
+          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="34" customHeight="1">
+      <c r="A274" s="30" t="inlineStr"/>
+      <c r="B274" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C274" s="32" t="inlineStr">
+        <is>
           <t>Panoramaweg for Heiterwanger See — take the higher Panoramaweg trail not the lakeside path · stays above the valley floor to catch alpenglow after sunset · 20 min from hotel · flat + easy</t>
         </is>
       </c>
     </row>
-    <row r="273" ht="3" customHeight="1">
-      <c r="A273" s="33" t="n"/>
-      <c r="B273" s="33" t="n"/>
-      <c r="C273" s="33" t="n"/>
-      <c r="D273" s="33" t="n"/>
-      <c r="E273" s="33" t="n"/>
-      <c r="F273" s="33" t="n"/>
-    </row>
-    <row r="274" ht="20" customHeight="1">
-      <c r="A274" s="3" t="inlineStr">
+    <row r="275" ht="3" customHeight="1">
+      <c r="A275" s="33" t="n"/>
+      <c r="B275" s="33" t="n"/>
+      <c r="C275" s="33" t="n"/>
+      <c r="D275" s="33" t="n"/>
+      <c r="E275" s="33" t="n"/>
+      <c r="F275" s="33" t="n"/>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="A276" s="3" t="inlineStr">
         <is>
           <t>DAY 15  |  Jul 4  |  The Fairy Tale Finale — Neuschwanstein · Ebenalp · Aescher → ZRH  |  ~280 km / 174 mi  ~3h 30m · Neuschwanstein → Ebenalp → ZRH</t>
         </is>
       </c>
     </row>
-    <row r="275" ht="15" customHeight="1">
-      <c r="A275" s="4" t="inlineStr">
+    <row r="277" ht="15" customHeight="1">
+      <c r="A277" s="4" t="inlineStr">
         <is>
           <t>Timeline: 7:30am Bichlbach checkout ▸ 8:15am P4 Neuschwanstein ▸ 8:30am Marienbrücke FIRST ▸ 9:20am castle gate ▸ 9:30am tour ▸ 11:30am drive Bregenz tunnel ▸ 1:15pm Wasserauen ▸ 1:30pm Ebenalp cable car ▸ 2pm Aescher (before Swing event 5pm) ▸ 4pm descent ▸ 6pm ZRH hotel + return car tonight ▸ 5am alarm tomorrow</t>
         </is>
       </c>
     </row>
-    <row r="276" ht="22" customHeight="1">
-      <c r="A276" s="5" t="inlineStr">
+    <row r="278" ht="22" customHeight="1">
+      <c r="A278" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Marienbrücke BEFORE the tour — go at 8:30am · virtually no queue · by 10am it's packed  |  ⚠️ Castle gate by 9:20am — NOT the ticket centre · guide will not wait for latecomers  |   Return car TONIGHT — drop bags at hotel · 5 min to Europcar ZRH · open until midnight · eliminates 5:30am stress</t>
         </is>
       </c>
     </row>
-    <row r="277" ht="34" customHeight="1">
-      <c r="A277" s="6" t="inlineStr"/>
-      <c r="B277" s="7" t="inlineStr">
+    <row r="279" ht="34" customHeight="1">
+      <c r="A279" s="6" t="inlineStr"/>
+      <c r="B279" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C277" s="8" t="inlineStr">
+      <c r="C279" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D277" s="7" t="inlineStr"/>
-      <c r="E277" s="9" t="inlineStr">
+      <c r="D279" s="7" t="inlineStr"/>
+      <c r="E279" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:30am — Checkout Landhaus Bichlbach + depart — 30 min earlier than original plan · 45 min drive to Schwangau</t>
         </is>
       </c>
-      <c r="F277" s="10" t="inlineStr">
+      <c r="F279" s="10" t="inlineStr">
         <is>
           <t>30 min / 45 min</t>
         </is>
       </c>
     </row>
-    <row r="278" ht="25" customHeight="1">
-      <c r="A278" s="16" t="inlineStr"/>
-      <c r="B278" s="17" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C278" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D278" s="17" t="inlineStr"/>
-      <c r="E278" s="18" t="inlineStr">
-        <is>
-          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
-        </is>
-      </c>
-      <c r="F278" s="19" t="inlineStr">
-        <is>
-          <t>CHF 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="279" ht="31" customHeight="1">
-      <c r="A279" s="16" t="inlineStr"/>
-      <c r="B279" s="17" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C279" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D279" s="17" t="inlineStr"/>
-      <c r="E279" s="18" t="inlineStr">
-        <is>
-          <t>8:15am — Park P4, Schwangau — €7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
-        </is>
-      </c>
-      <c r="F279" s="19" t="inlineStr">
-        <is>
-          <t>€7 / 10 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="280" ht="35" customHeight="1">
+    <row r="280" ht="25" customHeight="1">
       <c r="A280" s="16" t="inlineStr"/>
       <c r="B280" s="17" t="inlineStr">
         <is>
@@ -5997,16 +5986,16 @@
       <c r="D280" s="17" t="inlineStr"/>
       <c r="E280" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
+          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
         </is>
       </c>
       <c r="F280" s="19" t="inlineStr">
         <is>
-          <t>10 min / 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="29" customHeight="1">
+          <t>CHF 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="31" customHeight="1">
       <c r="A281" s="16" t="inlineStr"/>
       <c r="B281" s="17" t="inlineStr">
         <is>
@@ -6021,12 +6010,16 @@
       <c r="D281" s="17" t="inlineStr"/>
       <c r="E281" s="18" t="inlineStr">
         <is>
-          <t>⚠️ 9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
-        </is>
-      </c>
-      <c r="F281" s="19" t="inlineStr"/>
-    </row>
-    <row r="282" ht="34" customHeight="1">
+          <t>8:15am — Park P4, Schwangau — €7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
+        </is>
+      </c>
+      <c r="F281" s="19" t="inlineStr">
+        <is>
+          <t>€7 / 10 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="35" customHeight="1">
       <c r="A282" s="16" t="inlineStr"/>
       <c r="B282" s="17" t="inlineStr">
         <is>
@@ -6041,40 +6034,36 @@
       <c r="D282" s="17" t="inlineStr"/>
       <c r="E282" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
+          <t>⭐ ⭐ 8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
         </is>
       </c>
       <c r="F282" s="19" t="inlineStr">
         <is>
-          <t>40 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="37" customHeight="1">
-      <c r="A283" s="6" t="inlineStr"/>
-      <c r="B283" s="7" t="inlineStr">
+          <t>10 min / 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="29" customHeight="1">
+      <c r="A283" s="16" t="inlineStr"/>
+      <c r="B283" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C283" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D283" s="7" t="inlineStr"/>
-      <c r="E283" s="9" t="inlineStr">
-        <is>
-          <t>11:30am — Depart Neuschwanstein → Wasserauen — 1hr 30min drive · ⚠️ Saturday = absolute peak crowds on all German/Swiss roads</t>
-        </is>
-      </c>
-      <c r="F283" s="10" t="inlineStr">
-        <is>
-          <t>1hr / 30min</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="50" customHeight="1">
+      <c r="C283" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D283" s="17" t="inlineStr"/>
+      <c r="E283" s="18" t="inlineStr">
+        <is>
+          <t>⚠️ 9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
+        </is>
+      </c>
+      <c r="F283" s="19" t="inlineStr"/>
+    </row>
+    <row r="284" ht="34" customHeight="1">
       <c r="A284" s="16" t="inlineStr"/>
       <c r="B284" s="17" t="inlineStr">
         <is>
@@ -6089,40 +6078,40 @@
       <c r="D284" s="17" t="inlineStr"/>
       <c r="E284" s="18" t="inlineStr">
         <is>
-          <t>1:15pm — Park at Wasserauen cable car — CHF 36/adult return (2026 rate) · runs every 15 min · ⚠️ Peak Saturday: parking lot likely full — if full: park further down the valley on the roadside · local train/shuttle runs t</t>
+          <t>⭐ ⭐ 9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
         </is>
       </c>
       <c r="F284" s="19" t="inlineStr">
         <is>
-          <t>CHF 36 / 15 min / 20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="32" customHeight="1">
-      <c r="A285" s="20" t="inlineStr"/>
-      <c r="B285" s="21" t="inlineStr">
+          <t>40 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="37" customHeight="1">
+      <c r="A285" s="6" t="inlineStr"/>
+      <c r="B285" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C285" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D285" s="21" t="inlineStr"/>
-      <c r="E285" s="23" t="inlineStr">
-        <is>
-          <t>⭐ 1:30pm — Ebenalp cable car — CHF 36/adult · 6 min · last descent 6pm · ⚠️ caves 10°C — pack a layer</t>
-        </is>
-      </c>
-      <c r="F285" s="24" t="inlineStr">
-        <is>
-          <t>CHF 36 / 6 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="35" customHeight="1">
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D285" s="7" t="inlineStr"/>
+      <c r="E285" s="9" t="inlineStr">
+        <is>
+          <t>11:30am — Depart Neuschwanstein → Wasserauen — 1hr 30min drive · ⚠️ Saturday = absolute peak crowds on all German/Swiss roads</t>
+        </is>
+      </c>
+      <c r="F285" s="10" t="inlineStr">
+        <is>
+          <t>1hr / 30min</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="50" customHeight="1">
       <c r="A286" s="16" t="inlineStr"/>
       <c r="B286" s="17" t="inlineStr">
         <is>
@@ -6137,36 +6126,40 @@
       <c r="D286" s="17" t="inlineStr"/>
       <c r="E286" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 2:00pm — Berggasthaus Aescher — arrive before 4pm ·  Swing event 5pm · Chäs-Chnöpfli or Rösti · Siedwurst if full</t>
-        </is>
-      </c>
-      <c r="F286" s="19" t="inlineStr"/>
-    </row>
-    <row r="287" ht="39" customHeight="1">
-      <c r="A287" s="6" t="inlineStr"/>
-      <c r="B287" s="7" t="inlineStr">
+          <t>1:15pm — Park at Wasserauen cable car — CHF 36/adult return (2026 rate) · runs every 15 min · ⚠️ Peak Saturday: parking lot likely full — if full: park further down the valley on the roadside · local train/shuttle runs t</t>
+        </is>
+      </c>
+      <c r="F286" s="19" t="inlineStr">
+        <is>
+          <t>CHF 36 / 15 min / 20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="32" customHeight="1">
+      <c r="A287" s="20" t="inlineStr"/>
+      <c r="B287" s="21" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C287" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D287" s="7" t="inlineStr"/>
-      <c r="E287" s="9" t="inlineStr">
-        <is>
-          <t>4:00pm — Cable car down + drive to ZRH — walk 25 min back up to Ebenalp top station · cable car down · ~2hr drive to Zurich Airport area</t>
-        </is>
-      </c>
-      <c r="F287" s="10" t="inlineStr">
-        <is>
-          <t>25 min / ~2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="33" customHeight="1">
+      <c r="C287" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D287" s="21" t="inlineStr"/>
+      <c r="E287" s="23" t="inlineStr">
+        <is>
+          <t>⭐ 1:30pm — Ebenalp cable car — CHF 36/adult · 6 min · last descent 6pm · ⚠️ caves 10°C — pack a layer</t>
+        </is>
+      </c>
+      <c r="F287" s="24" t="inlineStr">
+        <is>
+          <t>CHF 36 / 6 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="35" customHeight="1">
       <c r="A288" s="16" t="inlineStr"/>
       <c r="B288" s="17" t="inlineStr">
         <is>
@@ -6181,16 +6174,12 @@
       <c r="D288" s="17" t="inlineStr"/>
       <c r="E288" s="18" t="inlineStr">
         <is>
-          <t>❌ Rhine Falls — SKIP TODAY — adding 45 min detour north on a peak Saturday risks missing car return window</t>
-        </is>
-      </c>
-      <c r="F288" s="19" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="50" customHeight="1">
+          <t>⭐ ⭐ 2:00pm — Berggasthaus Aescher — arrive before 4pm ·  Swing event 5pm · Chäs-Chnöpfli or Rösti · Siedwurst if full</t>
+        </is>
+      </c>
+      <c r="F288" s="19" t="inlineStr"/>
+    </row>
+    <row r="289" ht="39" customHeight="1">
       <c r="A289" s="6" t="inlineStr"/>
       <c r="B289" s="7" t="inlineStr">
         <is>
@@ -6205,66 +6194,88 @@
       <c r="D289" s="7" t="inlineStr"/>
       <c r="E289" s="9" t="inlineStr">
         <is>
+          <t>4:00pm — Cable car down + drive to ZRH — walk 25 min back up to Ebenalp top station · cable car down · ~2hr drive to Zurich Airport area</t>
+        </is>
+      </c>
+      <c r="F289" s="10" t="inlineStr">
+        <is>
+          <t>25 min / ~2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="33" customHeight="1">
+      <c r="A290" s="16" t="inlineStr"/>
+      <c r="B290" s="17" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C290" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D290" s="17" t="inlineStr"/>
+      <c r="E290" s="18" t="inlineStr">
+        <is>
+          <t>❌ Rhine Falls — SKIP TODAY — adding 45 min detour north on a peak Saturday risks missing car return window</t>
+        </is>
+      </c>
+      <c r="F290" s="19" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="50" customHeight="1">
+      <c r="A291" s="6" t="inlineStr"/>
+      <c r="B291" s="7" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="inlineStr"/>
+      <c r="E291" s="9" t="inlineStr">
+        <is>
           <t>Return Europcar ZRH tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH return · return by 11:30pm · Hilton shuttle back · check Booking.com email for return confirmation</t>
         </is>
       </c>
-      <c r="F289" s="10" t="inlineStr">
+      <c r="F291" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="290" ht="28" customHeight="1">
-      <c r="A290" s="25" t="inlineStr"/>
-      <c r="B290" s="26" t="inlineStr">
+    <row r="292" ht="28" customHeight="1">
+      <c r="A292" s="25" t="inlineStr"/>
+      <c r="B292" s="26" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C290" s="27" t="inlineStr">
+      <c r="C292" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D290" s="26" t="inlineStr"/>
-      <c r="E290" s="28" t="inlineStr">
+      <c r="D292" s="26" t="inlineStr"/>
+      <c r="E292" s="28" t="inlineStr">
         <is>
           <t>⚠️ Tonight — final checks — check-in opens 5:30am · hotel is 5 min walk to terminal</t>
         </is>
       </c>
-      <c r="F290" s="29" t="inlineStr">
+      <c r="F292" s="29" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="31" customHeight="1">
-      <c r="A291" s="30" t="inlineStr"/>
-      <c r="B291" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C291" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="34" customHeight="1">
-      <c r="A292" s="30" t="inlineStr"/>
-      <c r="B292" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C292" s="32" t="inlineStr">
-        <is>
-          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="30" customHeight="1">
+    <row r="293" ht="31" customHeight="1">
       <c r="A293" s="30" t="inlineStr"/>
       <c r="B293" s="31" t="inlineStr">
         <is>
@@ -6273,7 +6284,7 @@
       </c>
       <c r="C293" s="32" t="inlineStr">
         <is>
-          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
+          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
         </is>
       </c>
     </row>
@@ -6286,11 +6297,11 @@
       </c>
       <c r="C294" s="32" t="inlineStr">
         <is>
-          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="34" customHeight="1">
+          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="30" customHeight="1">
       <c r="A295" s="30" t="inlineStr"/>
       <c r="B295" s="31" t="inlineStr">
         <is>
@@ -6299,11 +6310,11 @@
       </c>
       <c r="C295" s="32" t="inlineStr">
         <is>
-          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="32" customHeight="1">
+          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="34" customHeight="1">
       <c r="A296" s="30" t="inlineStr"/>
       <c r="B296" s="31" t="inlineStr">
         <is>
@@ -6312,124 +6323,106 @@
       </c>
       <c r="C296" s="32" t="inlineStr">
         <is>
+          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="34" customHeight="1">
+      <c r="A297" s="30" t="inlineStr"/>
+      <c r="B297" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C297" s="32" t="inlineStr">
+        <is>
+          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="32" customHeight="1">
+      <c r="A298" s="30" t="inlineStr"/>
+      <c r="B298" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C298" s="32" t="inlineStr">
+        <is>
           <t>⚠️ 5:00am alarm Jul 5 — set two alarms · FI571 departs 7:55am · check-in opens 5:30am · hotel is 5 min walk to terminal · boarding passes on phone tonight</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="3" customHeight="1">
-      <c r="A297" s="33" t="n"/>
-      <c r="B297" s="33" t="n"/>
-      <c r="C297" s="33" t="n"/>
-      <c r="D297" s="33" t="n"/>
-      <c r="E297" s="33" t="n"/>
-      <c r="F297" s="33" t="n"/>
-    </row>
-    <row r="298" ht="20" customHeight="1">
-      <c r="A298" s="3" t="inlineStr">
+    <row r="299" ht="3" customHeight="1">
+      <c r="A299" s="33" t="n"/>
+      <c r="B299" s="33" t="n"/>
+      <c r="C299" s="33" t="n"/>
+      <c r="D299" s="33" t="n"/>
+      <c r="E299" s="33" t="n"/>
+      <c r="F299" s="33" t="n"/>
+    </row>
+    <row r="300" ht="20" customHeight="1">
+      <c r="A300" s="3" t="inlineStr">
         <is>
           <t>DAY 16  |  Jul 5  |  Homebound — ZRH → KEF → MCO · The Final Leg  |  —  —</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="15" customHeight="1">
-      <c r="A299" s="4" t="inlineStr">
+    <row r="301" ht="15" customHeight="1">
+      <c r="A301" s="4" t="inlineStr">
         <is>
           <t>Timeline: Sat night: app check-in ▸ confirm shuttle ▸ 5am wake ▸ 5:30am Hilton shuttle (NOT walk) ▸ 5:45am Terminal 2 · Check-in Row 3 ▸ 6am security + E Gate Skymetro ▸ 7:55am FI571 ZRH→KEF ▸ KEF Pylsur layover ▸ 8:50pm MCO home</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="22" customHeight="1">
-      <c r="A300" s="5" t="inlineStr">
+    <row r="302" ht="22" customHeight="1">
+      <c r="A302" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Take hotel shuttle NOT walk — Hilton is 2km from terminal · not walkable with luggage · CHF 7/person  |  ✅ Icelandair app check-in Saturday night — digital boarding pass · fast bag drop at Check-in 2 Row 3  |  ✅ US Customs at MCO not KEF — do not leave transit area in Iceland</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="39" customHeight="1">
-      <c r="A301" s="34" t="inlineStr"/>
-      <c r="B301" s="35" t="inlineStr">
+    <row r="303" ht="39" customHeight="1">
+      <c r="A303" s="34" t="inlineStr"/>
+      <c r="B303" s="35" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C301" s="36" t="inlineStr">
+      <c r="C303" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D301" s="35" t="inlineStr"/>
-      <c r="E301" s="37" t="inlineStr">
+      <c r="D303" s="35" t="inlineStr"/>
+      <c r="E303" s="37" t="inlineStr">
         <is>
           <t>✅ Night before (Jul 4 Saturday evening) — final prep — (2) Check Europcar/Booking.com email — confirm car return was closed out correctly</t>
         </is>
       </c>
-      <c r="F301" s="38" t="inlineStr"/>
-    </row>
-    <row r="302" ht="40" customHeight="1">
-      <c r="A302" s="11" t="inlineStr"/>
-      <c r="B302" s="12" t="inlineStr">
+      <c r="F303" s="38" t="inlineStr"/>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" s="11" t="inlineStr"/>
+      <c r="B304" s="12" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C302" s="13" t="inlineStr">
+      <c r="C304" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D302" s="12" t="inlineStr"/>
-      <c r="E302" s="14" t="inlineStr">
+      <c r="D304" s="12" t="inlineStr"/>
+      <c r="E304" s="14" t="inlineStr">
         <is>
           <t>⏰ 5:00am — Wake up — perfect timing · do not wake earlier unless extra bags need special handling · hotel breakfast starts at 5:30am if needed</t>
         </is>
       </c>
-      <c r="F302" s="15" t="inlineStr"/>
-    </row>
-    <row r="303" ht="31" customHeight="1">
-      <c r="A303" s="16" t="inlineStr"/>
-      <c r="B303" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C303" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D303" s="17" t="inlineStr"/>
-      <c r="E303" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ 5:30am — Hilton shuttle — ❌ do NOT walk · 2km to terminal · CHF 7/person · confirm seat tonight</t>
-        </is>
-      </c>
-      <c r="F303" s="19" t="inlineStr">
-        <is>
-          <t>2km / CHF 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="31" customHeight="1">
-      <c r="A304" s="25" t="inlineStr"/>
-      <c r="B304" s="26" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C304" s="27" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D304" s="26" t="inlineStr"/>
-      <c r="E304" s="28" t="inlineStr">
-        <is>
-          <t>✈️ 5:45am — Terminal 2, Check-in Row 3 — bag drop opens 5:25am · digital boarding pass on phone</t>
-        </is>
-      </c>
-      <c r="F304" s="29" t="inlineStr"/>
-    </row>
-    <row r="305" ht="30" customHeight="1">
+      <c r="F304" s="15" t="inlineStr"/>
+    </row>
+    <row r="305" ht="31" customHeight="1">
       <c r="A305" s="16" t="inlineStr"/>
       <c r="B305" s="17" t="inlineStr">
         <is>
@@ -6444,56 +6437,60 @@
       <c r="D305" s="17" t="inlineStr"/>
       <c r="E305" s="18" t="inlineStr">
         <is>
+          <t>⚠️ 5:30am — Hilton shuttle — ❌ do NOT walk · 2km to terminal · CHF 7/person · confirm seat tonight</t>
+        </is>
+      </c>
+      <c r="F305" s="19" t="inlineStr">
+        <is>
+          <t>2km / CHF 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="31" customHeight="1">
+      <c r="A306" s="25" t="inlineStr"/>
+      <c r="B306" s="26" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C306" s="27" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D306" s="26" t="inlineStr"/>
+      <c r="E306" s="28" t="inlineStr">
+        <is>
+          <t>✈️ 5:45am — Terminal 2, Check-in Row 3 — bag drop opens 5:25am · digital boarding pass on phone</t>
+        </is>
+      </c>
+      <c r="F306" s="29" t="inlineStr"/>
+    </row>
+    <row r="307" ht="30" customHeight="1">
+      <c r="A307" s="16" t="inlineStr"/>
+      <c r="B307" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C307" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D307" s="17" t="inlineStr"/>
+      <c r="E307" s="18" t="inlineStr">
+        <is>
           <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
         </is>
       </c>
-      <c r="F305" s="19" t="inlineStr">
+      <c r="F307" s="19" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="306" ht="38" customHeight="1">
-      <c r="A306" s="16" t="inlineStr"/>
-      <c r="B306" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C306" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D306" s="17" t="inlineStr"/>
-      <c r="E306" s="18" t="inlineStr">
-        <is>
-          <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
-        </is>
-      </c>
-      <c r="F306" s="19" t="inlineStr"/>
-    </row>
-    <row r="307" ht="19" customHeight="1">
-      <c r="A307" s="6" t="inlineStr"/>
-      <c r="B307" s="7" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C307" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D307" s="7" t="inlineStr"/>
-      <c r="E307" s="9" t="inlineStr">
-        <is>
-          <t>✈️ 7:55am — FI571 departs ZRH → KEF</t>
-        </is>
-      </c>
-      <c r="F307" s="10" t="inlineStr"/>
-    </row>
-    <row r="308" ht="37" customHeight="1">
+    <row r="308" ht="38" customHeight="1">
       <c r="A308" s="16" t="inlineStr"/>
       <c r="B308" s="17" t="inlineStr">
         <is>
@@ -6508,62 +6505,76 @@
       <c r="D308" s="17" t="inlineStr"/>
       <c r="E308" s="18" t="inlineStr">
         <is>
+          <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
+        </is>
+      </c>
+      <c r="F308" s="19" t="inlineStr"/>
+    </row>
+    <row r="309" ht="19" customHeight="1">
+      <c r="A309" s="6" t="inlineStr"/>
+      <c r="B309" s="7" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D309" s="7" t="inlineStr"/>
+      <c r="E309" s="9" t="inlineStr">
+        <is>
+          <t>✈️ 7:55am — FI571 departs ZRH → KEF</t>
+        </is>
+      </c>
+      <c r="F309" s="10" t="inlineStr"/>
+    </row>
+    <row r="310" ht="37" customHeight="1">
+      <c r="A310" s="16" t="inlineStr"/>
+      <c r="B310" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C310" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D310" s="17" t="inlineStr"/>
+      <c r="E310" s="18" t="inlineStr">
+        <is>
           <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
         </is>
       </c>
-      <c r="F308" s="19" t="inlineStr">
+      <c r="F310" s="19" t="inlineStr">
         <is>
           <t>2hr</t>
         </is>
       </c>
     </row>
-    <row r="309" ht="35" customHeight="1">
-      <c r="A309" s="16" t="inlineStr"/>
-      <c r="B309" s="17" t="inlineStr">
+    <row r="311" ht="35" customHeight="1">
+      <c r="A311" s="16" t="inlineStr"/>
+      <c r="B311" s="17" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C309" s="16" t="inlineStr">
+      <c r="C311" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D309" s="17" t="inlineStr"/>
-      <c r="E309" s="18" t="inlineStr">
+      <c r="D311" s="17" t="inlineStr"/>
+      <c r="E311" s="18" t="inlineStr">
         <is>
           <t>8:50pm — Arrive Orlando MCO — clear US Customs + Immigration at MCO · allow 45–60 min for customs on Sunday evening</t>
         </is>
       </c>
-      <c r="F309" s="19" t="inlineStr">
+      <c r="F311" s="19" t="inlineStr">
         <is>
           <t>60 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="310" ht="34" customHeight="1">
-      <c r="A310" s="30" t="inlineStr"/>
-      <c r="B310" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C310" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
-        </is>
-      </c>
-    </row>
-    <row r="311" ht="34" customHeight="1">
-      <c r="A311" s="30" t="inlineStr"/>
-      <c r="B311" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C311" s="32" t="inlineStr">
-        <is>
-          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
         </is>
       </c>
     </row>
@@ -6576,11 +6587,11 @@
       </c>
       <c r="C312" s="32" t="inlineStr">
         <is>
-          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="313" ht="31" customHeight="1">
+          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="34" customHeight="1">
       <c r="A313" s="30" t="inlineStr"/>
       <c r="B313" s="31" t="inlineStr">
         <is>
@@ -6589,92 +6600,121 @@
       </c>
       <c r="C313" s="32" t="inlineStr">
         <is>
+          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="34" customHeight="1">
+      <c r="A314" s="30" t="inlineStr"/>
+      <c r="B314" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C314" s="32" t="inlineStr">
+        <is>
+          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="31" customHeight="1">
+      <c r="A315" s="30" t="inlineStr"/>
+      <c r="B315" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C315" s="32" t="inlineStr">
+        <is>
           <t>KEF layover — 1.5–2hrs · Pylsur hot dog (best in the world) · Skyr yoghurt · duty-free is excellent · US customs at MCO not here · do not leave transit</t>
         </is>
       </c>
     </row>
-    <row r="314" ht="3" customHeight="1">
-      <c r="A314" s="33" t="n"/>
-      <c r="B314" s="33" t="n"/>
-      <c r="C314" s="33" t="n"/>
-      <c r="D314" s="33" t="n"/>
-      <c r="E314" s="33" t="n"/>
-      <c r="F314" s="33" t="n"/>
+    <row r="316" ht="3" customHeight="1">
+      <c r="A316" s="33" t="n"/>
+      <c r="B316" s="33" t="n"/>
+      <c r="C316" s="33" t="n"/>
+      <c r="D316" s="33" t="n"/>
+      <c r="E316" s="33" t="n"/>
+      <c r="F316" s="33" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="110">
+  <mergeCells count="111">
     <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C153:F153"/>
+    <mergeCell ref="A183:F183"/>
     <mergeCell ref="C233:F233"/>
-    <mergeCell ref="A158:F158"/>
     <mergeCell ref="A198:F198"/>
     <mergeCell ref="C72:F72"/>
     <mergeCell ref="A238:F238"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A301:F301"/>
+    <mergeCell ref="A239:F239"/>
+    <mergeCell ref="A160:F160"/>
     <mergeCell ref="C136:F136"/>
+    <mergeCell ref="C314:F314"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A159:F159"/>
     <mergeCell ref="C313:F313"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A200:F200"/>
     <mergeCell ref="C234:F234"/>
-    <mergeCell ref="C116:F116"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A274:F274"/>
+    <mergeCell ref="A161:F161"/>
     <mergeCell ref="C73:F73"/>
-    <mergeCell ref="C231:F231"/>
-    <mergeCell ref="C134:F134"/>
-    <mergeCell ref="C212:F212"/>
+    <mergeCell ref="C315:F315"/>
+    <mergeCell ref="A258:F258"/>
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="A257:F257"/>
+    <mergeCell ref="C236:F236"/>
     <mergeCell ref="C214:F214"/>
-    <mergeCell ref="C251:F251"/>
-    <mergeCell ref="A237:F237"/>
+    <mergeCell ref="C120:F120"/>
+    <mergeCell ref="A124:F124"/>
     <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A277:F277"/>
     <mergeCell ref="C253:F253"/>
-    <mergeCell ref="C135:F135"/>
-    <mergeCell ref="A236:F236"/>
     <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A278:F278"/>
     <mergeCell ref="C96:F96"/>
-    <mergeCell ref="C175:F175"/>
+    <mergeCell ref="C254:F254"/>
+    <mergeCell ref="A259:F259"/>
+    <mergeCell ref="A141:F141"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="C235:F235"/>
+    <mergeCell ref="A240:F240"/>
     <mergeCell ref="A122:F122"/>
+    <mergeCell ref="C216:F216"/>
     <mergeCell ref="C98:F98"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="C274:F274"/>
+    <mergeCell ref="C137:F137"/>
     <mergeCell ref="C177:F177"/>
+    <mergeCell ref="A142:F142"/>
     <mergeCell ref="A182:F182"/>
-    <mergeCell ref="A216:F216"/>
-    <mergeCell ref="C291:F291"/>
-    <mergeCell ref="C192:F192"/>
-    <mergeCell ref="C252:F252"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A218:F218"/>
     <mergeCell ref="C71:F71"/>
+    <mergeCell ref="C138:F138"/>
     <mergeCell ref="C194:F194"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A217:F217"/>
-    <mergeCell ref="C174:F174"/>
+    <mergeCell ref="C119:F119"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A139:F139"/>
     <mergeCell ref="C155:F155"/>
     <mergeCell ref="C293:F293"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="A181:F181"/>
-    <mergeCell ref="C310:F310"/>
+    <mergeCell ref="C179:F179"/>
+    <mergeCell ref="C157:F157"/>
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A180:F180"/>
     <mergeCell ref="C294:F294"/>
-    <mergeCell ref="A299:F299"/>
+    <mergeCell ref="C215:F215"/>
     <mergeCell ref="C97:F97"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="C271:F271"/>
     <mergeCell ref="C94:F94"/>
-    <mergeCell ref="C152:F152"/>
     <mergeCell ref="A276:F276"/>
-    <mergeCell ref="A157:F157"/>
-    <mergeCell ref="C193:F193"/>
+    <mergeCell ref="C255:F255"/>
     <mergeCell ref="C176:F176"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A300:F300"/>
@@ -6683,36 +6723,34 @@
     <mergeCell ref="C95:F95"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="C178:F178"/>
-    <mergeCell ref="A256:F256"/>
+    <mergeCell ref="C297:F297"/>
     <mergeCell ref="C272:F272"/>
     <mergeCell ref="C312:F312"/>
-    <mergeCell ref="A255:F255"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A120:F120"/>
     <mergeCell ref="C296:F296"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="C292:F292"/>
+    <mergeCell ref="C298:F298"/>
+    <mergeCell ref="A302:F302"/>
     <mergeCell ref="C154:F154"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="A298:F298"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="C195:F195"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C269:F269"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="A184:F184"/>
     <mergeCell ref="C74:F74"/>
+    <mergeCell ref="A220:F220"/>
     <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C196:F196"/>
     <mergeCell ref="C117:F117"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="C270:F270"/>
-    <mergeCell ref="A275:F275"/>
+    <mergeCell ref="C180:F180"/>
     <mergeCell ref="C118:F118"/>
     <mergeCell ref="C75:F75"/>
-    <mergeCell ref="C311:F311"/>
-    <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="C232:F232"/>
-    <mergeCell ref="C213:F213"/>
+    <mergeCell ref="A123:F123"/>
     <mergeCell ref="C295:F295"/>
-    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="C273:F273"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F316"/>
+  <dimension ref="A1:F319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="47" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="16" t="inlineStr"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
@@ -1216,12 +1216,16 @@
       <c r="D13" s="17" t="inlineStr"/>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 6:00pm — Reynisfjara black sand beach — ⚠️ Sneaker waves — never turn your back to the ocean · basalt columns + sea stacks · soft golden light at 6pm · Parka app ~1000 ISK</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
+          <t>⭐ Kvernufoss — the hidden waterfall — 5 min walk from Skógafoss car park · walk behind the waterfall into the canyon · most visitors completely miss this · completely different experience from Skógafoss · free · allow 15</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>5 min / 15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="47" customHeight="1">
       <c r="A14" s="16" t="inlineStr"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -1236,49 +1240,56 @@
       <c r="D14" s="17" t="inlineStr"/>
       <c r="E14" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 6:00pm — Reynisfjara black sand beach — ⚠️ Sneaker waves — never turn your back to the ocean · basalt columns + sea stacks · soft golden light at 6pm · Parka app ~1000 ISK</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="16" t="inlineStr"/>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Jun 20</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr"/>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
           <t>7:00pm — Vík village quick stop — red-roofed church viewpoint · fill the tank at N1 station · 15 min</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="37" customHeight="1">
-      <c r="A15" s="25" t="inlineStr"/>
-      <c r="B15" s="26" t="inlineStr">
+    <row r="16" ht="37" customHeight="1">
+      <c r="A16" s="25" t="inlineStr"/>
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Jun 20</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr"/>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr"/>
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>Farmhouse Lodge, 871 Vík, Iceland — ✅ Night 1 ·  Farmhouse Lodge, 871 Vík, Iceland ·  Airbnb · check in ~7:30pm · $290.36</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>$290.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="30" t="inlineStr"/>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C16" s="32" t="inlineStr">
-        <is>
-          <t>Parka app — download before landing · pay parking at Seljalandsfoss, Skógafoss, Reynisfjara · ~1000 ISK / €7 per stop · cameras read your plate</t>
         </is>
       </c>
     </row>
@@ -1291,11 +1302,11 @@
       </c>
       <c r="C17" s="32" t="inlineStr">
         <is>
-          <t>☀️ 24-hour daylight — Jun 20 sunset 12:03am · Reynisfjara at 6pm = golden light + no tour buses · Seljalandsfoss rainbow in the spray at 3pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="29" customHeight="1">
+          <t>Parka app — download before landing · pay parking at Seljalandsfoss, Skógafoss, Reynisfjara · ~1000 ISK / €7 per stop · cameras read your plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="30" t="inlineStr"/>
       <c r="B18" s="31" t="inlineStr">
         <is>
@@ -1304,208 +1315,197 @@
       </c>
       <c r="C18" s="32" t="inlineStr">
         <is>
+          <t>☀️ 24-hour daylight — Jun 20 sunset 12:03am · Reynisfjara at 6pm = golden light + no tour buses · Seljalandsfoss rainbow in the spray at 3pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="29" customHeight="1">
+      <c r="A19" s="30" t="inlineStr"/>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
           <t>⚠️ Sneaker waves at Reynisfjara — Iceland's most dangerous beach · never turn your back to the ocean · stay well behind the safety rope</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="3" customHeight="1">
-      <c r="A19" s="33" t="n"/>
-      <c r="B19" s="33" t="n"/>
-      <c r="C19" s="33" t="n"/>
-      <c r="D19" s="33" t="n"/>
-      <c r="E19" s="33" t="n"/>
-      <c r="F19" s="33" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20" ht="3" customHeight="1">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="33" t="n"/>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>DAY 2  |  Jun 21  |  Iceland Day 2 - Glacier Walk + Jokulsarlon  |  ~480 km  ~5h driving</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Timeline: Day 2: 7am &gt; Dyrholaey &gt; Glacier walk &gt; Skaftafell &gt; Jokulsarlon &gt; Diamond Beach &gt; 2pm drive &gt; 4pm Canyon &gt; Vik &gt; 8pm BergOne</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Key: Glacier walk free - kids touch ice  |  2pm departure firm  |  Canyon on return at 4pm</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="6" t="inlineStr"/>
-      <c r="B23" s="7" t="inlineStr">
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Jun 21</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:00am — Depart Skeidflot — already 10km from Dyrhólaey · head west first</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>10km</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="16" t="inlineStr"/>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="16" t="inlineStr"/>
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Jun 21</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr"/>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr"/>
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>⭐ 7:15am — Dyrhólaey arch — clifftop viewpoint over black sand coast · puffins nesting on Lágey islet in June — lower area · 30 min</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="50" customHeight="1">
-      <c r="A25" s="20" t="inlineStr"/>
-      <c r="B25" s="21" t="inlineStr">
+    <row r="26" ht="50" customHeight="1">
+      <c r="A26" s="20" t="inlineStr"/>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Jun 21</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr"/>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr"/>
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>10:00am — Skaftafellsjökull glacier walk — easy flat trail from Skaftafell visitor centre car park · 3mi / 4.8km RT · 1–1.5hrs · walk right up to the glacier edge · feel the cold air · kids can touch the ice · Game of Th</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>8km / 5hr</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="11" t="inlineStr"/>
-      <c r="B26" s="12" t="inlineStr">
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="11" t="inlineStr"/>
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Jun 21</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr"/>
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>11:30am — Lunch at Skaftafell — food trucks in the car park (lobster soup is outstanding) · or visitor centre café · use the toilets here · allow 30 min</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="50" customHeight="1">
-      <c r="A27" s="6" t="inlineStr"/>
-      <c r="B27" s="7" t="inlineStr">
+    <row r="28" ht="50" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Jun 21</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 12:30pm — Jökulsárlón — shore walk — 45 min drive east · floating blue icebergs glowing electric blue · walk the shore · seals resting on the ice · free · allow 30 min ·  every angle is a photo</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>45 min / 30 min</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="39" customHeight="1">
-      <c r="A28" s="16" t="inlineStr"/>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="29" ht="39" customHeight="1">
+      <c r="A29" s="16" t="inlineStr"/>
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Jun 21</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr"/>
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 1:15pm — Diamond Beach — cross the bridge · crystal ice blocks on jet-black volcanic sand · ⚠️ same sneaker wave warning · allow 30 min</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="37" customHeight="1">
-      <c r="A29" s="6" t="inlineStr"/>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Jun 21</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>2:00pm — Start the drive back west — ~5hrs to BergOne incl. canyon stop · Ring Road all the way · sun still up the entire drive</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>~5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="50" customHeight="1">
+    <row r="30" ht="37" customHeight="1">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -1520,16 +1520,16 @@
       <c r="D30" s="7" t="inlineStr"/>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">⭐ ⭐ ~4:00pm — Fjaðrárgljúfur Canyon — natural break on the return drive · Route 1 passes right by · 100m deep serpentine moss-covered canyon · Game of Thrones Season 8 · 2km rim walk · ISK 1000 Parka · allow 45 min · ➡️ </t>
+          <t>2:00pm — Start the drive back west — ~5hrs to BergOne incl. canyon stop · Ring Road all the way · sun still up the entire drive</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>2km / 45 min / 5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="38" customHeight="1">
+          <t>~5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1544,16 +1544,16 @@
       <c r="D31" s="7" t="inlineStr"/>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>~5:45pm — Dinner in Vík — Smiðjan Brugghsús — best burgers in South Iceland · or Suður-Vík · breaks the drive perfectly · allow 1hr</t>
+          <t xml:space="preserve">⭐ ⭐ ~4:00pm — Fjaðrárgljúfur Canyon — natural break on the return drive · Route 1 passes right by · 100m deep serpentine moss-covered canyon · Game of Thrones Season 8 · 2km rim walk · ISK 1000 Parka · allow 45 min · ➡️ </t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="46" customHeight="1">
+          <t>2km / 45 min / 5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="7" t="inlineStr">
         <is>
@@ -1568,29 +1568,40 @@
       <c r="D32" s="7" t="inlineStr"/>
       <c r="E32" s="9" t="inlineStr">
         <is>
+          <t>~5:45pm — Dinner in Vík — Smiðjan Brugghsús — best burgers in South Iceland · or Suður-Vík · breaks the drive perfectly · allow 1hr</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
           <t>BergOne, Ytri-Njarðvík — ✅ Night 2 ·  1 Bergás, 260 Ytri-Njarðvík, Iceland ·  Booking.com · check in ~8pm · $263.98 · ⏰ alarm 5:15am Jun 22 — FI568 departs KEF 7:20am</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>$263.98</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="30" t="inlineStr"/>
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>Skaftafellsjökull glacier walk — flat easy trail from car park · kids can walk right up to the ice · free · 1–1.5hrs · bring a warm layer — temperature drops near the ice</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="31" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="30" t="inlineStr"/>
       <c r="B34" s="31" t="inlineStr">
         <is>
@@ -1599,60 +1610,53 @@
       </c>
       <c r="C34" s="32" t="inlineStr">
         <is>
+          <t>Skaftafellsjökull glacier walk — flat easy trail from car park · kids can walk right up to the ice · free · 1–1.5hrs · bring a warm layer — temperature drops near the ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="30" t="inlineStr"/>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
           <t>⏰ 3pm departure from Diamond Beach is firm — BergOne by 8pm · 5:15am alarm next morning · don't linger at Jökulsárlón or you'll be driving past midnight</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="3" customHeight="1">
-      <c r="A35" s="33" t="n"/>
-      <c r="B35" s="33" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="33" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="36" ht="3" customHeight="1">
+      <c r="A36" s="33" t="n"/>
+      <c r="B36" s="33" t="n"/>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>DAY 3  |  Jun 22  |  Fly KEF→ZRH · Spiez · Lauterbrunnen — The Alpine Entry  |  ~144 km / 90 mi  ~1h 45m</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Timeline: 5:45am KEF drop-off ▸ 7:20am FI568 ▸ 1:05pm ZRH land ▸ 2:30pm Europcar pickup ▸ 4:15pm Spiez Castle ▸ Coop Lauterbrunnen ▸ 5:45pm Camping Jungfrau ▸ Staubbach Falls evening ▸ Austrian vignette tonight</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ At Europcar: confirm vignette · confirm cross-border Italy+Austria · photograph licence plate  |  ✅ Spiez Castle gardens (free) — Route 6 lakeside road NOT the motorway tunnel  |  ✅ Coop Lauterbrunnen before 6:30pm · Staubbach Falls evening walk · Austrian vignette tonight</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="31" customHeight="1">
-      <c r="A39" s="16" t="inlineStr"/>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr"/>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>⏰ 5:45am — KEF Airport — return Budget rental car at the airport lot · shuttle back to terminal</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr"/>
-    </row>
-    <row r="40" ht="26" customHeight="1">
+    <row r="40" ht="31" customHeight="1">
       <c r="A40" s="16" t="inlineStr"/>
       <c r="B40" s="17" t="inlineStr">
         <is>
@@ -1667,16 +1671,12 @@
       <c r="D40" s="17" t="inlineStr"/>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>✈️ 7:20am — FI568 KEF → ZRH — 3hr 45min · allow 60–90 min for car pickup</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>3hr / 45min / 90 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="50" customHeight="1">
+          <t>⏰ 5:45am — KEF Airport — return Budget rental car at the airport lot · shuttle back to terminal</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
       <c r="A41" s="16" t="inlineStr"/>
       <c r="B41" s="17" t="inlineStr">
         <is>
@@ -1691,12 +1691,16 @@
       <c r="D41" s="17" t="inlineStr"/>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>1:30pm — Europcar ZRH pickup — Booking #738796923 · Volkswagen Tiguan 4x4 or similar · Europcar counter in Arrivals · 5 seats · 2 large bags · unlimited mileage · ⚠️ Confirm cross-border Italy+Austria · photograph licenc</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="inlineStr"/>
-    </row>
-    <row r="42" ht="48" customHeight="1">
+          <t>✈️ 7:20am — FI568 KEF → ZRH — 3hr 45min · allow 60–90 min for car pickup</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>3hr / 45min / 90 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="50" customHeight="1">
       <c r="A42" s="16" t="inlineStr"/>
       <c r="B42" s="17" t="inlineStr">
         <is>
@@ -1711,16 +1715,12 @@
       <c r="D42" s="17" t="inlineStr"/>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>Swiss motorway vignette — the 2026 sticker must be on the windscreen before driving on any Swiss motorway · Europcar should include it — if not, buy at any petrol station for CHF 40</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>CHF 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="37" customHeight="1">
+          <t>1:30pm — Europcar ZRH pickup — Booking #738796923 · Volkswagen Tiguan 4x4 or similar · Europcar counter in Arrivals · 5 seats · 2 large bags · unlimited mileage · ⚠️ Confirm cross-border Italy+Austria · photograph licenc</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr"/>
+    </row>
+    <row r="43" ht="48" customHeight="1">
       <c r="A43" s="16" t="inlineStr"/>
       <c r="B43" s="17" t="inlineStr">
         <is>
@@ -1735,60 +1735,60 @@
       <c r="D43" s="17" t="inlineStr"/>
       <c r="E43" s="18" t="inlineStr">
         <is>
+          <t>Swiss motorway vignette — the 2026 sticker must be on the windscreen before driving on any Swiss motorway · Europcar should include it — if not, buy at any petrol station for CHF 40</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>CHF 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="37" customHeight="1">
+      <c r="A44" s="16" t="inlineStr"/>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr"/>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
           <t>⭐ 4:15pm — Spiez Castle &amp; Lake Thun — panoramic view: Lake Thun + Niesen pyramid mountain + Eiger on clear days · allow 30 min</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="33" customHeight="1">
-      <c r="A44" s="11" t="inlineStr"/>
-      <c r="B44" s="12" t="inlineStr">
+    <row r="45" ht="33" customHeight="1">
+      <c r="A45" s="11" t="inlineStr"/>
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr"/>
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Grocery stop — Coop Supermarket, Lauterbrunnen village — this is your first Alpine dinner — make it good</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr"/>
-    </row>
-    <row r="45" ht="25" customHeight="1">
-      <c r="A45" s="25" t="inlineStr"/>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>Jun 22</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D45" s="26" t="inlineStr"/>
-      <c r="E45" s="28" t="inlineStr">
-        <is>
-          <t>5:45pm — Check-in: Camping Jungfrau, Lauterbrunnen — CHF 398 / $499</t>
-        </is>
-      </c>
-      <c r="F45" s="29" t="inlineStr">
-        <is>
-          <t>CHF 398 / $499</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="33" customHeight="1">
+      <c r="F45" s="15" t="inlineStr"/>
+    </row>
+    <row r="46" ht="25" customHeight="1">
       <c r="A46" s="25" t="inlineStr"/>
       <c r="B46" s="26" t="inlineStr">
         <is>
@@ -1803,77 +1803,88 @@
       <c r="D46" s="26" t="inlineStr"/>
       <c r="E46" s="28" t="inlineStr">
         <is>
+          <t>5:45pm — Check-in: Camping Jungfrau, Lauterbrunnen — CHF 398 / $499</t>
+        </is>
+      </c>
+      <c r="F46" s="29" t="inlineStr">
+        <is>
+          <t>CHF 398 / $499</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1">
+      <c r="A47" s="25" t="inlineStr"/>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr"/>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
           <t>⭐ ⭐ Staubbach Falls — evening walk — 5 min walk from Camping Jungfrau · walk to the base and feel the mist</t>
         </is>
       </c>
-      <c r="F46" s="29" t="inlineStr">
+      <c r="F47" s="29" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="16" t="inlineStr"/>
-      <c r="B47" s="17" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="16" t="inlineStr"/>
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr"/>
-      <c r="E47" s="18" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr"/>
+      <c r="E48" s="18" t="inlineStr">
         <is>
           <t>Tonight: buy Austrian Digital Vignette — ~€16.50</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>€16.50</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="11" t="inlineStr"/>
-      <c r="B48" s="12" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="11" t="inlineStr"/>
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Jun 22</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr"/>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr"/>
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>Dinner — or Restaurant Jungfrau in the village (10 min walk)</t>
         </is>
       </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="F49" s="15" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="30" t="inlineStr"/>
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Swiss vignette (CHF 40) — must be on windscreen before driving on Swiss motorways · Europcar should include it — verify at counter · buy at petrol station if missing · fine = CHF 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="31" customHeight="1">
+    <row r="50" ht="34" customHeight="1">
       <c r="A50" s="30" t="inlineStr"/>
       <c r="B50" s="31" t="inlineStr">
         <is>
@@ -1882,11 +1893,11 @@
       </c>
       <c r="C50" s="32" t="inlineStr">
         <is>
-          <t>Take the lakeside road — from Interlaken to Lauterbrunnen use Route 6 along Lake Thun shore · far more scenic than motorway tunnels · adds only 5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+          <t>⚠️ Swiss vignette (CHF 40) — must be on windscreen before driving on Swiss motorways · Europcar should include it — verify at counter · buy at petrol station if missing · fine = CHF 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1">
       <c r="A51" s="30" t="inlineStr"/>
       <c r="B51" s="31" t="inlineStr">
         <is>
@@ -1895,11 +1906,11 @@
       </c>
       <c r="C51" s="32" t="inlineStr">
         <is>
-          <t>Austrian vignette tonight — asfinag.at · ~€16.50 · need your licence plate number · cameras check automatically when you enter Austria Jun 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="34" customHeight="1">
+          <t>Take the lakeside road — from Interlaken to Lauterbrunnen use Route 6 along Lake Thun shore · far more scenic than motorway tunnels · adds only 5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
       <c r="A52" s="30" t="inlineStr"/>
       <c r="B52" s="31" t="inlineStr">
         <is>
@@ -1908,84 +1919,73 @@
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
+          <t>Austrian vignette tonight — asfinag.at · ~€16.50 · need your licence plate number · cameras check automatically when you enter Austria Jun 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="30" t="inlineStr"/>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
           <t>Grocery strategy — Coop Lauterbrunnen today (Swiss days) · BIG shop at Rewe/Aldi Berchtesgaden Jun 24 (German prices 35% cheaper) · Hofer Bad Goisern Jun 27 (Austria + Dolomites days)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="3" customHeight="1">
-      <c r="A53" s="33" t="n"/>
-      <c r="B53" s="33" t="n"/>
-      <c r="C53" s="33" t="n"/>
-      <c r="D53" s="33" t="n"/>
-      <c r="E53" s="33" t="n"/>
-      <c r="F53" s="33" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="54" ht="3" customHeight="1">
+      <c r="A54" s="33" t="n"/>
+      <c r="B54" s="33" t="n"/>
+      <c r="C54" s="33" t="n"/>
+      <c r="D54" s="33" t="n"/>
+      <c r="E54" s="33" t="n"/>
+      <c r="F54" s="33" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>DAY 4  |  Jun 23  |  Oeschinensee Heuberg Ridge + Grindelwald First — Double Gondola Day  |  ~100 km / 62 mi  ~2h 30m incl. mountain roads</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Timeline: 7:30am Lauterbrunnen ▸ 8:15am Kandersteg park ▸ 8:30am Oeschinensee gondola ▸ Heuberg Ridge Trail #8 ▸ 10am viewpoint ▸ 11am lakeside picnic ▸ 12pm drive Grindelwald ▸ 1:45pm Firstbahn ▸ Cliff Walk ▸ Bachalpsee ▸ 4:30pm turn back ▸ 5pm First station ▸ 6:30pm Lauterbrunnen</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Heuberg Ridge Trail #8 — follow signs Läger → Heuberg · bird's-eye lake view · NOT the direct path  |  ⚠️ Last gondola down from First is 6:00pm — leave Bachalpsee by 4:30pm latest  |  ✅ Packed picnic at Heuberg viewpoint — bread + Swiss cheese from Coop last night</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="6" t="inlineStr"/>
-      <c r="B57" s="7" t="inlineStr">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="6" t="inlineStr"/>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:30am — Depart Lauterbrunnen — 45 min scenic drive to Kandersteg via the Kandertal valley</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
         <is>
           <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="23" customHeight="1">
-      <c r="A58" s="16" t="inlineStr"/>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr"/>
-      <c r="E58" s="18" t="inlineStr">
-        <is>
-          <t>8:15am — Park at Oeschinen Talstation — parking ~CHF 8</t>
-        </is>
-      </c>
-      <c r="F58" s="19" t="inlineStr">
-        <is>
-          <t>CHF 8</t>
         </is>
       </c>
     </row>
@@ -2004,128 +2004,132 @@
       <c r="D59" s="17" t="inlineStr"/>
       <c r="E59" s="18" t="inlineStr">
         <is>
+          <t>8:15am — Park at Oeschinen Talstation — parking ~CHF 8</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>CHF 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="23" customHeight="1">
+      <c r="A60" s="16" t="inlineStr"/>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr"/>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 8:30am — Oeschinensee gondola — ✅ Pre-booked · CHF 125</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>CHF 125</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="39" customHeight="1">
-      <c r="A60" s="20" t="inlineStr"/>
-      <c r="B60" s="21" t="inlineStr">
+    <row r="61" ht="39" customHeight="1">
+      <c r="A61" s="20" t="inlineStr"/>
+      <c r="B61" s="21" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C60" s="22" t="inlineStr">
+      <c r="C61" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D60" s="21" t="inlineStr"/>
-      <c r="E60" s="23" t="inlineStr">
+      <c r="D61" s="21" t="inlineStr"/>
+      <c r="E61" s="23" t="inlineStr">
         <is>
           <t>Heuberg Ridge Hike — Trail #8 (Priority) — ⚠️ Some steep drop-offs near the cliffs — if anyone has severe vertigo stick to lower Trail #1</t>
         </is>
       </c>
-      <c r="F60" s="24" t="inlineStr"/>
-    </row>
-    <row r="61" ht="23" customHeight="1">
-      <c r="A61" s="16" t="inlineStr"/>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="F61" s="24" t="inlineStr"/>
+    </row>
+    <row r="62" ht="23" customHeight="1">
+      <c r="A62" s="16" t="inlineStr"/>
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C61" s="16" t="inlineStr">
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr"/>
-      <c r="E61" s="18" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr"/>
+      <c r="E62" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 10:00am — Heuberg Panoramic Viewpoint — allow 30 min</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="20" t="inlineStr"/>
-      <c r="B62" s="21" t="inlineStr">
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="20" t="inlineStr"/>
+      <c r="B63" s="21" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C62" s="22" t="inlineStr">
+      <c r="C63" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D62" s="21" t="inlineStr"/>
-      <c r="E62" s="23" t="inlineStr">
+      <c r="D63" s="21" t="inlineStr"/>
+      <c r="E63" s="23" t="inlineStr">
         <is>
           <t>11:00am — Descent to lakeside — allow 1hr total</t>
         </is>
       </c>
-      <c r="F62" s="24" t="inlineStr">
+      <c r="F63" s="24" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="43" customHeight="1">
-      <c r="A63" s="6" t="inlineStr"/>
-      <c r="B63" s="7" t="inlineStr">
+    <row r="64" ht="43" customHeight="1">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>12:00pm — Depart Kandersteg → Grindelwald — cable car down first · 1hr 15min drive · park at Parkhaus Eiger+ or Sportzentrum — near Firstbahn · ~CHF 10–15</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>1hr / 15min / CHF 10</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="29" customHeight="1">
-      <c r="A64" s="16" t="inlineStr"/>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr"/>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 1:45pm — Grindelwald Firstbahn gondola — ✅ Booking #238070 · ride to First (2,168m)</t>
-        </is>
-      </c>
-      <c r="F64" s="19" t="inlineStr"/>
-    </row>
-    <row r="65" ht="33" customHeight="1">
+    <row r="65" ht="29" customHeight="1">
       <c r="A65" s="16" t="inlineStr"/>
       <c r="B65" s="17" t="inlineStr">
         <is>
@@ -2140,64 +2144,60 @@
       <c r="D65" s="17" t="inlineStr"/>
       <c r="E65" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 1:45pm — Grindelwald Firstbahn gondola — ✅ Booking #238070 · ride to First (2,168m)</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr"/>
+    </row>
+    <row r="66" ht="33" customHeight="1">
+      <c r="A66" s="16" t="inlineStr"/>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr"/>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 2:15pm — First Cliff Walk — Tissot-sponsored glass floor section — walk over 45m of air · allow 30 min</t>
         </is>
       </c>
-      <c r="F65" s="19" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="50" customHeight="1">
-      <c r="A66" s="20" t="inlineStr"/>
-      <c r="B66" s="21" t="inlineStr">
+    <row r="67" ht="50" customHeight="1">
+      <c r="A67" s="20" t="inlineStr"/>
+      <c r="B67" s="21" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C66" s="22" t="inlineStr">
+      <c r="C67" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D66" s="21" t="inlineStr"/>
-      <c r="E66" s="23" t="inlineStr">
+      <c r="D67" s="21" t="inlineStr"/>
+      <c r="E67" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">2:45pm — Bachalpsee hike — Trail from First station · 3km / 1.9mi one-way · ➡️ Optional if tired from Heuberg Ridge: stay at First station · enjoy the Cliff Walk views · skip the 6km RT hike · no shame — Heuberg was the </t>
         </is>
       </c>
-      <c r="F66" s="24" t="inlineStr">
+      <c r="F67" s="24" t="inlineStr">
         <is>
           <t>3km / 6km</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="16" t="inlineStr"/>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>Jun 23</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr"/>
-      <c r="E67" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 3:45pm — Bachalpsee "Blue Jewel" — allow 30–45 min</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
+    <row r="68" ht="22" customHeight="1">
       <c r="A68" s="16" t="inlineStr"/>
       <c r="B68" s="17" t="inlineStr">
         <is>
@@ -2212,77 +2212,88 @@
       <c r="D68" s="17" t="inlineStr"/>
       <c r="E68" s="18" t="inlineStr">
         <is>
+          <t>⭐ 3:45pm — Bachalpsee "Blue Jewel" — allow 30–45 min</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="16" t="inlineStr"/>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr"/>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
           <t>⚠️ 5:00pm — Back at First station — LAST gondola down is 6:00pm — do not miss it · allow 45 min walk back from Bachalpsee</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="7" t="inlineStr">
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="6" t="inlineStr"/>
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="9" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>5:30pm — Gondola down → drive back — 20 min drive to Camping Jungfrau, Lauterbrunnen · arrive ~6:30pm</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="34" customHeight="1">
-      <c r="A70" s="11" t="inlineStr"/>
-      <c r="B70" s="12" t="inlineStr">
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="11" t="inlineStr"/>
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>Jun 23</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr"/>
-      <c r="E70" s="14" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr"/>
+      <c r="E71" s="14" t="inlineStr">
         <is>
           <t>Dinner — campsite kitchen with Coop groceries · or Airtime Restaurant — in Lauterbrunnen village (10 min walk)</t>
         </is>
       </c>
-      <c r="F70" s="15" t="inlineStr">
+      <c r="F71" s="15" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="19" customHeight="1">
-      <c r="A71" s="30" t="inlineStr"/>
-      <c r="B71" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>✅ Grindelwald Firstbahn #238070 · Jun 23 · 2 adults + 2 children</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="34" customHeight="1">
+    <row r="72" ht="19" customHeight="1">
       <c r="A72" s="30" t="inlineStr"/>
       <c r="B72" s="31" t="inlineStr">
         <is>
@@ -2291,7 +2302,7 @@
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Heuberg Trail #8 — steep drop-offs — moderate difficulty · if severe vertigo in the family, take lower Trail #1 to lake directly · Trail #8 has exposed cliff sections near the viewpoint</t>
+          <t>✅ Grindelwald Firstbahn #238070 · Jun 23 · 2 adults + 2 children</t>
         </is>
       </c>
     </row>
@@ -2304,11 +2315,11 @@
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
-          <t>Bachalpsee in late June — small snow patches still possible on the trail · hiking boots with grip essential · cows with cowbells in the meadows · bring layers — 2,168m = cold even in June</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="32" customHeight="1">
+          <t>⚠️ Heuberg Trail #8 — steep drop-offs — moderate difficulty · if severe vertigo in the family, take lower Trail #1 to lake directly · Trail #8 has exposed cliff sections near the viewpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1">
       <c r="A74" s="30" t="inlineStr"/>
       <c r="B74" s="31" t="inlineStr">
         <is>
@@ -2317,11 +2328,11 @@
       </c>
       <c r="C74" s="32" t="inlineStr">
         <is>
-          <t>Grindelwald parking 2026 — very busy · Parkhaus Eiger+ or Sportzentrum first · if full: Grindelwald Grund → short train/bus to Firstbahn · CHF 10–15 either way</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="34" customHeight="1">
+          <t>Bachalpsee in late June — small snow patches still possible on the trail · hiking boots with grip essential · cows with cowbells in the meadows · bring layers — 2,168m = cold even in June</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
       <c r="A75" s="30" t="inlineStr"/>
       <c r="B75" s="31" t="inlineStr">
         <is>
@@ -2330,88 +2341,77 @@
       </c>
       <c r="C75" s="32" t="inlineStr">
         <is>
+          <t>Grindelwald parking 2026 — very busy · Parkhaus Eiger+ or Sportzentrum first · if full: Grindelwald Grund → short train/bus to Firstbahn · CHF 10–15 either way</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="30" t="inlineStr"/>
+      <c r="B76" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
           <t>Pack picnic tonight — Coop Lauterbrunnen · fresh bread + Swiss mountain cheese + fruit + water · eat at Heuberg viewpoint 10am · far better than any restaurant on the mountain</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="3" customHeight="1">
-      <c r="A76" s="33" t="n"/>
-      <c r="B76" s="33" t="n"/>
-      <c r="C76" s="33" t="n"/>
-      <c r="D76" s="33" t="n"/>
-      <c r="E76" s="33" t="n"/>
-      <c r="F76" s="33" t="n"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="77" ht="3" customHeight="1">
+      <c r="A77" s="33" t="n"/>
+      <c r="B77" s="33" t="n"/>
+      <c r="C77" s="33" t="n"/>
+      <c r="D77" s="33" t="n"/>
+      <c r="E77" s="33" t="n"/>
+      <c r="F77" s="33" t="n"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>DAY 5  |  Jun 24  |  Lauterbrunnen → Berchtesgaden — The Cross-Country Push  |  ~595 km / 370 mi  ~6h non-stop · longest drive day</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:30am Trümmelbach Falls ▸ 10am coffee ▸ 10:45am depart ▸ 12:30pm Vaduz/Liechtenstein lunch ▸ Germany border ▸ A8 Munich area ▸ Chiemsee stop ▸ Hintersee photo ▸ 5:30pm Berchtesgaden</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Trümmelbach Falls first — opens 9am · 3 min from campsite · wear waterproofs · do not skip  |   Vaduz/Liechtenstein lunch stop — Country #3 · passport stamp CHF 3 · 45 min total  |  ⚠️ Check A8 before Munich — if 60+ min delay switch to B31/B12 Deutsche Alpenstraße</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="35" customHeight="1">
-      <c r="A80" s="6" t="inlineStr"/>
-      <c r="B80" s="7" t="inlineStr">
+    <row r="81" ht="35" customHeight="1">
+      <c r="A81" s="6" t="inlineStr"/>
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr"/>
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:30am — Checkout Camping Jungfrau — walk to Trümmelbach Falls first (3 min drive or 15 min walk from the campsite)</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>3 min / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="16" t="inlineStr"/>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr"/>
-      <c r="E81" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:30am — Trümmelbach Falls — be first at the gate when it opens at 9:00am · ~€12/adult</t>
-        </is>
-      </c>
-      <c r="F81" s="19" t="inlineStr">
-        <is>
-          <t>€12</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="21" customHeight="1">
+    <row r="82" ht="30" customHeight="1">
       <c r="A82" s="16" t="inlineStr"/>
       <c r="B82" s="17" t="inlineStr">
         <is>
@@ -2426,84 +2426,88 @@
       <c r="D82" s="17" t="inlineStr"/>
       <c r="E82" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 8:30am — Trümmelbach Falls — be first at the gate when it opens at 9:00am · ~€12/adult</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="inlineStr">
+        <is>
+          <t>€12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="21" customHeight="1">
+      <c r="A83" s="16" t="inlineStr"/>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr"/>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
           <t>Lauterbrunnen valley exit photo stop — 5 min</t>
         </is>
       </c>
-      <c r="F82" s="19" t="inlineStr">
+      <c r="F83" s="19" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="41" customHeight="1">
-      <c r="A83" s="25" t="inlineStr"/>
-      <c r="B83" s="26" t="inlineStr">
+    <row r="84" ht="41" customHeight="1">
+      <c r="A84" s="25" t="inlineStr"/>
+      <c r="B84" s="26" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C83" s="27" t="inlineStr">
+      <c r="C84" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D83" s="26" t="inlineStr"/>
-      <c r="E83" s="28" t="inlineStr">
+      <c r="D84" s="26" t="inlineStr"/>
+      <c r="E84" s="28" t="inlineStr">
         <is>
           <t>☕ 10:00am — Final Lauterbrunnen coffee — quick espresso in the village before the motorway · Airtime Café or Camping Jungfrau café · allow 20 min</t>
         </is>
       </c>
-      <c r="F83" s="29" t="inlineStr">
+      <c r="F84" s="29" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="23" customHeight="1">
-      <c r="A84" s="6" t="inlineStr"/>
-      <c r="B84" s="7" t="inlineStr">
+    <row r="85" ht="23" customHeight="1">
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr"/>
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>10:45am — Depart Lauterbrunnen → Berchtesgaden — ~595 km</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>~595 km</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="39" customHeight="1">
-      <c r="A85" s="16" t="inlineStr"/>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>Jun 24</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D85" s="17" t="inlineStr"/>
-      <c r="E85" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ Austrian Pfändertunnel near Bregenz — you clip a corner of Austria near Bregenz on the standard route · your Austrian Digital Vignette</t>
-        </is>
-      </c>
-      <c r="F85" s="19" t="inlineStr"/>
-    </row>
-    <row r="86" ht="23" customHeight="1">
+    <row r="86" ht="39" customHeight="1">
       <c r="A86" s="16" t="inlineStr"/>
       <c r="B86" s="17" t="inlineStr">
         <is>
@@ -2518,181 +2522,188 @@
       <c r="D86" s="17" t="inlineStr"/>
       <c r="E86" s="18" t="inlineStr">
         <is>
+          <t>⚠️ Austrian Pfändertunnel near Bregenz — you clip a corner of Austria near Bregenz on the standard route · your Austrian Digital Vignette</t>
+        </is>
+      </c>
+      <c r="F86" s="19" t="inlineStr"/>
+    </row>
+    <row r="87" ht="23" customHeight="1">
+      <c r="A87" s="16" t="inlineStr"/>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr"/>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
           <t>⛽ Fuel strategy — first opportunity: Bregenz area (Austria)</t>
         </is>
       </c>
-      <c r="F86" s="19" t="inlineStr"/>
-    </row>
-    <row r="87" ht="50" customHeight="1">
-      <c r="A87" s="11" t="inlineStr"/>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="F87" s="19" t="inlineStr"/>
+    </row>
+    <row r="88" ht="50" customHeight="1">
+      <c r="A88" s="11" t="inlineStr"/>
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr"/>
-      <c r="E87" s="14" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr"/>
+      <c r="E88" s="14" t="inlineStr">
         <is>
           <t>12:30pm — Lunch stop: Vaduz, Liechtenstein — 45 min “Country #3” stop · passport stamp CHF 3 · ➡️ If A8 is red on Google Maps: skip Vaduz entirely — treat it as a drive-through · grab food at a German Autobahn stop inste</t>
         </is>
       </c>
-      <c r="F87" s="15" t="inlineStr">
+      <c r="F88" s="15" t="inlineStr">
         <is>
           <t>45 min / CHF 3</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="50" customHeight="1">
-      <c r="A88" s="16" t="inlineStr"/>
-      <c r="B88" s="17" t="inlineStr">
+    <row r="89" ht="50" customHeight="1">
+      <c r="A89" s="16" t="inlineStr"/>
+      <c r="B89" s="17" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C88" s="16" t="inlineStr">
+      <c r="C89" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr"/>
-      <c r="E88" s="18" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr"/>
+      <c r="E89" s="18" t="inlineStr">
         <is>
           <t>⚠️ A8 Construction Warning 2026 — A8 between Ulm and Munich is under major renovation in 2026 · check Google Maps live before Munich · if showing 60+ min red delay: switch to the scenic B31/B12 southern route — slower bu</t>
         </is>
       </c>
-      <c r="F88" s="19" t="inlineStr"/>
-    </row>
-    <row r="89" ht="47" customHeight="1">
-      <c r="A89" s="11" t="inlineStr"/>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="F89" s="19" t="inlineStr"/>
+    </row>
+    <row r="90" ht="47" customHeight="1">
+      <c r="A90" s="11" t="inlineStr"/>
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C89" s="13" t="inlineStr">
+      <c r="C90" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr"/>
-      <c r="E89" s="14" t="inlineStr">
+      <c r="D90" s="12" t="inlineStr"/>
+      <c r="E90" s="14" t="inlineStr">
         <is>
           <t>Grocery stop — REWE or Lidl, Lindau or Berchtesgaden — cross into Germany at Lindau — first stop after Switzerland · or use REWE Berchtesgaden on arrival (Maximilianstr. 26)</t>
         </is>
       </c>
-      <c r="F89" s="15" t="inlineStr"/>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="16" t="inlineStr"/>
-      <c r="B90" s="17" t="inlineStr">
+      <c r="F90" s="15" t="inlineStr"/>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="16" t="inlineStr"/>
+      <c r="B91" s="17" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C90" s="16" t="inlineStr">
+      <c r="C91" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D90" s="17" t="inlineStr"/>
-      <c r="E90" s="18" t="inlineStr">
+      <c r="D91" s="17" t="inlineStr"/>
+      <c r="E91" s="18" t="inlineStr">
         <is>
           <t>Chiemsee photo stop — Bernau Exit 106 — 2km to Felden lakeshore · allow 15 min</t>
         </is>
       </c>
-      <c r="F90" s="19" t="inlineStr">
+      <c r="F91" s="19" t="inlineStr">
         <is>
           <t>2km / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="48" customHeight="1">
-      <c r="A91" s="6" t="inlineStr"/>
-      <c r="B91" s="7" t="inlineStr">
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="6" t="inlineStr"/>
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr"/>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="9" t="inlineStr">
         <is>
           <t>~5:00pm — Hintersee lake photo stop — 15 min drive from Berchtesgaden · allow 20 min · ➡️ Optional on arrival — skip if tired: easily visited on Day 6 or 7 when already based locally</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t>15 min / 20 min</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="29" customHeight="1">
-      <c r="A92" s="25" t="inlineStr"/>
-      <c r="B92" s="26" t="inlineStr">
+    <row r="93" ht="29" customHeight="1">
+      <c r="A93" s="25" t="inlineStr"/>
+      <c r="B93" s="26" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C92" s="27" t="inlineStr">
+      <c r="C93" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D92" s="26" t="inlineStr"/>
-      <c r="E92" s="28" t="inlineStr">
+      <c r="D93" s="26" t="inlineStr"/>
+      <c r="E93" s="28" t="inlineStr">
         <is>
           <t>~5:30pm — Check-in: One-Bedroom Apartment, Berchtesgaden —  Booking.com message host</t>
         </is>
       </c>
-      <c r="F92" s="29" t="inlineStr"/>
-    </row>
-    <row r="93" ht="24" customHeight="1">
-      <c r="A93" s="11" t="inlineStr"/>
-      <c r="B93" s="12" t="inlineStr">
+      <c r="F93" s="29" t="inlineStr"/>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="11" t="inlineStr"/>
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>Jun 24</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr"/>
-      <c r="E93" s="14" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr"/>
+      <c r="E94" s="14" t="inlineStr">
         <is>
           <t>Dinner — Berchtesgaden — Bräustüberl Berchtesgaden — allow 1hr</t>
         </is>
       </c>
-      <c r="F93" s="15" t="inlineStr">
+      <c r="F94" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="34" customHeight="1">
-      <c r="A94" s="30" t="inlineStr"/>
-      <c r="B94" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C94" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Austrian vignette at Pfändertunnel — cameras check automatically near Bregenz · no booth to stop at · instant fine if not purchased · should be bought at asfinag.at on Day 3 evening</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="32" customHeight="1">
+    <row r="95" ht="34" customHeight="1">
       <c r="A95" s="30" t="inlineStr"/>
       <c r="B95" s="31" t="inlineStr">
         <is>
@@ -2701,11 +2712,11 @@
       </c>
       <c r="C95" s="32" t="inlineStr">
         <is>
-          <t>⚠️ A8 2026 construction — major roadworks Ulm–Munich · check Google Maps before Munich · alternative: B31/B12 Deutsche Alpenstraße — beautiful but adds 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="29" customHeight="1">
+          <t>⚠️ Austrian vignette at Pfändertunnel — cameras check automatically near Bregenz · no booth to stop at · instant fine if not purchased · should be bought at asfinag.at on Day 3 evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
       <c r="A96" s="30" t="inlineStr"/>
       <c r="B96" s="31" t="inlineStr">
         <is>
@@ -2714,7 +2725,7 @@
       </c>
       <c r="C96" s="32" t="inlineStr">
         <is>
-          <t>⛽ Fuel — fill in Austria (Bregenz area) or Germany · never in Switzerland · Rosenheim or Bad Reichenhall last cheap before Berchtesgaden</t>
+          <t>⚠️ A8 2026 construction — major roadworks Ulm–Munich · check Google Maps before Munich · alternative: B31/B12 Deutsche Alpenstraße — beautiful but adds 45 min</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2738,7 @@
       </c>
       <c r="C97" s="32" t="inlineStr">
         <is>
-          <t>Liechtenstein passport stamp — tourist office in Vaduz · CHF 3 per passport · one of the rarest stamps in Europe · great for the kids</t>
+          <t>⛽ Fuel — fill in Austria (Bregenz area) or Germany · never in Switzerland · Rosenheim or Bad Reichenhall last cheap before Berchtesgaden</t>
         </is>
       </c>
     </row>
@@ -2740,88 +2751,77 @@
       </c>
       <c r="C98" s="32" t="inlineStr">
         <is>
+          <t>Liechtenstein passport stamp — tourist office in Vaduz · CHF 3 per passport · one of the rarest stamps in Europe · great for the kids</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="29" customHeight="1">
+      <c r="A99" s="30" t="inlineStr"/>
+      <c r="B99" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
           <t>Grocery — REWE Berchtesgaden (Maximilianstr. 26) · open until 8pm · German prices 30–40% cheaper than Swiss · stock up for 2 nights here</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="3" customHeight="1">
-      <c r="A99" s="33" t="n"/>
-      <c r="B99" s="33" t="n"/>
-      <c r="C99" s="33" t="n"/>
-      <c r="D99" s="33" t="n"/>
-      <c r="E99" s="33" t="n"/>
-      <c r="F99" s="33" t="n"/>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="100" ht="3" customHeight="1">
+      <c r="A100" s="33" t="n"/>
+      <c r="B100" s="33" t="n"/>
+      <c r="C100" s="33" t="n"/>
+      <c r="D100" s="33" t="n"/>
+      <c r="E100" s="33" t="n"/>
+      <c r="F100" s="33" t="n"/>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>DAY 6  |  Jun 25  |  Königssee · Eagle's Nest · Hintersee — Lakes, Legends &amp; Luxury  |  ~80 km / 50 mi  ~2h total · short loops around Berchtesgaden</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:15am Königssee park ▸ 8:30am boat to Salet ▸ Obersee + Röthbachfall 9:45am ▸ St. Bartholomä lunch 12pm ▸ 1:30pm Eagle's Nest Kehlsteinbus ▸ 4pm Rossfeld Road ▸ 4:45pm Hintersee/Zauberwald ▸ 6:30pm Berchtesgaden dinner</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Go to Salet (final stop) NOT St. Bartholomä — Obersee + Röthbachfall is the highlight  |  ⚠️ Eagle's Nest: register return bus time at counter BEFORE taking elevator — fills fast  |  ✅ Rossfeld Road after Eagle's Nest — same area · €9 · straddle the D/A border stone  |  ️ Eagle's Nest if clear · Salt Mine if foggy — both at 1:30pm · same area · book Salt Mine online at salzbergwerk.de</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="45" customHeight="1">
-      <c r="A103" s="6" t="inlineStr"/>
-      <c r="B103" s="7" t="inlineStr">
+    <row r="104" ht="45" customHeight="1">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr"/>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:15am — Königssee Seelände car park — only 10 min drive from Berchtesgaden apartment · car park is huge but the dock is a 10 min walk from the lot — factor this in</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
+      <c r="F104" s="10" t="inlineStr">
         <is>
           <t>10 min / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="50" customHeight="1">
-      <c r="A104" s="16" t="inlineStr"/>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D104" s="17" t="inlineStr"/>
-      <c r="E104" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:30am — Königssee electric boat — completely silent electric boats — only powered vessels allowed on this lake · ⚠️ Go all the way to Salet — 55 min to Salet · ~€28–30 return to Salet per adult</t>
-        </is>
-      </c>
-      <c r="F104" s="19" t="inlineStr">
-        <is>
-          <t>55 min / €28</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="32" customHeight="1">
+    <row r="105" ht="50" customHeight="1">
       <c r="A105" s="16" t="inlineStr"/>
       <c r="B105" s="17" t="inlineStr">
         <is>
@@ -2836,16 +2836,16 @@
       <c r="D105" s="17" t="inlineStr"/>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>The mountain echo tradition — midway the captain stops and plays a trumpet · have €1–2 ready to tip</t>
+          <t>⭐ ⭐ 8:30am — Königssee electric boat — completely silent electric boats — only powered vessels allowed on this lake · ⚠️ Go all the way to Salet — 55 min to Salet · ~€28–30 return to Salet per adult</t>
         </is>
       </c>
       <c r="F105" s="19" t="inlineStr">
         <is>
-          <t>€1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="50" customHeight="1">
+          <t>55 min / €28</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
       <c r="A106" s="16" t="inlineStr"/>
       <c r="B106" s="17" t="inlineStr">
         <is>
@@ -2860,12 +2860,12 @@
       <c r="D106" s="17" t="inlineStr"/>
       <c r="E106" s="18" t="inlineStr">
         <is>
-          <t>9:45am — Obersee &amp; Röthbachfall — flat 15 min walk from Salet dock · mirror-like glacial lake · iconic half-submerged wooden boathouse · walk all the way to Fischunkelalm hut on the far side · look straight up the valley</t>
+          <t>The mountain echo tradition — midway the captain stops and plays a trumpet · have €1–2 ready to tip</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
         <is>
-          <t>15 min / 5hr</t>
+          <t>€1</t>
         </is>
       </c>
     </row>
@@ -2884,112 +2884,112 @@
       <c r="D107" s="17" t="inlineStr"/>
       <c r="E107" s="18" t="inlineStr">
         <is>
+          <t>9:45am — Obersee &amp; Röthbachfall — flat 15 min walk from Salet dock · mirror-like glacial lake · iconic half-submerged wooden boathouse · walk all the way to Fischunkelalm hut on the far side · look straight up the valley</t>
+        </is>
+      </c>
+      <c r="F107" s="19" t="inlineStr">
+        <is>
+          <t>15 min / 5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="50" customHeight="1">
+      <c r="A108" s="16" t="inlineStr"/>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr"/>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
           <t>Malerwinkel — Painter's Corner viewpoint — on the walk back from Obersee toward St. Bartholomä · wooden bench overlook · most famous postcard view of the lake · red onion domes of St. Bartholomä perfectly reflected · mos</t>
         </is>
       </c>
-      <c r="F107" s="19" t="inlineStr">
+      <c r="F108" s="19" t="inlineStr">
         <is>
           <t>2 min</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="11" t="inlineStr"/>
-      <c r="B108" s="12" t="inlineStr">
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="11" t="inlineStr"/>
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C108" s="13" t="inlineStr">
+      <c r="C109" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D108" s="12" t="inlineStr"/>
-      <c r="E108" s="14" t="inlineStr">
+      <c r="D109" s="12" t="inlineStr"/>
+      <c r="E109" s="14" t="inlineStr">
         <is>
           <t>12:00pm — St. Bartholomä lunch stop — allow 45 min</t>
         </is>
       </c>
-      <c r="F108" s="15" t="inlineStr">
+      <c r="F109" s="15" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="16" t="inlineStr"/>
-      <c r="B109" s="17" t="inlineStr">
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="16" t="inlineStr"/>
+      <c r="B110" s="17" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C109" s="16" t="inlineStr">
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D109" s="17" t="inlineStr"/>
-      <c r="E109" s="18" t="inlineStr">
+      <c r="D110" s="17" t="inlineStr"/>
+      <c r="E110" s="18" t="inlineStr">
         <is>
           <t>⛵ 12:45pm — Final boat back to Königssee Seelände — 35 min · arrive ~1:15pm · walk 10 min to car park</t>
         </is>
       </c>
-      <c r="F109" s="19" t="inlineStr">
+      <c r="F110" s="19" t="inlineStr">
         <is>
           <t>35 min / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="50" customHeight="1">
-      <c r="A110" s="6" t="inlineStr"/>
-      <c r="B110" s="7" t="inlineStr">
+    <row r="111" ht="50" customHeight="1">
+      <c r="A111" s="6" t="inlineStr"/>
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr"/>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 1:30pm — Eagle's Nest (Kehlsteinhaus) — drive 10 min to Obersalzberg car park · Kehlsteinbus ~€32 (bus + brass elevator) ·  Golden Rule: immediately book 4:00 or 4:15pm return slot at top counter · 360° Alpine panora</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>10 min / €32 / 2hr</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="50" customHeight="1">
-      <c r="A111" s="16" t="inlineStr"/>
-      <c r="B111" s="17" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D111" s="17" t="inlineStr"/>
-      <c r="E111" s="18" t="inlineStr">
-        <is>
-          <t>➕ Optional: Berchtesgaden Salt Mine — ☁️ Weather backup for Eagle's Nest · Salzburger Str. 24 · open 9am–5pm · ~€20/adult · ~€12/child · miners' overalls + underground raft on salt lake + glittering crystals · constant 1</t>
-        </is>
-      </c>
-      <c r="F111" s="19" t="inlineStr">
-        <is>
-          <t>€20 / €12 / 2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="24" customHeight="1">
+    <row r="112" ht="50" customHeight="1">
       <c r="A112" s="16" t="inlineStr"/>
       <c r="B112" s="17" t="inlineStr">
         <is>
@@ -3004,16 +3004,16 @@
       <c r="D112" s="17" t="inlineStr"/>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>Dokumentation Obersalzberg WWII Museum — 30 min · €10/adult</t>
+          <t>➕ Optional: Berchtesgaden Salt Mine — ☁️ Weather backup for Eagle's Nest · Salzburger Str. 24 · open 9am–5pm · ~€20/adult · ~€12/child · miners' overalls + underground raft on salt lake + glittering crystals · constant 1</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>30 min / €10</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="30" customHeight="1">
+          <t>€20 / €12 / 2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="24" customHeight="1">
       <c r="A113" s="16" t="inlineStr"/>
       <c r="B113" s="17" t="inlineStr">
         <is>
@@ -3028,93 +3028,104 @@
       <c r="D113" s="17" t="inlineStr"/>
       <c r="E113" s="18" t="inlineStr">
         <is>
+          <t>Dokumentation Obersalzberg WWII Museum — 30 min · €10/adult</t>
+        </is>
+      </c>
+      <c r="F113" s="19" t="inlineStr">
+        <is>
+          <t>30 min / €10</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="16" t="inlineStr"/>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr"/>
+      <c r="E114" s="18" t="inlineStr">
+        <is>
           <t>⭐ ~4:00pm — Rossfeld Panorama Road — €9 toll · Germany's highest panoramic toll road at 1,570m</t>
         </is>
       </c>
-      <c r="F113" s="19" t="inlineStr">
+      <c r="F114" s="19" t="inlineStr">
         <is>
           <t>€9</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="35" customHeight="1">
-      <c r="A114" s="6" t="inlineStr"/>
-      <c r="B114" s="7" t="inlineStr">
+    <row r="115" ht="35" customHeight="1">
+      <c r="A115" s="6" t="inlineStr"/>
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr"/>
-      <c r="E114" s="9" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr"/>
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>~4:45pm — Hintersee &amp; Zauberwald (Magic Forest) — 15 min drive toward Ramsau · follow the trail into the Zauberwald</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="34" customHeight="1">
-      <c r="A115" s="25" t="inlineStr"/>
-      <c r="B115" s="26" t="inlineStr">
+    <row r="116" ht="34" customHeight="1">
+      <c r="A116" s="25" t="inlineStr"/>
+      <c r="B116" s="26" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C115" s="27" t="inlineStr">
+      <c r="C116" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D115" s="26" t="inlineStr"/>
-      <c r="E115" s="28" t="inlineStr">
+      <c r="D116" s="26" t="inlineStr"/>
+      <c r="E116" s="28" t="inlineStr">
         <is>
           <t>Night 2 — Berchtesgaden Apartment — ✅ Already checked in ·  Kälbersteinstraße 4, 83471 Berchtesgaden, Germany</t>
         </is>
       </c>
-      <c r="F115" s="29" t="inlineStr"/>
-    </row>
-    <row r="116" ht="34" customHeight="1">
-      <c r="A116" s="11" t="inlineStr"/>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="F116" s="29" t="inlineStr"/>
+    </row>
+    <row r="117" ht="34" customHeight="1">
+      <c r="A117" s="11" t="inlineStr"/>
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
+      <c r="C117" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D116" s="12" t="inlineStr"/>
-      <c r="E116" s="14" t="inlineStr">
+      <c r="D117" s="12" t="inlineStr"/>
+      <c r="E117" s="14" t="inlineStr">
         <is>
           <t>Dinner — Berchtesgaden — Bräustüberl Berchtesgaden (Bräuhausstraße 13) if not done Day 5 · or Gasthof Neuhaus</t>
         </is>
       </c>
-      <c r="F116" s="15" t="inlineStr"/>
-    </row>
-    <row r="117" ht="34" customHeight="1">
-      <c r="A117" s="30" t="inlineStr"/>
-      <c r="B117" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C117" s="32" t="inlineStr">
-        <is>
-          <t>⛵ Königssee boat tips — ~€28–30 return to Salet per adult · book at seenschifffahrt.de 1 week before · dock is 10 min walk from car park · tip the captain €1–2 for the trumpet echo</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="31" customHeight="1">
+      <c r="F117" s="15" t="inlineStr"/>
+    </row>
+    <row r="118" ht="34" customHeight="1">
       <c r="A118" s="30" t="inlineStr"/>
       <c r="B118" s="31" t="inlineStr">
         <is>
@@ -3123,11 +3134,11 @@
       </c>
       <c r="C118" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Eagle's Nest return bus — book 4:00 or 4:15pm slot at the top counter IMMEDIATELY · slots fill fast in peak season · missing it = stranded at the top</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="23" customHeight="1">
+          <t>⛵ Königssee boat tips — ~€28–30 return to Salet per adult · book at seenschifffahrt.de 1 week before · dock is 10 min walk from car park · tip the captain €1–2 for the trumpet echo</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="31" customHeight="1">
       <c r="A119" s="30" t="inlineStr"/>
       <c r="B119" s="31" t="inlineStr">
         <is>
@@ -3136,11 +3147,11 @@
       </c>
       <c r="C119" s="32" t="inlineStr">
         <is>
-          <t>⛵ Königssee booking — book at seenschifffahrt.de · reserve ~1 week before Jun 25 · non-refundable</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="34" customHeight="1">
+          <t>⚠️ Eagle's Nest return bus — book 4:00 or 4:15pm slot at the top counter IMMEDIATELY · slots fill fast in peak season · missing it = stranded at the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="23" customHeight="1">
       <c r="A120" s="30" t="inlineStr"/>
       <c r="B120" s="31" t="inlineStr">
         <is>
@@ -3149,84 +3160,77 @@
       </c>
       <c r="C120" s="32" t="inlineStr">
         <is>
+          <t>⛵ Königssee booking — book at seenschifffahrt.de · reserve ~1 week before Jun 25 · non-refundable</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="34" customHeight="1">
+      <c r="A121" s="30" t="inlineStr"/>
+      <c r="B121" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C121" s="32" t="inlineStr">
+        <is>
           <t>Ramsau village — 10 min from Berchtesgaden — stone bridge over the fast-moving turquoise Ramsauer Ache river · Reiteralpe massif behind it · one of the most photographed spots in Bavaria · zero crowds at 7am · drive through on the way to Kö</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="3" customHeight="1">
-      <c r="A121" s="33" t="n"/>
-      <c r="B121" s="33" t="n"/>
-      <c r="C121" s="33" t="n"/>
-      <c r="D121" s="33" t="n"/>
-      <c r="E121" s="33" t="n"/>
-      <c r="F121" s="33" t="n"/>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="3" t="inlineStr">
+    <row r="122" ht="3" customHeight="1">
+      <c r="A122" s="33" t="n"/>
+      <c r="B122" s="33" t="n"/>
+      <c r="C122" s="33" t="n"/>
+      <c r="D122" s="33" t="n"/>
+      <c r="E122" s="33" t="n"/>
+      <c r="F122" s="33" t="n"/>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>DAY 7  |  Jun 26  |  The Salzkammergut Sprint — Klamm · Salzburg · Wolfgangsee · Hallstatt  |  ~180 km / 112 mi  ~3h 30m incl. Salzburg parking</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:15am depart Berchtesgaden ▸ 9:00am Liechtensteinklamm ▸ 11am drive Salzburg ▸ 12pm P+R South + Altstadt ▸ Hohensalzburg Panorama Tour ▸ 3pm drive Wolfgangsee ▸ 4pm St. Gilgen→St. Wolfgang ferry ▸ 5:30pm Hallstatt golden hour ▸ 7:30pm Kaiserblick Goisern</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Liechtensteinklamm 9:00am sharp — be first at the gate · €16/adult · wear sturdy shoes  |  ✅ Salzburg: P+R South (Alpenstraße) €15 family combo — do NOT park in city centre · 2026 restricted zone  |  ⚠️ Hallstatt tunnel signs: if "Full" — go straight to Goisern · park Obertraun + ferry instead</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="47" customHeight="1">
-      <c r="A125" s="6" t="inlineStr"/>
-      <c r="B125" s="7" t="inlineStr">
+    <row r="126" ht="47" customHeight="1">
+      <c r="A126" s="6" t="inlineStr"/>
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr"/>
-      <c r="E125" s="9" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr"/>
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:15am — Checkout Berchtesgaden + depart — drive 35 min south toward St. Johann im Pongau — Austrian motorway A10 · ✅ Austrian vignette must be active — you are on the A10 today</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>35 min</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="41" customHeight="1">
-      <c r="A126" s="16" t="inlineStr"/>
-      <c r="B126" s="17" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D126" s="17" t="inlineStr"/>
-      <c r="E126" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 9:00am — Liechtensteinklamm Gorge — be there at opening (9:00am) — experience the helix staircase without crowds · thundering waterfalls + mist</t>
-        </is>
-      </c>
-      <c r="F126" s="19" t="inlineStr"/>
-    </row>
-    <row r="127" ht="50" customHeight="1">
+    <row r="127" ht="41" customHeight="1">
       <c r="A127" s="16" t="inlineStr"/>
       <c r="B127" s="17" t="inlineStr">
         <is>
@@ -3241,60 +3245,60 @@
       <c r="D127" s="17" t="inlineStr"/>
       <c r="E127" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 9:00am — Liechtensteinklamm Gorge — be there at opening (9:00am) — experience the helix staircase without crowds · thundering waterfalls + mist</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="inlineStr"/>
+    </row>
+    <row r="128" ht="50" customHeight="1">
+      <c r="A128" s="16" t="inlineStr"/>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr"/>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
           <t>⭐ Sound of Music meadow — Gschwandtanger, Werfen — just off the B159 near Liechtensteinklamm · the exact meadow where the Do-Re-Mi picnic scene was filmed · jaw-dropping views of Hohenwerfen Castle + mountains · no crowd</t>
         </is>
       </c>
-      <c r="F127" s="19" t="inlineStr">
+      <c r="F128" s="19" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="50" customHeight="1">
-      <c r="A128" s="6" t="inlineStr"/>
-      <c r="B128" s="7" t="inlineStr">
+    <row r="129" ht="50" customHeight="1">
+      <c r="A129" s="6" t="inlineStr"/>
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C128" s="8" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr"/>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr"/>
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>11:00am — Drive north to Salzburg — ~1hr on A10 · arrive ~12:00pm · ⚠️ Do NOT park in the city centre — 2026 restricted traffic zone + construction everywhere · use P+R South (Alpenstraße) — €15 combo-ticket covers parki</t>
         </is>
       </c>
-      <c r="F128" s="10" t="inlineStr">
+      <c r="F129" s="10" t="inlineStr">
         <is>
           <t>~1hr / €15</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="16" t="inlineStr"/>
-      <c r="B129" s="17" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C129" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D129" s="17" t="inlineStr"/>
-      <c r="E129" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 12:00pm — Salzburg old town</t>
-        </is>
-      </c>
-      <c r="F129" s="19" t="inlineStr"/>
-    </row>
-    <row r="130" ht="38" customHeight="1">
+    <row r="130" ht="18" customHeight="1">
       <c r="A130" s="16" t="inlineStr"/>
       <c r="B130" s="17" t="inlineStr">
         <is>
@@ -3309,64 +3313,60 @@
       <c r="D130" s="17" t="inlineStr"/>
       <c r="E130" s="18" t="inlineStr">
         <is>
+          <t>⭐ 12:00pm — Salzburg old town</t>
+        </is>
+      </c>
+      <c r="F130" s="19" t="inlineStr"/>
+    </row>
+    <row r="131" ht="38" customHeight="1">
+      <c r="A131" s="16" t="inlineStr"/>
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr"/>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
           <t>⭐ 12:30pm — Hohensalzburg Fortress — funicular up from Kapitelplatz · stick to the Panorama Tour — ➕ Interior: €16/adult · allow 1hr</t>
         </is>
       </c>
-      <c r="F130" s="19" t="inlineStr">
+      <c r="F131" s="19" t="inlineStr">
         <is>
           <t>€16 / 1hr</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="34" customHeight="1">
-      <c r="A131" s="6" t="inlineStr"/>
-      <c r="B131" s="7" t="inlineStr">
+    <row r="132" ht="34" customHeight="1">
+      <c r="A132" s="6" t="inlineStr"/>
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="C132" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr"/>
-      <c r="E131" s="9" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr"/>
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>3:00pm — Drive east to Wolfgangsee — 45 min to St. Gilgen · arrive ~3:45pm · park in St. Gilgen village car park</t>
         </is>
       </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="F132" s="10" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="39" customHeight="1">
-      <c r="A132" s="16" t="inlineStr"/>
-      <c r="B132" s="17" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D132" s="17" t="inlineStr"/>
-      <c r="E132" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 4:00pm — Wolfgangsee ferry: St. Gilgen → St. Wolfgang → back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
-        </is>
-      </c>
-      <c r="F132" s="19" t="inlineStr">
-        <is>
-          <t>~20 min / 90 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="22" customHeight="1">
+    <row r="133" ht="39" customHeight="1">
       <c r="A133" s="16" t="inlineStr"/>
       <c r="B133" s="17" t="inlineStr">
         <is>
@@ -3381,16 +3381,16 @@
       <c r="D133" s="17" t="inlineStr"/>
       <c r="E133" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
+          <t>⭐ 4:00pm — Wolfgangsee ferry: St. Gilgen → St. Wolfgang → back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
         </is>
       </c>
       <c r="F133" s="19" t="inlineStr">
         <is>
-          <t>2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="38" customHeight="1">
+          <t>~20 min / 90 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
       <c r="A134" s="16" t="inlineStr"/>
       <c r="B134" s="17" t="inlineStr">
         <is>
@@ -3405,49 +3405,60 @@
       <c r="D134" s="17" t="inlineStr"/>
       <c r="E134" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
+        </is>
+      </c>
+      <c r="F134" s="19" t="inlineStr">
+        <is>
+          <t>2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="38" customHeight="1">
+      <c r="A135" s="16" t="inlineStr"/>
+      <c r="B135" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C135" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="inlineStr"/>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
           <t>⚠️ Hallstatt 2026 camera parking system — alternative: park at Obertraun (5 min drive) + take the ferry to Hallstatt (€4 · 10 min)</t>
         </is>
       </c>
-      <c r="F134" s="19" t="inlineStr">
+      <c r="F135" s="19" t="inlineStr">
         <is>
           <t>5 min / €4 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="28" customHeight="1">
-      <c r="A135" s="6" t="inlineStr"/>
-      <c r="B135" s="7" t="inlineStr">
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="6" t="inlineStr"/>
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C135" s="8" t="inlineStr">
+      <c r="C136" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr"/>
-      <c r="E135" s="9" t="inlineStr">
+      <c r="D136" s="7" t="inlineStr"/>
+      <c r="E136" s="9" t="inlineStr">
         <is>
           <t>7:30pm — Kaiserblick Goisern, Bad Goisern — 15 min drive from Hallstatt · $333</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F136" s="10" t="inlineStr">
         <is>
           <t>15 min / $333</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="34" customHeight="1">
-      <c r="A136" s="30" t="inlineStr"/>
-      <c r="B136" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C136" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Salzburg parking 2026 — Old Town becoming restricted traffic zone · construction barriers everywhere · use P+R South (Alpenstraße) · €15 combo = parking + shuttle bus for whole family · much faster than city garage hunting</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3471,7 @@
       </c>
       <c r="C137" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Hallstatt 2026 camera system — electronic signs at tunnel entrance · if "Full": do not enter · drive straight to Kaiserblick Goisern · return via ferry from Obertraun (€4 · 10 min) or bus on Day 8</t>
+          <t>⚠️ Salzburg parking 2026 — Old Town becoming restricted traffic zone · construction barriers everywhere · use P+R South (Alpenstraße) · €15 combo = parking + shuttle bus for whole family · much faster than city garage hunting</t>
         </is>
       </c>
     </row>
@@ -3473,112 +3484,101 @@
       </c>
       <c r="C138" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Hallstatt 2026 camera system — electronic signs at tunnel entrance · if "Full": do not enter · drive straight to Kaiserblick Goisern · return via ferry from Obertraun (€4 · 10 min) or bus on Day 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="34" customHeight="1">
+      <c r="A139" s="30" t="inlineStr"/>
+      <c r="B139" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C139" s="32" t="inlineStr">
+        <is>
           <t>☕ Hohensalzburg tip — stick to Panorama Tour only (courtyards + bastions) · skip the individual museums to stay on schedule · the view is the reason to go up · allow 1hr max</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="3" customHeight="1">
-      <c r="A139" s="33" t="n"/>
-      <c r="B139" s="33" t="n"/>
-      <c r="C139" s="33" t="n"/>
-      <c r="D139" s="33" t="n"/>
-      <c r="E139" s="33" t="n"/>
-      <c r="F139" s="33" t="n"/>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="3" t="inlineStr">
+    <row r="140" ht="3" customHeight="1">
+      <c r="A140" s="33" t="n"/>
+      <c r="B140" s="33" t="n"/>
+      <c r="C140" s="33" t="n"/>
+      <c r="D140" s="33" t="n"/>
+      <c r="E140" s="33" t="n"/>
+      <c r="F140" s="33" t="n"/>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>DAY 8  |  Jun 27  |  Dachstein Krippenstein · Gosausee · Hallstatt Evening — The High-Alpine Day  |  ~40 km / 25 mi  ~1h total · very local day</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:15am depart Bad Goisern ▸ 8:45am Krippenstein cable car ▸ 9:30am 5 Fingers viewpoint ▸ Ice Cave optional ▸ 1:30pm Gosausee Mirror Lake ▸ 2:00pm Gosaukammbahn ▸ 4:30pm Hallstatt golden hour + dinner ▸ Beinhaus ▸ ~7pm Kaiserblick Goisern</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>Key: Salt Mine + Skywalk CLOSED Jun 27 — reopens Jun 30 · do not book these  |  ✅ Dachstein Krippenstein 8:45am → 5 Fingers → Gosausee 1:30pm → Gosaukammbahn → Hallstatt 4:30pm  |  ⚠️ Saturday = busy Hallstatt · check digital signs · if Full → park Obertraun + NAVIA ferry €4</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="50" customHeight="1">
-      <c r="A143" s="34" t="inlineStr"/>
-      <c r="B143" s="35" t="inlineStr">
+    <row r="144" ht="50" customHeight="1">
+      <c r="A144" s="34" t="inlineStr"/>
+      <c r="B144" s="35" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C143" s="36" t="inlineStr">
+      <c r="C144" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D143" s="35" t="inlineStr"/>
-      <c r="E143" s="37" t="inlineStr">
+      <c r="D144" s="35" t="inlineStr"/>
+      <c r="E144" s="37" t="inlineStr">
         <is>
           <t>2026 Alert: Hallstatt Salt Mine + Skywalk CLOSED Jun 27 — major renovation underway · scheduled to reopen June 30, 2026 · do not attempt to book these for today · alternative: Salzwelten Altaussee — (25 min from Bad Gois</t>
         </is>
       </c>
-      <c r="F143" s="38" t="inlineStr">
+      <c r="F144" s="38" t="inlineStr">
         <is>
           <t>25 min</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="41" customHeight="1">
-      <c r="A144" s="6" t="inlineStr"/>
-      <c r="B144" s="7" t="inlineStr">
+    <row r="145" ht="41" customHeight="1">
+      <c r="A145" s="6" t="inlineStr"/>
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C144" s="8" t="inlineStr">
+      <c r="C145" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr"/>
-      <c r="E144" s="9" t="inlineStr">
+      <c r="D145" s="7" t="inlineStr"/>
+      <c r="E145" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:15am — Depart Bad Goisern — 20 min drive to Obertraun · arrive by 8:40am · park at the Dachstein Krippenstein cable car base station in Obertraun</t>
         </is>
       </c>
-      <c r="F144" s="10" t="inlineStr">
+      <c r="F145" s="10" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="30" customHeight="1">
-      <c r="A145" s="16" t="inlineStr"/>
-      <c r="B145" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C145" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D145" s="17" t="inlineStr"/>
-      <c r="E145" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · €44.90/adult</t>
-        </is>
-      </c>
-      <c r="F145" s="19" t="inlineStr">
-        <is>
-          <t>€44.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="32" customHeight="1">
+    <row r="146" ht="30" customHeight="1">
       <c r="A146" s="16" t="inlineStr"/>
       <c r="B146" s="17" t="inlineStr">
         <is>
@@ -3593,12 +3593,12 @@
       <c r="D146" s="17" t="inlineStr"/>
       <c r="E146" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
+          <t>⭐ ⭐ 8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · €44.90/adult</t>
         </is>
       </c>
       <c r="F146" s="19" t="inlineStr">
         <is>
-          <t>20 min / 45 min</t>
+          <t>€44.90</t>
         </is>
       </c>
     </row>
@@ -3617,64 +3617,64 @@
       <c r="D147" s="17" t="inlineStr"/>
       <c r="E147" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
+        </is>
+      </c>
+      <c r="F147" s="19" t="inlineStr">
+        <is>
+          <t>20 min / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="32" customHeight="1">
+      <c r="A148" s="16" t="inlineStr"/>
+      <c r="B148" s="17" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr"/>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
           <t>➕ Optional: Giant Ice Cave (Section 1) — accessible from Section 1 midstation · extra cost ~€10/adult</t>
         </is>
       </c>
-      <c r="F147" s="19" t="inlineStr">
+      <c r="F148" s="19" t="inlineStr">
         <is>
           <t>€10</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="30" customHeight="1">
-      <c r="A148" s="6" t="inlineStr"/>
-      <c r="B148" s="7" t="inlineStr">
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="6" t="inlineStr"/>
+      <c r="B149" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C148" s="8" t="inlineStr">
+      <c r="C149" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr"/>
-      <c r="E148" s="9" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr"/>
+      <c r="E149" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 1:30pm — Vorderer Gosausee — the Mirror Lake — 25 min drive from Obertraun · allow 30 min</t>
         </is>
       </c>
-      <c r="F148" s="10" t="inlineStr">
+      <c r="F149" s="10" t="inlineStr">
         <is>
           <t>25 min / 30 min</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="33" customHeight="1">
-      <c r="A149" s="16" t="inlineStr"/>
-      <c r="B149" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C149" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D149" s="17" t="inlineStr"/>
-      <c r="E149" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 2:00pm — Gosaukammbahn cable car — ~€28 return/adult · panoramic view of the Dachstein glacier from above</t>
-        </is>
-      </c>
-      <c r="F149" s="19" t="inlineStr">
-        <is>
-          <t>€28</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="31" customHeight="1">
+    <row r="150" ht="33" customHeight="1">
       <c r="A150" s="16" t="inlineStr"/>
       <c r="B150" s="17" t="inlineStr">
         <is>
@@ -3689,16 +3689,16 @@
       <c r="D150" s="17" t="inlineStr"/>
       <c r="E150" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 4:30pm — Hallstatt village evening — mine renovation crowds have gone by now · allow 1.5hrs</t>
+          <t>⭐ 2:00pm — Gosaukammbahn cable car — ~€28 return/adult · panoramic view of the Dachstein glacier from above</t>
         </is>
       </c>
       <c r="F150" s="19" t="inlineStr">
         <is>
-          <t>5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="38" customHeight="1">
+          <t>€28</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="31" customHeight="1">
       <c r="A151" s="16" t="inlineStr"/>
       <c r="B151" s="17" t="inlineStr">
         <is>
@@ -3713,16 +3713,16 @@
       <c r="D151" s="17" t="inlineStr"/>
       <c r="E151" s="18" t="inlineStr">
         <is>
-          <t>⚠️ Saturday parking warning — if P1/P2 show "Full": park in Obertraun (5 min drive) + take the ferry across · NAVIA ferry: €4 cash</t>
+          <t>⭐ ⭐ 4:30pm — Hallstatt village evening — mine renovation crowds have gone by now · allow 1.5hrs</t>
         </is>
       </c>
       <c r="F151" s="19" t="inlineStr">
         <is>
-          <t>5 min / €4</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="21" customHeight="1">
+          <t>5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="38" customHeight="1">
       <c r="A152" s="16" t="inlineStr"/>
       <c r="B152" s="17" t="inlineStr">
         <is>
@@ -3737,49 +3737,60 @@
       <c r="D152" s="17" t="inlineStr"/>
       <c r="E152" s="18" t="inlineStr">
         <is>
+          <t>⚠️ Saturday parking warning — if P1/P2 show "Full": park in Obertraun (5 min drive) + take the ferry across · NAVIA ferry: €4 cash</t>
+        </is>
+      </c>
+      <c r="F152" s="19" t="inlineStr">
+        <is>
+          <t>5 min / €4</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="21" customHeight="1">
+      <c r="A153" s="16" t="inlineStr"/>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr"/>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
           <t>⭐ Beinhaus (Bone Chapel) — €1.50/adult · 10 min</t>
         </is>
       </c>
-      <c r="F152" s="19" t="inlineStr">
+      <c r="F153" s="19" t="inlineStr">
         <is>
           <t>€1.50 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="37" customHeight="1">
-      <c r="A153" s="6" t="inlineStr"/>
-      <c r="B153" s="7" t="inlineStr">
+    <row r="154" ht="37" customHeight="1">
+      <c r="A154" s="6" t="inlineStr"/>
+      <c r="B154" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C153" s="8" t="inlineStr">
+      <c r="C154" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D153" s="7" t="inlineStr"/>
-      <c r="E153" s="9" t="inlineStr">
+      <c r="D154" s="7" t="inlineStr"/>
+      <c r="E154" s="9" t="inlineStr">
         <is>
           <t>Night 2 — Kaiserblick Goisern — ✅ Already checked in ·  38 Unterjoch, 4822 Bad Goisern, Austria · 15 min drive from Hallstatt</t>
         </is>
       </c>
-      <c r="F153" s="10" t="inlineStr">
+      <c r="F154" s="10" t="inlineStr">
         <is>
           <t>15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="34" customHeight="1">
-      <c r="A154" s="30" t="inlineStr"/>
-      <c r="B154" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C154" s="32" t="inlineStr">
-        <is>
-          <t>Salt Mine + Skywalk CLOSED Jun 27 — major renovation · reopens Jun 30, 2026 · alternative: Salzwelten Altaussee (25 min from Bad Goisern) · active mine · most authentic</t>
         </is>
       </c>
     </row>
@@ -3792,11 +3803,11 @@
       </c>
       <c r="C155" s="32" t="inlineStr">
         <is>
-          <t>⚠️ 5 Fingers vs Skywalk — 5 Fingers on Krippenstein is higher, more dramatic, free with cable car ticket · direct aerial view down into Hallstatt village · Skywalk is closed anyway — 5 Fingers is the better experience</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="33" customHeight="1">
+          <t>Salt Mine + Skywalk CLOSED Jun 27 — major renovation · reopens Jun 30, 2026 · alternative: Salzwelten Altaussee (25 min from Bad Goisern) · active mine · most authentic</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="34" customHeight="1">
       <c r="A156" s="30" t="inlineStr"/>
       <c r="B156" s="31" t="inlineStr">
         <is>
@@ -3805,11 +3816,11 @@
       </c>
       <c r="C156" s="32" t="inlineStr">
         <is>
-          <t>Gosausee afternoon tip — best photos happen when the sun hits the Dachstein glacier face-on in the afternoon · go at 3pm not morning for the mirror reflection shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="34" customHeight="1">
+          <t>⚠️ 5 Fingers vs Skywalk — 5 Fingers on Krippenstein is higher, more dramatic, free with cable car ticket · direct aerial view down into Hallstatt village · Skywalk is closed anyway — 5 Fingers is the better experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="33" customHeight="1">
       <c r="A157" s="30" t="inlineStr"/>
       <c r="B157" s="31" t="inlineStr">
         <is>
@@ -3818,136 +3829,114 @@
       </c>
       <c r="C157" s="32" t="inlineStr">
         <is>
+          <t>Gosausee afternoon tip — best photos happen when the sun hits the Dachstein glacier face-on in the afternoon · go at 3pm not morning for the mirror reflection shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="34" customHeight="1">
+      <c r="A158" s="30" t="inlineStr"/>
+      <c r="B158" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C158" s="32" t="inlineStr">
+        <is>
           <t>Hofer (Aldi) Bad Goisern — stock up this morning or evening · discount prices · buy for Jun 27–Jul 1: Grossglockner · Sillian · Dolomites 3 nights · Hofrat-Renner-Weg 1 · open Tue 7:15am</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="3" customHeight="1">
-      <c r="A158" s="33" t="n"/>
-      <c r="B158" s="33" t="n"/>
-      <c r="C158" s="33" t="n"/>
-      <c r="D158" s="33" t="n"/>
-      <c r="E158" s="33" t="n"/>
-      <c r="F158" s="33" t="n"/>
-    </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="3" t="inlineStr">
+    <row r="159" ht="34" customHeight="1">
+      <c r="A159" s="30" t="inlineStr"/>
+      <c r="B159" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C159" s="32" t="inlineStr">
+        <is>
+          <t>Löckenmoos alpine lake — Bad Goisern — minutes from Kaiserblick hotel · almost no international tourists · small alpine bog lake with mountain reflections · ☀️ clear weather only — magical when calm · perfect 20 min evening walk from the ho</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="3" customHeight="1">
+      <c r="A160" s="33" t="n"/>
+      <c r="B160" s="33" t="n"/>
+      <c r="C160" s="33" t="n"/>
+      <c r="D160" s="33" t="n"/>
+      <c r="E160" s="33" t="n"/>
+      <c r="F160" s="33" t="n"/>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>DAY 9  |  Jun 28  |  The Roof of Austria — Grossglockner High Alpine Road → Sillian  |  ~280 km / 174 mi  ~4h 30m incl. Grossglockner slow drive</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="4" t="inlineStr">
+    <row r="162" ht="15" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:00am checkout ▸ 9:30am Ferleiten toll €46.50 ▸ 10:15am Edelweiß-Spitze ▸ 11:30am Hochtor tunnel ▸ 12:15pm KFJ-Höhe + marmots ▸ 1:30pm glacier lunch ▸ 3:30pm Heiligenblut church photo ▸ 5:30pm Sillian ▸ alarm 5am</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="22" customHeight="1">
-      <c r="A161" s="5" t="inlineStr">
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Edelweiß-Spitze FIRST — go before motorcycles arrive · dead-end road congests by afternoon  |  ✅ Gamsgrubenweg 10 min from KFJ-Höhe — best marmot spotting on the road · kids will love it  |  ⚠️ Descent: engine brake in low gear · do NOT ride the brakes · they will overheat</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="43" customHeight="1">
-      <c r="A162" s="6" t="inlineStr"/>
-      <c r="B162" s="7" t="inlineStr">
+    <row r="164" ht="43" customHeight="1">
+      <c r="A164" s="6" t="inlineStr"/>
+      <c r="B164" s="7" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C162" s="8" t="inlineStr">
+      <c r="C164" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D162" s="7" t="inlineStr"/>
-      <c r="E162" s="9" t="inlineStr">
+      <c r="D164" s="7" t="inlineStr"/>
+      <c r="E164" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:00am — Checkout Kaiserblick Goisern — 1.5hr drive to the Ferleiten toll gate via the B311 · download offline maps for the Dolomites tonight if not done yet</t>
         </is>
       </c>
-      <c r="F162" s="10" t="inlineStr">
+      <c r="F164" s="10" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="46" customHeight="1">
-      <c r="A163" s="16" t="inlineStr"/>
-      <c r="B163" s="17" t="inlineStr">
+    <row r="165" ht="46" customHeight="1">
+      <c r="A165" s="16" t="inlineStr"/>
+      <c r="B165" s="17" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C163" s="16" t="inlineStr">
+      <c r="C165" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D163" s="17" t="inlineStr"/>
-      <c r="E163" s="18" t="inlineStr">
+      <c r="D165" s="17" t="inlineStr"/>
+      <c r="E165" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ Grossglockner High Alpine Road — 48km of switchbacks across the highest surfaced alpine pass in Austria · road open from 5:30am — last entry 45 min before 9pm closing</t>
         </is>
       </c>
-      <c r="F163" s="19" t="inlineStr">
+      <c r="F165" s="19" t="inlineStr">
         <is>
           <t>48km / 45 min</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="38" customHeight="1">
-      <c r="A164" s="16" t="inlineStr"/>
-      <c r="B164" s="17" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D164" s="17" t="inlineStr"/>
-      <c r="E164" s="18" t="inlineStr">
-        <is>
-          <t>9:30am — Ferleiten Toll Gate — 2026 rate: €46.50/car — first stop: Edelweiß-Spitze — go there FIRST before the motorcycles arrive</t>
-        </is>
-      </c>
-      <c r="F164" s="19" t="inlineStr">
-        <is>
-          <t>€46.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="34" customHeight="1">
-      <c r="A165" s="20" t="inlineStr"/>
-      <c r="B165" s="21" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C165" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D165" s="21" t="inlineStr"/>
-      <c r="E165" s="23" t="inlineStr">
-        <is>
-          <t>Haus Alpine Naturschau — natural history museum — 15 min · great context for the kids before reaching the summit</t>
-        </is>
-      </c>
-      <c r="F165" s="24" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="32" customHeight="1">
+    <row r="166" ht="38" customHeight="1">
       <c r="A166" s="16" t="inlineStr"/>
       <c r="B166" s="17" t="inlineStr">
         <is>
@@ -3962,60 +3951,60 @@
       <c r="D166" s="17" t="inlineStr"/>
       <c r="E166" s="18" t="inlineStr">
         <is>
+          <t>9:30am — Ferleiten Toll Gate — 2026 rate: €46.50/car — first stop: Edelweiß-Spitze — go there FIRST before the motorcycles arrive</t>
+        </is>
+      </c>
+      <c r="F166" s="19" t="inlineStr">
+        <is>
+          <t>€46.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="34" customHeight="1">
+      <c r="A167" s="20" t="inlineStr"/>
+      <c r="B167" s="21" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C167" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D167" s="21" t="inlineStr"/>
+      <c r="E167" s="23" t="inlineStr">
+        <is>
+          <t>Haus Alpine Naturschau — natural history museum — 15 min · great context for the kids before reaching the summit</t>
+        </is>
+      </c>
+      <c r="F167" s="24" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="32" customHeight="1">
+      <c r="A168" s="16" t="inlineStr"/>
+      <c r="B168" s="17" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D168" s="17" t="inlineStr"/>
+      <c r="E168" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 10:15am — Edelweiß-Spitze (2,571m) — MUST STOP · dead-end cobblestone branch road — go here FIRST</t>
         </is>
       </c>
-      <c r="F166" s="19" t="inlineStr"/>
-    </row>
-    <row r="167" ht="21" customHeight="1">
-      <c r="A167" s="16" t="inlineStr"/>
-      <c r="B167" s="17" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D167" s="17" t="inlineStr"/>
-      <c r="E167" s="18" t="inlineStr">
-        <is>
-          <t>11:30am — Hochtor Tunnel (2,504m) — 10 min stop</t>
-        </is>
-      </c>
-      <c r="F167" s="19" t="inlineStr">
-        <is>
-          <t>10 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="50" customHeight="1">
-      <c r="A168" s="20" t="inlineStr"/>
-      <c r="B168" s="21" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C168" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D168" s="21" t="inlineStr"/>
-      <c r="E168" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⭐ ⭐ 12:15pm — Kaiser-Franz-Josefs-Höhe (2,369m) — Austria's longest glacier (8km) stretching toward the Grossglockner · ⚠️ 2026: glacier has receded significantly — to touch the ice take the Gletscherbahn funicular down </t>
-        </is>
-      </c>
-      <c r="F168" s="24" t="inlineStr">
-        <is>
-          <t>8km / 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="36" customHeight="1">
+      <c r="F168" s="19" t="inlineStr"/>
+    </row>
+    <row r="169" ht="21" customHeight="1">
       <c r="A169" s="16" t="inlineStr"/>
       <c r="B169" s="17" t="inlineStr">
         <is>
@@ -4030,178 +4019,200 @@
       <c r="D169" s="17" t="inlineStr"/>
       <c r="E169" s="18" t="inlineStr">
         <is>
+          <t>11:30am — Hochtor Tunnel (2,504m) — 10 min stop</t>
+        </is>
+      </c>
+      <c r="F169" s="19" t="inlineStr">
+        <is>
+          <t>10 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="50" customHeight="1">
+      <c r="A170" s="20" t="inlineStr"/>
+      <c r="B170" s="21" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C170" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D170" s="21" t="inlineStr"/>
+      <c r="E170" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⭐ ⭐ 12:15pm — Kaiser-Franz-Josefs-Höhe (2,369m) — Austria's longest glacier (8km) stretching toward the Grossglockner · ⚠️ 2026: glacier has receded significantly — to touch the ice take the Gletscherbahn funicular down </t>
+        </is>
+      </c>
+      <c r="F170" s="24" t="inlineStr">
+        <is>
+          <t>8km / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="36" customHeight="1">
+      <c r="A171" s="16" t="inlineStr"/>
+      <c r="B171" s="17" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D171" s="17" t="inlineStr"/>
+      <c r="E171" s="18" t="inlineStr">
+        <is>
           <t>Marmot &amp; ibex spotting — Gamsgrubenweg — from Kaiser-Franz-Josefs-Höhe: follow the Gamsgrubenweg tunnel path for 10 min</t>
         </is>
       </c>
-      <c r="F169" s="19" t="inlineStr">
+      <c r="F171" s="19" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="31" customHeight="1">
-      <c r="A170" s="11" t="inlineStr"/>
-      <c r="B170" s="12" t="inlineStr">
+    <row r="172" ht="31" customHeight="1">
+      <c r="A172" s="11" t="inlineStr"/>
+      <c r="B172" s="12" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C170" s="13" t="inlineStr">
+      <c r="C172" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D170" s="12" t="inlineStr"/>
-      <c r="E170" s="14" t="inlineStr">
+      <c r="D172" s="12" t="inlineStr"/>
+      <c r="E172" s="14" t="inlineStr">
         <is>
           <t>1:30pm — Lunch at Kaiser-Franz-Josefs-Höhe — panoramic terrace facing the glacier · allow 1hr</t>
         </is>
       </c>
-      <c r="F170" s="15" t="inlineStr">
+      <c r="F172" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="21" customHeight="1">
-      <c r="A171" s="20" t="inlineStr"/>
-      <c r="B171" s="21" t="inlineStr">
+    <row r="173" ht="21" customHeight="1">
+      <c r="A173" s="20" t="inlineStr"/>
+      <c r="B173" s="21" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C171" s="22" t="inlineStr">
+      <c r="C173" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D171" s="21" t="inlineStr"/>
-      <c r="E171" s="23" t="inlineStr">
+      <c r="D173" s="21" t="inlineStr"/>
+      <c r="E173" s="23" t="inlineStr">
         <is>
           <t>⚠️ Descent toward Heiligenblut — brake warning</t>
         </is>
       </c>
-      <c r="F171" s="24" t="inlineStr"/>
-    </row>
-    <row r="172" ht="21" customHeight="1">
-      <c r="A172" s="16" t="inlineStr"/>
-      <c r="B172" s="17" t="inlineStr">
+      <c r="F173" s="24" t="inlineStr"/>
+    </row>
+    <row r="174" ht="21" customHeight="1">
+      <c r="A174" s="16" t="inlineStr"/>
+      <c r="B174" s="17" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C172" s="16" t="inlineStr">
+      <c r="C174" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D172" s="17" t="inlineStr"/>
-      <c r="E172" s="18" t="inlineStr">
+      <c r="D174" s="17" t="inlineStr"/>
+      <c r="E174" s="18" t="inlineStr">
         <is>
           <t>⭐ 3:30pm — Heiligenblut village — allow 30 min</t>
         </is>
       </c>
-      <c r="F172" s="19" t="inlineStr">
+      <c r="F174" s="19" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="50" customHeight="1">
-      <c r="A173" s="16" t="inlineStr"/>
-      <c r="B173" s="17" t="inlineStr">
+    <row r="175" ht="50" customHeight="1">
+      <c r="A175" s="16" t="inlineStr"/>
+      <c r="B175" s="17" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C173" s="16" t="inlineStr">
+      <c r="C175" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D173" s="17" t="inlineStr"/>
-      <c r="E173" s="18" t="inlineStr">
+      <c r="D175" s="17" t="inlineStr"/>
+      <c r="E175" s="18" t="inlineStr">
         <is>
           <t>Gößnitzfall waterfall — Heiligenblut — right outside the village · easy 20 min walk through shaded forest to dramatic wooden viewing platform · thunderous alpine waterfall · stroller-friendly · free · perfect for shaking</t>
         </is>
       </c>
-      <c r="F173" s="19" t="inlineStr">
+      <c r="F175" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="23" customHeight="1">
-      <c r="A174" s="25" t="inlineStr"/>
-      <c r="B174" s="26" t="inlineStr">
+    <row r="176" ht="23" customHeight="1">
+      <c r="A176" s="25" t="inlineStr"/>
+      <c r="B176" s="26" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C174" s="27" t="inlineStr">
+      <c r="C176" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D174" s="26" t="inlineStr"/>
-      <c r="E174" s="28" t="inlineStr">
+      <c r="D176" s="26" t="inlineStr"/>
+      <c r="E176" s="28" t="inlineStr">
         <is>
           <t>5:30pm — Hotel Schwarzer Adler, Sillian — $115 / €99.40</t>
         </is>
       </c>
-      <c r="F174" s="29" t="inlineStr">
+      <c r="F176" s="29" t="inlineStr">
         <is>
           <t>$115 / €99.40</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="40" customHeight="1">
-      <c r="A175" s="11" t="inlineStr"/>
-      <c r="B175" s="12" t="inlineStr">
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="11" t="inlineStr"/>
+      <c r="B177" s="12" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C175" s="13" t="inlineStr">
+      <c r="C177" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D175" s="12" t="inlineStr"/>
-      <c r="E175" s="14" t="inlineStr">
+      <c r="D177" s="12" t="inlineStr"/>
+      <c r="E177" s="14" t="inlineStr">
         <is>
           <t>Dinner in Sillian —  Download offline Dolomites maps tonight (Maps.me or Google Maps) · check Rifugio Auronzo parking booking confirmation</t>
         </is>
       </c>
-      <c r="F175" s="15" t="inlineStr"/>
-    </row>
-    <row r="176" ht="34" customHeight="1">
-      <c r="A176" s="30" t="inlineStr"/>
-      <c r="B176" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C176" s="32" t="inlineStr">
-        <is>
-          <t>Grossglockner toll 2026: €46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="34" customHeight="1">
-      <c r="A177" s="30" t="inlineStr"/>
-      <c r="B177" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C177" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="33" customHeight="1">
+      <c r="F177" s="15" t="inlineStr"/>
+    </row>
+    <row r="178" ht="34" customHeight="1">
       <c r="A178" s="30" t="inlineStr"/>
       <c r="B178" s="31" t="inlineStr">
         <is>
@@ -4210,7 +4221,7 @@
       </c>
       <c r="C178" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
+          <t>Grossglockner toll 2026: €46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
         </is>
       </c>
     </row>
@@ -4223,11 +4234,11 @@
       </c>
       <c r="C179" s="32" t="inlineStr">
         <is>
-          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="34" customHeight="1">
+          <t>⚠️ Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="33" customHeight="1">
       <c r="A180" s="30" t="inlineStr"/>
       <c r="B180" s="31" t="inlineStr">
         <is>
@@ -4236,88 +4247,66 @@
       </c>
       <c r="C180" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="34" customHeight="1">
+      <c r="A181" s="30" t="inlineStr"/>
+      <c r="B181" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C181" s="32" t="inlineStr">
+        <is>
+          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="34" customHeight="1">
+      <c r="A182" s="30" t="inlineStr"/>
+      <c r="B182" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C182" s="32" t="inlineStr">
+        <is>
           <t>Tonight: prep for Dolomites — download offline maps (Google Maps or Maps.me) for the Dolomites · confirm Rifugio Auronzo parking booking · 5am alarm tomorrow · Braies gate opens 7:30am</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="3" customHeight="1">
-      <c r="A181" s="33" t="n"/>
-      <c r="B181" s="33" t="n"/>
-      <c r="C181" s="33" t="n"/>
-      <c r="D181" s="33" t="n"/>
-      <c r="E181" s="33" t="n"/>
-      <c r="F181" s="33" t="n"/>
-    </row>
-    <row r="182" ht="20" customHeight="1">
-      <c r="A182" s="3" t="inlineStr">
+    <row r="183" ht="3" customHeight="1">
+      <c r="A183" s="33" t="n"/>
+      <c r="B183" s="33" t="n"/>
+      <c r="C183" s="33" t="n"/>
+      <c r="D183" s="33" t="n"/>
+      <c r="E183" s="33" t="n"/>
+      <c r="F183" s="33" t="n"/>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>DAY 10  |  Jun 29  |  The Iconic Dolomites — Braies Sunrise · Tre Cime · Prato Piazza · Gardena  |  ~200 km / 124 mi  ~5h total driving · many short hops</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Sillian ▸ 8:45am Braies P3 ▸ 10:15am depart ▸ Misurina coffee ▸ 11:15am Auronzo gate ▸ 11:45am Cadini Trail 117 ▸ 1:30pm lunch ▸ 2:30pm Tre Cime walk ▸ 3:45pm Gardena Pass ▸ 5pm Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="5" t="inlineStr">
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ 8am departure — relaxed start · Braies 8:45am · still beautiful · P3 no reservation  |  ❌ Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |  ✅ Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |  ⚠️ Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |  ⚠️ Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="48" customHeight="1">
-      <c r="A185" s="6" t="inlineStr"/>
-      <c r="B185" s="7" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C185" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D185" s="7" t="inlineStr"/>
-      <c r="E185" s="9" t="inlineStr">
-        <is>
-          <t>8:00am — Depart Sillian — 45 min straight across the Italian border · download offline Dolomites maps tonight if not done · update Auronzo plate at pass.auronzo.info tonight (Jun 28)</t>
-        </is>
-      </c>
-      <c r="F185" s="10" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="49" customHeight="1">
-      <c r="A186" s="16" t="inlineStr"/>
-      <c r="B186" s="17" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C186" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D186" s="17" t="inlineStr"/>
-      <c r="E186" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 · no reservation needed · walk the best half of the lakeside circuit · famous stilt boathouse · morning views · allow 1.5hrs · leave by 10:15am</t>
-        </is>
-      </c>
-      <c r="F186" s="19" t="inlineStr">
-        <is>
-          <t>€12 / 5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="44" customHeight="1">
+    <row r="187" ht="48" customHeight="1">
       <c r="A187" s="6" t="inlineStr"/>
       <c r="B187" s="7" t="inlineStr">
         <is>
@@ -4332,180 +4321,202 @@
       <c r="D187" s="7" t="inlineStr"/>
       <c r="E187" s="9" t="inlineStr">
         <is>
+          <t>8:00am — Depart Sillian — 45 min straight across the Italian border · download offline Dolomites maps tonight if not done · update Auronzo plate at pass.auronzo.info tonight (Jun 28)</t>
+        </is>
+      </c>
+      <c r="F187" s="10" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="49" customHeight="1">
+      <c r="A188" s="16" t="inlineStr"/>
+      <c r="B188" s="17" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D188" s="17" t="inlineStr"/>
+      <c r="E188" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 · no reservation needed · walk the best half of the lakeside circuit · famous stilt boathouse · morning views · allow 1.5hrs · leave by 10:15am</t>
+        </is>
+      </c>
+      <c r="F188" s="19" t="inlineStr">
+        <is>
+          <t>€12 / 5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="44" customHeight="1">
+      <c r="A189" s="6" t="inlineStr"/>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr"/>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
           <t>☕ 10:15am — Drive via Lago di Misurina — 1hr drive down the valley · stop at Rifugio Misurina café · 15 min coffee + mirror-reflection photo of Tre Cime in the lake</t>
         </is>
       </c>
-      <c r="F187" s="10" t="inlineStr">
+      <c r="F189" s="10" t="inlineStr">
         <is>
           <t>1hr / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="45" customHeight="1">
-      <c r="A188" s="6" t="inlineStr"/>
-      <c r="B188" s="7" t="inlineStr">
+    <row r="190" ht="45" customHeight="1">
+      <c r="A190" s="6" t="inlineStr"/>
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr">
+      <c r="C190" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D188" s="7" t="inlineStr"/>
-      <c r="E188" s="9" t="inlineStr">
+      <c r="D190" s="7" t="inlineStr"/>
+      <c r="E190" s="9" t="inlineStr">
         <is>
           <t>⚠️ 11:15am — Auronzo gate — ✅ Pre-booked · PASS3CIME_26017885 · Ticket P26134547 · 9am–8:59pm slot · plate reads automatically · drive straight up · €40 paid · no queue</t>
         </is>
       </c>
-      <c r="F188" s="10" t="inlineStr">
+      <c r="F190" s="10" t="inlineStr">
         <is>
           <t>€40</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="50" customHeight="1">
-      <c r="A189" s="20" t="inlineStr"/>
-      <c r="B189" s="21" t="inlineStr">
+    <row r="191" ht="50" customHeight="1">
+      <c r="A191" s="20" t="inlineStr"/>
+      <c r="B191" s="21" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C189" s="22" t="inlineStr">
+      <c r="C191" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D189" s="21" t="inlineStr"/>
-      <c r="E189" s="23" t="inlineStr">
+      <c r="D191" s="21" t="inlineStr"/>
+      <c r="E191" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⭐ ⭐ 11:45am — Cadini di Misurina Trail 117 — hike out to the iconic jagged peak viewpoint · 45 min RT at normal pace · ⚠️ final 50m is a narrow ridge · secondary viewpoint 20m back is 95% as good · allow 1hr 45min total </t>
         </is>
       </c>
-      <c r="F189" s="24" t="inlineStr">
+      <c r="F191" s="24" t="inlineStr">
         <is>
           <t>45 min / 1hr / 45min</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="29" customHeight="1">
-      <c r="A190" s="11" t="inlineStr"/>
-      <c r="B190" s="12" t="inlineStr">
+    <row r="192" ht="29" customHeight="1">
+      <c r="A192" s="11" t="inlineStr"/>
+      <c r="B192" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C190" s="13" t="inlineStr">
+      <c r="C192" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D190" s="12" t="inlineStr"/>
-      <c r="E190" s="14" t="inlineStr">
+      <c r="D192" s="12" t="inlineStr"/>
+      <c r="E192" s="14" t="inlineStr">
         <is>
           <t>1:30pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr</t>
         </is>
       </c>
-      <c r="F190" s="15" t="inlineStr">
+      <c r="F192" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="40" customHeight="1">
-      <c r="A191" s="11" t="inlineStr"/>
-      <c r="B191" s="12" t="inlineStr">
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" s="11" t="inlineStr"/>
+      <c r="B193" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C191" s="13" t="inlineStr">
+      <c r="C193" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D191" s="12" t="inlineStr"/>
-      <c r="E191" s="14" t="inlineStr">
+      <c r="D193" s="12" t="inlineStr"/>
+      <c r="E193" s="14" t="inlineStr">
         <is>
           <t>2:30pm — Tre Cime Highlights Walk — flat path to Rifugio Lavaredo (20 min each way) · see the towering north faces up close · allow 1hr 15min</t>
         </is>
       </c>
-      <c r="F191" s="15" t="inlineStr">
+      <c r="F193" s="15" t="inlineStr">
         <is>
           <t>20 min / 1hr / 15min</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="50" customHeight="1">
-      <c r="A192" s="6" t="inlineStr"/>
-      <c r="B192" s="7" t="inlineStr">
+    <row r="194" ht="50" customHeight="1">
+      <c r="A194" s="6" t="inlineStr"/>
+      <c r="B194" s="7" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C192" s="8" t="inlineStr">
+      <c r="C194" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D192" s="7" t="inlineStr"/>
-      <c r="E192" s="9" t="inlineStr">
+      <c r="D194" s="7" t="inlineStr"/>
+      <c r="E194" s="9" t="inlineStr">
         <is>
           <t>3:45pm — Passo Gardena scenic drive — drive back down toll road · SS243 Gardena Pass (2,121m) · hairpin turns · low gear descent · ➕ Lagazuoi cable car optional if energy · ~1hr 15min drive</t>
         </is>
       </c>
-      <c r="F192" s="10" t="inlineStr">
+      <c r="F194" s="10" t="inlineStr">
         <is>
           <t>~1hr / 15min</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="43" customHeight="1">
-      <c r="A193" s="25" t="inlineStr"/>
-      <c r="B193" s="26" t="inlineStr">
+    <row r="195" ht="43" customHeight="1">
+      <c r="A195" s="25" t="inlineStr"/>
+      <c r="B195" s="26" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C193" s="27" t="inlineStr">
+      <c r="C195" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D193" s="26" t="inlineStr"/>
-      <c r="E193" s="28" t="inlineStr">
+      <c r="D195" s="26" t="inlineStr"/>
+      <c r="E195" s="28" t="inlineStr">
         <is>
           <t>5:00pm — Kaiserau 1907, Collalbo — ✅ Check in · Via Peter Mayr 65, 39054 Collalbo · check-in 15:00–22:00 · unpack · rest · open a bottle of Italian wine</t>
         </is>
       </c>
-      <c r="F193" s="29" t="inlineStr"/>
-    </row>
-    <row r="194" ht="34" customHeight="1">
-      <c r="A194" s="30" t="inlineStr"/>
-      <c r="B194" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C194" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Braies 2026 access — road blocked 9am–4pm in peak season · arrive by 5:30am · P3 no reservation before 8am · €12 · leave before 8:30am · pivot to Prato Piazza if cloudy</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="34" customHeight="1">
-      <c r="A195" s="30" t="inlineStr"/>
-      <c r="B195" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C195" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Auronzo toll road 2026 — book at pass.auronzo.info · €40/car · 12-hour slot · book May 30 (exactly 30 days before) · rental plate: leave blank · update night before at Sillian hotel</t>
-        </is>
-      </c>
+      <c r="F195" s="29" t="inlineStr"/>
     </row>
     <row r="196" ht="34" customHeight="1">
       <c r="A196" s="30" t="inlineStr"/>
@@ -4516,356 +4527,356 @@
       </c>
       <c r="C196" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Braies 2026 access — road blocked 9am–4pm in peak season · arrive by 5:30am · P3 no reservation before 8am · €12 · leave before 8:30am · pivot to Prato Piazza if cloudy</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="34" customHeight="1">
+      <c r="A197" s="30" t="inlineStr"/>
+      <c r="B197" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C197" s="32" t="inlineStr">
+        <is>
+          <t>⚠️ Auronzo toll road 2026 — book at pass.auronzo.info · €40/car · 12-hour slot · book May 30 (exactly 30 days before) · rental plate: leave blank · update night before at Sillian hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="34" customHeight="1">
+      <c r="A198" s="30" t="inlineStr"/>
+      <c r="B198" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C198" s="32" t="inlineStr">
+        <is>
           <t>Cadini viewpoint tip — final 50m is a narrow ridge · secondary viewpoint 20m before the narrow section · 95% as good · go early — very crowded by midday · most dramatic jagged peak view in the Dolomites</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="3" customHeight="1">
-      <c r="A197" s="33" t="n"/>
-      <c r="B197" s="33" t="n"/>
-      <c r="C197" s="33" t="n"/>
-      <c r="D197" s="33" t="n"/>
-      <c r="E197" s="33" t="n"/>
-      <c r="F197" s="33" t="n"/>
-    </row>
-    <row r="198" ht="20" customHeight="1">
-      <c r="A198" s="3" t="inlineStr">
+    <row r="199" ht="3" customHeight="1">
+      <c r="A199" s="33" t="n"/>
+      <c r="B199" s="33" t="n"/>
+      <c r="C199" s="33" t="n"/>
+      <c r="D199" s="33" t="n"/>
+      <c r="E199" s="33" t="n"/>
+      <c r="F199" s="33" t="n"/>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>DAY 11  |  Jun 30  |  The Razor-Edge Peaks — Seceda · Val di Funes · Adolf Munkel Trail  |  ~80 km / 50 mi  ~2h total · Collalbo loop day</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="15" customHeight="1">
-      <c r="A199" s="4" t="inlineStr">
+    <row r="201" ht="15" customHeight="1">
+      <c r="A201" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Collalbo ▸ 8:45am Seceda cable car ▸ Trail 1 ridge + Rifugio Firenze lunch ▸ 1pm drive Val di Funes ▸ Santa Maddalena barrier + Panorama Trail ▸ St. Johann Ranui ▸ Zans traffic light ▸ 1:30pm Adolf Munkel Trail 35 ▸ Rifugio Odle lounge chairs ▸ 5:30pm descent ▸ 7pm Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="5" t="inlineStr">
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Seceda 8:45am — pre-booked · photos best 9–10:30am before clouds form · razor ridge Trail 1  |   Santa Maddalena 2026 barrier — park at Filler/Putzen lot · walk 25min Panorama Trail · cannot drive up  |   Zans traffic light Red → don't wait · park Ranui immediately + Bus 330 · saves hiking time</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="50" customHeight="1">
-      <c r="A201" s="16" t="inlineStr"/>
-      <c r="B201" s="17" t="inlineStr">
+    <row r="203" ht="50" customHeight="1">
+      <c r="A203" s="16" t="inlineStr"/>
+      <c r="B203" s="17" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C201" s="16" t="inlineStr">
+      <c r="C203" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D201" s="17" t="inlineStr"/>
-      <c r="E201" s="18" t="inlineStr">
+      <c r="D203" s="17" t="inlineStr"/>
+      <c r="E203" s="18" t="inlineStr">
         <is>
           <t>️ Parking at Seceda valley station — no booking needed · €2.80/hr · 250+ spaces · arrive before 9am (your 8:45am slot guarantees this) · if full: Garage Central Ortisei €19.80/day · 10 min walk via La Curta escalator tun</t>
         </is>
       </c>
-      <c r="F201" s="19" t="inlineStr">
+      <c r="F203" s="19" t="inlineStr">
         <is>
           <t>€2.80 / €19.80 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="49" customHeight="1">
-      <c r="A202" s="6" t="inlineStr"/>
-      <c r="B202" s="7" t="inlineStr">
+    <row r="204" ht="49" customHeight="1">
+      <c r="A204" s="6" t="inlineStr"/>
+      <c r="B204" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C202" s="8" t="inlineStr">
+      <c r="C204" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D202" s="7" t="inlineStr"/>
-      <c r="E202" s="9" t="inlineStr">
+      <c r="D204" s="7" t="inlineStr"/>
+      <c r="E204" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 8:45am — Seceda 360 cable car — ✅ Booked · Receipt 1161/678/554260 · €255 total · 2 adults €84.50 + 2 juniors €43 · print tickets before departure · best photos 9–10:30am before clouds</t>
         </is>
       </c>
-      <c r="F202" s="10" t="inlineStr">
+      <c r="F204" s="10" t="inlineStr">
         <is>
           <t>€255 / €84.50 / €43</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="37" customHeight="1">
-      <c r="A203" s="20" t="inlineStr"/>
-      <c r="B203" s="21" t="inlineStr">
+    <row r="205" ht="37" customHeight="1">
+      <c r="A205" s="20" t="inlineStr"/>
+      <c r="B205" s="21" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C203" s="22" t="inlineStr">
+      <c r="C205" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D203" s="21" t="inlineStr"/>
-      <c r="E203" s="23" t="inlineStr">
+      <c r="D205" s="21" t="inlineStr"/>
+      <c r="E205" s="23" t="inlineStr">
         <is>
           <t>Trail 1 — Razor Edge ridge walk — from the cable car top follow Trail 1 to the summit cross · allow 1.5hrs for the ridge walk</t>
         </is>
       </c>
-      <c r="F203" s="24" t="inlineStr">
+      <c r="F205" s="24" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="11" t="inlineStr"/>
-      <c r="B204" s="12" t="inlineStr">
+    <row r="206" ht="22" customHeight="1">
+      <c r="A206" s="11" t="inlineStr"/>
+      <c r="B206" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C204" s="13" t="inlineStr">
+      <c r="C206" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D204" s="12" t="inlineStr"/>
-      <c r="E204" s="14" t="inlineStr">
+      <c r="D206" s="12" t="inlineStr"/>
+      <c r="E206" s="14" t="inlineStr">
         <is>
           <t>Lunch at Rifugio Firenze (2,039m) — allow 45 min</t>
         </is>
       </c>
-      <c r="F204" s="15" t="inlineStr">
+      <c r="F206" s="15" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="38" customHeight="1">
-      <c r="A205" s="6" t="inlineStr"/>
-      <c r="B205" s="7" t="inlineStr">
+    <row r="207" ht="38" customHeight="1">
+      <c r="A207" s="6" t="inlineStr"/>
+      <c r="B207" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C205" s="8" t="inlineStr">
+      <c r="C207" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D205" s="7" t="inlineStr"/>
-      <c r="E205" s="9" t="inlineStr">
+      <c r="D207" s="7" t="inlineStr"/>
+      <c r="E207" s="9" t="inlineStr">
         <is>
           <t>1:00pm — Val di Funes (Santa Maddalena) —  2026 barrier — park Filler/Putzen lots · walk 25 min Panorama Trail · cannot drive up</t>
         </is>
       </c>
-      <c r="F205" s="10" t="inlineStr">
+      <c r="F207" s="10" t="inlineStr">
         <is>
           <t>25 min</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="27" customHeight="1">
-      <c r="A206" s="16" t="inlineStr"/>
-      <c r="B206" s="17" t="inlineStr">
+    <row r="208" ht="27" customHeight="1">
+      <c r="A208" s="16" t="inlineStr"/>
+      <c r="B208" s="17" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C206" s="16" t="inlineStr">
+      <c r="C208" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D206" s="17" t="inlineStr"/>
-      <c r="E206" s="18" t="inlineStr">
+      <c r="D208" s="17" t="inlineStr"/>
+      <c r="E208" s="18" t="inlineStr">
         <is>
           <t>⭐ St. Johann in Ranui — €4 turnstile for meadow access · card only · 15 min</t>
         </is>
       </c>
-      <c r="F206" s="19" t="inlineStr">
+      <c r="F208" s="19" t="inlineStr">
         <is>
           <t>€4 / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="31" customHeight="1">
-      <c r="A207" s="16" t="inlineStr"/>
-      <c r="B207" s="17" t="inlineStr">
+    <row r="209" ht="31" customHeight="1">
+      <c r="A209" s="16" t="inlineStr"/>
+      <c r="B209" s="17" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C207" s="16" t="inlineStr">
+      <c r="C209" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D207" s="17" t="inlineStr"/>
-      <c r="E207" s="18" t="inlineStr">
+      <c r="D209" s="17" t="inlineStr"/>
+      <c r="E209" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ Santa Maddalena viewpoint — most photographed scene in South Tyrol · best light: late afternoon</t>
         </is>
       </c>
-      <c r="F207" s="19" t="inlineStr"/>
-    </row>
-    <row r="208" ht="29" customHeight="1">
-      <c r="A208" s="6" t="inlineStr"/>
-      <c r="B208" s="7" t="inlineStr">
+      <c r="F209" s="19" t="inlineStr"/>
+    </row>
+    <row r="210" ht="29" customHeight="1">
+      <c r="A210" s="6" t="inlineStr"/>
+      <c r="B210" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C208" s="8" t="inlineStr">
+      <c r="C210" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D208" s="7" t="inlineStr"/>
-      <c r="E208" s="9" t="inlineStr">
+      <c r="D210" s="7" t="inlineStr"/>
+      <c r="E210" s="9" t="inlineStr">
         <is>
           <t>⚠️ Zans traffic light —  Green = drive up ·  Red = park Ranui + Bus 330 · don't wait</t>
         </is>
       </c>
-      <c r="F208" s="10" t="inlineStr"/>
-    </row>
-    <row r="209" ht="33" customHeight="1">
-      <c r="A209" s="20" t="inlineStr"/>
-      <c r="B209" s="21" t="inlineStr">
+      <c r="F210" s="10" t="inlineStr"/>
+    </row>
+    <row r="211" ht="33" customHeight="1">
+      <c r="A211" s="20" t="inlineStr"/>
+      <c r="B211" s="21" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C209" s="22" t="inlineStr">
+      <c r="C211" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D209" s="21" t="inlineStr"/>
-      <c r="E209" s="23" t="inlineStr">
+      <c r="D211" s="21" t="inlineStr"/>
+      <c r="E211" s="23" t="inlineStr">
         <is>
           <t>1:30pm — Adolf Munkel Trail 35 — from Parkplatz Zanser Alm (Zannes) trailhead · Trail 35 (Via delle Odle)</t>
         </is>
       </c>
-      <c r="F209" s="24" t="inlineStr"/>
-    </row>
-    <row r="210" ht="38" customHeight="1">
-      <c r="A210" s="11" t="inlineStr"/>
-      <c r="B210" s="12" t="inlineStr">
+      <c r="F211" s="24" t="inlineStr"/>
+    </row>
+    <row r="212" ht="38" customHeight="1">
+      <c r="A212" s="11" t="inlineStr"/>
+      <c r="B212" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C210" s="13" t="inlineStr">
+      <c r="C212" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D210" s="12" t="inlineStr"/>
-      <c r="E210" s="14" t="inlineStr">
+      <c r="D212" s="12" t="inlineStr"/>
+      <c r="E212" s="14" t="inlineStr">
         <is>
           <t>⭐ ⭐ Rifugio Odle / Geisler Alm (1,986m) — the Cinema of the Odle — the best seats in the Dolomites · cash is faster but cards accepted</t>
         </is>
       </c>
-      <c r="F210" s="15" t="inlineStr"/>
-    </row>
-    <row r="211" ht="36" customHeight="1">
-      <c r="A211" s="6" t="inlineStr"/>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="F212" s="15" t="inlineStr"/>
+    </row>
+    <row r="213" ht="36" customHeight="1">
+      <c r="A213" s="6" t="inlineStr"/>
+      <c r="B213" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C211" s="8" t="inlineStr">
+      <c r="C213" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D211" s="7" t="inlineStr"/>
-      <c r="E211" s="9" t="inlineStr">
+      <c r="D213" s="7" t="inlineStr"/>
+      <c r="E213" s="9" t="inlineStr">
         <is>
           <t>5:30pm — Descent to Zannes car park — ~1hr back down · same trail · arrive Zannes ~6:30pm · drive 50 min back to Collalbo</t>
         </is>
       </c>
-      <c r="F211" s="10" t="inlineStr">
+      <c r="F213" s="10" t="inlineStr">
         <is>
           <t>~1hr / 50 min</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="29" customHeight="1">
-      <c r="A212" s="25" t="inlineStr"/>
-      <c r="B212" s="26" t="inlineStr">
+    <row r="214" ht="29" customHeight="1">
+      <c r="A214" s="25" t="inlineStr"/>
+      <c r="B214" s="26" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C212" s="27" t="inlineStr">
+      <c r="C214" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D212" s="26" t="inlineStr"/>
-      <c r="E212" s="28" t="inlineStr">
+      <c r="D214" s="26" t="inlineStr"/>
+      <c r="E214" s="28" t="inlineStr">
         <is>
           <t>⭐ Renon Earth Pyramids — evening walk — ➕ Optional if energy allows · 5 min from hotel</t>
         </is>
       </c>
-      <c r="F212" s="29" t="inlineStr">
+      <c r="F214" s="29" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="19" customHeight="1">
-      <c r="A213" s="25" t="inlineStr"/>
-      <c r="B213" s="26" t="inlineStr">
+    <row r="215" ht="19" customHeight="1">
+      <c r="A215" s="25" t="inlineStr"/>
+      <c r="B215" s="26" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C213" s="27" t="inlineStr">
+      <c r="C215" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D213" s="26" t="inlineStr"/>
-      <c r="E213" s="28" t="inlineStr">
+      <c r="D215" s="26" t="inlineStr"/>
+      <c r="E215" s="28" t="inlineStr">
         <is>
           <t>Night 2 — Kaiserau 1907, Collalbo</t>
         </is>
       </c>
-      <c r="F213" s="29" t="inlineStr"/>
-    </row>
-    <row r="214" ht="34" customHeight="1">
-      <c r="A214" s="30" t="inlineStr"/>
-      <c r="B214" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C214" s="32" t="inlineStr">
-        <is>
-          <t>Santa Maddalena 2026 barrier — physical barrier blocks non-resident cars since May 2026 · park Filler or Putzen lots in village · follow Panorama Trail signs · 25 min uphill walk to the viewpoint · you can no longer drive to the famous phot</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="30" customHeight="1">
-      <c r="A215" s="30" t="inlineStr"/>
-      <c r="B215" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C215" s="32" t="inlineStr">
-        <is>
-          <t>Zans traffic light 2026 — Green = drive up · Red = park at Ranui immediately + Bus 330 every 30–60 min · do not wait at the gate — bus is faster</t>
-        </is>
-      </c>
+      <c r="F215" s="29" t="inlineStr"/>
     </row>
     <row r="216" ht="34" customHeight="1">
       <c r="A216" s="30" t="inlineStr"/>
@@ -4876,132 +4887,114 @@
       </c>
       <c r="C216" s="32" t="inlineStr">
         <is>
+          <t>Santa Maddalena 2026 barrier — physical barrier blocks non-resident cars since May 2026 · park Filler or Putzen lots in village · follow Panorama Trail signs · 25 min uphill walk to the viewpoint · you can no longer drive to the famous phot</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="30" customHeight="1">
+      <c r="A217" s="30" t="inlineStr"/>
+      <c r="B217" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C217" s="32" t="inlineStr">
+        <is>
+          <t>Zans traffic light 2026 — Green = drive up · Red = park at Ranui immediately + Bus 330 every 30–60 min · do not wait at the gate — bus is faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="34" customHeight="1">
+      <c r="A218" s="30" t="inlineStr"/>
+      <c r="B218" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C218" s="32" t="inlineStr">
+        <is>
           <t>Photography windows — Seceda ridge: 9:00–10:30am before clouds form · Santa Maddalena viewpoint: late afternoon — sun behind you · Odle peaks lit directly · morning light hits the wrong side of the peaks</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="3" customHeight="1">
-      <c r="A217" s="33" t="n"/>
-      <c r="B217" s="33" t="n"/>
-      <c r="C217" s="33" t="n"/>
-      <c r="D217" s="33" t="n"/>
-      <c r="E217" s="33" t="n"/>
-      <c r="F217" s="33" t="n"/>
-    </row>
-    <row r="218" ht="20" customHeight="1">
-      <c r="A218" s="3" t="inlineStr">
+    <row r="219" ht="3" customHeight="1">
+      <c r="A219" s="33" t="n"/>
+      <c r="B219" s="33" t="n"/>
+      <c r="C219" s="33" t="n"/>
+      <c r="D219" s="33" t="n"/>
+      <c r="E219" s="33" t="n"/>
+      <c r="F219" s="33" t="n"/>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="3" t="inlineStr">
         <is>
           <t>DAY 12  |  Jul 1  |  Alpe di Siusi + Brenner Pass → Finkenberg — The Plateau &amp; The Pass  |  ~120 km / 75 mi  ~1h 45m · Collalbo → Finkenberg via Brenner</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="15" customHeight="1">
-      <c r="A219" s="4" t="inlineStr">
+    <row r="221" ht="15" customHeight="1">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>Timeline: 7:45am Collalbo ▸ 8:30am St. Valentin gate (must be before 9am) ▸ 8:45am P2 Compatsch ▸ 9:15am Bullaccia loop ▸ Hexenbänke viewpoint ▸ 12pm Tschötsch Alm lunch ▸ 1:30pm depart ▸ Brenner construction ▸ M-Preis Mayrhofen ▸ 4:30pm Keyone Rooms Finkenberg</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="22" customHeight="1">
-      <c r="A220" s="5" t="inlineStr">
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="5" t="inlineStr">
         <is>
           <t>Key: ️ Plan A: P2 Compatsch — keep checking seiseralm.it for cancellations · must arrive before 9am · €30  |   Plan B: Seis cable car → Compatsch — park in Seis · ~€30/adult RT · no booking · no 9am rule · same trailhead  |   St. Valentin gate closes 9:00am SHARP — leave Collalbo 7:45am · arrive 8:30am · no exceptions  |  ❌ Skip Rifugio Zallinger — 4hr RT or 2 extra lifts · impractical · eat at Tschötsch Alm instead  |  ⚠️ Brenner Lueg Bridge construction 2026 — 30–45 min delay · Digital Flex toll essential</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="40" customHeight="1">
-      <c r="A221" s="6" t="inlineStr"/>
-      <c r="B221" s="7" t="inlineStr">
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" s="6" t="inlineStr"/>
+      <c r="B223" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C221" s="8" t="inlineStr">
+      <c r="C223" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D221" s="7" t="inlineStr"/>
-      <c r="E221" s="9" t="inlineStr">
+      <c r="D223" s="7" t="inlineStr"/>
+      <c r="E223" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:45am — Depart Collalbo — 40 min drive to the Alpe di Siusi St. Valentin gate · checkout Kaiserau 1907 before leaving · luggage in the car</t>
         </is>
       </c>
-      <c r="F221" s="10" t="inlineStr">
+      <c r="F223" s="10" t="inlineStr">
         <is>
           <t>40 min</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="31" customHeight="1">
-      <c r="A222" s="34" t="inlineStr"/>
-      <c r="B222" s="35" t="inlineStr">
+    <row r="224" ht="31" customHeight="1">
+      <c r="A224" s="34" t="inlineStr"/>
+      <c r="B224" s="35" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C222" s="36" t="inlineStr">
+      <c r="C224" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D222" s="35" t="inlineStr"/>
-      <c r="E222" s="37" t="inlineStr">
+      <c r="D224" s="35" t="inlineStr"/>
+      <c r="E224" s="37" t="inlineStr">
         <is>
           <t>⚠️ CRITICAL: St. Valentin Gate — before 9:00am — 9:01am = turned back · €120+ cable car alternative</t>
         </is>
       </c>
-      <c r="F222" s="38" t="inlineStr">
+      <c r="F224" s="38" t="inlineStr">
         <is>
           <t>€120</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="50" customHeight="1">
-      <c r="A223" s="20" t="inlineStr"/>
-      <c r="B223" s="21" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C223" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D223" s="21" t="inlineStr"/>
-      <c r="E223" s="23" t="inlineStr">
-        <is>
-          <t>P2 Compatsch parking — ⚠️ Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · €30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch ca</t>
-        </is>
-      </c>
-      <c r="F223" s="24" t="inlineStr">
-        <is>
-          <t>€30 / €30 / €65</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="34" customHeight="1">
-      <c r="A224" s="20" t="inlineStr"/>
-      <c r="B224" s="21" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C224" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D224" s="21" t="inlineStr"/>
-      <c r="E224" s="23" t="inlineStr">
-        <is>
-          <t>9:15am — Bullaccia (Puflatsch) Loop — take the Telemix lift up from Compatsch · Trail PU (Puflatschumrundung)</t>
-        </is>
-      </c>
-      <c r="F224" s="24" t="inlineStr"/>
-    </row>
-    <row r="225" ht="23" customHeight="1">
+    <row r="225" ht="50" customHeight="1">
       <c r="A225" s="20" t="inlineStr"/>
       <c r="B225" s="21" t="inlineStr">
         <is>
@@ -5016,124 +5009,124 @@
       <c r="D225" s="21" t="inlineStr"/>
       <c r="E225" s="23" t="inlineStr">
         <is>
+          <t>P2 Compatsch parking — ⚠️ Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · €30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch ca</t>
+        </is>
+      </c>
+      <c r="F225" s="24" t="inlineStr">
+        <is>
+          <t>€30 / €30 / €65</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="34" customHeight="1">
+      <c r="A226" s="20" t="inlineStr"/>
+      <c r="B226" s="21" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C226" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D226" s="21" t="inlineStr"/>
+      <c r="E226" s="23" t="inlineStr">
+        <is>
+          <t>9:15am — Bullaccia (Puflatsch) Loop — take the Telemix lift up from Compatsch · Trail PU (Puflatschumrundung)</t>
+        </is>
+      </c>
+      <c r="F226" s="24" t="inlineStr"/>
+    </row>
+    <row r="227" ht="23" customHeight="1">
+      <c r="A227" s="20" t="inlineStr"/>
+      <c r="B227" s="21" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C227" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D227" s="21" t="inlineStr"/>
+      <c r="E227" s="23" t="inlineStr">
+        <is>
           <t>⭐ Hexenbänke — Witches' Benches — signed from the trail</t>
         </is>
       </c>
-      <c r="F225" s="24" t="inlineStr"/>
-    </row>
-    <row r="226" ht="31" customHeight="1">
-      <c r="A226" s="11" t="inlineStr"/>
-      <c r="B226" s="12" t="inlineStr">
+      <c r="F227" s="24" t="inlineStr"/>
+    </row>
+    <row r="228" ht="31" customHeight="1">
+      <c r="A228" s="11" t="inlineStr"/>
+      <c r="B228" s="12" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C226" s="13" t="inlineStr">
+      <c r="C228" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D226" s="12" t="inlineStr"/>
-      <c r="E226" s="14" t="inlineStr">
+      <c r="D228" s="12" t="inlineStr"/>
+      <c r="E228" s="14" t="inlineStr">
         <is>
           <t>️ 12:00pm — Lunch: Tschötsch Alm or Arnika Hütte — ⚠️ Do NOT go to Rifugio Zallinger — allow 1hr</t>
         </is>
       </c>
-      <c r="F226" s="15" t="inlineStr">
+      <c r="F228" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="27" customHeight="1">
-      <c r="A227" s="6" t="inlineStr"/>
-      <c r="B227" s="7" t="inlineStr">
+    <row r="229" ht="27" customHeight="1">
+      <c r="A229" s="6" t="inlineStr"/>
+      <c r="B229" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C227" s="8" t="inlineStr">
+      <c r="C229" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D227" s="7" t="inlineStr"/>
-      <c r="E227" s="9" t="inlineStr">
+      <c r="D229" s="7" t="inlineStr"/>
+      <c r="E229" s="9" t="inlineStr">
         <is>
           <t>1:30pm — Depart Alpe di Siusi — unrestricted descent · head north to Brenner</t>
         </is>
       </c>
-      <c r="F227" s="10" t="inlineStr"/>
-    </row>
-    <row r="228" ht="50" customHeight="1">
-      <c r="A228" s="16" t="inlineStr"/>
-      <c r="B228" s="17" t="inlineStr">
+      <c r="F229" s="10" t="inlineStr"/>
+    </row>
+    <row r="230" ht="50" customHeight="1">
+      <c r="A230" s="16" t="inlineStr"/>
+      <c r="B230" s="17" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C228" s="16" t="inlineStr">
+      <c r="C230" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D228" s="17" t="inlineStr"/>
-      <c r="E228" s="18" t="inlineStr">
+      <c r="D230" s="17" t="inlineStr"/>
+      <c r="E230" s="18" t="inlineStr">
         <is>
           <t>⚠️ Brenner Pass — Lueg Bridge construction — 30–45 min delay expected · Digital Flex toll green lanes · €11.50 · ➡️ If standstill at A22/A13 toll plaza: take B182 Brenner Route Nationale — free state road running paralle</t>
         </is>
       </c>
-      <c r="F228" s="19" t="inlineStr">
+      <c r="F230" s="19" t="inlineStr">
         <is>
           <t>45 min / €11.50</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="18" customHeight="1">
-      <c r="A229" s="16" t="inlineStr"/>
-      <c r="B229" s="17" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C229" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D229" s="17" t="inlineStr"/>
-      <c r="E229" s="18" t="inlineStr">
-        <is>
-          <t>Austrian vignette still valid?</t>
-        </is>
-      </c>
-      <c r="F229" s="19" t="inlineStr"/>
-    </row>
-    <row r="230" ht="35" customHeight="1">
-      <c r="A230" s="11" t="inlineStr"/>
-      <c r="B230" s="12" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C230" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D230" s="12" t="inlineStr"/>
-      <c r="E230" s="14" t="inlineStr">
-        <is>
-          <t>M-Preis Supermarket, Mayrhofen — Finkenberg is up a winding road — nothing open nearby in the evening · allow 20 min</t>
-        </is>
-      </c>
-      <c r="F230" s="15" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="34" customHeight="1">
+    <row r="231" ht="18" customHeight="1">
       <c r="A231" s="16" t="inlineStr"/>
       <c r="B231" s="17" t="inlineStr">
         <is>
@@ -5148,62 +5141,80 @@
       <c r="D231" s="17" t="inlineStr"/>
       <c r="E231" s="18" t="inlineStr">
         <is>
+          <t>Austrian vignette still valid?</t>
+        </is>
+      </c>
+      <c r="F231" s="19" t="inlineStr"/>
+    </row>
+    <row r="232" ht="35" customHeight="1">
+      <c r="A232" s="11" t="inlineStr"/>
+      <c r="B232" s="12" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C232" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D232" s="12" t="inlineStr"/>
+      <c r="E232" s="14" t="inlineStr">
+        <is>
+          <t>M-Preis Supermarket, Mayrhofen — Finkenberg is up a winding road — nothing open nearby in the evening · allow 20 min</t>
+        </is>
+      </c>
+      <c r="F232" s="15" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="34" customHeight="1">
+      <c r="A233" s="16" t="inlineStr"/>
+      <c r="B233" s="17" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C233" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D233" s="17" t="inlineStr"/>
+      <c r="E233" s="18" t="inlineStr">
+        <is>
           <t>4:30pm — Keyone Rooms, Finkenberg — $176 / €152.92 · ⚠️ Driveway can be steep — take it slowly on the approach</t>
         </is>
       </c>
-      <c r="F231" s="19" t="inlineStr">
+      <c r="F233" s="19" t="inlineStr">
         <is>
           <t>$176 / €152.92</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="29" customHeight="1">
-      <c r="A232" s="6" t="inlineStr"/>
-      <c r="B232" s="7" t="inlineStr">
+    <row r="234" ht="29" customHeight="1">
+      <c r="A234" s="6" t="inlineStr"/>
+      <c r="B234" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C232" s="8" t="inlineStr">
+      <c r="C234" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D232" s="7" t="inlineStr"/>
-      <c r="E232" s="9" t="inlineStr">
+      <c r="D234" s="7" t="inlineStr"/>
+      <c r="E234" s="9" t="inlineStr">
         <is>
           <t>Dinner in Finkenberg or Mayrhofen — or drive 5 min down to Mayrhofen for more options</t>
         </is>
       </c>
-      <c r="F232" s="10" t="inlineStr">
+      <c r="F234" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="34" customHeight="1">
-      <c r="A233" s="30" t="inlineStr"/>
-      <c r="B233" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C233" s="32" t="inlineStr">
-        <is>
-          <t>9:00am St. Valentin gate — non-negotiable — electronic barrier closes to private cars at exactly 9am · 9:01am = turned back · €120+ family cable car alternative · leave Collalbo by 7:45am</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="34" customHeight="1">
-      <c r="A234" s="30" t="inlineStr"/>
-      <c r="B234" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C234" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Brenner Lueg Bridge 2026 — single-lane renovation · 30–45 min delay expected · Digital Flex toll at autobrennero.it · €11.50 · green Video Toll lanes · saves 1hr vs manual queue</t>
         </is>
       </c>
     </row>
@@ -5216,11 +5227,11 @@
       </c>
       <c r="C235" s="32" t="inlineStr">
         <is>
-          <t>Hexenbänke — Witches' Benches — giant stone formations on the Bullaccia ridge · highest point of the plateau · best 360° photo spot · signed from the trail · kids love the legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="32" customHeight="1">
+          <t>9:00am St. Valentin gate — non-negotiable — electronic barrier closes to private cars at exactly 9am · 9:01am = turned back · €120+ family cable car alternative · leave Collalbo by 7:45am</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="34" customHeight="1">
       <c r="A236" s="30" t="inlineStr"/>
       <c r="B236" s="31" t="inlineStr">
         <is>
@@ -5229,112 +5240,90 @@
       </c>
       <c r="C236" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Brenner Lueg Bridge 2026 — single-lane renovation · 30–45 min delay expected · Digital Flex toll at autobrennero.it · €11.50 · green Video Toll lanes · saves 1hr vs manual queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="34" customHeight="1">
+      <c r="A237" s="30" t="inlineStr"/>
+      <c r="B237" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C237" s="32" t="inlineStr">
+        <is>
+          <t>Hexenbänke — Witches' Benches — giant stone formations on the Bullaccia ridge · highest point of the plateau · best 360° photo spot · signed from the trail · kids love the legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="32" customHeight="1">
+      <c r="A238" s="30" t="inlineStr"/>
+      <c r="B238" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C238" s="32" t="inlineStr">
+        <is>
           <t>M-Preis Mayrhofen — stop before Finkenberg · buy breakfast for Day 13 · nothing open near Keyone in evenings · steep winding road to Finkenberg — take slowly</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="3" customHeight="1">
-      <c r="A237" s="33" t="n"/>
-      <c r="B237" s="33" t="n"/>
-      <c r="C237" s="33" t="n"/>
-      <c r="D237" s="33" t="n"/>
-      <c r="E237" s="33" t="n"/>
-      <c r="F237" s="33" t="n"/>
-    </row>
-    <row r="238" ht="20" customHeight="1">
-      <c r="A238" s="3" t="inlineStr">
+    <row r="239" ht="3" customHeight="1">
+      <c r="A239" s="33" t="n"/>
+      <c r="B239" s="33" t="n"/>
+      <c r="C239" s="33" t="n"/>
+      <c r="D239" s="33" t="n"/>
+      <c r="E239" s="33" t="n"/>
+      <c r="F239" s="33" t="n"/>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="3" t="inlineStr">
         <is>
           <t>DAY 13  |  Jul 2  |  High Bridges &amp; Deep Lakes — Olpererhütte · Achensee · Swarovski → Bichlbach  |  ~150 km / 93 mi  ~2h 30m incl. Achensee + Swarovski stops</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="15" customHeight="1">
-      <c r="A239" s="4" t="inlineStr">
+    <row r="241" ht="15" customHeight="1">
+      <c r="A241" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Finkenberg ▸ 8:30am Schlegeis toll €17 ▸ 9am Olpererhütte hike ▸ 10:30am Kebema bridge ▸ 11am lunch ▸ 1:30pm descent ▸ Swarovski (if rain) ▸ Achensee optional ▸ Fern Pass ▸ 7:30pm Bichlbach ▸ Heiterwanger See sunset</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="22" customHeight="1">
-      <c r="A240" s="5" t="inlineStr">
+    <row r="242" ht="22" customHeight="1">
+      <c r="A242" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Arrive dam by 8:45am — reach Kebema bridge 10:30am · beats 45min photo queue by midday  |  ☀️ Plan A (sunny): Achensee — steamboat ~€22/adult OR free Gaisalm promenade walk if kids tired  |  ️ Plan B (rain/cloudy): Swarovski Crystal Worlds — 5min off A12 · ~€22/adult · no booking needed</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="31" customHeight="1">
-      <c r="A241" s="6" t="inlineStr"/>
-      <c r="B241" s="7" t="inlineStr">
+    <row r="243" ht="31" customHeight="1">
+      <c r="A243" s="6" t="inlineStr"/>
+      <c r="B243" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C241" s="8" t="inlineStr">
+      <c r="C243" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D241" s="7" t="inlineStr"/>
-      <c r="E241" s="9" t="inlineStr">
+      <c r="D243" s="7" t="inlineStr"/>
+      <c r="E243" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:00am — Depart Finkenberg — 20 min to Schlegeis · ⚠️ tunnel traffic lights = up to 15 min wait</t>
         </is>
       </c>
-      <c r="F241" s="10" t="inlineStr">
+      <c r="F243" s="10" t="inlineStr">
         <is>
           <t>20 min / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="27" customHeight="1">
-      <c r="A242" s="16" t="inlineStr"/>
-      <c r="B242" s="17" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C242" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D242" s="17" t="inlineStr"/>
-      <c r="E242" s="18" t="inlineStr">
-        <is>
-          <t>8:30am — Schlegeis Alpine Road toll — €17 · pay at the gate (cash or card)</t>
-        </is>
-      </c>
-      <c r="F242" s="19" t="inlineStr">
-        <is>
-          <t>€17</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="29" customHeight="1">
-      <c r="A243" s="20" t="inlineStr"/>
-      <c r="B243" s="21" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C243" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D243" s="21" t="inlineStr"/>
-      <c r="E243" s="23" t="inlineStr">
-        <is>
-          <t>9:00am — Olpererhütte Hike (Trail 502) — 3km / 1.9mi each way · well-maintained trail</t>
-        </is>
-      </c>
-      <c r="F243" s="24" t="inlineStr">
-        <is>
-          <t>3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="41" customHeight="1">
+    <row r="244" ht="27" customHeight="1">
       <c r="A244" s="16" t="inlineStr"/>
       <c r="B244" s="17" t="inlineStr">
         <is>
@@ -5349,88 +5338,88 @@
       <c r="D244" s="17" t="inlineStr"/>
       <c r="E244" s="18" t="inlineStr">
         <is>
+          <t>8:30am — Schlegeis Alpine Road toll — €17 · pay at the gate (cash or card)</t>
+        </is>
+      </c>
+      <c r="F244" s="19" t="inlineStr">
+        <is>
+          <t>€17</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="29" customHeight="1">
+      <c r="A245" s="20" t="inlineStr"/>
+      <c r="B245" s="21" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C245" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D245" s="21" t="inlineStr"/>
+      <c r="E245" s="23" t="inlineStr">
+        <is>
+          <t>9:00am — Olpererhütte Hike (Trail 502) — 3km / 1.9mi each way · well-maintained trail</t>
+        </is>
+      </c>
+      <c r="F245" s="24" t="inlineStr">
+        <is>
+          <t>3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="41" customHeight="1">
+      <c r="A246" s="16" t="inlineStr"/>
+      <c r="B246" s="17" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C246" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D246" s="17" t="inlineStr"/>
+      <c r="E246" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 10:30am — Kebema Suspension Bridge (Olperer Panoramabrücke) — 3–4 min past the hut · floats in mid-air above the turquoise reservoir 600m below</t>
         </is>
       </c>
-      <c r="F244" s="19" t="inlineStr">
+      <c r="F246" s="19" t="inlineStr">
         <is>
           <t>4 min</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="36" customHeight="1">
-      <c r="A245" s="11" t="inlineStr"/>
-      <c r="B245" s="12" t="inlineStr">
+    <row r="247" ht="36" customHeight="1">
+      <c r="A247" s="11" t="inlineStr"/>
+      <c r="B247" s="12" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C245" s="13" t="inlineStr">
+      <c r="C247" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D245" s="12" t="inlineStr"/>
-      <c r="E245" s="14" t="inlineStr">
+      <c r="D247" s="12" t="inlineStr"/>
+      <c r="E247" s="14" t="inlineStr">
         <is>
           <t>️ 11:00am — Lunch at Olpererhütte — cash preferred (but Wi-Fi available — check your Neuschwanstein booking!) · allow 1hr</t>
         </is>
       </c>
-      <c r="F245" s="15" t="inlineStr">
+      <c r="F247" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="35" customHeight="1">
-      <c r="A246" s="20" t="inlineStr"/>
-      <c r="B246" s="21" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C246" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D246" s="21" t="inlineStr"/>
-      <c r="E246" s="23" t="inlineStr">
-        <is>
-          <t>1:30pm — Descent to the dam — ~1hr back down same trail · easier on the knees than going up · back at car ~2:30pm</t>
-        </is>
-      </c>
-      <c r="F246" s="24" t="inlineStr">
-        <is>
-          <t>~1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="50" customHeight="1">
-      <c r="A247" s="6" t="inlineStr"/>
-      <c r="B247" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2</t>
-        </is>
-      </c>
-      <c r="C247" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D247" s="7" t="inlineStr"/>
-      <c r="E247" s="9" t="inlineStr">
-        <is>
-          <t>☀️ Plan A — Sunny: Achensee — 50 min drive north from Schlegeis · park at Pertisau · Option 1: Achensee steamboat ~€22/adult · allow 1.5hrs · Option 2 (kids tired): Gaisalm promenade walk — free · same fjord-like views ·</t>
-        </is>
-      </c>
-      <c r="F247" s="10" t="inlineStr">
-        <is>
-          <t>50 min / €22 / 5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="50" customHeight="1">
+    <row r="248" ht="35" customHeight="1">
       <c r="A248" s="20" t="inlineStr"/>
       <c r="B248" s="21" t="inlineStr">
         <is>
@@ -5445,16 +5434,16 @@
       <c r="D248" s="21" t="inlineStr"/>
       <c r="E248" s="23" t="inlineStr">
         <is>
-          <t>️ Plan B — Rain/Cloudy: Swarovski Crystal Worlds — 5 min off A12 at Wattens · ~€22/adult · allow 1.5–2hrs · indoor immersive art installation · perfect rainy-day refuge after cold wet Olpererhütte hike · no booking neede</t>
+          <t>1:30pm — Descent to the dam — ~1hr back down same trail · easier on the knees than going up · back at car ~2:30pm</t>
         </is>
       </c>
       <c r="F248" s="24" t="inlineStr">
         <is>
-          <t>5 min / €22 / 2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="29" customHeight="1">
+          <t>~1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="50" customHeight="1">
       <c r="A249" s="6" t="inlineStr"/>
       <c r="B249" s="7" t="inlineStr">
         <is>
@@ -5469,104 +5458,126 @@
       <c r="D249" s="7" t="inlineStr"/>
       <c r="E249" s="9" t="inlineStr">
         <is>
+          <t>☀️ Plan A — Sunny: Achensee — 50 min drive north from Schlegeis · park at Pertisau · Option 1: Achensee steamboat ~€22/adult · allow 1.5hrs · Option 2 (kids tired): Gaisalm promenade walk — free · same fjord-like views ·</t>
+        </is>
+      </c>
+      <c r="F249" s="10" t="inlineStr">
+        <is>
+          <t>50 min / €22 / 5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="50" customHeight="1">
+      <c r="A250" s="20" t="inlineStr"/>
+      <c r="B250" s="21" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C250" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D250" s="21" t="inlineStr"/>
+      <c r="E250" s="23" t="inlineStr">
+        <is>
+          <t>️ Plan B — Rain/Cloudy: Swarovski Crystal Worlds — 5 min off A12 at Wattens · ~€22/adult · allow 1.5–2hrs · indoor immersive art installation · perfect rainy-day refuge after cold wet Olpererhütte hike · no booking neede</t>
+        </is>
+      </c>
+      <c r="F250" s="24" t="inlineStr">
+        <is>
+          <t>5 min / €22 / 2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="29" customHeight="1">
+      <c r="A251" s="6" t="inlineStr"/>
+      <c r="B251" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D251" s="7" t="inlineStr"/>
+      <c r="E251" s="9" t="inlineStr">
+        <is>
           <t>⚠️ Fern Pass warning on drive to Bichlbach — village Gasthäuser are relaxed about timing</t>
         </is>
       </c>
-      <c r="F249" s="10" t="inlineStr"/>
-    </row>
-    <row r="250" ht="33" customHeight="1">
-      <c r="A250" s="25" t="inlineStr"/>
-      <c r="B250" s="26" t="inlineStr">
+      <c r="F251" s="10" t="inlineStr"/>
+    </row>
+    <row r="252" ht="33" customHeight="1">
+      <c r="A252" s="25" t="inlineStr"/>
+      <c r="B252" s="26" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C250" s="27" t="inlineStr">
+      <c r="C252" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D250" s="26" t="inlineStr"/>
-      <c r="E250" s="28" t="inlineStr">
+      <c r="D252" s="26" t="inlineStr"/>
+      <c r="E252" s="28" t="inlineStr">
         <is>
           <t>~7:30pm — Landhaus Bichlbach — $467 / €405 · Heiterwanger See lake is a 20 min evening walk from the hotel</t>
         </is>
       </c>
-      <c r="F250" s="29" t="inlineStr">
+      <c r="F252" s="29" t="inlineStr">
         <is>
           <t>$467 / €405 / 20 min</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="28" customHeight="1">
-      <c r="A251" s="16" t="inlineStr"/>
-      <c r="B251" s="17" t="inlineStr">
+    <row r="253" ht="28" customHeight="1">
+      <c r="A253" s="16" t="inlineStr"/>
+      <c r="B253" s="17" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C251" s="16" t="inlineStr">
+      <c r="C253" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D251" s="17" t="inlineStr"/>
-      <c r="E251" s="18" t="inlineStr">
+      <c r="D253" s="17" t="inlineStr"/>
+      <c r="E253" s="18" t="inlineStr">
         <is>
           <t>⭐ Heiterwanger See sunset walk — easy 20 min walk from Landhaus along Panoramaweg</t>
         </is>
       </c>
-      <c r="F251" s="19" t="inlineStr">
+      <c r="F253" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="25" customHeight="1">
-      <c r="A252" s="6" t="inlineStr"/>
-      <c r="B252" s="7" t="inlineStr">
+    <row r="254" ht="25" customHeight="1">
+      <c r="A254" s="6" t="inlineStr"/>
+      <c r="B254" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C252" s="8" t="inlineStr">
+      <c r="C254" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D252" s="7" t="inlineStr"/>
-      <c r="E252" s="9" t="inlineStr">
+      <c r="D254" s="7" t="inlineStr"/>
+      <c r="E254" s="9" t="inlineStr">
         <is>
           <t>Dinner + pack bags — Gasthof Bichlbach · checkout 8am · alarm 7am</t>
         </is>
       </c>
-      <c r="F252" s="10" t="inlineStr"/>
-    </row>
-    <row r="253" ht="32" customHeight="1">
-      <c r="A253" s="30" t="inlineStr"/>
-      <c r="B253" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C253" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Schlegeis tunnel traffic lights — one-way sections · red light = up to 15 min wait · factor into morning timing · aim to be at the dam car park by 8:45am</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="34" customHeight="1">
-      <c r="A254" s="30" t="inlineStr"/>
-      <c r="B254" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C254" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Fern Pass congestion 2026 — slow trucks · one of the most congested alpine roads · flexible dinner only — no reservations · Bichlbach Gasthäuser are relaxed about timing</t>
-        </is>
-      </c>
+      <c r="F254" s="10" t="inlineStr"/>
     </row>
     <row r="255" ht="32" customHeight="1">
       <c r="A255" s="30" t="inlineStr"/>
@@ -5577,136 +5588,103 @@
       </c>
       <c r="C255" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Schlegeis tunnel traffic lights — one-way sections · red light = up to 15 min wait · factor into morning timing · aim to be at the dam car park by 8:45am</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="34" customHeight="1">
+      <c r="A256" s="30" t="inlineStr"/>
+      <c r="B256" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C256" s="32" t="inlineStr">
+        <is>
+          <t>⚠️ Fern Pass congestion 2026 — slow trucks · one of the most congested alpine roads · flexible dinner only — no reservations · Bichlbach Gasthäuser are relaxed about timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="32" customHeight="1">
+      <c r="A257" s="30" t="inlineStr"/>
+      <c r="B257" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C257" s="32" t="inlineStr">
+        <is>
           <t>At Olpererhütte: check Neuschwanstein booking — the hut has excellent Wi-Fi · confirm your 9:30am slot for tomorrow · cash preferred for food but cards accepted</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="3" customHeight="1">
-      <c r="A256" s="33" t="n"/>
-      <c r="B256" s="33" t="n"/>
-      <c r="C256" s="33" t="n"/>
-      <c r="D256" s="33" t="n"/>
-      <c r="E256" s="33" t="n"/>
-      <c r="F256" s="33" t="n"/>
-    </row>
-    <row r="257" ht="20" customHeight="1">
-      <c r="A257" s="3" t="inlineStr">
+    <row r="258" ht="34" customHeight="1">
+      <c r="A258" s="30" t="inlineStr"/>
+      <c r="B258" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C258" s="32" t="inlineStr">
+        <is>
+          <t>Blindsee — 2km from Landhaus Bichlbach — one of Austria's most photogenic lakes · emerald green · often misty in the morning · short walk or 3 min drive from the hotel · many visitors prefer it over Achensee · perfect early morning walk bef</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="3" customHeight="1">
+      <c r="A259" s="33" t="n"/>
+      <c r="B259" s="33" t="n"/>
+      <c r="C259" s="33" t="n"/>
+      <c r="D259" s="33" t="n"/>
+      <c r="E259" s="33" t="n"/>
+      <c r="F259" s="33" t="n"/>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
         <is>
           <t>DAY 14  |  Jul 3  |  The Lakes of the Dragon — Seebensee · Drachensee · Coburger Hütte  |  ~20 km / 12 mi  ~30m · just Bichlbach ↔ Ehrwald</t>
         </is>
       </c>
     </row>
-    <row r="258" ht="15" customHeight="1">
-      <c r="A258" s="4" t="inlineStr">
+    <row r="261" ht="15" customHeight="1">
+      <c r="A261" s="4" t="inlineStr">
         <is>
           <t>Timeline: Tonight: ATM Ehrwald €60–80 ▸ 7:45am Bichlbach ▸ 8:00am Ehrwalder Almbahn (first car) ▸ 8:10am hike ▸ 9:45am Seebensee mirror ▸ 10:15am Drachensee climb ▸ 11:00am Coburger Hütte Kaiserschmarrn ▸ 12:45pm descent ▸ 2:45pm back at car ▸ 3pm Bichlbach ▸ 7:30pm Heiterwanger See sunset</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="22" customHeight="1">
-      <c r="A259" s="5" t="inlineStr">
+    <row r="262" ht="22" customHeight="1">
+      <c r="A262" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ ATM in Ehrwald tonight — €60–80 cash · Coburger Hütte cash only · no card reader  |  ✅ 7:45am departure — first cable car 8:00am · arrive Seebensee 9:45am · beats 10:30am winds  |  ⚠️ Seebensee mirror reflection before 10:30am — winds create ripples by midday · 9:45am arrival ✅  |  ⚠️ Drachensee path slippery if rained Jul 2 — best-grip boots · 217m steep climb · 30–45 min  |  ➕ E-bikes optional at valley station — cuts Seebensee hike from 1.5hrs to 25 min · saves legs for Drachensee</t>
         </is>
       </c>
     </row>
-    <row r="260" ht="50" customHeight="1">
-      <c r="A260" s="16" t="inlineStr"/>
-      <c r="B260" s="17" t="inlineStr">
+    <row r="263" ht="50" customHeight="1">
+      <c r="A263" s="16" t="inlineStr"/>
+      <c r="B263" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C260" s="16" t="inlineStr">
+      <c r="C263" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D260" s="17" t="inlineStr"/>
-      <c r="E260" s="18" t="inlineStr">
+      <c r="D263" s="17" t="inlineStr"/>
+      <c r="E263" s="18" t="inlineStr">
         <is>
           <t>Tonight (Jul 2 evening): ATM in Ehrwald — withdraw €60–80 cash for the family · Coburger Hütte is cash only — no card reader on the mountain · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
         </is>
       </c>
-      <c r="F260" s="19" t="inlineStr">
+      <c r="F263" s="19" t="inlineStr">
         <is>
           <t>€60 / €12 / €14</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="38" customHeight="1">
-      <c r="A261" s="6" t="inlineStr"/>
-      <c r="B261" s="7" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C261" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D261" s="7" t="inlineStr"/>
-      <c r="E261" s="9" t="inlineStr">
-        <is>
-          <t>7:45am — Depart Bichlbach — 5 min drive to Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~7:55am</t>
-        </is>
-      </c>
-      <c r="F261" s="10" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="44" customHeight="1">
-      <c r="A262" s="16" t="inlineStr"/>
-      <c r="B262" s="17" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C262" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D262" s="17" t="inlineStr"/>
-      <c r="E262" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 8:00am — Ehrwalder Almbahn — first cable car of the day · ~€26/adult · free parking · 5 min at top for Zugspitze platform view · ⚠️ July high season: opens 8:00am</t>
-        </is>
-      </c>
-      <c r="F262" s="19" t="inlineStr">
-        <is>
-          <t>€26 / 5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="50" customHeight="1">
-      <c r="A263" s="20" t="inlineStr"/>
-      <c r="B263" s="21" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C263" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D263" s="21" t="inlineStr"/>
-      <c r="E263" s="23" t="inlineStr">
-        <is>
-          <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am · ➕ E-bikes available at valley station — cuts hike to 25 min if family wants to save le</t>
-        </is>
-      </c>
-      <c r="F263" s="24" t="inlineStr">
-        <is>
-          <t>6km / 5hr / 25 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="50" customHeight="1">
+    <row r="264" ht="38" customHeight="1">
       <c r="A264" s="6" t="inlineStr"/>
       <c r="B264" s="7" t="inlineStr">
         <is>
@@ -5721,106 +5699,110 @@
       <c r="D264" s="7" t="inlineStr"/>
       <c r="E264" s="9" t="inlineStr">
         <is>
+          <t>7:45am — Depart Bichlbach — 5 min drive to Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~7:55am</t>
+        </is>
+      </c>
+      <c r="F264" s="10" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="44" customHeight="1">
+      <c r="A265" s="16" t="inlineStr"/>
+      <c r="B265" s="17" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C265" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D265" s="17" t="inlineStr"/>
+      <c r="E265" s="18" t="inlineStr">
+        <is>
+          <t>⭐ 8:00am — Ehrwalder Almbahn — first cable car of the day · ~€26/adult · free parking · 5 min at top for Zugspitze platform view · ⚠️ July high season: opens 8:00am</t>
+        </is>
+      </c>
+      <c r="F265" s="19" t="inlineStr">
+        <is>
+          <t>€26 / 5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="50" customHeight="1">
+      <c r="A266" s="20" t="inlineStr"/>
+      <c r="B266" s="21" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C266" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D266" s="21" t="inlineStr"/>
+      <c r="E266" s="23" t="inlineStr">
+        <is>
+          <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am · ➕ E-bikes available at valley station — cuts hike to 25 min if family wants to save le</t>
+        </is>
+      </c>
+      <c r="F266" s="24" t="inlineStr">
+        <is>
+          <t>6km / 5hr / 25 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="50" customHeight="1">
+      <c r="A267" s="6" t="inlineStr"/>
+      <c r="B267" s="7" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D267" s="7" t="inlineStr"/>
+      <c r="E267" s="9" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 9:45am — Seebensee mirror reflection — crystal-clear turquoise water · Zugspitze reflected · winds pick up after 10:30am — 9:45am arrival is perfectly timed · allow 30 min · benches along the southern shore</t>
         </is>
       </c>
-      <c r="F264" s="10" t="inlineStr">
+      <c r="F267" s="10" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="44" customHeight="1">
-      <c r="A265" s="20" t="inlineStr"/>
-      <c r="B265" s="21" t="inlineStr">
+    <row r="268" ht="44" customHeight="1">
+      <c r="A268" s="20" t="inlineStr"/>
+      <c r="B268" s="21" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C265" s="22" t="inlineStr">
+      <c r="C268" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D265" s="21" t="inlineStr"/>
-      <c r="E265" s="23" t="inlineStr">
+      <c r="D268" s="21" t="inlineStr"/>
+      <c r="E268" s="23" t="inlineStr">
         <is>
           <t>10:15am — Drachensee ascent — 1.4km · 217m elevation gain · 30–45 min · ⚠️ slippery if rained Jul 2 · best-grip boots · steeper than Seebensee section but short</t>
         </is>
       </c>
-      <c r="F265" s="24" t="inlineStr">
+      <c r="F268" s="24" t="inlineStr">
         <is>
           <t>4km / 45 min</t>
         </is>
       </c>
-    </row>
-    <row r="266" ht="46" customHeight="1">
-      <c r="A266" s="16" t="inlineStr"/>
-      <c r="B266" s="17" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C266" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D266" s="17" t="inlineStr"/>
-      <c r="E266" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring €60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
-        </is>
-      </c>
-      <c r="F266" s="19" t="inlineStr">
-        <is>
-          <t>€60 / 1hr / 45min</t>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="40" customHeight="1">
-      <c r="A267" s="20" t="inlineStr"/>
-      <c r="B267" s="21" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C267" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D267" s="21" t="inlineStr"/>
-      <c r="E267" s="23" t="inlineStr">
-        <is>
-          <t>12:45pm — Descent to cable car station — ~1.5hrs back down · same trail · arrive top station ~2:15pm · cable car down · back at car ~2:45pm</t>
-        </is>
-      </c>
-      <c r="F267" s="24" t="inlineStr">
-        <is>
-          <t>5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="39" customHeight="1">
-      <c r="A268" s="6" t="inlineStr"/>
-      <c r="B268" s="7" t="inlineStr">
-        <is>
-          <t>Jul 3</t>
-        </is>
-      </c>
-      <c r="C268" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D268" s="7" t="inlineStr"/>
-      <c r="E268" s="9" t="inlineStr">
-        <is>
-          <t>3:00pm — Back at Landhaus Bichlbach — shower · rest legs · pack bags for tomorrow · checkout 8am — Neuschwanstein 9:30am · alarm 7:00am</t>
-        </is>
-      </c>
-      <c r="F268" s="10" t="inlineStr"/>
     </row>
     <row r="269" ht="46" customHeight="1">
       <c r="A269" s="16" t="inlineStr"/>
@@ -5837,75 +5819,104 @@
       <c r="D269" s="17" t="inlineStr"/>
       <c r="E269" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring €60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
+        </is>
+      </c>
+      <c r="F269" s="19" t="inlineStr">
+        <is>
+          <t>€60 / 1hr / 45min</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" s="20" t="inlineStr"/>
+      <c r="B270" s="21" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C270" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D270" s="21" t="inlineStr"/>
+      <c r="E270" s="23" t="inlineStr">
+        <is>
+          <t>12:45pm — Descent to cable car station — ~1.5hrs back down · same trail · arrive top station ~2:15pm · cable car down · back at car ~2:45pm</t>
+        </is>
+      </c>
+      <c r="F270" s="24" t="inlineStr">
+        <is>
+          <t>5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="39" customHeight="1">
+      <c r="A271" s="6" t="inlineStr"/>
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D271" s="7" t="inlineStr"/>
+      <c r="E271" s="9" t="inlineStr">
+        <is>
+          <t>3:00pm — Back at Landhaus Bichlbach — shower · rest legs · pack bags for tomorrow · checkout 8am — Neuschwanstein 9:30am · alarm 7:00am</t>
+        </is>
+      </c>
+      <c r="F271" s="10" t="inlineStr"/>
+    </row>
+    <row r="272" ht="46" customHeight="1">
+      <c r="A272" s="16" t="inlineStr"/>
+      <c r="B272" s="17" t="inlineStr">
+        <is>
+          <t>Jul 3</t>
+        </is>
+      </c>
+      <c r="C272" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D272" s="17" t="inlineStr"/>
+      <c r="E272" s="18" t="inlineStr">
+        <is>
           <t>⭐ 7:30pm — Heiterwanger See sunset walk — 20 min walk from Landhaus along the Panoramaweg · flat · easy · clears the lactic acid · alpenglow after sunset on the higher path</t>
         </is>
       </c>
-      <c r="F269" s="19" t="inlineStr">
+      <c r="F272" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="39" customHeight="1">
-      <c r="A270" s="11" t="inlineStr"/>
-      <c r="B270" s="12" t="inlineStr">
+    <row r="273" ht="39" customHeight="1">
+      <c r="A273" s="11" t="inlineStr"/>
+      <c r="B273" s="12" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C270" s="13" t="inlineStr">
+      <c r="C273" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D270" s="12" t="inlineStr"/>
-      <c r="E270" s="14" t="inlineStr">
+      <c r="D273" s="12" t="inlineStr"/>
+      <c r="E273" s="14" t="inlineStr">
         <is>
           <t>Dinner — Gasthof Bichlbach or hotel restaurant — early dinner + early bed · alarm 7:00am tomorrow · Neuschwanstein 9:30am — last big day</t>
         </is>
       </c>
-      <c r="F270" s="15" t="inlineStr"/>
-    </row>
-    <row r="271" ht="33" customHeight="1">
-      <c r="A271" s="30" t="inlineStr"/>
-      <c r="B271" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C271" s="32" t="inlineStr">
-        <is>
-          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="34" customHeight="1">
-      <c r="A272" s="30" t="inlineStr"/>
-      <c r="B272" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C272" s="32" t="inlineStr">
-        <is>
-          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="34" customHeight="1">
-      <c r="A273" s="30" t="inlineStr"/>
-      <c r="B273" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C273" s="32" t="inlineStr">
-        <is>
-          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="34" customHeight="1">
+      <c r="F273" s="15" t="inlineStr"/>
+    </row>
+    <row r="274" ht="33" customHeight="1">
       <c r="A274" s="30" t="inlineStr"/>
       <c r="B274" s="31" t="inlineStr">
         <is>
@@ -5914,136 +5925,103 @@
       </c>
       <c r="C274" s="32" t="inlineStr">
         <is>
+          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="34" customHeight="1">
+      <c r="A275" s="30" t="inlineStr"/>
+      <c r="B275" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C275" s="32" t="inlineStr">
+        <is>
+          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="34" customHeight="1">
+      <c r="A276" s="30" t="inlineStr"/>
+      <c r="B276" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C276" s="32" t="inlineStr">
+        <is>
+          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="34" customHeight="1">
+      <c r="A277" s="30" t="inlineStr"/>
+      <c r="B277" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C277" s="32" t="inlineStr">
+        <is>
           <t>Panoramaweg for Heiterwanger See — take the higher Panoramaweg trail not the lakeside path · stays above the valley floor to catch alpenglow after sunset · 20 min from hotel · flat + easy</t>
         </is>
       </c>
     </row>
-    <row r="275" ht="3" customHeight="1">
-      <c r="A275" s="33" t="n"/>
-      <c r="B275" s="33" t="n"/>
-      <c r="C275" s="33" t="n"/>
-      <c r="D275" s="33" t="n"/>
-      <c r="E275" s="33" t="n"/>
-      <c r="F275" s="33" t="n"/>
-    </row>
-    <row r="276" ht="20" customHeight="1">
-      <c r="A276" s="3" t="inlineStr">
+    <row r="278" ht="3" customHeight="1">
+      <c r="A278" s="33" t="n"/>
+      <c r="B278" s="33" t="n"/>
+      <c r="C278" s="33" t="n"/>
+      <c r="D278" s="33" t="n"/>
+      <c r="E278" s="33" t="n"/>
+      <c r="F278" s="33" t="n"/>
+    </row>
+    <row r="279" ht="20" customHeight="1">
+      <c r="A279" s="3" t="inlineStr">
         <is>
           <t>DAY 15  |  Jul 4  |  The Fairy Tale Finale — Neuschwanstein · Ebenalp · Aescher → ZRH  |  ~280 km / 174 mi  ~3h 30m · Neuschwanstein → Ebenalp → ZRH</t>
         </is>
       </c>
     </row>
-    <row r="277" ht="15" customHeight="1">
-      <c r="A277" s="4" t="inlineStr">
+    <row r="280" ht="15" customHeight="1">
+      <c r="A280" s="4" t="inlineStr">
         <is>
           <t>Timeline: 7:30am Bichlbach checkout ▸ 8:15am P4 Neuschwanstein ▸ 8:30am Marienbrücke FIRST ▸ 9:20am castle gate ▸ 9:30am tour ▸ 11:30am drive Bregenz tunnel ▸ 1:15pm Wasserauen ▸ 1:30pm Ebenalp cable car ▸ 2pm Aescher (before Swing event 5pm) ▸ 4pm descent ▸ 6pm ZRH hotel + return car tonight ▸ 5am alarm tomorrow</t>
         </is>
       </c>
     </row>
-    <row r="278" ht="22" customHeight="1">
-      <c r="A278" s="5" t="inlineStr">
+    <row r="281" ht="22" customHeight="1">
+      <c r="A281" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Marienbrücke BEFORE the tour — go at 8:30am · virtually no queue · by 10am it's packed  |  ⚠️ Castle gate by 9:20am — NOT the ticket centre · guide will not wait for latecomers  |   Return car TONIGHT — drop bags at hotel · 5 min to Europcar ZRH · open until midnight · eliminates 5:30am stress</t>
         </is>
       </c>
     </row>
-    <row r="279" ht="34" customHeight="1">
-      <c r="A279" s="6" t="inlineStr"/>
-      <c r="B279" s="7" t="inlineStr">
+    <row r="282" ht="34" customHeight="1">
+      <c r="A282" s="6" t="inlineStr"/>
+      <c r="B282" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C279" s="8" t="inlineStr">
+      <c r="C282" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D279" s="7" t="inlineStr"/>
-      <c r="E279" s="9" t="inlineStr">
+      <c r="D282" s="7" t="inlineStr"/>
+      <c r="E282" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:30am — Checkout Landhaus Bichlbach + depart — 30 min earlier than original plan · 45 min drive to Schwangau</t>
         </is>
       </c>
-      <c r="F279" s="10" t="inlineStr">
+      <c r="F282" s="10" t="inlineStr">
         <is>
           <t>30 min / 45 min</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="25" customHeight="1">
-      <c r="A280" s="16" t="inlineStr"/>
-      <c r="B280" s="17" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C280" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D280" s="17" t="inlineStr"/>
-      <c r="E280" s="18" t="inlineStr">
-        <is>
-          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
-        </is>
-      </c>
-      <c r="F280" s="19" t="inlineStr">
-        <is>
-          <t>CHF 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="31" customHeight="1">
-      <c r="A281" s="16" t="inlineStr"/>
-      <c r="B281" s="17" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C281" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D281" s="17" t="inlineStr"/>
-      <c r="E281" s="18" t="inlineStr">
-        <is>
-          <t>8:15am — Park P4, Schwangau — €7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
-        </is>
-      </c>
-      <c r="F281" s="19" t="inlineStr">
-        <is>
-          <t>€7 / 10 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="35" customHeight="1">
-      <c r="A282" s="16" t="inlineStr"/>
-      <c r="B282" s="17" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C282" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D282" s="17" t="inlineStr"/>
-      <c r="E282" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
-        </is>
-      </c>
-      <c r="F282" s="19" t="inlineStr">
-        <is>
-          <t>10 min / 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="29" customHeight="1">
+    <row r="283" ht="25" customHeight="1">
       <c r="A283" s="16" t="inlineStr"/>
       <c r="B283" s="17" t="inlineStr">
         <is>
@@ -6058,12 +6036,16 @@
       <c r="D283" s="17" t="inlineStr"/>
       <c r="E283" s="18" t="inlineStr">
         <is>
-          <t>⚠️ 9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
-        </is>
-      </c>
-      <c r="F283" s="19" t="inlineStr"/>
-    </row>
-    <row r="284" ht="34" customHeight="1">
+          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
+        </is>
+      </c>
+      <c r="F283" s="19" t="inlineStr">
+        <is>
+          <t>CHF 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="31" customHeight="1">
       <c r="A284" s="16" t="inlineStr"/>
       <c r="B284" s="17" t="inlineStr">
         <is>
@@ -6078,40 +6060,40 @@
       <c r="D284" s="17" t="inlineStr"/>
       <c r="E284" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
+          <t>8:15am — Park P4, Schwangau — €7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
         </is>
       </c>
       <c r="F284" s="19" t="inlineStr">
         <is>
-          <t>40 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="37" customHeight="1">
-      <c r="A285" s="6" t="inlineStr"/>
-      <c r="B285" s="7" t="inlineStr">
+          <t>€7 / 10 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="35" customHeight="1">
+      <c r="A285" s="16" t="inlineStr"/>
+      <c r="B285" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C285" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D285" s="7" t="inlineStr"/>
-      <c r="E285" s="9" t="inlineStr">
-        <is>
-          <t>11:30am — Depart Neuschwanstein → Wasserauen — 1hr 30min drive · ⚠️ Saturday = absolute peak crowds on all German/Swiss roads</t>
-        </is>
-      </c>
-      <c r="F285" s="10" t="inlineStr">
-        <is>
-          <t>1hr / 30min</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="50" customHeight="1">
+      <c r="C285" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D285" s="17" t="inlineStr"/>
+      <c r="E285" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
+        </is>
+      </c>
+      <c r="F285" s="19" t="inlineStr">
+        <is>
+          <t>10 min / 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="29" customHeight="1">
       <c r="A286" s="16" t="inlineStr"/>
       <c r="B286" s="17" t="inlineStr">
         <is>
@@ -6126,195 +6108,224 @@
       <c r="D286" s="17" t="inlineStr"/>
       <c r="E286" s="18" t="inlineStr">
         <is>
+          <t>⚠️ 9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
+        </is>
+      </c>
+      <c r="F286" s="19" t="inlineStr"/>
+    </row>
+    <row r="287" ht="34" customHeight="1">
+      <c r="A287" s="16" t="inlineStr"/>
+      <c r="B287" s="17" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C287" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D287" s="17" t="inlineStr"/>
+      <c r="E287" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
+        </is>
+      </c>
+      <c r="F287" s="19" t="inlineStr">
+        <is>
+          <t>40 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="37" customHeight="1">
+      <c r="A288" s="6" t="inlineStr"/>
+      <c r="B288" s="7" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C288" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D288" s="7" t="inlineStr"/>
+      <c r="E288" s="9" t="inlineStr">
+        <is>
+          <t>11:30am — Depart Neuschwanstein → Wasserauen — 1hr 30min drive · ⚠️ Saturday = absolute peak crowds on all German/Swiss roads</t>
+        </is>
+      </c>
+      <c r="F288" s="10" t="inlineStr">
+        <is>
+          <t>1hr / 30min</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="50" customHeight="1">
+      <c r="A289" s="16" t="inlineStr"/>
+      <c r="B289" s="17" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C289" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D289" s="17" t="inlineStr"/>
+      <c r="E289" s="18" t="inlineStr">
+        <is>
           <t>1:15pm — Park at Wasserauen cable car — CHF 36/adult return (2026 rate) · runs every 15 min · ⚠️ Peak Saturday: parking lot likely full — if full: park further down the valley on the roadside · local train/shuttle runs t</t>
         </is>
       </c>
-      <c r="F286" s="19" t="inlineStr">
+      <c r="F289" s="19" t="inlineStr">
         <is>
           <t>CHF 36 / 15 min / 20 min</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="32" customHeight="1">
-      <c r="A287" s="20" t="inlineStr"/>
-      <c r="B287" s="21" t="inlineStr">
+    <row r="290" ht="32" customHeight="1">
+      <c r="A290" s="20" t="inlineStr"/>
+      <c r="B290" s="21" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C287" s="22" t="inlineStr">
+      <c r="C290" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D287" s="21" t="inlineStr"/>
-      <c r="E287" s="23" t="inlineStr">
+      <c r="D290" s="21" t="inlineStr"/>
+      <c r="E290" s="23" t="inlineStr">
         <is>
           <t>⭐ 1:30pm — Ebenalp cable car — CHF 36/adult · 6 min · last descent 6pm · ⚠️ caves 10°C — pack a layer</t>
         </is>
       </c>
-      <c r="F287" s="24" t="inlineStr">
+      <c r="F290" s="24" t="inlineStr">
         <is>
           <t>CHF 36 / 6 min</t>
         </is>
       </c>
     </row>
-    <row r="288" ht="35" customHeight="1">
-      <c r="A288" s="16" t="inlineStr"/>
-      <c r="B288" s="17" t="inlineStr">
+    <row r="291" ht="35" customHeight="1">
+      <c r="A291" s="16" t="inlineStr"/>
+      <c r="B291" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C288" s="16" t="inlineStr">
+      <c r="C291" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D288" s="17" t="inlineStr"/>
-      <c r="E288" s="18" t="inlineStr">
+      <c r="D291" s="17" t="inlineStr"/>
+      <c r="E291" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 2:00pm — Berggasthaus Aescher — arrive before 4pm ·  Swing event 5pm · Chäs-Chnöpfli or Rösti · Siedwurst if full</t>
         </is>
       </c>
-      <c r="F288" s="19" t="inlineStr"/>
-    </row>
-    <row r="289" ht="39" customHeight="1">
-      <c r="A289" s="6" t="inlineStr"/>
-      <c r="B289" s="7" t="inlineStr">
+      <c r="F291" s="19" t="inlineStr"/>
+    </row>
+    <row r="292" ht="39" customHeight="1">
+      <c r="A292" s="6" t="inlineStr"/>
+      <c r="B292" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C289" s="8" t="inlineStr">
+      <c r="C292" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D289" s="7" t="inlineStr"/>
-      <c r="E289" s="9" t="inlineStr">
+      <c r="D292" s="7" t="inlineStr"/>
+      <c r="E292" s="9" t="inlineStr">
         <is>
           <t>4:00pm — Cable car down + drive to ZRH — walk 25 min back up to Ebenalp top station · cable car down · ~2hr drive to Zurich Airport area</t>
         </is>
       </c>
-      <c r="F289" s="10" t="inlineStr">
+      <c r="F292" s="10" t="inlineStr">
         <is>
           <t>25 min / ~2hr</t>
         </is>
       </c>
     </row>
-    <row r="290" ht="33" customHeight="1">
-      <c r="A290" s="16" t="inlineStr"/>
-      <c r="B290" s="17" t="inlineStr">
+    <row r="293" ht="33" customHeight="1">
+      <c r="A293" s="16" t="inlineStr"/>
+      <c r="B293" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C290" s="16" t="inlineStr">
+      <c r="C293" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D290" s="17" t="inlineStr"/>
-      <c r="E290" s="18" t="inlineStr">
+      <c r="D293" s="17" t="inlineStr"/>
+      <c r="E293" s="18" t="inlineStr">
         <is>
           <t>❌ Rhine Falls — SKIP TODAY — adding 45 min detour north on a peak Saturday risks missing car return window</t>
         </is>
       </c>
-      <c r="F290" s="19" t="inlineStr">
+      <c r="F293" s="19" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="50" customHeight="1">
-      <c r="A291" s="6" t="inlineStr"/>
-      <c r="B291" s="7" t="inlineStr">
+    <row r="294" ht="50" customHeight="1">
+      <c r="A294" s="6" t="inlineStr"/>
+      <c r="B294" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C291" s="8" t="inlineStr">
+      <c r="C294" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D291" s="7" t="inlineStr"/>
-      <c r="E291" s="9" t="inlineStr">
+      <c r="D294" s="7" t="inlineStr"/>
+      <c r="E294" s="9" t="inlineStr">
         <is>
           <t>Return Europcar ZRH tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH return · return by 11:30pm · Hilton shuttle back · check Booking.com email for return confirmation</t>
         </is>
       </c>
-      <c r="F291" s="10" t="inlineStr">
+      <c r="F294" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="292" ht="28" customHeight="1">
-      <c r="A292" s="25" t="inlineStr"/>
-      <c r="B292" s="26" t="inlineStr">
+    <row r="295" ht="28" customHeight="1">
+      <c r="A295" s="25" t="inlineStr"/>
+      <c r="B295" s="26" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C292" s="27" t="inlineStr">
+      <c r="C295" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D292" s="26" t="inlineStr"/>
-      <c r="E292" s="28" t="inlineStr">
+      <c r="D295" s="26" t="inlineStr"/>
+      <c r="E295" s="28" t="inlineStr">
         <is>
           <t>⚠️ Tonight — final checks — check-in opens 5:30am · hotel is 5 min walk to terminal</t>
         </is>
       </c>
-      <c r="F292" s="29" t="inlineStr">
+      <c r="F295" s="29" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="293" ht="31" customHeight="1">
-      <c r="A293" s="30" t="inlineStr"/>
-      <c r="B293" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C293" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="34" customHeight="1">
-      <c r="A294" s="30" t="inlineStr"/>
-      <c r="B294" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C294" s="32" t="inlineStr">
-        <is>
-          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="30" customHeight="1">
-      <c r="A295" s="30" t="inlineStr"/>
-      <c r="B295" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C295" s="32" t="inlineStr">
-        <is>
-          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="34" customHeight="1">
+    <row r="296" ht="31" customHeight="1">
       <c r="A296" s="30" t="inlineStr"/>
       <c r="B296" s="31" t="inlineStr">
         <is>
@@ -6323,7 +6334,7 @@
       </c>
       <c r="C296" s="32" t="inlineStr">
         <is>
-          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
         </is>
       </c>
     </row>
@@ -6336,11 +6347,11 @@
       </c>
       <c r="C297" s="32" t="inlineStr">
         <is>
-          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="32" customHeight="1">
+          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="30" customHeight="1">
       <c r="A298" s="30" t="inlineStr"/>
       <c r="B298" s="31" t="inlineStr">
         <is>
@@ -6349,148 +6360,119 @@
       </c>
       <c r="C298" s="32" t="inlineStr">
         <is>
+          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="34" customHeight="1">
+      <c r="A299" s="30" t="inlineStr"/>
+      <c r="B299" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C299" s="32" t="inlineStr">
+        <is>
+          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="34" customHeight="1">
+      <c r="A300" s="30" t="inlineStr"/>
+      <c r="B300" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C300" s="32" t="inlineStr">
+        <is>
+          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="32" customHeight="1">
+      <c r="A301" s="30" t="inlineStr"/>
+      <c r="B301" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C301" s="32" t="inlineStr">
+        <is>
           <t>⚠️ 5:00am alarm Jul 5 — set two alarms · FI571 departs 7:55am · check-in opens 5:30am · hotel is 5 min walk to terminal · boarding passes on phone tonight</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="3" customHeight="1">
-      <c r="A299" s="33" t="n"/>
-      <c r="B299" s="33" t="n"/>
-      <c r="C299" s="33" t="n"/>
-      <c r="D299" s="33" t="n"/>
-      <c r="E299" s="33" t="n"/>
-      <c r="F299" s="33" t="n"/>
-    </row>
-    <row r="300" ht="20" customHeight="1">
-      <c r="A300" s="3" t="inlineStr">
+    <row r="302" ht="3" customHeight="1">
+      <c r="A302" s="33" t="n"/>
+      <c r="B302" s="33" t="n"/>
+      <c r="C302" s="33" t="n"/>
+      <c r="D302" s="33" t="n"/>
+      <c r="E302" s="33" t="n"/>
+      <c r="F302" s="33" t="n"/>
+    </row>
+    <row r="303" ht="20" customHeight="1">
+      <c r="A303" s="3" t="inlineStr">
         <is>
           <t>DAY 16  |  Jul 5  |  Homebound — ZRH → KEF → MCO · The Final Leg  |  —  —</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="15" customHeight="1">
-      <c r="A301" s="4" t="inlineStr">
+    <row r="304" ht="15" customHeight="1">
+      <c r="A304" s="4" t="inlineStr">
         <is>
           <t>Timeline: Sat night: app check-in ▸ confirm shuttle ▸ 5am wake ▸ 5:30am Hilton shuttle (NOT walk) ▸ 5:45am Terminal 2 · Check-in Row 3 ▸ 6am security + E Gate Skymetro ▸ 7:55am FI571 ZRH→KEF ▸ KEF Pylsur layover ▸ 8:50pm MCO home</t>
         </is>
       </c>
     </row>
-    <row r="302" ht="22" customHeight="1">
-      <c r="A302" s="5" t="inlineStr">
+    <row r="305" ht="22" customHeight="1">
+      <c r="A305" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Take hotel shuttle NOT walk — Hilton is 2km from terminal · not walkable with luggage · CHF 7/person  |  ✅ Icelandair app check-in Saturday night — digital boarding pass · fast bag drop at Check-in 2 Row 3  |  ✅ US Customs at MCO not KEF — do not leave transit area in Iceland</t>
         </is>
       </c>
     </row>
-    <row r="303" ht="39" customHeight="1">
-      <c r="A303" s="34" t="inlineStr"/>
-      <c r="B303" s="35" t="inlineStr">
+    <row r="306" ht="39" customHeight="1">
+      <c r="A306" s="34" t="inlineStr"/>
+      <c r="B306" s="35" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C303" s="36" t="inlineStr">
+      <c r="C306" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D303" s="35" t="inlineStr"/>
-      <c r="E303" s="37" t="inlineStr">
+      <c r="D306" s="35" t="inlineStr"/>
+      <c r="E306" s="37" t="inlineStr">
         <is>
           <t>✅ Night before (Jul 4 Saturday evening) — final prep — (2) Check Europcar/Booking.com email — confirm car return was closed out correctly</t>
         </is>
       </c>
-      <c r="F303" s="38" t="inlineStr"/>
-    </row>
-    <row r="304" ht="40" customHeight="1">
-      <c r="A304" s="11" t="inlineStr"/>
-      <c r="B304" s="12" t="inlineStr">
+      <c r="F306" s="38" t="inlineStr"/>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" s="11" t="inlineStr"/>
+      <c r="B307" s="12" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C304" s="13" t="inlineStr">
+      <c r="C307" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D304" s="12" t="inlineStr"/>
-      <c r="E304" s="14" t="inlineStr">
+      <c r="D307" s="12" t="inlineStr"/>
+      <c r="E307" s="14" t="inlineStr">
         <is>
           <t>⏰ 5:00am — Wake up — perfect timing · do not wake earlier unless extra bags need special handling · hotel breakfast starts at 5:30am if needed</t>
         </is>
       </c>
-      <c r="F304" s="15" t="inlineStr"/>
-    </row>
-    <row r="305" ht="31" customHeight="1">
-      <c r="A305" s="16" t="inlineStr"/>
-      <c r="B305" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C305" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D305" s="17" t="inlineStr"/>
-      <c r="E305" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ 5:30am — Hilton shuttle — ❌ do NOT walk · 2km to terminal · CHF 7/person · confirm seat tonight</t>
-        </is>
-      </c>
-      <c r="F305" s="19" t="inlineStr">
-        <is>
-          <t>2km / CHF 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="31" customHeight="1">
-      <c r="A306" s="25" t="inlineStr"/>
-      <c r="B306" s="26" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C306" s="27" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D306" s="26" t="inlineStr"/>
-      <c r="E306" s="28" t="inlineStr">
-        <is>
-          <t>✈️ 5:45am — Terminal 2, Check-in Row 3 — bag drop opens 5:25am · digital boarding pass on phone</t>
-        </is>
-      </c>
-      <c r="F306" s="29" t="inlineStr"/>
-    </row>
-    <row r="307" ht="30" customHeight="1">
-      <c r="A307" s="16" t="inlineStr"/>
-      <c r="B307" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C307" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D307" s="17" t="inlineStr"/>
-      <c r="E307" s="18" t="inlineStr">
-        <is>
-          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
-        </is>
-      </c>
-      <c r="F307" s="19" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="308" ht="38" customHeight="1">
+      <c r="F307" s="15" t="inlineStr"/>
+    </row>
+    <row r="308" ht="31" customHeight="1">
       <c r="A308" s="16" t="inlineStr"/>
       <c r="B308" s="17" t="inlineStr">
         <is>
@@ -6505,32 +6487,36 @@
       <c r="D308" s="17" t="inlineStr"/>
       <c r="E308" s="18" t="inlineStr">
         <is>
-          <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
-        </is>
-      </c>
-      <c r="F308" s="19" t="inlineStr"/>
-    </row>
-    <row r="309" ht="19" customHeight="1">
-      <c r="A309" s="6" t="inlineStr"/>
-      <c r="B309" s="7" t="inlineStr">
+          <t>⚠️ 5:30am — Hilton shuttle — ❌ do NOT walk · 2km to terminal · CHF 7/person · confirm seat tonight</t>
+        </is>
+      </c>
+      <c r="F308" s="19" t="inlineStr">
+        <is>
+          <t>2km / CHF 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="31" customHeight="1">
+      <c r="A309" s="25" t="inlineStr"/>
+      <c r="B309" s="26" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C309" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D309" s="7" t="inlineStr"/>
-      <c r="E309" s="9" t="inlineStr">
-        <is>
-          <t>✈️ 7:55am — FI571 departs ZRH → KEF</t>
-        </is>
-      </c>
-      <c r="F309" s="10" t="inlineStr"/>
-    </row>
-    <row r="310" ht="37" customHeight="1">
+      <c r="C309" s="27" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D309" s="26" t="inlineStr"/>
+      <c r="E309" s="28" t="inlineStr">
+        <is>
+          <t>✈️ 5:45am — Terminal 2, Check-in Row 3 — bag drop opens 5:25am · digital boarding pass on phone</t>
+        </is>
+      </c>
+      <c r="F309" s="29" t="inlineStr"/>
+    </row>
+    <row r="310" ht="30" customHeight="1">
       <c r="A310" s="16" t="inlineStr"/>
       <c r="B310" s="17" t="inlineStr">
         <is>
@@ -6545,16 +6531,16 @@
       <c r="D310" s="17" t="inlineStr"/>
       <c r="E310" s="18" t="inlineStr">
         <is>
-          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
+          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
         </is>
       </c>
       <c r="F310" s="19" t="inlineStr">
         <is>
-          <t>2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="311" ht="35" customHeight="1">
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="38" customHeight="1">
       <c r="A311" s="16" t="inlineStr"/>
       <c r="B311" s="17" t="inlineStr">
         <is>
@@ -6569,55 +6555,80 @@
       <c r="D311" s="17" t="inlineStr"/>
       <c r="E311" s="18" t="inlineStr">
         <is>
+          <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
+        </is>
+      </c>
+      <c r="F311" s="19" t="inlineStr"/>
+    </row>
+    <row r="312" ht="19" customHeight="1">
+      <c r="A312" s="6" t="inlineStr"/>
+      <c r="B312" s="7" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C312" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D312" s="7" t="inlineStr"/>
+      <c r="E312" s="9" t="inlineStr">
+        <is>
+          <t>✈️ 7:55am — FI571 departs ZRH → KEF</t>
+        </is>
+      </c>
+      <c r="F312" s="10" t="inlineStr"/>
+    </row>
+    <row r="313" ht="37" customHeight="1">
+      <c r="A313" s="16" t="inlineStr"/>
+      <c r="B313" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C313" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D313" s="17" t="inlineStr"/>
+      <c r="E313" s="18" t="inlineStr">
+        <is>
+          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
+        </is>
+      </c>
+      <c r="F313" s="19" t="inlineStr">
+        <is>
+          <t>2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="35" customHeight="1">
+      <c r="A314" s="16" t="inlineStr"/>
+      <c r="B314" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C314" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D314" s="17" t="inlineStr"/>
+      <c r="E314" s="18" t="inlineStr">
+        <is>
           <t>8:50pm — Arrive Orlando MCO — clear US Customs + Immigration at MCO · allow 45–60 min for customs on Sunday evening</t>
         </is>
       </c>
-      <c r="F311" s="19" t="inlineStr">
+      <c r="F314" s="19" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
     </row>
-    <row r="312" ht="34" customHeight="1">
-      <c r="A312" s="30" t="inlineStr"/>
-      <c r="B312" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C312" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
-        </is>
-      </c>
-    </row>
-    <row r="313" ht="34" customHeight="1">
-      <c r="A313" s="30" t="inlineStr"/>
-      <c r="B313" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C313" s="32" t="inlineStr">
-        <is>
-          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="34" customHeight="1">
-      <c r="A314" s="30" t="inlineStr"/>
-      <c r="B314" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C314" s="32" t="inlineStr">
-        <is>
-          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="31" customHeight="1">
+    <row r="315" ht="34" customHeight="1">
       <c r="A315" s="30" t="inlineStr"/>
       <c r="B315" s="31" t="inlineStr">
         <is>
@@ -6626,131 +6637,172 @@
       </c>
       <c r="C315" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="34" customHeight="1">
+      <c r="A316" s="30" t="inlineStr"/>
+      <c r="B316" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C316" s="32" t="inlineStr">
+        <is>
+          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="34" customHeight="1">
+      <c r="A317" s="30" t="inlineStr"/>
+      <c r="B317" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C317" s="32" t="inlineStr">
+        <is>
+          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="31" customHeight="1">
+      <c r="A318" s="30" t="inlineStr"/>
+      <c r="B318" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C318" s="32" t="inlineStr">
+        <is>
           <t>KEF layover — 1.5–2hrs · Pylsur hot dog (best in the world) · Skyr yoghurt · duty-free is excellent · US customs at MCO not here · do not leave transit</t>
         </is>
       </c>
     </row>
-    <row r="316" ht="3" customHeight="1">
-      <c r="A316" s="33" t="n"/>
-      <c r="B316" s="33" t="n"/>
-      <c r="C316" s="33" t="n"/>
-      <c r="D316" s="33" t="n"/>
-      <c r="E316" s="33" t="n"/>
-      <c r="F316" s="33" t="n"/>
+    <row r="319" ht="3" customHeight="1">
+      <c r="A319" s="33" t="n"/>
+      <c r="B319" s="33" t="n"/>
+      <c r="C319" s="33" t="n"/>
+      <c r="D319" s="33" t="n"/>
+      <c r="E319" s="33" t="n"/>
+      <c r="F319" s="33" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="111">
+  <mergeCells count="113">
     <mergeCell ref="C52:F52"/>
-    <mergeCell ref="A183:F183"/>
-    <mergeCell ref="C233:F233"/>
-    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="C159:F159"/>
     <mergeCell ref="C72:F72"/>
-    <mergeCell ref="A238:F238"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A301:F301"/>
-    <mergeCell ref="A239:F239"/>
-    <mergeCell ref="A160:F160"/>
-    <mergeCell ref="C136:F136"/>
-    <mergeCell ref="C314:F314"/>
+    <mergeCell ref="C217:F217"/>
+    <mergeCell ref="C258:F258"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A159:F159"/>
-    <mergeCell ref="C313:F313"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A303:F303"/>
     <mergeCell ref="A200:F200"/>
-    <mergeCell ref="C234:F234"/>
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A280:F280"/>
     <mergeCell ref="A161:F161"/>
     <mergeCell ref="C73:F73"/>
     <mergeCell ref="C315:F315"/>
-    <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="C121:F121"/>
     <mergeCell ref="C50:F50"/>
-    <mergeCell ref="A257:F257"/>
+    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="C277:F277"/>
+    <mergeCell ref="A260:F260"/>
     <mergeCell ref="C236:F236"/>
-    <mergeCell ref="C214:F214"/>
+    <mergeCell ref="C276:F276"/>
+    <mergeCell ref="A241:F241"/>
     <mergeCell ref="C120:F120"/>
     <mergeCell ref="A124:F124"/>
+    <mergeCell ref="C300:F300"/>
+    <mergeCell ref="A305:F305"/>
+    <mergeCell ref="A221:F221"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A277:F277"/>
-    <mergeCell ref="C253:F253"/>
+    <mergeCell ref="C158:F158"/>
+    <mergeCell ref="A163:F163"/>
     <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A278:F278"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C317:F317"/>
     <mergeCell ref="C96:F96"/>
-    <mergeCell ref="C254:F254"/>
-    <mergeCell ref="A259:F259"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="C235:F235"/>
+    <mergeCell ref="A262:F262"/>
     <mergeCell ref="A240:F240"/>
-    <mergeCell ref="A122:F122"/>
     <mergeCell ref="C216:F216"/>
     <mergeCell ref="C98:F98"/>
-    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="C218:F218"/>
     <mergeCell ref="C274:F274"/>
     <mergeCell ref="C137:F137"/>
-    <mergeCell ref="C177:F177"/>
     <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A182:F182"/>
+    <mergeCell ref="A304:F304"/>
     <mergeCell ref="A79:F79"/>
-    <mergeCell ref="A218:F218"/>
-    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="C139:F139"/>
+    <mergeCell ref="A162:F162"/>
     <mergeCell ref="C138:F138"/>
-    <mergeCell ref="C194:F194"/>
-    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="C316:F316"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="C181:F181"/>
     <mergeCell ref="C119:F119"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="C155:F155"/>
-    <mergeCell ref="C293:F293"/>
+    <mergeCell ref="C237:F237"/>
+    <mergeCell ref="A242:F242"/>
     <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C53:F53"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C179:F179"/>
     <mergeCell ref="C157:F157"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A140:F140"/>
-    <mergeCell ref="C294:F294"/>
-    <mergeCell ref="C215:F215"/>
     <mergeCell ref="C97:F97"/>
     <mergeCell ref="A102:F102"/>
-    <mergeCell ref="C271:F271"/>
-    <mergeCell ref="C94:F94"/>
-    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="C318:F318"/>
+    <mergeCell ref="C256:F256"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A279:F279"/>
     <mergeCell ref="C255:F255"/>
-    <mergeCell ref="C176:F176"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A300:F300"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A281:F281"/>
+    <mergeCell ref="C257:F257"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C95:F95"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="C178:F178"/>
     <mergeCell ref="C297:F297"/>
-    <mergeCell ref="C272:F272"/>
-    <mergeCell ref="C312:F312"/>
+    <mergeCell ref="C299:F299"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="C296:F296"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="C298:F298"/>
-    <mergeCell ref="A302:F302"/>
-    <mergeCell ref="C154:F154"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="A219:F219"/>
-    <mergeCell ref="C195:F195"/>
-    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="C275:F275"/>
     <mergeCell ref="C156:F156"/>
     <mergeCell ref="A184:F184"/>
     <mergeCell ref="C74:F74"/>
+    <mergeCell ref="C197:F197"/>
+    <mergeCell ref="C35:F35"/>
     <mergeCell ref="A220:F220"/>
-    <mergeCell ref="C16:F16"/>
     <mergeCell ref="C196:F196"/>
-    <mergeCell ref="C117:F117"/>
-    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="A261:F261"/>
+    <mergeCell ref="C301:F301"/>
     <mergeCell ref="C180:F180"/>
     <mergeCell ref="C118:F118"/>
     <mergeCell ref="C75:F75"/>
+    <mergeCell ref="A222:F222"/>
     <mergeCell ref="A123:F123"/>
-    <mergeCell ref="C295:F295"/>
-    <mergeCell ref="C273:F273"/>
+    <mergeCell ref="C198:F198"/>
+    <mergeCell ref="C238:F238"/>
+    <mergeCell ref="C182:F182"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -5979,25 +5979,25 @@
     <row r="279" ht="20" customHeight="1">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>DAY 15  |  Jul 4  |  The Fairy Tale Finale — Neuschwanstein · Ebenalp · Aescher → ZRH  |  ~280 km / 174 mi  ~3h 30m · Neuschwanstein → Ebenalp → ZRH</t>
+          <t>DAY 15  |  Jul 4  |  Zurich Day — Old Town · Lake · Caliente Festival → ZRH  |  ~185 km / 115 mi  ~2h direct · saves 100km vs castle route</t>
         </is>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>Timeline: 7:30am Bichlbach checkout ▸ 8:15am P4 Neuschwanstein ▸ 8:30am Marienbrücke FIRST ▸ 9:20am castle gate ▸ 9:30am tour ▸ 11:30am drive Bregenz tunnel ▸ 1:15pm Wasserauen ▸ 1:30pm Ebenalp cable car ▸ 2pm Aescher (before Swing event 5pm) ▸ 4pm descent ▸ 6pm ZRH hotel + return car tonight ▸ 5am alarm tomorrow</t>
+          <t>Timeline: 8:00am Bichlbach checkout ▸ ~10:00am Airport Hotel ZRH ▸ 10:30am return Europcar ▸ 11:00am train to Zurich HB ▸ 11:15am Lindenhof + Grossmünster + Fraumünster ▸ 1:00pm Bahnhofstrasse + Sprüngli ▸ 1:45pm Lake Zurich waterfront ▸ 2:30pm Caliente! Latin Festival ▸ 4:30pm dinner by the lake ▸ 6:00pm train back ▸ early bed</t>
         </is>
       </c>
     </row>
     <row r="281" ht="22" customHeight="1">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>Key: ✅ Marienbrücke BEFORE the tour — go at 8:30am · virtually no queue · by 10am it's packed  |  ⚠️ Castle gate by 9:20am — NOT the ticket centre · guide will not wait for latecomers  |   Return car TONIGHT — drop bags at hotel · 5 min to Europcar ZRH · open until midnight · eliminates 5:30am stress</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="34" customHeight="1">
+          <t>Key: ✅ Return Europcar ZRH first thing — 10:30am · 5 min drive · done before Zurich  |  ✅ Caliente! Latin Festival Jul 4 — final day · Europe's largest Latin festival · lakefront · family-friendly  |  ✅ Confirm Hilton shuttle 5:30am at front desk tonight — CHF 7/person · NOT walk (2km)  |  ⚠️ Swiss vignette — verify on windscreen before crossing border</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="44" customHeight="1">
       <c r="A282" s="6" t="inlineStr"/>
       <c r="B282" s="7" t="inlineStr">
         <is>
@@ -6012,16 +6012,16 @@
       <c r="D282" s="7" t="inlineStr"/>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>⏰ 7:30am — Checkout Landhaus Bichlbach + depart — 30 min earlier than original plan · 45 min drive to Schwangau</t>
+          <t>8:00am — Checkout Landhaus Bichlbach + depart — ~185km direct to Zurich Airport · ~2hrs via A17/A12/A14 · no border stress · no peak Saturday mountain parking</t>
         </is>
       </c>
       <c r="F282" s="10" t="inlineStr">
         <is>
-          <t>30 min / 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="25" customHeight="1">
+          <t>~185km / ~2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="35" customHeight="1">
       <c r="A283" s="16" t="inlineStr"/>
       <c r="B283" s="17" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
       <c r="D283" s="17" t="inlineStr"/>
       <c r="E283" s="18" t="inlineStr">
         <is>
-          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing</t>
+          <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing · verify on windscreen before entering Switzerland</t>
         </is>
       </c>
       <c r="F283" s="19" t="inlineStr">
@@ -6045,55 +6045,51 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="31" customHeight="1">
-      <c r="A284" s="16" t="inlineStr"/>
-      <c r="B284" s="17" t="inlineStr">
+    <row r="284" ht="41" customHeight="1">
+      <c r="A284" s="25" t="inlineStr"/>
+      <c r="B284" s="26" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C284" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D284" s="17" t="inlineStr"/>
-      <c r="E284" s="18" t="inlineStr">
-        <is>
-          <t>8:15am — Park P4, Schwangau — €7 · 10 min walk to ticket centre · go straight to Marienbrücke</t>
-        </is>
-      </c>
-      <c r="F284" s="19" t="inlineStr">
-        <is>
-          <t>€7 / 10 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="35" customHeight="1">
-      <c r="A285" s="16" t="inlineStr"/>
-      <c r="B285" s="17" t="inlineStr">
+      <c r="C284" s="27" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D284" s="26" t="inlineStr"/>
+      <c r="E284" s="28" t="inlineStr">
+        <is>
+          <t>~10:00am — Airport Hotel Zurich — drop bags at hotel · Lindbergh-Platz 1, 8152 Glattbrugg · check-in may not be ready — leave bags at reception</t>
+        </is>
+      </c>
+      <c r="F284" s="29" t="inlineStr"/>
+    </row>
+    <row r="285" ht="46" customHeight="1">
+      <c r="A285" s="6" t="inlineStr"/>
+      <c r="B285" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C285" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D285" s="17" t="inlineStr"/>
-      <c r="E285" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:30am — Marienbrücke (Mary's Bridge) — go here FIRST — 10 min walk above the castle · allow 20–30 min for photos</t>
-        </is>
-      </c>
-      <c r="F285" s="19" t="inlineStr">
-        <is>
-          <t>10 min / 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="29" customHeight="1">
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D285" s="7" t="inlineStr"/>
+      <c r="E285" s="9" t="inlineStr">
+        <is>
+          <t>10:30am — Return Europcar ZRH — 5 min drive from hotel · confirm return closed out correctly · take Hilton shuttle back · keep boarding passes + passports in hand-carry</t>
+        </is>
+      </c>
+      <c r="F285" s="10" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="38" customHeight="1">
       <c r="A286" s="16" t="inlineStr"/>
       <c r="B286" s="17" t="inlineStr">
         <is>
@@ -6108,60 +6104,64 @@
       <c r="D286" s="17" t="inlineStr"/>
       <c r="E286" s="18" t="inlineStr">
         <is>
-          <t>⚠️ 9:20am — Castle GATE (not ticket centre) — entry strictly timed · guide will not wait</t>
-        </is>
-      </c>
-      <c r="F286" s="19" t="inlineStr"/>
-    </row>
-    <row r="287" ht="34" customHeight="1">
-      <c r="A287" s="16" t="inlineStr"/>
-      <c r="B287" s="17" t="inlineStr">
+          <t>11:00am — Train to Zurich HB — Zurich Airport → Zurich HB · 10 min · CHF 7 · runs every 10 min from the airport underground station</t>
+        </is>
+      </c>
+      <c r="F286" s="19" t="inlineStr">
+        <is>
+          <t>10 min / CHF 7 / 10 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="37" customHeight="1">
+      <c r="A287" s="20" t="inlineStr"/>
+      <c r="B287" s="21" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C287" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D287" s="17" t="inlineStr"/>
-      <c r="E287" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 9:30am — Neuschwanstein Castle interior tour — guided tour 35–40 min inside · photography not allowed inside</t>
-        </is>
-      </c>
-      <c r="F287" s="19" t="inlineStr">
-        <is>
-          <t>40 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="37" customHeight="1">
-      <c r="A288" s="6" t="inlineStr"/>
-      <c r="B288" s="7" t="inlineStr">
+      <c r="C287" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D287" s="21" t="inlineStr"/>
+      <c r="E287" s="23" t="inlineStr">
+        <is>
+          <t>⭐ 11:15am — Lindenhof viewpoint — hilltop square · best city panorama without climbing · Romans used it as a fort · free · 15 min</t>
+        </is>
+      </c>
+      <c r="F287" s="24" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" s="20" t="inlineStr"/>
+      <c r="B288" s="21" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C288" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D288" s="7" t="inlineStr"/>
-      <c r="E288" s="9" t="inlineStr">
-        <is>
-          <t>11:30am — Depart Neuschwanstein → Wasserauen — 1hr 30min drive · ⚠️ Saturday = absolute peak crowds on all German/Swiss roads</t>
-        </is>
-      </c>
-      <c r="F288" s="10" t="inlineStr">
-        <is>
-          <t>1hr / 30min</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="50" customHeight="1">
+      <c r="C288" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D288" s="21" t="inlineStr"/>
+      <c r="E288" s="23" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 11:30am — Grossmünster — twin-towered landmark · climb to the top for panorama of city + Lake Zurich · kids love the tower climb · ~CHF 5</t>
+        </is>
+      </c>
+      <c r="F288" s="24" t="inlineStr">
+        <is>
+          <t>CHF 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="37" customHeight="1">
       <c r="A289" s="16" t="inlineStr"/>
       <c r="B289" s="17" t="inlineStr">
         <is>
@@ -6176,40 +6176,40 @@
       <c r="D289" s="17" t="inlineStr"/>
       <c r="E289" s="18" t="inlineStr">
         <is>
-          <t>1:15pm — Park at Wasserauen cable car — CHF 36/adult return (2026 rate) · runs every 15 min · ⚠️ Peak Saturday: parking lot likely full — if full: park further down the valley on the roadside · local train/shuttle runs t</t>
+          <t>⭐ 12:15pm — Fraumünster — Marc Chagall stained glass windows — genuinely stunning · unlike anything else on the trip · ~CHF 5</t>
         </is>
       </c>
       <c r="F289" s="19" t="inlineStr">
         <is>
-          <t>CHF 36 / 15 min / 20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" ht="32" customHeight="1">
-      <c r="A290" s="20" t="inlineStr"/>
-      <c r="B290" s="21" t="inlineStr">
+          <t>CHF 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="43" customHeight="1">
+      <c r="A290" s="16" t="inlineStr"/>
+      <c r="B290" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C290" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D290" s="21" t="inlineStr"/>
-      <c r="E290" s="23" t="inlineStr">
-        <is>
-          <t>⭐ 1:30pm — Ebenalp cable car — CHF 36/adult · 6 min · last descent 6pm · ⚠️ caves 10°C — pack a layer</t>
-        </is>
-      </c>
-      <c r="F290" s="24" t="inlineStr">
-        <is>
-          <t>CHF 36 / 6 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" ht="35" customHeight="1">
+      <c r="C290" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D290" s="17" t="inlineStr"/>
+      <c r="E290" s="18" t="inlineStr">
+        <is>
+          <t>1:00pm — Bahnhofstrasse — one of the world's great shopping streets · Confiserie Sprüngli for Swiss chocolate + Luxemburgerli macarons — MUST · 30 min stroll</t>
+        </is>
+      </c>
+      <c r="F290" s="19" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="39" customHeight="1">
       <c r="A291" s="16" t="inlineStr"/>
       <c r="B291" s="17" t="inlineStr">
         <is>
@@ -6224,84 +6224,84 @@
       <c r="D291" s="17" t="inlineStr"/>
       <c r="E291" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 2:00pm — Berggasthaus Aescher — arrive before 4pm ·  Swing event 5pm · Chäs-Chnöpfli or Rösti · Siedwurst if full</t>
-        </is>
-      </c>
-      <c r="F291" s="19" t="inlineStr"/>
-    </row>
-    <row r="292" ht="39" customHeight="1">
-      <c r="A292" s="6" t="inlineStr"/>
-      <c r="B292" s="7" t="inlineStr">
+          <t>⭐ ⭐ 1:45pm — Lake Zurich waterfront — Bürkliplatz · swans · paddle boats · Alps visible in the background on a clear day · free · 45 min</t>
+        </is>
+      </c>
+      <c r="F291" s="19" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="50" customHeight="1">
+      <c r="A292" s="16" t="inlineStr"/>
+      <c r="B292" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C292" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D292" s="7" t="inlineStr"/>
-      <c r="E292" s="9" t="inlineStr">
-        <is>
-          <t>4:00pm — Cable car down + drive to ZRH — walk 25 min back up to Ebenalp top station · cable car down · ~2hr drive to Zurich Airport area</t>
-        </is>
-      </c>
-      <c r="F292" s="10" t="inlineStr">
-        <is>
-          <t>25 min / ~2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="33" customHeight="1">
-      <c r="A293" s="16" t="inlineStr"/>
-      <c r="B293" s="17" t="inlineStr">
+      <c r="C292" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D292" s="17" t="inlineStr"/>
+      <c r="E292" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 2:30pm — Caliente! Latin Festival — Jul 3–5 2026 · Europe's largest Latin festival · Kasernenareal · South American music + dancing + food stalls · Jul 4 is the final day — biggest atmosphere · family-friendly · free</t>
+        </is>
+      </c>
+      <c r="F292" s="19" t="inlineStr"/>
+    </row>
+    <row r="293" ht="44" customHeight="1">
+      <c r="A293" s="11" t="inlineStr"/>
+      <c r="B293" s="12" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C293" s="16" t="inlineStr">
+      <c r="C293" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D293" s="12" t="inlineStr"/>
+      <c r="E293" s="14" t="inlineStr">
+        <is>
+          <t>4:30pm — Early dinner by Lake Zurich — Zeughauskeller (15th century armory beer hall · hearty Swiss meals) · or lakeside restaurant at Bürkliplatz · allow 1.5hrs</t>
+        </is>
+      </c>
+      <c r="F293" s="15" t="inlineStr">
+        <is>
+          <t>5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="27" customHeight="1">
+      <c r="A294" s="16" t="inlineStr"/>
+      <c r="B294" s="17" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C294" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D293" s="17" t="inlineStr"/>
-      <c r="E293" s="18" t="inlineStr">
-        <is>
-          <t>❌ Rhine Falls — SKIP TODAY — adding 45 min detour north on a peak Saturday risks missing car return window</t>
-        </is>
-      </c>
-      <c r="F293" s="19" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="50" customHeight="1">
-      <c r="A294" s="6" t="inlineStr"/>
-      <c r="B294" s="7" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C294" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D294" s="7" t="inlineStr"/>
-      <c r="E294" s="9" t="inlineStr">
-        <is>
-          <t>Return Europcar ZRH tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH return · return by 11:30pm · Hilton shuttle back · check Booking.com email for return confirmation</t>
-        </is>
-      </c>
-      <c r="F294" s="10" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="28" customHeight="1">
+      <c r="D294" s="17" t="inlineStr"/>
+      <c r="E294" s="18" t="inlineStr">
+        <is>
+          <t>6:00pm — Train back to airport — Zurich HB → Zurich Airport · 10 min · CHF 7</t>
+        </is>
+      </c>
+      <c r="F294" s="19" t="inlineStr">
+        <is>
+          <t>10 min / CHF 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="47" customHeight="1">
       <c r="A295" s="25" t="inlineStr"/>
       <c r="B295" s="26" t="inlineStr">
         <is>
@@ -6316,14 +6316,10 @@
       <c r="D295" s="26" t="inlineStr"/>
       <c r="E295" s="28" t="inlineStr">
         <is>
-          <t>⚠️ Tonight — final checks — check-in opens 5:30am · hotel is 5 min walk to terminal</t>
-        </is>
-      </c>
-      <c r="F295" s="29" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
+          <t>6:30pm — Airport Hotel Zurich — pack final bags · passports in hand-carry · boarding passes to phone wallet · confirm 5:30am shuttle at front desk · set two alarms · early bed</t>
+        </is>
+      </c>
+      <c r="F295" s="29" t="inlineStr"/>
     </row>
     <row r="296" ht="31" customHeight="1">
       <c r="A296" s="30" t="inlineStr"/>
@@ -7436,7 +7432,7 @@
       </c>
       <c r="F17" s="46" t="inlineStr">
         <is>
-          <t>~280 km / 174 mi ~3h 30m · Neuschwanstein → Ebenalp → ZRH</t>
+          <t>~185 km / 115 mi ~2h direct to ZRH</t>
         </is>
       </c>
       <c r="G17" s="48" t="inlineStr">
@@ -7519,7 +7515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7702,96 +7698,92 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Seceda 360 cable car — Jun 30 · 4 tickets</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Receipt 1161/678/554260 · 2 adults €84.50 + 2 juniors €43.00 · Total €255 · Valid Jun 30, 2026 · Print at home</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Booked ✅ — print tickets before departure</t>
+        </is>
+      </c>
+      <c r="E9" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>Urgent</t>
         </is>
       </c>
-      <c r="B9" s="69" t="inlineStr">
-        <is>
-          <t>Neuschwanstein Castle tickets — Jul 4 · 9:30am entry slot</t>
-        </is>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t>€17.50/adult incl. booking fee · tickets.hohenschwangau.de · be at GATE (not ticket centre) by 9:20am</t>
-        </is>
-      </c>
-      <c r="D9" s="38" t="inlineStr">
-        <is>
-          <t>Book NOW — July sells out weeks ahead</t>
-        </is>
-      </c>
-      <c r="E9" s="70" t="inlineStr"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>Austrian digital vignette</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr"/>
+      <c r="D10" s="38" t="inlineStr">
+        <is>
+          <t>Buy on Jun 22 at asfinag.at after picking up Europcar car · need licence plate · ~€16.50 · 10-day pass</t>
+        </is>
+      </c>
+      <c r="E10" s="70" t="inlineStr"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Seceda 360 cable car — Jun 30 · 4 tickets</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>Receipt 1161/678/554260 · 2 adults €84.50 + 2 juniors €43.00 · Total €255 · Valid Jun 30, 2026 · Print at home</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>Booked ✅ — print tickets before departure</t>
-        </is>
-      </c>
-      <c r="E10" s="67" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Oeschinensee timed slot — Jun 23 · 8:30am</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Order 254-SK2MH6 · CHF 125 · 08:30–10:00 Jun 23</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr"/>
+      <c r="E11" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="68" t="inlineStr">
-        <is>
-          <t>Urgent</t>
-        </is>
-      </c>
-      <c r="B11" s="69" t="inlineStr">
-        <is>
-          <t>Austrian digital vignette</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr"/>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t>Buy on Jun 22 at asfinag.at after picking up Europcar car · need licence plate · ~€16.50 · 10-day pass</t>
-        </is>
-      </c>
-      <c r="E11" s="70" t="inlineStr"/>
-    </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="66" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>Oeschinensee timed slot — Jun 23 · 8:30am</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>Order 254-SK2MH6 · CHF 125 · 08:30–10:00 Jun 23</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr"/>
-      <c r="E12" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="A12" s="71" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B12" s="72" t="inlineStr">
+        <is>
+          <t>⛵ Königssee electric boat — Jun 25 · 9:15am</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="inlineStr"/>
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>Book 1–2 weeks before Jun 25 (non-refundable · pick time you are confident about) · seenschifffahrt.de</t>
+        </is>
+      </c>
+      <c r="E12" s="74" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="71" t="inlineStr">
@@ -7801,66 +7793,70 @@
       </c>
       <c r="B13" s="72" t="inlineStr">
         <is>
-          <t>⛵ Königssee electric boat — Jun 25 · 9:15am</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="inlineStr"/>
+          <t>Gosaukammbahn cable car — Jun 27</t>
+        </is>
+      </c>
+      <c r="C13" s="73" t="inlineStr">
+        <is>
+          <t>~€28 return/adult · book at gosaukammbahn.at · afternoon after Krippenstein</t>
+        </is>
+      </c>
       <c r="D13" s="73" t="inlineStr">
         <is>
-          <t>Book 1–2 weeks before Jun 25 (non-refundable · pick time you are confident about) · seenschifffahrt.de</t>
+          <t>Book soon — Jun 27 Saturday peak season</t>
         </is>
       </c>
       <c r="E13" s="74" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="71" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>⛏ Hallstatt Salt Mine — CLOSED Jun 27 (renovation)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Closed for renovation · reopens Jun 30 · Salzwelten Altaussee is the alternative (25 min away)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>N/A — closed during our visit</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="B14" s="72" t="inlineStr">
-        <is>
-          <t>Gosaukammbahn cable car — Jun 27</t>
-        </is>
-      </c>
-      <c r="C14" s="73" t="inlineStr">
-        <is>
-          <t>~€28 return/adult · book at gosaukammbahn.at · afternoon after Krippenstein</t>
-        </is>
-      </c>
-      <c r="D14" s="73" t="inlineStr">
-        <is>
-          <t>Book soon — Jun 27 Saturday peak season</t>
-        </is>
-      </c>
-      <c r="E14" s="74" t="inlineStr"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="66" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>⛏ Hallstatt Salt Mine — CLOSED Jun 27 (renovation)</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>Closed for renovation · reopens Jun 30 · Salzwelten Altaussee is the alternative (25 min away)</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>N/A — closed during our visit</t>
-        </is>
-      </c>
-      <c r="E15" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="B15" s="72" t="inlineStr">
+        <is>
+          <t>Dachstein Krippenstein cable car + 5 Fingers — Jun 27</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="inlineStr">
+        <is>
+          <t>Book at dachstein.at · Sections 1+2 ~€44.90/adult · 5 Fingers free at top · arrive Obertraun 8:15am</t>
+        </is>
+      </c>
+      <c r="D15" s="73" t="inlineStr">
+        <is>
+          <t>Book before departure</t>
+        </is>
+      </c>
+      <c r="E15" s="74" t="inlineStr"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="71" t="inlineStr">
@@ -7870,17 +7866,13 @@
       </c>
       <c r="B16" s="72" t="inlineStr">
         <is>
-          <t>Dachstein Krippenstein cable car + 5 Fingers — Jun 27</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="inlineStr">
-        <is>
-          <t>Book at dachstein.at · Sections 1+2 ~€44.90/adult · 5 Fingers free at top · arrive Obertraun 8:15am</t>
-        </is>
-      </c>
+          <t>⛴ Achensee steamboat — Jul 2</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr"/>
       <c r="D16" s="73" t="inlineStr">
         <is>
-          <t>Book before departure</t>
+          <t>Day-of or day-before fine · large boats · no timed slots · achensee.com</t>
         </is>
       </c>
       <c r="E16" s="74" t="inlineStr"/>
@@ -7893,13 +7885,17 @@
       </c>
       <c r="B17" s="72" t="inlineStr">
         <is>
-          <t>⛴ Achensee steamboat — Jul 2</t>
-        </is>
-      </c>
-      <c r="C17" s="73" t="inlineStr"/>
+          <t>Eagle's Nest bus — Jun 25 · ~1pm from Obersalzberg</t>
+        </is>
+      </c>
+      <c r="C17" s="73" t="inlineStr">
+        <is>
+          <t>~€32/person (bus + elevator) · buy at Obersalzberg car park · no advance booking · register return bus time immediately at top</t>
+        </is>
+      </c>
       <c r="D17" s="73" t="inlineStr">
         <is>
-          <t>Day-of or day-before fine · large boats · no timed slots · achensee.com</t>
+          <t>Buy on day — no pre-booking needed</t>
         </is>
       </c>
       <c r="E17" s="74" t="inlineStr"/>
@@ -7912,17 +7908,13 @@
       </c>
       <c r="B18" s="72" t="inlineStr">
         <is>
-          <t>Eagle's Nest bus — Jun 25 · ~1pm from Obersalzberg</t>
-        </is>
-      </c>
-      <c r="C18" s="73" t="inlineStr">
-        <is>
-          <t>~€32/person (bus + elevator) · buy at Obersalzberg car park · no advance booking · register return bus time immediately at top</t>
-        </is>
-      </c>
+          <t>Travel insurance × 4</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="inlineStr"/>
       <c r="D18" s="73" t="inlineStr">
         <is>
-          <t>Buy on day — no pre-booking needed</t>
+          <t>Before departure</t>
         </is>
       </c>
       <c r="E18" s="74" t="inlineStr"/>
@@ -7935,13 +7927,17 @@
       </c>
       <c r="B19" s="72" t="inlineStr">
         <is>
-          <t>Travel insurance × 4</t>
-        </is>
-      </c>
-      <c r="C19" s="73" t="inlineStr"/>
+          <t>️ P2 Compatsch parking — Jul 1 (fully booked · keep checking)</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="inlineStr">
+        <is>
+          <t>seiseralm.it · €30 · must arrive before 9am · cancellations appear · check daily · Plan B: Seis cable car €30/adult RT</t>
+        </is>
+      </c>
       <c r="D19" s="73" t="inlineStr">
         <is>
-          <t>Before departure</t>
+          <t>Keep checking daily — cancellations appear · Plan B = Seis–Compatsch cable car (no booking needed)</t>
         </is>
       </c>
       <c r="E19" s="74" t="inlineStr"/>
@@ -7954,43 +7950,47 @@
       </c>
       <c r="B20" s="72" t="inlineStr">
         <is>
-          <t>️ P2 Compatsch parking — Jul 1 (fully booked · keep checking)</t>
+          <t>Brenner Pass Digital Flex toll — buy online</t>
         </is>
       </c>
       <c r="C20" s="73" t="inlineStr">
         <is>
-          <t>seiseralm.it · €30 · must arrive before 9am · cancellations appear · check daily · Plan B: Seis cable car €30/adult RT</t>
+          <t>autobrennero.it · cameras read plate · skip queue · needed Jun 30→Jul 1</t>
         </is>
       </c>
       <c r="D20" s="73" t="inlineStr">
         <is>
-          <t>Keep checking daily — cancellations appear · Plan B = Seis–Compatsch cable car (no booking needed)</t>
+          <t>Buy before Jun 30</t>
         </is>
       </c>
       <c r="E20" s="74" t="inlineStr"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B21" s="72" t="inlineStr">
-        <is>
-          <t>Brenner Pass Digital Flex toll — buy online</t>
-        </is>
-      </c>
-      <c r="C21" s="73" t="inlineStr">
-        <is>
-          <t>autobrennero.it · cameras read plate · skip queue · needed Jun 30→Jul 1</t>
-        </is>
-      </c>
-      <c r="D21" s="73" t="inlineStr">
-        <is>
-          <t>Buy before Jun 30</t>
-        </is>
-      </c>
-      <c r="E21" s="74" t="inlineStr"/>
+      <c r="A21" s="66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>️ Rifugio Auronzo parking — Jun 29 · Tre Cime</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>Transaction PASS3CIME_26017885 · Ticket P26134547 · €40 · 9:00am–8:59pm Jun 29 · update plate Jun 28 at pass.auronzo.info</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Booked ✅ · update licence plate night before (Jun 28 in Sillian)</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="66" t="inlineStr">
@@ -8000,47 +8000,20 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>️ Rifugio Auronzo parking — Jun 29 · Tre Cime</t>
+          <t>Siusi Alm e-bikes — Jul 1 · optional</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Transaction PASS3CIME_26017885 · Ticket P26134547 · €40 · 9:00am–8:59pm Jun 29 · update plate Jun 28 at pass.auronzo.info</t>
+          <t>Removed from itinerary — time constraints on Jul 1</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>Booked ✅ · update licence plate night before (Jun 28 in Sillian)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E22" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="66" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>Siusi Alm e-bikes — Jul 1 · optional</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>Removed from itinerary — time constraints on Jul 1</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -2786,7 +2786,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Timeline: 8:15am Königssee park ▸ 8:30am boat to Salet ▸ Obersee + Röthbachfall 9:45am ▸ St. Bartholomä lunch 12pm ▸ 1:30pm Eagle's Nest Kehlsteinbus ▸ 4pm Rossfeld Road ▸ 4:45pm Hintersee/Zauberwald ▸ 6:30pm Berchtesgaden dinner</t>
+          <t>Timeline: 8:55am Königssee dock ▸ 9:15am boat to Salet ▸ Obersee + Röthbachfall + Malerwinkel 10:10am ▸ St. Bartholomä lunch 12pm ▸ 12:45pm boat back ▸ 1:30pm Eagle's Nest (clear) or Salt Mine (cloudy) ▸ 4pm Rossfeld ▸ 4:45pm Hintersee/Zauberwald ▸ 6:30pm Berchtesgaden dinner</t>
         </is>
       </c>
     </row>
@@ -2836,12 +2836,12 @@
       <c r="D105" s="17" t="inlineStr"/>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 8:30am — Königssee electric boat — completely silent electric boats — only powered vessels allowed on this lake · ⚠️ Go all the way to Salet — 55 min to Salet · ~€28–30 return to Salet per adult</t>
+          <t xml:space="preserve">⭐ ⭐ 9:15am — Königssee electric boat — ✅ Booked · OB6A2C80290DB89 · Fahrt-Nr. 16 · arrive dock by 8:55am (20 min before) · completely silent electric boats — only powered vessels allowed on this lake · 55 min to Salet · </t>
         </is>
       </c>
       <c r="F105" s="19" t="inlineStr">
         <is>
-          <t>55 min / €28</t>
+          <t>20 min / 55 min / €29.80</t>
         </is>
       </c>
     </row>
@@ -7767,23 +7767,31 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B12" s="72" t="inlineStr">
-        <is>
-          <t>⛵ Königssee electric boat — Jun 25 · 9:15am</t>
-        </is>
-      </c>
-      <c r="C12" s="73" t="inlineStr"/>
-      <c r="D12" s="73" t="inlineStr">
-        <is>
-          <t>Book 1–2 weeks before Jun 25 (non-refundable · pick time you are confident about) · seenschifffahrt.de</t>
-        </is>
-      </c>
-      <c r="E12" s="74" t="inlineStr"/>
+      <c r="A12" s="66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Königssee electric boat — Jun 25 · 9:15am</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Booking OB6A2C80290DB89 · Vorgangs-Nr. 95019 · €89.40 · 2 adults + 2 children · Fahrt-Nr. 16 · Seelände → Salet return · 4 individual tickets</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Booked ✅ · Arrive Seelände dock by 8:55am (20 min before) · Keep return tickets separately</t>
+        </is>
+      </c>
+      <c r="E12" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="71" t="inlineStr">

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -151,12 +151,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C2F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
@@ -169,6 +163,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="004A7C2F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -533,22 +533,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -557,7 +551,13 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -572,13 +572,13 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,7 +587,7 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7515,7 +7515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7562,466 +7562,370 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="66" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>All accommodation — 10 properties confirmed</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>All 10 nights booked · see Accommodation section below</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr"/>
-      <c r="E3" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="B3" s="67" t="inlineStr">
+        <is>
+          <t>Travel insurance × 4</t>
+        </is>
+      </c>
+      <c r="C3" s="38" t="inlineStr"/>
+      <c r="D3" s="38" t="inlineStr">
+        <is>
+          <t>BOOK TODAY — trip departs Jun 19 · only 7 days away</t>
+        </is>
+      </c>
+      <c r="E3" s="68" t="inlineStr"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="66" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>✈️ Icelandair flights × 4</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Ref A77762 · $4,087.92</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr"/>
-      <c r="E4" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="B4" s="67" t="inlineStr">
+        <is>
+          <t>Dachstein Krippenstein cable car + 5 Fingers — Jun 27</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>Book at dachstein.at · Sections 1+2 ~€44.90/adult · 5 Fingers free at top · arrive Obertraun 8:15am</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>Book before departure</t>
+        </is>
+      </c>
+      <c r="E4" s="68" t="inlineStr"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="66" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Europcar ZRH — Volkswagen Tiguan 4x4 · Jun 22–Jul 4</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Booking #738796923 · Booking.com · $746.30 · Pickup 1:30pm · Return 11:30pm Jul 4 · Unlimited mileage</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr"/>
-      <c r="E5" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="B5" s="67" t="inlineStr">
+        <is>
+          <t>Gosaukammbahn cable car — Jun 27</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>~€28 return/adult · book at gosaukammbahn.at · afternoon after Krippenstein</t>
+        </is>
+      </c>
+      <c r="D5" s="38" t="inlineStr">
+        <is>
+          <t>Book soon — Jun 27 Saturday peak season</t>
+        </is>
+      </c>
+      <c r="E5" s="68" t="inlineStr"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="66" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>Budget car — Keflavik KEF · Jun 20–22</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>Conf. #42334482US1 · $289 · pay at pickup</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr"/>
-      <c r="E6" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>Brenner Pass Digital Flex toll — buy online</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>autobrennero.it · cameras read plate · skip queue · needed Jun 30→Jul 1</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>Buy before Jun 30 (Day 12) · autobrennero.it · €11.50</t>
+        </is>
+      </c>
+      <c r="E6" s="68" t="inlineStr"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="66" t="inlineStr">
         <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t>Austrian digital vignette</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr"/>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>Buy on Jun 22 at asfinag.at after picking up Europcar car · need licence plate · ~€16.50 · 10-day pass</t>
+        </is>
+      </c>
+      <c r="E7" s="68" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="69" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B8" s="70" t="inlineStr">
+        <is>
+          <t>️ P2 Compatsch parking — Jul 1 (fully booked · keep checking)</t>
+        </is>
+      </c>
+      <c r="C8" s="71" t="inlineStr">
+        <is>
+          <t>seiseralm.it · €30 · must arrive before 9am · cancellations appear · check daily · Plan B: Seis cable car €30/adult RT</t>
+        </is>
+      </c>
+      <c r="D8" s="71" t="inlineStr">
+        <is>
+          <t>Keep checking daily — cancellations appear · Plan B = Seis–Compatsch cable car (no booking needed)</t>
+        </is>
+      </c>
+      <c r="E8" s="72" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="73" t="inlineStr">
+        <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>All accommodation — 10 properties confirmed</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>All 10 nights booked · see Accommodation section below</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr"/>
+      <c r="E9" s="74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>✈️ Icelandair flights × 4</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Ref A77762 · $4,087.92</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="E10" s="74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="73" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Europcar ZRH — Volkswagen Tiguan 4x4 · Jun 22–Jul 4</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Booking #738796923 · Booking.com · $746.30 · Pickup 1:30pm · Return 11:30pm Jul 4 · Unlimited mileage</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr"/>
+      <c r="E11" s="74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Budget car — Keflavik KEF · Jun 20–22</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Conf. #42334482US1 · $289 · pay at pickup</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr"/>
+      <c r="E12" s="74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="73" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Grindelwald First gondola — Jun 23</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Booking #238070</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr"/>
-      <c r="E7" s="67" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr"/>
+      <c r="E13" s="74" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="66" t="inlineStr">
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="73" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Check 4 passports (valid Oct 2026+)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr"/>
-      <c r="E8" s="67" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="E14" s="74" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="66" t="inlineStr">
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Seceda 360 cable car — Jun 30 · 4 tickets</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Receipt 1161/678/554260 · 2 adults €84.50 + 2 juniors €43.00 · Total €255 · Valid Jun 30, 2026 · Print at home</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>Booked ✅ — print tickets before departure</t>
         </is>
       </c>
-      <c r="E9" s="67" t="inlineStr">
+      <c r="E15" s="74" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
-        <is>
-          <t>Urgent</t>
-        </is>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>Austrian digital vignette</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr"/>
-      <c r="D10" s="38" t="inlineStr">
-        <is>
-          <t>Buy on Jun 22 at asfinag.at after picking up Europcar car · need licence plate · ~€16.50 · 10-day pass</t>
-        </is>
-      </c>
-      <c r="E10" s="70" t="inlineStr"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="66" t="inlineStr">
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>Oeschinensee timed slot — Jun 23 · 8:30am</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Order 254-SK2MH6 · CHF 125 · 08:30–10:00 Jun 23</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr"/>
-      <c r="E11" s="67" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr"/>
+      <c r="E16" s="74" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="66" t="inlineStr">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="73" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Königssee electric boat — Jun 25 · 9:15am</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Booking OB6A2C80290DB89 · Vorgangs-Nr. 95019 · €89.40 · 2 adults + 2 children · Fahrt-Nr. 16 · Seelände → Salet return · 4 individual tickets</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Booked ✅ · Arrive Seelände dock by 8:55am (20 min before) · Keep return tickets separately</t>
         </is>
       </c>
-      <c r="E12" s="67" t="inlineStr">
+      <c r="E17" s="74" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>Gosaukammbahn cable car — Jun 27</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="inlineStr">
-        <is>
-          <t>~€28 return/adult · book at gosaukammbahn.at · afternoon after Krippenstein</t>
-        </is>
-      </c>
-      <c r="D13" s="73" t="inlineStr">
-        <is>
-          <t>Book soon — Jun 27 Saturday peak season</t>
-        </is>
-      </c>
-      <c r="E13" s="74" t="inlineStr"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="73" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>⛏ Hallstatt Salt Mine — CLOSED Jun 27 (renovation)</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>Closed for renovation · reopens Jun 30 · Salzwelten Altaussee is the alternative (25 min away)</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>N/A — closed during our visit</t>
-        </is>
-      </c>
-      <c r="E14" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B15" s="72" t="inlineStr">
-        <is>
-          <t>Dachstein Krippenstein cable car + 5 Fingers — Jun 27</t>
-        </is>
-      </c>
-      <c r="C15" s="73" t="inlineStr">
-        <is>
-          <t>Book at dachstein.at · Sections 1+2 ~€44.90/adult · 5 Fingers free at top · arrive Obertraun 8:15am</t>
-        </is>
-      </c>
-      <c r="D15" s="73" t="inlineStr">
-        <is>
-          <t>Book before departure</t>
-        </is>
-      </c>
-      <c r="E15" s="74" t="inlineStr"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B16" s="72" t="inlineStr">
-        <is>
-          <t>⛴ Achensee steamboat — Jul 2</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="inlineStr"/>
-      <c r="D16" s="73" t="inlineStr">
-        <is>
-          <t>Day-of or day-before fine · large boats · no timed slots · achensee.com</t>
-        </is>
-      </c>
-      <c r="E16" s="74" t="inlineStr"/>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B17" s="72" t="inlineStr">
-        <is>
-          <t>Eagle's Nest bus — Jun 25 · ~1pm from Obersalzberg</t>
-        </is>
-      </c>
-      <c r="C17" s="73" t="inlineStr">
-        <is>
-          <t>~€32/person (bus + elevator) · buy at Obersalzberg car park · no advance booking · register return bus time immediately at top</t>
-        </is>
-      </c>
-      <c r="D17" s="73" t="inlineStr">
-        <is>
-          <t>Buy on day — no pre-booking needed</t>
-        </is>
-      </c>
-      <c r="E17" s="74" t="inlineStr"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B18" s="72" t="inlineStr">
-        <is>
-          <t>Travel insurance × 4</t>
-        </is>
-      </c>
-      <c r="C18" s="73" t="inlineStr"/>
-      <c r="D18" s="73" t="inlineStr">
-        <is>
-          <t>Before departure</t>
-        </is>
-      </c>
-      <c r="E18" s="74" t="inlineStr"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B19" s="72" t="inlineStr">
-        <is>
-          <t>️ P2 Compatsch parking — Jul 1 (fully booked · keep checking)</t>
-        </is>
-      </c>
-      <c r="C19" s="73" t="inlineStr">
-        <is>
-          <t>seiseralm.it · €30 · must arrive before 9am · cancellations appear · check daily · Plan B: Seis cable car €30/adult RT</t>
-        </is>
-      </c>
-      <c r="D19" s="73" t="inlineStr">
-        <is>
-          <t>Keep checking daily — cancellations appear · Plan B = Seis–Compatsch cable car (no booking needed)</t>
-        </is>
-      </c>
-      <c r="E19" s="74" t="inlineStr"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="71" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B20" s="72" t="inlineStr">
-        <is>
-          <t>Brenner Pass Digital Flex toll — buy online</t>
-        </is>
-      </c>
-      <c r="C20" s="73" t="inlineStr">
-        <is>
-          <t>autobrennero.it · cameras read plate · skip queue · needed Jun 30→Jul 1</t>
-        </is>
-      </c>
-      <c r="D20" s="73" t="inlineStr">
-        <is>
-          <t>Buy before Jun 30</t>
-        </is>
-      </c>
-      <c r="E20" s="74" t="inlineStr"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="66" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>️ Rifugio Auronzo parking — Jun 29 · Tre Cime</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Transaction PASS3CIME_26017885 · Ticket P26134547 · €40 · 9:00am–8:59pm Jun 29 · update plate Jun 28 at pass.auronzo.info</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>Booked ✅ · update licence plate night before (Jun 28 in Sillian)</t>
         </is>
       </c>
-      <c r="E21" s="67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="66" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>Siusi Alm e-bikes — Jul 1 · optional</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>Removed from itinerary — time constraints on Jul 1</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="67" t="inlineStr">
+      <c r="E18" s="74" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -8100,7 +8100,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="75" t="inlineStr">
         <is>
-          <t>7–8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" s="76" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>+43 xxx · Airbnb message host · key box on arrival</t>
+          <t>Key box with code at apartment entrance · schedule time with host via Booking.com</t>
         </is>
       </c>
     </row>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -7674,17 +7674,17 @@
       </c>
       <c r="B8" s="70" t="inlineStr">
         <is>
-          <t>️ P2 Compatsch parking — Jul 1 (fully booked · keep checking)</t>
+          <t>P2 Compatsch parking — Jul 1</t>
         </is>
       </c>
       <c r="C8" s="71" t="inlineStr">
         <is>
-          <t>seiseralm.it · €30 · must arrive before 9am · cancellations appear · check daily · Plan B: Seis cable car €30/adult RT</t>
+          <t>seiseralm.it · €30/day · must arrive before 9am · QR code scan at barrier above Hotel Zorzi · booking system opens end of June 2026</t>
         </is>
       </c>
       <c r="D8" s="71" t="inlineStr">
         <is>
-          <t>Keep checking daily — cancellations appear · Plan B = Seis–Compatsch cable car (no booking needed)</t>
+          <t>Booking NOT open yet — system opens ~Jun 25 · check seiseralm.it daily from Jun 25 · book immediately when live · within 6-day window from Collalbo · Plan B: Seis cable car (no booking needed)</t>
         </is>
       </c>
       <c r="E8" s="72" t="inlineStr"/>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F319"/>
+  <dimension ref="A1:F320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3195,14 +3195,14 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Timeline: 8:15am depart Berchtesgaden ▸ 9:00am Liechtensteinklamm ▸ 11am drive Salzburg ▸ 12pm P+R South + Altstadt ▸ Hohensalzburg Panorama Tour ▸ 3pm drive Wolfgangsee ▸ 4pm St. Gilgen→St. Wolfgang ferry ▸ 5:30pm Hallstatt golden hour ▸ 7:30pm Kaiserblick Goisern</t>
+          <t>Timeline: 8:15am Berchtesgaden ▸ 9:00am Liechtensteinklamm ▸ 10:30am Gschwandtanger meadow ▸ 10:45am Salzachöfen Gorge ▸ 12:15pm drive ▸ 1:15pm St. Gilgen lunch ▸ 2:15pm Hallstatt ▸ 6:00pm Bad Goisern</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Key: ✅ Liechtensteinklamm 9:00am sharp — be first at the gate · €16/adult · wear sturdy shoes  |  ✅ Salzburg: P+R South (Alpenstraße) €15 family combo — do NOT park in city centre · 2026 restricted zone  |  ⚠️ Hallstatt tunnel signs: if "Full" — go straight to Goisern · park Obertraun + ferry instead</t>
+          <t>Key: ✅ Salzachöfen Gorge after Gschwandtanger — €5/adult · 1.5hrs · free parking · no booking needed  |  ✅ Liechtensteinklamm 9:00am sharp — be first at the gate · €16/adult · wear sturdy shoes  |  ⚠️ Hallstatt tunnel signs: if "Full" — go straight to Goisern · park Obertraun + ferry instead</t>
         </is>
       </c>
     </row>
@@ -3275,50 +3275,54 @@
       </c>
     </row>
     <row r="129" ht="50" customHeight="1">
-      <c r="A129" s="6" t="inlineStr"/>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="A129" s="16" t="inlineStr"/>
+      <c r="B129" s="17" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C129" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr"/>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ Salzachöfen Gorge — Paß-Lueg-Straße 82, Golling · 5 min away · €5/adult · €3/child · free parking · 90m deep gorge · narrow cathedral cave section · different experience to Liechtensteinklamm · allow 1.5hrs</t>
+        </is>
+      </c>
+      <c r="F129" s="19" t="inlineStr">
+        <is>
+          <t>5 min / €5 / €3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="50" customHeight="1">
+      <c r="A130" s="6" t="inlineStr"/>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr"/>
-      <c r="E129" s="9" t="inlineStr">
+      <c r="D130" s="7" t="inlineStr"/>
+      <c r="E130" s="9" t="inlineStr">
         <is>
           <t>11:00am — Drive north to Salzburg — ~1hr on A10 · arrive ~12:00pm · ⚠️ Do NOT park in the city centre — 2026 restricted traffic zone + construction everywhere · use P+R South (Alpenstraße) — €15 combo-ticket covers parki</t>
         </is>
       </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="F130" s="10" t="inlineStr">
         <is>
           <t>~1hr / €15</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="16" t="inlineStr"/>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D130" s="17" t="inlineStr"/>
-      <c r="E130" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 12:00pm — Salzburg old town</t>
-        </is>
-      </c>
-      <c r="F130" s="19" t="inlineStr"/>
-    </row>
-    <row r="131" ht="38" customHeight="1">
+    <row r="131" ht="18" customHeight="1">
       <c r="A131" s="16" t="inlineStr"/>
       <c r="B131" s="17" t="inlineStr">
         <is>
@@ -3333,64 +3337,60 @@
       <c r="D131" s="17" t="inlineStr"/>
       <c r="E131" s="18" t="inlineStr">
         <is>
+          <t>⭐ 12:00pm — Salzburg old town</t>
+        </is>
+      </c>
+      <c r="F131" s="19" t="inlineStr"/>
+    </row>
+    <row r="132" ht="38" customHeight="1">
+      <c r="A132" s="16" t="inlineStr"/>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr"/>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
           <t>⭐ 12:30pm — Hohensalzburg Fortress — funicular up from Kapitelplatz · stick to the Panorama Tour — ➕ Interior: €16/adult · allow 1hr</t>
         </is>
       </c>
-      <c r="F131" s="19" t="inlineStr">
+      <c r="F132" s="19" t="inlineStr">
         <is>
           <t>€16 / 1hr</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="34" customHeight="1">
-      <c r="A132" s="6" t="inlineStr"/>
-      <c r="B132" s="7" t="inlineStr">
+    <row r="133" ht="34" customHeight="1">
+      <c r="A133" s="6" t="inlineStr"/>
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C132" s="8" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr"/>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="D133" s="7" t="inlineStr"/>
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>3:00pm — Drive east to Wolfgangsee — 45 min to St. Gilgen · arrive ~3:45pm · park in St. Gilgen village car park</t>
         </is>
       </c>
-      <c r="F132" s="10" t="inlineStr">
+      <c r="F133" s="10" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="39" customHeight="1">
-      <c r="A133" s="16" t="inlineStr"/>
-      <c r="B133" s="17" t="inlineStr">
-        <is>
-          <t>Jun 26</t>
-        </is>
-      </c>
-      <c r="C133" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D133" s="17" t="inlineStr"/>
-      <c r="E133" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 4:00pm — Wolfgangsee ferry: St. Gilgen → St. Wolfgang → back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
-        </is>
-      </c>
-      <c r="F133" s="19" t="inlineStr">
-        <is>
-          <t>~20 min / 90 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="22" customHeight="1">
+    <row r="134" ht="39" customHeight="1">
       <c r="A134" s="16" t="inlineStr"/>
       <c r="B134" s="17" t="inlineStr">
         <is>
@@ -3405,16 +3405,16 @@
       <c r="D134" s="17" t="inlineStr"/>
       <c r="E134" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
+          <t>⭐ 4:00pm — Wolfgangsee ferry: St. Gilgen → St. Wolfgang → back — take the ferry to St. Wolfgang (~20 min) · most relaxing 90 min of the day</t>
         </is>
       </c>
       <c r="F134" s="19" t="inlineStr">
         <is>
-          <t>2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="38" customHeight="1">
+          <t>~20 min / 90 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
       <c r="A135" s="16" t="inlineStr"/>
       <c r="B135" s="17" t="inlineStr">
         <is>
@@ -3429,49 +3429,60 @@
       <c r="D135" s="17" t="inlineStr"/>
       <c r="E135" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 5:30pm — Hallstatt golden hour — allow 1.5–2hrs</t>
+        </is>
+      </c>
+      <c r="F135" s="19" t="inlineStr">
+        <is>
+          <t>2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="38" customHeight="1">
+      <c r="A136" s="16" t="inlineStr"/>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr"/>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
           <t>⚠️ Hallstatt 2026 camera parking system — alternative: park at Obertraun (5 min drive) + take the ferry to Hallstatt (€4 · 10 min)</t>
         </is>
       </c>
-      <c r="F135" s="19" t="inlineStr">
+      <c r="F136" s="19" t="inlineStr">
         <is>
           <t>5 min / €4 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="28" customHeight="1">
-      <c r="A136" s="6" t="inlineStr"/>
-      <c r="B136" s="7" t="inlineStr">
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="6" t="inlineStr"/>
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="C136" s="8" t="inlineStr">
+      <c r="C137" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr"/>
-      <c r="E136" s="9" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr"/>
+      <c r="E137" s="9" t="inlineStr">
         <is>
           <t>7:30pm — Kaiserblick Goisern, Bad Goisern — 15 min drive from Hallstatt · $333</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>15 min / $333</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="34" customHeight="1">
-      <c r="A137" s="30" t="inlineStr"/>
-      <c r="B137" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C137" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Salzburg parking 2026 — Old Town becoming restricted traffic zone · construction barriers everywhere · use P+R South (Alpenstraße) · €15 combo = parking + shuttle bus for whole family · much faster than city garage hunting</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3495,7 @@
       </c>
       <c r="C138" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Hallstatt 2026 camera system — electronic signs at tunnel entrance · if "Full": do not enter · drive straight to Kaiserblick Goisern · return via ferry from Obertraun (€4 · 10 min) or bus on Day 8</t>
+          <t>⚠️ Salzburg parking 2026 — Old Town becoming restricted traffic zone · construction barriers everywhere · use P+R South (Alpenstraße) · €15 combo = parking + shuttle bus for whole family · much faster than city garage hunting</t>
         </is>
       </c>
     </row>
@@ -3497,112 +3508,101 @@
       </c>
       <c r="C139" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Hallstatt 2026 camera system — electronic signs at tunnel entrance · if "Full": do not enter · drive straight to Kaiserblick Goisern · return via ferry from Obertraun (€4 · 10 min) or bus on Day 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="34" customHeight="1">
+      <c r="A140" s="30" t="inlineStr"/>
+      <c r="B140" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C140" s="32" t="inlineStr">
+        <is>
           <t>☕ Hohensalzburg tip — stick to Panorama Tour only (courtyards + bastions) · skip the individual museums to stay on schedule · the view is the reason to go up · allow 1hr max</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="3" customHeight="1">
-      <c r="A140" s="33" t="n"/>
-      <c r="B140" s="33" t="n"/>
-      <c r="C140" s="33" t="n"/>
-      <c r="D140" s="33" t="n"/>
-      <c r="E140" s="33" t="n"/>
-      <c r="F140" s="33" t="n"/>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
+    <row r="141" ht="3" customHeight="1">
+      <c r="A141" s="33" t="n"/>
+      <c r="B141" s="33" t="n"/>
+      <c r="C141" s="33" t="n"/>
+      <c r="D141" s="33" t="n"/>
+      <c r="E141" s="33" t="n"/>
+      <c r="F141" s="33" t="n"/>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>DAY 8  |  Jun 27  |  Dachstein Krippenstein · Gosausee · Hallstatt Evening — The High-Alpine Day  |  ~40 km / 25 mi  ~1h total · very local day</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:15am depart Bad Goisern ▸ 8:45am Krippenstein cable car ▸ 9:30am 5 Fingers viewpoint ▸ Ice Cave optional ▸ 1:30pm Gosausee Mirror Lake ▸ 2:00pm Gosaukammbahn ▸ 4:30pm Hallstatt golden hour + dinner ▸ Beinhaus ▸ ~7pm Kaiserblick Goisern</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>Key: Salt Mine + Skywalk CLOSED Jun 27 — reopens Jun 30 · do not book these  |  ✅ Dachstein Krippenstein 8:45am → 5 Fingers → Gosausee 1:30pm → Gosaukammbahn → Hallstatt 4:30pm  |  ⚠️ Saturday = busy Hallstatt · check digital signs · if Full → park Obertraun + NAVIA ferry €4</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="50" customHeight="1">
-      <c r="A144" s="34" t="inlineStr"/>
-      <c r="B144" s="35" t="inlineStr">
+    <row r="145" ht="50" customHeight="1">
+      <c r="A145" s="34" t="inlineStr"/>
+      <c r="B145" s="35" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C144" s="36" t="inlineStr">
+      <c r="C145" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D144" s="35" t="inlineStr"/>
-      <c r="E144" s="37" t="inlineStr">
+      <c r="D145" s="35" t="inlineStr"/>
+      <c r="E145" s="37" t="inlineStr">
         <is>
           <t>2026 Alert: Hallstatt Salt Mine + Skywalk CLOSED Jun 27 — major renovation underway · scheduled to reopen June 30, 2026 · do not attempt to book these for today · alternative: Salzwelten Altaussee — (25 min from Bad Gois</t>
         </is>
       </c>
-      <c r="F144" s="38" t="inlineStr">
+      <c r="F145" s="38" t="inlineStr">
         <is>
           <t>25 min</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="41" customHeight="1">
-      <c r="A145" s="6" t="inlineStr"/>
-      <c r="B145" s="7" t="inlineStr">
+    <row r="146" ht="41" customHeight="1">
+      <c r="A146" s="6" t="inlineStr"/>
+      <c r="B146" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C145" s="8" t="inlineStr">
+      <c r="C146" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr"/>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr"/>
+      <c r="E146" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:15am — Depart Bad Goisern — 20 min drive to Obertraun · arrive by 8:40am · park at the Dachstein Krippenstein cable car base station in Obertraun</t>
         </is>
       </c>
-      <c r="F145" s="10" t="inlineStr">
+      <c r="F146" s="10" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="30" customHeight="1">
-      <c r="A146" s="16" t="inlineStr"/>
-      <c r="B146" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C146" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D146" s="17" t="inlineStr"/>
-      <c r="E146" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · €44.90/adult</t>
-        </is>
-      </c>
-      <c r="F146" s="19" t="inlineStr">
-        <is>
-          <t>€44.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="32" customHeight="1">
+    <row r="147" ht="30" customHeight="1">
       <c r="A147" s="16" t="inlineStr"/>
       <c r="B147" s="17" t="inlineStr">
         <is>
@@ -3617,12 +3617,12 @@
       <c r="D147" s="17" t="inlineStr"/>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
+          <t>⭐ ⭐ 8:45am — Dachstein Krippenstein cable car — Sections 1 + 2 up to 2,109m · €44.90/adult</t>
         </is>
       </c>
       <c r="F147" s="19" t="inlineStr">
         <is>
-          <t>20 min / 45 min</t>
+          <t>€44.90</t>
         </is>
       </c>
     </row>
@@ -3641,64 +3641,64 @@
       <c r="D148" s="17" t="inlineStr"/>
       <c r="E148" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 9:30am — 5 Fingers Viewpoint — 20 min walk from the Section 2 top station · allow 45 min at the top</t>
+        </is>
+      </c>
+      <c r="F148" s="19" t="inlineStr">
+        <is>
+          <t>20 min / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="32" customHeight="1">
+      <c r="A149" s="16" t="inlineStr"/>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="inlineStr"/>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
           <t>➕ Optional: Giant Ice Cave (Section 1) — accessible from Section 1 midstation · extra cost ~€10/adult</t>
         </is>
       </c>
-      <c r="F148" s="19" t="inlineStr">
+      <c r="F149" s="19" t="inlineStr">
         <is>
           <t>€10</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="6" t="inlineStr"/>
-      <c r="B149" s="7" t="inlineStr">
+    <row r="150" ht="30" customHeight="1">
+      <c r="A150" s="6" t="inlineStr"/>
+      <c r="B150" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C149" s="8" t="inlineStr">
+      <c r="C150" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D149" s="7" t="inlineStr"/>
-      <c r="E149" s="9" t="inlineStr">
+      <c r="D150" s="7" t="inlineStr"/>
+      <c r="E150" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 1:30pm — Vorderer Gosausee — the Mirror Lake — 25 min drive from Obertraun · allow 30 min</t>
         </is>
       </c>
-      <c r="F149" s="10" t="inlineStr">
+      <c r="F150" s="10" t="inlineStr">
         <is>
           <t>25 min / 30 min</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="33" customHeight="1">
-      <c r="A150" s="16" t="inlineStr"/>
-      <c r="B150" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27</t>
-        </is>
-      </c>
-      <c r="C150" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D150" s="17" t="inlineStr"/>
-      <c r="E150" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 2:00pm — Gosaukammbahn cable car — ~€28 return/adult · panoramic view of the Dachstein glacier from above</t>
-        </is>
-      </c>
-      <c r="F150" s="19" t="inlineStr">
-        <is>
-          <t>€28</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="31" customHeight="1">
+    <row r="151" ht="33" customHeight="1">
       <c r="A151" s="16" t="inlineStr"/>
       <c r="B151" s="17" t="inlineStr">
         <is>
@@ -3713,16 +3713,16 @@
       <c r="D151" s="17" t="inlineStr"/>
       <c r="E151" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 4:30pm — Hallstatt village evening — mine renovation crowds have gone by now · allow 1.5hrs</t>
+          <t>⭐ 2:00pm — Gosaukammbahn cable car — ~€28 return/adult · panoramic view of the Dachstein glacier from above</t>
         </is>
       </c>
       <c r="F151" s="19" t="inlineStr">
         <is>
-          <t>5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="38" customHeight="1">
+          <t>€28</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="31" customHeight="1">
       <c r="A152" s="16" t="inlineStr"/>
       <c r="B152" s="17" t="inlineStr">
         <is>
@@ -3737,16 +3737,16 @@
       <c r="D152" s="17" t="inlineStr"/>
       <c r="E152" s="18" t="inlineStr">
         <is>
-          <t>⚠️ Saturday parking warning — if P1/P2 show "Full": park in Obertraun (5 min drive) + take the ferry across · NAVIA ferry: €4 cash</t>
+          <t>⭐ ⭐ 4:30pm — Hallstatt village evening — mine renovation crowds have gone by now · allow 1.5hrs</t>
         </is>
       </c>
       <c r="F152" s="19" t="inlineStr">
         <is>
-          <t>5 min / €4</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="21" customHeight="1">
+          <t>5hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="38" customHeight="1">
       <c r="A153" s="16" t="inlineStr"/>
       <c r="B153" s="17" t="inlineStr">
         <is>
@@ -3761,49 +3761,60 @@
       <c r="D153" s="17" t="inlineStr"/>
       <c r="E153" s="18" t="inlineStr">
         <is>
+          <t>⚠️ Saturday parking warning — if P1/P2 show "Full": park in Obertraun (5 min drive) + take the ferry across · NAVIA ferry: €4 cash</t>
+        </is>
+      </c>
+      <c r="F153" s="19" t="inlineStr">
+        <is>
+          <t>5 min / €4</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="21" customHeight="1">
+      <c r="A154" s="16" t="inlineStr"/>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>Jun 27</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D154" s="17" t="inlineStr"/>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
           <t>⭐ Beinhaus (Bone Chapel) — €1.50/adult · 10 min</t>
         </is>
       </c>
-      <c r="F153" s="19" t="inlineStr">
+      <c r="F154" s="19" t="inlineStr">
         <is>
           <t>€1.50 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="37" customHeight="1">
-      <c r="A154" s="6" t="inlineStr"/>
-      <c r="B154" s="7" t="inlineStr">
+    <row r="155" ht="37" customHeight="1">
+      <c r="A155" s="6" t="inlineStr"/>
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>Jun 27</t>
         </is>
       </c>
-      <c r="C154" s="8" t="inlineStr">
+      <c r="C155" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D154" s="7" t="inlineStr"/>
-      <c r="E154" s="9" t="inlineStr">
+      <c r="D155" s="7" t="inlineStr"/>
+      <c r="E155" s="9" t="inlineStr">
         <is>
           <t>Night 2 — Kaiserblick Goisern — ✅ Already checked in ·  38 Unterjoch, 4822 Bad Goisern, Austria · 15 min drive from Hallstatt</t>
         </is>
       </c>
-      <c r="F154" s="10" t="inlineStr">
+      <c r="F155" s="10" t="inlineStr">
         <is>
           <t>15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="34" customHeight="1">
-      <c r="A155" s="30" t="inlineStr"/>
-      <c r="B155" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C155" s="32" t="inlineStr">
-        <is>
-          <t>Salt Mine + Skywalk CLOSED Jun 27 — major renovation · reopens Jun 30, 2026 · alternative: Salzwelten Altaussee (25 min from Bad Goisern) · active mine · most authentic</t>
         </is>
       </c>
     </row>
@@ -3816,11 +3827,11 @@
       </c>
       <c r="C156" s="32" t="inlineStr">
         <is>
-          <t>⚠️ 5 Fingers vs Skywalk — 5 Fingers on Krippenstein is higher, more dramatic, free with cable car ticket · direct aerial view down into Hallstatt village · Skywalk is closed anyway — 5 Fingers is the better experience</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="33" customHeight="1">
+          <t>Salt Mine + Skywalk CLOSED Jun 27 — major renovation · reopens Jun 30, 2026 · alternative: Salzwelten Altaussee (25 min from Bad Goisern) · active mine · most authentic</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="34" customHeight="1">
       <c r="A157" s="30" t="inlineStr"/>
       <c r="B157" s="31" t="inlineStr">
         <is>
@@ -3829,11 +3840,11 @@
       </c>
       <c r="C157" s="32" t="inlineStr">
         <is>
-          <t>Gosausee afternoon tip — best photos happen when the sun hits the Dachstein glacier face-on in the afternoon · go at 3pm not morning for the mirror reflection shot</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="34" customHeight="1">
+          <t>⚠️ 5 Fingers vs Skywalk — 5 Fingers on Krippenstein is higher, more dramatic, free with cable car ticket · direct aerial view down into Hallstatt village · Skywalk is closed anyway — 5 Fingers is the better experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="33" customHeight="1">
       <c r="A158" s="30" t="inlineStr"/>
       <c r="B158" s="31" t="inlineStr">
         <is>
@@ -3842,7 +3853,7 @@
       </c>
       <c r="C158" s="32" t="inlineStr">
         <is>
-          <t>Hofer (Aldi) Bad Goisern — stock up this morning or evening · discount prices · buy for Jun 27–Jul 1: Grossglockner · Sillian · Dolomites 3 nights · Hofrat-Renner-Weg 1 · open Tue 7:15am</t>
+          <t>Gosausee afternoon tip — best photos happen when the sun hits the Dachstein glacier face-on in the afternoon · go at 3pm not morning for the mirror reflection shot</t>
         </is>
       </c>
     </row>
@@ -3855,88 +3866,77 @@
       </c>
       <c r="C159" s="32" t="inlineStr">
         <is>
+          <t>Hofer (Aldi) Bad Goisern — stock up this morning or evening · discount prices · buy for Jun 27–Jul 1: Grossglockner · Sillian · Dolomites 3 nights · Hofrat-Renner-Weg 1 · open Tue 7:15am</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="34" customHeight="1">
+      <c r="A160" s="30" t="inlineStr"/>
+      <c r="B160" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C160" s="32" t="inlineStr">
+        <is>
           <t>Löckenmoos alpine lake — Bad Goisern — minutes from Kaiserblick hotel · almost no international tourists · small alpine bog lake with mountain reflections · ☀️ clear weather only — magical when calm · perfect 20 min evening walk from the ho</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="3" customHeight="1">
-      <c r="A160" s="33" t="n"/>
-      <c r="B160" s="33" t="n"/>
-      <c r="C160" s="33" t="n"/>
-      <c r="D160" s="33" t="n"/>
-      <c r="E160" s="33" t="n"/>
-      <c r="F160" s="33" t="n"/>
-    </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="3" t="inlineStr">
+    <row r="161" ht="3" customHeight="1">
+      <c r="A161" s="33" t="n"/>
+      <c r="B161" s="33" t="n"/>
+      <c r="C161" s="33" t="n"/>
+      <c r="D161" s="33" t="n"/>
+      <c r="E161" s="33" t="n"/>
+      <c r="F161" s="33" t="n"/>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>DAY 9  |  Jun 28  |  The Roof of Austria — Grossglockner High Alpine Road → Sillian  |  ~280 km / 174 mi  ~4h 30m incl. Grossglockner slow drive</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="4" t="inlineStr">
+    <row r="163" ht="15" customHeight="1">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:00am checkout ▸ 9:30am Ferleiten toll €46.50 ▸ 10:15am Edelweiß-Spitze ▸ 11:30am Hochtor tunnel ▸ 12:15pm KFJ-Höhe + marmots ▸ 1:30pm glacier lunch ▸ 3:30pm Heiligenblut church photo ▸ 5:30pm Sillian ▸ alarm 5am</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="5" t="inlineStr">
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Edelweiß-Spitze FIRST — go before motorcycles arrive · dead-end road congests by afternoon  |  ✅ Gamsgrubenweg 10 min from KFJ-Höhe — best marmot spotting on the road · kids will love it  |  ⚠️ Descent: engine brake in low gear · do NOT ride the brakes · they will overheat</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="43" customHeight="1">
-      <c r="A164" s="6" t="inlineStr"/>
-      <c r="B164" s="7" t="inlineStr">
+    <row r="165" ht="43" customHeight="1">
+      <c r="A165" s="6" t="inlineStr"/>
+      <c r="B165" s="7" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C165" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D164" s="7" t="inlineStr"/>
-      <c r="E164" s="9" t="inlineStr">
+      <c r="D165" s="7" t="inlineStr"/>
+      <c r="E165" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:00am — Checkout Kaiserblick Goisern — 1.5hr drive to the Ferleiten toll gate via the B311 · download offline maps for the Dolomites tonight if not done yet</t>
         </is>
       </c>
-      <c r="F164" s="10" t="inlineStr">
+      <c r="F165" s="10" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="46" customHeight="1">
-      <c r="A165" s="16" t="inlineStr"/>
-      <c r="B165" s="17" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D165" s="17" t="inlineStr"/>
-      <c r="E165" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ Grossglockner High Alpine Road — 48km of switchbacks across the highest surfaced alpine pass in Austria · road open from 5:30am — last entry 45 min before 9pm closing</t>
-        </is>
-      </c>
-      <c r="F165" s="19" t="inlineStr">
-        <is>
-          <t>48km / 45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="38" customHeight="1">
+    <row r="166" ht="46" customHeight="1">
       <c r="A166" s="16" t="inlineStr"/>
       <c r="B166" s="17" t="inlineStr">
         <is>
@@ -3951,60 +3951,64 @@
       <c r="D166" s="17" t="inlineStr"/>
       <c r="E166" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ Grossglockner High Alpine Road — 48km of switchbacks across the highest surfaced alpine pass in Austria · road open from 5:30am — last entry 45 min before 9pm closing</t>
+        </is>
+      </c>
+      <c r="F166" s="19" t="inlineStr">
+        <is>
+          <t>48km / 45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="38" customHeight="1">
+      <c r="A167" s="16" t="inlineStr"/>
+      <c r="B167" s="17" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D167" s="17" t="inlineStr"/>
+      <c r="E167" s="18" t="inlineStr">
+        <is>
           <t>9:30am — Ferleiten Toll Gate — 2026 rate: €46.50/car — first stop: Edelweiß-Spitze — go there FIRST before the motorcycles arrive</t>
         </is>
       </c>
-      <c r="F166" s="19" t="inlineStr">
+      <c r="F167" s="19" t="inlineStr">
         <is>
           <t>€46.50</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="34" customHeight="1">
-      <c r="A167" s="20" t="inlineStr"/>
-      <c r="B167" s="21" t="inlineStr">
+    <row r="168" ht="34" customHeight="1">
+      <c r="A168" s="20" t="inlineStr"/>
+      <c r="B168" s="21" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C167" s="22" t="inlineStr">
+      <c r="C168" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D167" s="21" t="inlineStr"/>
-      <c r="E167" s="23" t="inlineStr">
+      <c r="D168" s="21" t="inlineStr"/>
+      <c r="E168" s="23" t="inlineStr">
         <is>
           <t>Haus Alpine Naturschau — natural history museum — 15 min · great context for the kids before reaching the summit</t>
         </is>
       </c>
-      <c r="F167" s="24" t="inlineStr">
+      <c r="F168" s="24" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="32" customHeight="1">
-      <c r="A168" s="16" t="inlineStr"/>
-      <c r="B168" s="17" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D168" s="17" t="inlineStr"/>
-      <c r="E168" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 10:15am — Edelweiß-Spitze (2,571m) — MUST STOP · dead-end cobblestone branch road — go here FIRST</t>
-        </is>
-      </c>
-      <c r="F168" s="19" t="inlineStr"/>
-    </row>
-    <row r="169" ht="21" customHeight="1">
+    <row r="169" ht="32" customHeight="1">
       <c r="A169" s="16" t="inlineStr"/>
       <c r="B169" s="17" t="inlineStr">
         <is>
@@ -4019,132 +4023,128 @@
       <c r="D169" s="17" t="inlineStr"/>
       <c r="E169" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 10:15am — Edelweiß-Spitze (2,571m) — MUST STOP · dead-end cobblestone branch road — go here FIRST</t>
+        </is>
+      </c>
+      <c r="F169" s="19" t="inlineStr"/>
+    </row>
+    <row r="170" ht="21" customHeight="1">
+      <c r="A170" s="16" t="inlineStr"/>
+      <c r="B170" s="17" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D170" s="17" t="inlineStr"/>
+      <c r="E170" s="18" t="inlineStr">
+        <is>
           <t>11:30am — Hochtor Tunnel (2,504m) — 10 min stop</t>
         </is>
       </c>
-      <c r="F169" s="19" t="inlineStr">
+      <c r="F170" s="19" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="50" customHeight="1">
-      <c r="A170" s="20" t="inlineStr"/>
-      <c r="B170" s="21" t="inlineStr">
+    <row r="171" ht="50" customHeight="1">
+      <c r="A171" s="20" t="inlineStr"/>
+      <c r="B171" s="21" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C170" s="22" t="inlineStr">
+      <c r="C171" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D170" s="21" t="inlineStr"/>
-      <c r="E170" s="23" t="inlineStr">
+      <c r="D171" s="21" t="inlineStr"/>
+      <c r="E171" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⭐ ⭐ 12:15pm — Kaiser-Franz-Josefs-Höhe (2,369m) — Austria's longest glacier (8km) stretching toward the Grossglockner · ⚠️ 2026: glacier has receded significantly — to touch the ice take the Gletscherbahn funicular down </t>
         </is>
       </c>
-      <c r="F170" s="24" t="inlineStr">
+      <c r="F171" s="24" t="inlineStr">
         <is>
           <t>8km / 45 min</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="36" customHeight="1">
-      <c r="A171" s="16" t="inlineStr"/>
-      <c r="B171" s="17" t="inlineStr">
+    <row r="172" ht="36" customHeight="1">
+      <c r="A172" s="16" t="inlineStr"/>
+      <c r="B172" s="17" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C171" s="16" t="inlineStr">
+      <c r="C172" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D171" s="17" t="inlineStr"/>
-      <c r="E171" s="18" t="inlineStr">
+      <c r="D172" s="17" t="inlineStr"/>
+      <c r="E172" s="18" t="inlineStr">
         <is>
           <t>Marmot &amp; ibex spotting — Gamsgrubenweg — from Kaiser-Franz-Josefs-Höhe: follow the Gamsgrubenweg tunnel path for 10 min</t>
         </is>
       </c>
-      <c r="F171" s="19" t="inlineStr">
+      <c r="F172" s="19" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="31" customHeight="1">
-      <c r="A172" s="11" t="inlineStr"/>
-      <c r="B172" s="12" t="inlineStr">
+    <row r="173" ht="31" customHeight="1">
+      <c r="A173" s="11" t="inlineStr"/>
+      <c r="B173" s="12" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C172" s="13" t="inlineStr">
+      <c r="C173" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D172" s="12" t="inlineStr"/>
-      <c r="E172" s="14" t="inlineStr">
+      <c r="D173" s="12" t="inlineStr"/>
+      <c r="E173" s="14" t="inlineStr">
         <is>
           <t>1:30pm — Lunch at Kaiser-Franz-Josefs-Höhe — panoramic terrace facing the glacier · allow 1hr</t>
         </is>
       </c>
-      <c r="F172" s="15" t="inlineStr">
+      <c r="F173" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="21" customHeight="1">
-      <c r="A173" s="20" t="inlineStr"/>
-      <c r="B173" s="21" t="inlineStr">
+    <row r="174" ht="21" customHeight="1">
+      <c r="A174" s="20" t="inlineStr"/>
+      <c r="B174" s="21" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C173" s="22" t="inlineStr">
+      <c r="C174" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D173" s="21" t="inlineStr"/>
-      <c r="E173" s="23" t="inlineStr">
+      <c r="D174" s="21" t="inlineStr"/>
+      <c r="E174" s="23" t="inlineStr">
         <is>
           <t>⚠️ Descent toward Heiligenblut — brake warning</t>
         </is>
       </c>
-      <c r="F173" s="24" t="inlineStr"/>
-    </row>
-    <row r="174" ht="21" customHeight="1">
-      <c r="A174" s="16" t="inlineStr"/>
-      <c r="B174" s="17" t="inlineStr">
-        <is>
-          <t>Jun 28</t>
-        </is>
-      </c>
-      <c r="C174" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D174" s="17" t="inlineStr"/>
-      <c r="E174" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 3:30pm — Heiligenblut village — allow 30 min</t>
-        </is>
-      </c>
-      <c r="F174" s="19" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="50" customHeight="1">
+      <c r="F174" s="24" t="inlineStr"/>
+    </row>
+    <row r="175" ht="21" customHeight="1">
       <c r="A175" s="16" t="inlineStr"/>
       <c r="B175" s="17" t="inlineStr">
         <is>
@@ -4159,71 +4159,82 @@
       <c r="D175" s="17" t="inlineStr"/>
       <c r="E175" s="18" t="inlineStr">
         <is>
+          <t>⭐ 3:30pm — Heiligenblut village — allow 30 min</t>
+        </is>
+      </c>
+      <c r="F175" s="19" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="50" customHeight="1">
+      <c r="A176" s="16" t="inlineStr"/>
+      <c r="B176" s="17" t="inlineStr">
+        <is>
+          <t>Jun 28</t>
+        </is>
+      </c>
+      <c r="C176" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D176" s="17" t="inlineStr"/>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
           <t>Gößnitzfall waterfall — Heiligenblut — right outside the village · easy 20 min walk through shaded forest to dramatic wooden viewing platform · thunderous alpine waterfall · stroller-friendly · free · perfect for shaking</t>
         </is>
       </c>
-      <c r="F175" s="19" t="inlineStr">
+      <c r="F176" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="23" customHeight="1">
-      <c r="A176" s="25" t="inlineStr"/>
-      <c r="B176" s="26" t="inlineStr">
+    <row r="177" ht="23" customHeight="1">
+      <c r="A177" s="25" t="inlineStr"/>
+      <c r="B177" s="26" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C176" s="27" t="inlineStr">
+      <c r="C177" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D176" s="26" t="inlineStr"/>
-      <c r="E176" s="28" t="inlineStr">
+      <c r="D177" s="26" t="inlineStr"/>
+      <c r="E177" s="28" t="inlineStr">
         <is>
           <t>5:30pm — Hotel Schwarzer Adler, Sillian — $115 / €99.40</t>
         </is>
       </c>
-      <c r="F176" s="29" t="inlineStr">
+      <c r="F177" s="29" t="inlineStr">
         <is>
           <t>$115 / €99.40</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="40" customHeight="1">
-      <c r="A177" s="11" t="inlineStr"/>
-      <c r="B177" s="12" t="inlineStr">
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="11" t="inlineStr"/>
+      <c r="B178" s="12" t="inlineStr">
         <is>
           <t>Jun 28</t>
         </is>
       </c>
-      <c r="C177" s="13" t="inlineStr">
+      <c r="C178" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D177" s="12" t="inlineStr"/>
-      <c r="E177" s="14" t="inlineStr">
+      <c r="D178" s="12" t="inlineStr"/>
+      <c r="E178" s="14" t="inlineStr">
         <is>
           <t>Dinner in Sillian —  Download offline Dolomites maps tonight (Maps.me or Google Maps) · check Rifugio Auronzo parking booking confirmation</t>
         </is>
       </c>
-      <c r="F177" s="15" t="inlineStr"/>
-    </row>
-    <row r="178" ht="34" customHeight="1">
-      <c r="A178" s="30" t="inlineStr"/>
-      <c r="B178" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C178" s="32" t="inlineStr">
-        <is>
-          <t>Grossglockner toll 2026: €46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
-        </is>
-      </c>
+      <c r="F178" s="15" t="inlineStr"/>
     </row>
     <row r="179" ht="34" customHeight="1">
       <c r="A179" s="30" t="inlineStr"/>
@@ -4234,11 +4245,11 @@
       </c>
       <c r="C179" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="33" customHeight="1">
+          <t>Grossglockner toll 2026: €46.50/car — buy Day Ticket online at grossglockner.at to skip queue · road open 5:30am–9pm · last entry 45 min before closing · check road status for snow/closures before departing</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="34" customHeight="1">
       <c r="A180" s="30" t="inlineStr"/>
       <c r="B180" s="31" t="inlineStr">
         <is>
@@ -4247,11 +4258,11 @@
       </c>
       <c r="C180" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="34" customHeight="1">
+          <t>⚠️ Pasterze Glacier 2026 — glacier has receded significantly · to touch the ice: Gletscherbahn funicular down + 30–45 min hike · terrace view is still spectacular without going down</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="33" customHeight="1">
       <c r="A181" s="30" t="inlineStr"/>
       <c r="B181" s="31" t="inlineStr">
         <is>
@@ -4260,7 +4271,7 @@
       </c>
       <c r="C181" s="32" t="inlineStr">
         <is>
-          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
+          <t>⚠️ Brake warning on descent — Heiligenblut descent is steep and long · use 2nd/3rd gear engine braking · continuous brake use = overheating + brake fade = dangerous</t>
         </is>
       </c>
     </row>
@@ -4273,112 +4284,101 @@
       </c>
       <c r="C182" s="32" t="inlineStr">
         <is>
+          <t>Heiligenblut church photo — upper car park near the cemetery · Grossglockner peak frames behind the church spire · 4pm light is ideal · one of the most iconic shots in Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="34" customHeight="1">
+      <c r="A183" s="30" t="inlineStr"/>
+      <c r="B183" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C183" s="32" t="inlineStr">
+        <is>
           <t>Tonight: prep for Dolomites — download offline maps (Google Maps or Maps.me) for the Dolomites · confirm Rifugio Auronzo parking booking · 5am alarm tomorrow · Braies gate opens 7:30am</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="3" customHeight="1">
-      <c r="A183" s="33" t="n"/>
-      <c r="B183" s="33" t="n"/>
-      <c r="C183" s="33" t="n"/>
-      <c r="D183" s="33" t="n"/>
-      <c r="E183" s="33" t="n"/>
-      <c r="F183" s="33" t="n"/>
-    </row>
-    <row r="184" ht="20" customHeight="1">
-      <c r="A184" s="3" t="inlineStr">
+    <row r="184" ht="3" customHeight="1">
+      <c r="A184" s="33" t="n"/>
+      <c r="B184" s="33" t="n"/>
+      <c r="C184" s="33" t="n"/>
+      <c r="D184" s="33" t="n"/>
+      <c r="E184" s="33" t="n"/>
+      <c r="F184" s="33" t="n"/>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>DAY 10  |  Jun 29  |  The Iconic Dolomites — Braies Sunrise · Tre Cime · Prato Piazza · Gardena  |  ~200 km / 124 mi  ~5h total driving · many short hops</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
+    <row r="186" ht="15" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Sillian ▸ 8:45am Braies P3 ▸ 10:15am depart ▸ Misurina coffee ▸ 11:15am Auronzo gate ▸ 11:45am Cadini Trail 117 ▸ 1:30pm lunch ▸ 2:30pm Tre Cime walk ▸ 3:45pm Gardena Pass ▸ 5pm Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="22" customHeight="1">
-      <c r="A186" s="5" t="inlineStr">
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ 8am departure — relaxed start · Braies 8:45am · still beautiful · P3 no reservation  |  ❌ Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |  ✅ Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |  ⚠️ Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |  ⚠️ Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="48" customHeight="1">
-      <c r="A187" s="6" t="inlineStr"/>
-      <c r="B187" s="7" t="inlineStr">
+    <row r="188" ht="48" customHeight="1">
+      <c r="A188" s="6" t="inlineStr"/>
+      <c r="B188" s="7" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C187" s="8" t="inlineStr">
+      <c r="C188" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr"/>
-      <c r="E187" s="9" t="inlineStr">
+      <c r="D188" s="7" t="inlineStr"/>
+      <c r="E188" s="9" t="inlineStr">
         <is>
           <t>8:00am — Depart Sillian — 45 min straight across the Italian border · download offline Dolomites maps tonight if not done · update Auronzo plate at pass.auronzo.info tonight (Jun 28)</t>
         </is>
       </c>
-      <c r="F187" s="10" t="inlineStr">
+      <c r="F188" s="10" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="49" customHeight="1">
-      <c r="A188" s="16" t="inlineStr"/>
-      <c r="B188" s="17" t="inlineStr">
+    <row r="189" ht="49" customHeight="1">
+      <c r="A189" s="16" t="inlineStr"/>
+      <c r="B189" s="17" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C188" s="16" t="inlineStr">
+      <c r="C189" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D188" s="17" t="inlineStr"/>
-      <c r="E188" s="18" t="inlineStr">
+      <c r="D189" s="17" t="inlineStr"/>
+      <c r="E189" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 · no reservation needed · walk the best half of the lakeside circuit · famous stilt boathouse · morning views · allow 1.5hrs · leave by 10:15am</t>
         </is>
       </c>
-      <c r="F188" s="19" t="inlineStr">
+      <c r="F189" s="19" t="inlineStr">
         <is>
           <t>€12 / 5hr</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="44" customHeight="1">
-      <c r="A189" s="6" t="inlineStr"/>
-      <c r="B189" s="7" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C189" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D189" s="7" t="inlineStr"/>
-      <c r="E189" s="9" t="inlineStr">
-        <is>
-          <t>☕ 10:15am — Drive via Lago di Misurina — 1hr drive down the valley · stop at Rifugio Misurina café · 15 min coffee + mirror-reflection photo of Tre Cime in the lake</t>
-        </is>
-      </c>
-      <c r="F189" s="10" t="inlineStr">
-        <is>
-          <t>1hr / 15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="45" customHeight="1">
+    <row r="190" ht="44" customHeight="1">
       <c r="A190" s="6" t="inlineStr"/>
       <c r="B190" s="7" t="inlineStr">
         <is>
@@ -4393,64 +4393,64 @@
       <c r="D190" s="7" t="inlineStr"/>
       <c r="E190" s="9" t="inlineStr">
         <is>
+          <t>☕ 10:15am — Drive via Lago di Misurina — 1hr drive down the valley · stop at Rifugio Misurina café · 15 min coffee + mirror-reflection photo of Tre Cime in the lake</t>
+        </is>
+      </c>
+      <c r="F190" s="10" t="inlineStr">
+        <is>
+          <t>1hr / 15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="45" customHeight="1">
+      <c r="A191" s="6" t="inlineStr"/>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr"/>
+      <c r="E191" s="9" t="inlineStr">
+        <is>
           <t>⚠️ 11:15am — Auronzo gate — ✅ Pre-booked · PASS3CIME_26017885 · Ticket P26134547 · 9am–8:59pm slot · plate reads automatically · drive straight up · €40 paid · no queue</t>
         </is>
       </c>
-      <c r="F190" s="10" t="inlineStr">
+      <c r="F191" s="10" t="inlineStr">
         <is>
           <t>€40</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="50" customHeight="1">
-      <c r="A191" s="20" t="inlineStr"/>
-      <c r="B191" s="21" t="inlineStr">
+    <row r="192" ht="50" customHeight="1">
+      <c r="A192" s="20" t="inlineStr"/>
+      <c r="B192" s="21" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C191" s="22" t="inlineStr">
+      <c r="C192" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D191" s="21" t="inlineStr"/>
-      <c r="E191" s="23" t="inlineStr">
+      <c r="D192" s="21" t="inlineStr"/>
+      <c r="E192" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⭐ ⭐ 11:45am — Cadini di Misurina Trail 117 — hike out to the iconic jagged peak viewpoint · 45 min RT at normal pace · ⚠️ final 50m is a narrow ridge · secondary viewpoint 20m back is 95% as good · allow 1hr 45min total </t>
         </is>
       </c>
-      <c r="F191" s="24" t="inlineStr">
+      <c r="F192" s="24" t="inlineStr">
         <is>
           <t>45 min / 1hr / 45min</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="29" customHeight="1">
-      <c r="A192" s="11" t="inlineStr"/>
-      <c r="B192" s="12" t="inlineStr">
-        <is>
-          <t>Jun 29</t>
-        </is>
-      </c>
-      <c r="C192" s="13" t="inlineStr">
-        <is>
-          <t>Eat</t>
-        </is>
-      </c>
-      <c r="D192" s="12" t="inlineStr"/>
-      <c r="E192" s="14" t="inlineStr">
-        <is>
-          <t>1:30pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr</t>
-        </is>
-      </c>
-      <c r="F192" s="15" t="inlineStr">
-        <is>
-          <t>1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="40" customHeight="1">
+    <row r="193" ht="29" customHeight="1">
       <c r="A193" s="11" t="inlineStr"/>
       <c r="B193" s="12" t="inlineStr">
         <is>
@@ -4465,71 +4465,82 @@
       <c r="D193" s="12" t="inlineStr"/>
       <c r="E193" s="14" t="inlineStr">
         <is>
+          <t>1:30pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr</t>
+        </is>
+      </c>
+      <c r="F193" s="15" t="inlineStr">
+        <is>
+          <t>1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" s="11" t="inlineStr"/>
+      <c r="B194" s="12" t="inlineStr">
+        <is>
+          <t>Jun 29</t>
+        </is>
+      </c>
+      <c r="C194" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D194" s="12" t="inlineStr"/>
+      <c r="E194" s="14" t="inlineStr">
+        <is>
           <t>2:30pm — Tre Cime Highlights Walk — flat path to Rifugio Lavaredo (20 min each way) · see the towering north faces up close · allow 1hr 15min</t>
         </is>
       </c>
-      <c r="F193" s="15" t="inlineStr">
+      <c r="F194" s="15" t="inlineStr">
         <is>
           <t>20 min / 1hr / 15min</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="50" customHeight="1">
-      <c r="A194" s="6" t="inlineStr"/>
-      <c r="B194" s="7" t="inlineStr">
+    <row r="195" ht="50" customHeight="1">
+      <c r="A195" s="6" t="inlineStr"/>
+      <c r="B195" s="7" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C195" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D194" s="7" t="inlineStr"/>
-      <c r="E194" s="9" t="inlineStr">
+      <c r="D195" s="7" t="inlineStr"/>
+      <c r="E195" s="9" t="inlineStr">
         <is>
           <t>3:45pm — Passo Gardena scenic drive — drive back down toll road · SS243 Gardena Pass (2,121m) · hairpin turns · low gear descent · ➕ Lagazuoi cable car optional if energy · ~1hr 15min drive</t>
         </is>
       </c>
-      <c r="F194" s="10" t="inlineStr">
+      <c r="F195" s="10" t="inlineStr">
         <is>
           <t>~1hr / 15min</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="43" customHeight="1">
-      <c r="A195" s="25" t="inlineStr"/>
-      <c r="B195" s="26" t="inlineStr">
+    <row r="196" ht="43" customHeight="1">
+      <c r="A196" s="25" t="inlineStr"/>
+      <c r="B196" s="26" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C195" s="27" t="inlineStr">
+      <c r="C196" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D195" s="26" t="inlineStr"/>
-      <c r="E195" s="28" t="inlineStr">
+      <c r="D196" s="26" t="inlineStr"/>
+      <c r="E196" s="28" t="inlineStr">
         <is>
           <t>5:00pm — Kaiserau 1907, Collalbo — ✅ Check in · Via Peter Mayr 65, 39054 Collalbo · check-in 15:00–22:00 · unpack · rest · open a bottle of Italian wine</t>
         </is>
       </c>
-      <c r="F195" s="29" t="inlineStr"/>
-    </row>
-    <row r="196" ht="34" customHeight="1">
-      <c r="A196" s="30" t="inlineStr"/>
-      <c r="B196" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C196" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Braies 2026 access — road blocked 9am–4pm in peak season · arrive by 5:30am · P3 no reservation before 8am · €12 · leave before 8:30am · pivot to Prato Piazza if cloudy</t>
-        </is>
-      </c>
+      <c r="F196" s="29" t="inlineStr"/>
     </row>
     <row r="197" ht="34" customHeight="1">
       <c r="A197" s="30" t="inlineStr"/>
@@ -4540,7 +4551,7 @@
       </c>
       <c r="C197" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Auronzo toll road 2026 — book at pass.auronzo.info · €40/car · 12-hour slot · book May 30 (exactly 30 days before) · rental plate: leave blank · update night before at Sillian hotel</t>
+          <t>⚠️ Braies 2026 access — road blocked 9am–4pm in peak season · arrive by 5:30am · P3 no reservation before 8am · €12 · leave before 8:30am · pivot to Prato Piazza if cloudy</t>
         </is>
       </c>
     </row>
@@ -4553,184 +4564,173 @@
       </c>
       <c r="C198" s="32" t="inlineStr">
         <is>
+          <t>⚠️ Auronzo toll road 2026 — book at pass.auronzo.info · €40/car · 12-hour slot · book May 30 (exactly 30 days before) · rental plate: leave blank · update night before at Sillian hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="34" customHeight="1">
+      <c r="A199" s="30" t="inlineStr"/>
+      <c r="B199" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C199" s="32" t="inlineStr">
+        <is>
           <t>Cadini viewpoint tip — final 50m is a narrow ridge · secondary viewpoint 20m before the narrow section · 95% as good · go early — very crowded by midday · most dramatic jagged peak view in the Dolomites</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="3" customHeight="1">
-      <c r="A199" s="33" t="n"/>
-      <c r="B199" s="33" t="n"/>
-      <c r="C199" s="33" t="n"/>
-      <c r="D199" s="33" t="n"/>
-      <c r="E199" s="33" t="n"/>
-      <c r="F199" s="33" t="n"/>
-    </row>
-    <row r="200" ht="20" customHeight="1">
-      <c r="A200" s="3" t="inlineStr">
+    <row r="200" ht="3" customHeight="1">
+      <c r="A200" s="33" t="n"/>
+      <c r="B200" s="33" t="n"/>
+      <c r="C200" s="33" t="n"/>
+      <c r="D200" s="33" t="n"/>
+      <c r="E200" s="33" t="n"/>
+      <c r="F200" s="33" t="n"/>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>DAY 11  |  Jun 30  |  The Razor-Edge Peaks — Seceda · Val di Funes · Adolf Munkel Trail  |  ~80 km / 50 mi  ~2h total · Collalbo loop day</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="15" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
+    <row r="202" ht="15" customHeight="1">
+      <c r="A202" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Collalbo ▸ 8:45am Seceda cable car ▸ Trail 1 ridge + Rifugio Firenze lunch ▸ 1pm drive Val di Funes ▸ Santa Maddalena barrier + Panorama Trail ▸ St. Johann Ranui ▸ Zans traffic light ▸ 1:30pm Adolf Munkel Trail 35 ▸ Rifugio Odle lounge chairs ▸ 5:30pm descent ▸ 7pm Collalbo</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="5" t="inlineStr">
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Seceda 8:45am — pre-booked · photos best 9–10:30am before clouds form · razor ridge Trail 1  |   Santa Maddalena 2026 barrier — park at Filler/Putzen lot · walk 25min Panorama Trail · cannot drive up  |   Zans traffic light Red → don't wait · park Ranui immediately + Bus 330 · saves hiking time</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="50" customHeight="1">
-      <c r="A203" s="16" t="inlineStr"/>
-      <c r="B203" s="17" t="inlineStr">
+    <row r="204" ht="50" customHeight="1">
+      <c r="A204" s="16" t="inlineStr"/>
+      <c r="B204" s="17" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C203" s="16" t="inlineStr">
+      <c r="C204" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D203" s="17" t="inlineStr"/>
-      <c r="E203" s="18" t="inlineStr">
+      <c r="D204" s="17" t="inlineStr"/>
+      <c r="E204" s="18" t="inlineStr">
         <is>
           <t>️ Parking at Seceda valley station — no booking needed · €2.80/hr · 250+ spaces · arrive before 9am (your 8:45am slot guarantees this) · if full: Garage Central Ortisei €19.80/day · 10 min walk via La Curta escalator tun</t>
         </is>
       </c>
-      <c r="F203" s="19" t="inlineStr">
+      <c r="F204" s="19" t="inlineStr">
         <is>
           <t>€2.80 / €19.80 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="49" customHeight="1">
-      <c r="A204" s="6" t="inlineStr"/>
-      <c r="B204" s="7" t="inlineStr">
+    <row r="205" ht="49" customHeight="1">
+      <c r="A205" s="6" t="inlineStr"/>
+      <c r="B205" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C204" s="8" t="inlineStr">
+      <c r="C205" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D204" s="7" t="inlineStr"/>
-      <c r="E204" s="9" t="inlineStr">
+      <c r="D205" s="7" t="inlineStr"/>
+      <c r="E205" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 8:45am — Seceda 360 cable car — ✅ Booked · Receipt 1161/678/554260 · €255 total · 2 adults €84.50 + 2 juniors €43 · print tickets before departure · best photos 9–10:30am before clouds</t>
         </is>
       </c>
-      <c r="F204" s="10" t="inlineStr">
+      <c r="F205" s="10" t="inlineStr">
         <is>
           <t>€255 / €84.50 / €43</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="37" customHeight="1">
-      <c r="A205" s="20" t="inlineStr"/>
-      <c r="B205" s="21" t="inlineStr">
+    <row r="206" ht="37" customHeight="1">
+      <c r="A206" s="20" t="inlineStr"/>
+      <c r="B206" s="21" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C205" s="22" t="inlineStr">
+      <c r="C206" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D205" s="21" t="inlineStr"/>
-      <c r="E205" s="23" t="inlineStr">
+      <c r="D206" s="21" t="inlineStr"/>
+      <c r="E206" s="23" t="inlineStr">
         <is>
           <t>Trail 1 — Razor Edge ridge walk — from the cable car top follow Trail 1 to the summit cross · allow 1.5hrs for the ridge walk</t>
         </is>
       </c>
-      <c r="F205" s="24" t="inlineStr">
+      <c r="F206" s="24" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="22" customHeight="1">
-      <c r="A206" s="11" t="inlineStr"/>
-      <c r="B206" s="12" t="inlineStr">
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="11" t="inlineStr"/>
+      <c r="B207" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C206" s="13" t="inlineStr">
+      <c r="C207" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D206" s="12" t="inlineStr"/>
-      <c r="E206" s="14" t="inlineStr">
+      <c r="D207" s="12" t="inlineStr"/>
+      <c r="E207" s="14" t="inlineStr">
         <is>
           <t>Lunch at Rifugio Firenze (2,039m) — allow 45 min</t>
         </is>
       </c>
-      <c r="F206" s="15" t="inlineStr">
+      <c r="F207" s="15" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="38" customHeight="1">
-      <c r="A207" s="6" t="inlineStr"/>
-      <c r="B207" s="7" t="inlineStr">
+    <row r="208" ht="38" customHeight="1">
+      <c r="A208" s="6" t="inlineStr"/>
+      <c r="B208" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C207" s="8" t="inlineStr">
+      <c r="C208" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D207" s="7" t="inlineStr"/>
-      <c r="E207" s="9" t="inlineStr">
+      <c r="D208" s="7" t="inlineStr"/>
+      <c r="E208" s="9" t="inlineStr">
         <is>
           <t>1:00pm — Val di Funes (Santa Maddalena) —  2026 barrier — park Filler/Putzen lots · walk 25 min Panorama Trail · cannot drive up</t>
         </is>
       </c>
-      <c r="F207" s="10" t="inlineStr">
+      <c r="F208" s="10" t="inlineStr">
         <is>
           <t>25 min</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="27" customHeight="1">
-      <c r="A208" s="16" t="inlineStr"/>
-      <c r="B208" s="17" t="inlineStr">
-        <is>
-          <t>Jun 30</t>
-        </is>
-      </c>
-      <c r="C208" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D208" s="17" t="inlineStr"/>
-      <c r="E208" s="18" t="inlineStr">
-        <is>
-          <t>⭐ St. Johann in Ranui — €4 turnstile for meadow access · card only · 15 min</t>
-        </is>
-      </c>
-      <c r="F208" s="19" t="inlineStr">
-        <is>
-          <t>€4 / 15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="31" customHeight="1">
+    <row r="209" ht="27" customHeight="1">
       <c r="A209" s="16" t="inlineStr"/>
       <c r="B209" s="17" t="inlineStr">
         <is>
@@ -4745,120 +4745,120 @@
       <c r="D209" s="17" t="inlineStr"/>
       <c r="E209" s="18" t="inlineStr">
         <is>
+          <t>⭐ St. Johann in Ranui — €4 turnstile for meadow access · card only · 15 min</t>
+        </is>
+      </c>
+      <c r="F209" s="19" t="inlineStr">
+        <is>
+          <t>€4 / 15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="31" customHeight="1">
+      <c r="A210" s="16" t="inlineStr"/>
+      <c r="B210" s="17" t="inlineStr">
+        <is>
+          <t>Jun 30</t>
+        </is>
+      </c>
+      <c r="C210" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D210" s="17" t="inlineStr"/>
+      <c r="E210" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ Santa Maddalena viewpoint — most photographed scene in South Tyrol · best light: late afternoon</t>
         </is>
       </c>
-      <c r="F209" s="19" t="inlineStr"/>
-    </row>
-    <row r="210" ht="29" customHeight="1">
-      <c r="A210" s="6" t="inlineStr"/>
-      <c r="B210" s="7" t="inlineStr">
+      <c r="F210" s="19" t="inlineStr"/>
+    </row>
+    <row r="211" ht="29" customHeight="1">
+      <c r="A211" s="6" t="inlineStr"/>
+      <c r="B211" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C210" s="8" t="inlineStr">
+      <c r="C211" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D210" s="7" t="inlineStr"/>
-      <c r="E210" s="9" t="inlineStr">
+      <c r="D211" s="7" t="inlineStr"/>
+      <c r="E211" s="9" t="inlineStr">
         <is>
           <t>⚠️ Zans traffic light —  Green = drive up ·  Red = park Ranui + Bus 330 · don't wait</t>
         </is>
       </c>
-      <c r="F210" s="10" t="inlineStr"/>
-    </row>
-    <row r="211" ht="33" customHeight="1">
-      <c r="A211" s="20" t="inlineStr"/>
-      <c r="B211" s="21" t="inlineStr">
+      <c r="F211" s="10" t="inlineStr"/>
+    </row>
+    <row r="212" ht="33" customHeight="1">
+      <c r="A212" s="20" t="inlineStr"/>
+      <c r="B212" s="21" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C211" s="22" t="inlineStr">
+      <c r="C212" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D211" s="21" t="inlineStr"/>
-      <c r="E211" s="23" t="inlineStr">
+      <c r="D212" s="21" t="inlineStr"/>
+      <c r="E212" s="23" t="inlineStr">
         <is>
           <t>1:30pm — Adolf Munkel Trail 35 — from Parkplatz Zanser Alm (Zannes) trailhead · Trail 35 (Via delle Odle)</t>
         </is>
       </c>
-      <c r="F211" s="24" t="inlineStr"/>
-    </row>
-    <row r="212" ht="38" customHeight="1">
-      <c r="A212" s="11" t="inlineStr"/>
-      <c r="B212" s="12" t="inlineStr">
+      <c r="F212" s="24" t="inlineStr"/>
+    </row>
+    <row r="213" ht="38" customHeight="1">
+      <c r="A213" s="11" t="inlineStr"/>
+      <c r="B213" s="12" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C212" s="13" t="inlineStr">
+      <c r="C213" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D212" s="12" t="inlineStr"/>
-      <c r="E212" s="14" t="inlineStr">
+      <c r="D213" s="12" t="inlineStr"/>
+      <c r="E213" s="14" t="inlineStr">
         <is>
           <t>⭐ ⭐ Rifugio Odle / Geisler Alm (1,986m) — the Cinema of the Odle — the best seats in the Dolomites · cash is faster but cards accepted</t>
         </is>
       </c>
-      <c r="F212" s="15" t="inlineStr"/>
-    </row>
-    <row r="213" ht="36" customHeight="1">
-      <c r="A213" s="6" t="inlineStr"/>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="F213" s="15" t="inlineStr"/>
+    </row>
+    <row r="214" ht="36" customHeight="1">
+      <c r="A214" s="6" t="inlineStr"/>
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t>Jun 30</t>
         </is>
       </c>
-      <c r="C213" s="8" t="inlineStr">
+      <c r="C214" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D213" s="7" t="inlineStr"/>
-      <c r="E213" s="9" t="inlineStr">
+      <c r="D214" s="7" t="inlineStr"/>
+      <c r="E214" s="9" t="inlineStr">
         <is>
           <t>5:30pm — Descent to Zannes car park — ~1hr back down · same trail · arrive Zannes ~6:30pm · drive 50 min back to Collalbo</t>
         </is>
       </c>
-      <c r="F213" s="10" t="inlineStr">
+      <c r="F214" s="10" t="inlineStr">
         <is>
           <t>~1hr / 50 min</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="29" customHeight="1">
-      <c r="A214" s="25" t="inlineStr"/>
-      <c r="B214" s="26" t="inlineStr">
-        <is>
-          <t>Jun 30</t>
-        </is>
-      </c>
-      <c r="C214" s="27" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D214" s="26" t="inlineStr"/>
-      <c r="E214" s="28" t="inlineStr">
-        <is>
-          <t>⭐ Renon Earth Pyramids — evening walk — ➕ Optional if energy allows · 5 min from hotel</t>
-        </is>
-      </c>
-      <c r="F214" s="29" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="19" customHeight="1">
+    <row r="215" ht="29" customHeight="1">
       <c r="A215" s="25" t="inlineStr"/>
       <c r="B215" s="26" t="inlineStr">
         <is>
@@ -4873,25 +4873,36 @@
       <c r="D215" s="26" t="inlineStr"/>
       <c r="E215" s="28" t="inlineStr">
         <is>
+          <t>⭐ Renon Earth Pyramids — evening walk — ➕ Optional if energy allows · 5 min from hotel</t>
+        </is>
+      </c>
+      <c r="F215" s="29" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="19" customHeight="1">
+      <c r="A216" s="25" t="inlineStr"/>
+      <c r="B216" s="26" t="inlineStr">
+        <is>
+          <t>Jun 30</t>
+        </is>
+      </c>
+      <c r="C216" s="27" t="inlineStr">
+        <is>
+          <t>Stay</t>
+        </is>
+      </c>
+      <c r="D216" s="26" t="inlineStr"/>
+      <c r="E216" s="28" t="inlineStr">
+        <is>
           <t>Night 2 — Kaiserau 1907, Collalbo</t>
         </is>
       </c>
-      <c r="F215" s="29" t="inlineStr"/>
-    </row>
-    <row r="216" ht="34" customHeight="1">
-      <c r="A216" s="30" t="inlineStr"/>
-      <c r="B216" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C216" s="32" t="inlineStr">
-        <is>
-          <t>Santa Maddalena 2026 barrier — physical barrier blocks non-resident cars since May 2026 · park Filler or Putzen lots in village · follow Panorama Trail signs · 25 min uphill walk to the viewpoint · you can no longer drive to the famous phot</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="30" customHeight="1">
+      <c r="F216" s="29" t="inlineStr"/>
+    </row>
+    <row r="217" ht="34" customHeight="1">
       <c r="A217" s="30" t="inlineStr"/>
       <c r="B217" s="31" t="inlineStr">
         <is>
@@ -4900,11 +4911,11 @@
       </c>
       <c r="C217" s="32" t="inlineStr">
         <is>
-          <t>Zans traffic light 2026 — Green = drive up · Red = park at Ranui immediately + Bus 330 every 30–60 min · do not wait at the gate — bus is faster</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="34" customHeight="1">
+          <t>Santa Maddalena 2026 barrier — physical barrier blocks non-resident cars since May 2026 · park Filler or Putzen lots in village · follow Panorama Trail signs · 25 min uphill walk to the viewpoint · you can no longer drive to the famous phot</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="30" customHeight="1">
       <c r="A218" s="30" t="inlineStr"/>
       <c r="B218" s="31" t="inlineStr">
         <is>
@@ -4913,112 +4924,101 @@
       </c>
       <c r="C218" s="32" t="inlineStr">
         <is>
+          <t>Zans traffic light 2026 — Green = drive up · Red = park at Ranui immediately + Bus 330 every 30–60 min · do not wait at the gate — bus is faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="34" customHeight="1">
+      <c r="A219" s="30" t="inlineStr"/>
+      <c r="B219" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C219" s="32" t="inlineStr">
+        <is>
           <t>Photography windows — Seceda ridge: 9:00–10:30am before clouds form · Santa Maddalena viewpoint: late afternoon — sun behind you · Odle peaks lit directly · morning light hits the wrong side of the peaks</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="3" customHeight="1">
-      <c r="A219" s="33" t="n"/>
-      <c r="B219" s="33" t="n"/>
-      <c r="C219" s="33" t="n"/>
-      <c r="D219" s="33" t="n"/>
-      <c r="E219" s="33" t="n"/>
-      <c r="F219" s="33" t="n"/>
-    </row>
-    <row r="220" ht="20" customHeight="1">
-      <c r="A220" s="3" t="inlineStr">
+    <row r="220" ht="3" customHeight="1">
+      <c r="A220" s="33" t="n"/>
+      <c r="B220" s="33" t="n"/>
+      <c r="C220" s="33" t="n"/>
+      <c r="D220" s="33" t="n"/>
+      <c r="E220" s="33" t="n"/>
+      <c r="F220" s="33" t="n"/>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="3" t="inlineStr">
         <is>
           <t>DAY 12  |  Jul 1  |  Alpe di Siusi + Brenner Pass → Finkenberg — The Plateau &amp; The Pass  |  ~120 km / 75 mi  ~1h 45m · Collalbo → Finkenberg via Brenner</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="15" customHeight="1">
-      <c r="A221" s="4" t="inlineStr">
+    <row r="222" ht="15" customHeight="1">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t>Timeline: 7:45am Collalbo ▸ 8:30am St. Valentin gate (must be before 9am) ▸ 8:45am P2 Compatsch ▸ 9:15am Bullaccia loop ▸ Hexenbänke viewpoint ▸ 12pm Tschötsch Alm lunch ▸ 1:30pm depart ▸ Brenner construction ▸ M-Preis Mayrhofen ▸ 4:30pm Keyone Rooms Finkenberg</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="22" customHeight="1">
-      <c r="A222" s="5" t="inlineStr">
+    <row r="223" ht="22" customHeight="1">
+      <c r="A223" s="5" t="inlineStr">
         <is>
           <t>Key: ️ Plan A: P2 Compatsch — keep checking seiseralm.it for cancellations · must arrive before 9am · €30  |   Plan B: Seis cable car → Compatsch — park in Seis · ~€30/adult RT · no booking · no 9am rule · same trailhead  |   St. Valentin gate closes 9:00am SHARP — leave Collalbo 7:45am · arrive 8:30am · no exceptions  |  ❌ Skip Rifugio Zallinger — 4hr RT or 2 extra lifts · impractical · eat at Tschötsch Alm instead  |  ⚠️ Brenner Lueg Bridge construction 2026 — 30–45 min delay · Digital Flex toll essential</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="40" customHeight="1">
-      <c r="A223" s="6" t="inlineStr"/>
-      <c r="B223" s="7" t="inlineStr">
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" s="6" t="inlineStr"/>
+      <c r="B224" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C223" s="8" t="inlineStr">
+      <c r="C224" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D223" s="7" t="inlineStr"/>
-      <c r="E223" s="9" t="inlineStr">
+      <c r="D224" s="7" t="inlineStr"/>
+      <c r="E224" s="9" t="inlineStr">
         <is>
           <t>⏰ 7:45am — Depart Collalbo — 40 min drive to the Alpe di Siusi St. Valentin gate · checkout Kaiserau 1907 before leaving · luggage in the car</t>
         </is>
       </c>
-      <c r="F223" s="10" t="inlineStr">
+      <c r="F224" s="10" t="inlineStr">
         <is>
           <t>40 min</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="31" customHeight="1">
-      <c r="A224" s="34" t="inlineStr"/>
-      <c r="B224" s="35" t="inlineStr">
+    <row r="225" ht="31" customHeight="1">
+      <c r="A225" s="34" t="inlineStr"/>
+      <c r="B225" s="35" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C224" s="36" t="inlineStr">
+      <c r="C225" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D224" s="35" t="inlineStr"/>
-      <c r="E224" s="37" t="inlineStr">
+      <c r="D225" s="35" t="inlineStr"/>
+      <c r="E225" s="37" t="inlineStr">
         <is>
           <t>⚠️ CRITICAL: St. Valentin Gate — before 9:00am — 9:01am = turned back · €120+ cable car alternative</t>
         </is>
       </c>
-      <c r="F224" s="38" t="inlineStr">
+      <c r="F225" s="38" t="inlineStr">
         <is>
           <t>€120</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="50" customHeight="1">
-      <c r="A225" s="20" t="inlineStr"/>
-      <c r="B225" s="21" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C225" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D225" s="21" t="inlineStr"/>
-      <c r="E225" s="23" t="inlineStr">
-        <is>
-          <t>P2 Compatsch parking — ⚠️ Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · €30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch ca</t>
-        </is>
-      </c>
-      <c r="F225" s="24" t="inlineStr">
-        <is>
-          <t>€30 / €30 / €65</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="34" customHeight="1">
+    <row r="226" ht="50" customHeight="1">
       <c r="A226" s="20" t="inlineStr"/>
       <c r="B226" s="21" t="inlineStr">
         <is>
@@ -5033,12 +5033,16 @@
       <c r="D226" s="21" t="inlineStr"/>
       <c r="E226" s="23" t="inlineStr">
         <is>
-          <t>9:15am — Bullaccia (Puflatsch) Loop — take the Telemix lift up from Compatsch · Trail PU (Puflatschumrundung)</t>
-        </is>
-      </c>
-      <c r="F226" s="24" t="inlineStr"/>
-    </row>
-    <row r="227" ht="23" customHeight="1">
+          <t>P2 Compatsch parking — ⚠️ Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · €30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch ca</t>
+        </is>
+      </c>
+      <c r="F226" s="24" t="inlineStr">
+        <is>
+          <t>€30 / €30 / €65</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="34" customHeight="1">
       <c r="A227" s="20" t="inlineStr"/>
       <c r="B227" s="21" t="inlineStr">
         <is>
@@ -5053,80 +5057,76 @@
       <c r="D227" s="21" t="inlineStr"/>
       <c r="E227" s="23" t="inlineStr">
         <is>
+          <t>9:15am — Bullaccia (Puflatsch) Loop — take the Telemix lift up from Compatsch · Trail PU (Puflatschumrundung)</t>
+        </is>
+      </c>
+      <c r="F227" s="24" t="inlineStr"/>
+    </row>
+    <row r="228" ht="23" customHeight="1">
+      <c r="A228" s="20" t="inlineStr"/>
+      <c r="B228" s="21" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C228" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D228" s="21" t="inlineStr"/>
+      <c r="E228" s="23" t="inlineStr">
+        <is>
           <t>⭐ Hexenbänke — Witches' Benches — signed from the trail</t>
         </is>
       </c>
-      <c r="F227" s="24" t="inlineStr"/>
-    </row>
-    <row r="228" ht="31" customHeight="1">
-      <c r="A228" s="11" t="inlineStr"/>
-      <c r="B228" s="12" t="inlineStr">
+      <c r="F228" s="24" t="inlineStr"/>
+    </row>
+    <row r="229" ht="31" customHeight="1">
+      <c r="A229" s="11" t="inlineStr"/>
+      <c r="B229" s="12" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C228" s="13" t="inlineStr">
+      <c r="C229" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D228" s="12" t="inlineStr"/>
-      <c r="E228" s="14" t="inlineStr">
+      <c r="D229" s="12" t="inlineStr"/>
+      <c r="E229" s="14" t="inlineStr">
         <is>
           <t>️ 12:00pm — Lunch: Tschötsch Alm or Arnika Hütte — ⚠️ Do NOT go to Rifugio Zallinger — allow 1hr</t>
         </is>
       </c>
-      <c r="F228" s="15" t="inlineStr">
+      <c r="F229" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="27" customHeight="1">
-      <c r="A229" s="6" t="inlineStr"/>
-      <c r="B229" s="7" t="inlineStr">
+    <row r="230" ht="27" customHeight="1">
+      <c r="A230" s="6" t="inlineStr"/>
+      <c r="B230" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C229" s="8" t="inlineStr">
+      <c r="C230" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D229" s="7" t="inlineStr"/>
-      <c r="E229" s="9" t="inlineStr">
+      <c r="D230" s="7" t="inlineStr"/>
+      <c r="E230" s="9" t="inlineStr">
         <is>
           <t>1:30pm — Depart Alpe di Siusi — unrestricted descent · head north to Brenner</t>
         </is>
       </c>
-      <c r="F229" s="10" t="inlineStr"/>
-    </row>
-    <row r="230" ht="50" customHeight="1">
-      <c r="A230" s="16" t="inlineStr"/>
-      <c r="B230" s="17" t="inlineStr">
-        <is>
-          <t>Jul 1</t>
-        </is>
-      </c>
-      <c r="C230" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D230" s="17" t="inlineStr"/>
-      <c r="E230" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ Brenner Pass — Lueg Bridge construction — 30–45 min delay expected · Digital Flex toll green lanes · €11.50 · ➡️ If standstill at A22/A13 toll plaza: take B182 Brenner Route Nationale — free state road running paralle</t>
-        </is>
-      </c>
-      <c r="F230" s="19" t="inlineStr">
-        <is>
-          <t>45 min / €11.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="18" customHeight="1">
+      <c r="F230" s="10" t="inlineStr"/>
+    </row>
+    <row r="231" ht="50" customHeight="1">
       <c r="A231" s="16" t="inlineStr"/>
       <c r="B231" s="17" t="inlineStr">
         <is>
@@ -5141,93 +5141,104 @@
       <c r="D231" s="17" t="inlineStr"/>
       <c r="E231" s="18" t="inlineStr">
         <is>
+          <t>⚠️ Brenner Pass — Lueg Bridge construction — 30–45 min delay expected · Digital Flex toll green lanes · €11.50 · ➡️ If standstill at A22/A13 toll plaza: take B182 Brenner Route Nationale — free state road running paralle</t>
+        </is>
+      </c>
+      <c r="F231" s="19" t="inlineStr">
+        <is>
+          <t>45 min / €11.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="16" t="inlineStr"/>
+      <c r="B232" s="17" t="inlineStr">
+        <is>
+          <t>Jul 1</t>
+        </is>
+      </c>
+      <c r="C232" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D232" s="17" t="inlineStr"/>
+      <c r="E232" s="18" t="inlineStr">
+        <is>
           <t>Austrian vignette still valid?</t>
         </is>
       </c>
-      <c r="F231" s="19" t="inlineStr"/>
-    </row>
-    <row r="232" ht="35" customHeight="1">
-      <c r="A232" s="11" t="inlineStr"/>
-      <c r="B232" s="12" t="inlineStr">
+      <c r="F232" s="19" t="inlineStr"/>
+    </row>
+    <row r="233" ht="35" customHeight="1">
+      <c r="A233" s="11" t="inlineStr"/>
+      <c r="B233" s="12" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C232" s="13" t="inlineStr">
+      <c r="C233" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D232" s="12" t="inlineStr"/>
-      <c r="E232" s="14" t="inlineStr">
+      <c r="D233" s="12" t="inlineStr"/>
+      <c r="E233" s="14" t="inlineStr">
         <is>
           <t>M-Preis Supermarket, Mayrhofen — Finkenberg is up a winding road — nothing open nearby in the evening · allow 20 min</t>
         </is>
       </c>
-      <c r="F232" s="15" t="inlineStr">
+      <c r="F233" s="15" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="34" customHeight="1">
-      <c r="A233" s="16" t="inlineStr"/>
-      <c r="B233" s="17" t="inlineStr">
+    <row r="234" ht="34" customHeight="1">
+      <c r="A234" s="16" t="inlineStr"/>
+      <c r="B234" s="17" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C233" s="16" t="inlineStr">
+      <c r="C234" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D233" s="17" t="inlineStr"/>
-      <c r="E233" s="18" t="inlineStr">
+      <c r="D234" s="17" t="inlineStr"/>
+      <c r="E234" s="18" t="inlineStr">
         <is>
           <t>4:30pm — Keyone Rooms, Finkenberg — $176 / €152.92 · ⚠️ Driveway can be steep — take it slowly on the approach</t>
         </is>
       </c>
-      <c r="F233" s="19" t="inlineStr">
+      <c r="F234" s="19" t="inlineStr">
         <is>
           <t>$176 / €152.92</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="29" customHeight="1">
-      <c r="A234" s="6" t="inlineStr"/>
-      <c r="B234" s="7" t="inlineStr">
+    <row r="235" ht="29" customHeight="1">
+      <c r="A235" s="6" t="inlineStr"/>
+      <c r="B235" s="7" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C234" s="8" t="inlineStr">
+      <c r="C235" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D234" s="7" t="inlineStr"/>
-      <c r="E234" s="9" t="inlineStr">
+      <c r="D235" s="7" t="inlineStr"/>
+      <c r="E235" s="9" t="inlineStr">
         <is>
           <t>Dinner in Finkenberg or Mayrhofen — or drive 5 min down to Mayrhofen for more options</t>
         </is>
       </c>
-      <c r="F234" s="10" t="inlineStr">
+      <c r="F235" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="34" customHeight="1">
-      <c r="A235" s="30" t="inlineStr"/>
-      <c r="B235" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C235" s="32" t="inlineStr">
-        <is>
-          <t>9:00am St. Valentin gate — non-negotiable — electronic barrier closes to private cars at exactly 9am · 9:01am = turned back · €120+ family cable car alternative · leave Collalbo by 7:45am</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5251,7 @@
       </c>
       <c r="C236" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Brenner Lueg Bridge 2026 — single-lane renovation · 30–45 min delay expected · Digital Flex toll at autobrennero.it · €11.50 · green Video Toll lanes · saves 1hr vs manual queue</t>
+          <t>9:00am St. Valentin gate — non-negotiable — electronic barrier closes to private cars at exactly 9am · 9:01am = turned back · €120+ family cable car alternative · leave Collalbo by 7:45am</t>
         </is>
       </c>
     </row>
@@ -5253,11 +5264,11 @@
       </c>
       <c r="C237" s="32" t="inlineStr">
         <is>
-          <t>Hexenbänke — Witches' Benches — giant stone formations on the Bullaccia ridge · highest point of the plateau · best 360° photo spot · signed from the trail · kids love the legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="32" customHeight="1">
+          <t>⚠️ Brenner Lueg Bridge 2026 — single-lane renovation · 30–45 min delay expected · Digital Flex toll at autobrennero.it · €11.50 · green Video Toll lanes · saves 1hr vs manual queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="34" customHeight="1">
       <c r="A238" s="30" t="inlineStr"/>
       <c r="B238" s="31" t="inlineStr">
         <is>
@@ -5266,333 +5277,333 @@
       </c>
       <c r="C238" s="32" t="inlineStr">
         <is>
+          <t>Hexenbänke — Witches' Benches — giant stone formations on the Bullaccia ridge · highest point of the plateau · best 360° photo spot · signed from the trail · kids love the legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="32" customHeight="1">
+      <c r="A239" s="30" t="inlineStr"/>
+      <c r="B239" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C239" s="32" t="inlineStr">
+        <is>
           <t>M-Preis Mayrhofen — stop before Finkenberg · buy breakfast for Day 13 · nothing open near Keyone in evenings · steep winding road to Finkenberg — take slowly</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="3" customHeight="1">
-      <c r="A239" s="33" t="n"/>
-      <c r="B239" s="33" t="n"/>
-      <c r="C239" s="33" t="n"/>
-      <c r="D239" s="33" t="n"/>
-      <c r="E239" s="33" t="n"/>
-      <c r="F239" s="33" t="n"/>
-    </row>
-    <row r="240" ht="20" customHeight="1">
-      <c r="A240" s="3" t="inlineStr">
+    <row r="240" ht="3" customHeight="1">
+      <c r="A240" s="33" t="n"/>
+      <c r="B240" s="33" t="n"/>
+      <c r="C240" s="33" t="n"/>
+      <c r="D240" s="33" t="n"/>
+      <c r="E240" s="33" t="n"/>
+      <c r="F240" s="33" t="n"/>
+    </row>
+    <row r="241" ht="20" customHeight="1">
+      <c r="A241" s="3" t="inlineStr">
         <is>
           <t>DAY 13  |  Jul 2  |  High Bridges &amp; Deep Lakes — Olpererhütte · Achensee · Swarovski → Bichlbach  |  ~150 km / 93 mi  ~2h 30m incl. Achensee + Swarovski stops</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="15" customHeight="1">
-      <c r="A241" s="4" t="inlineStr">
+    <row r="242" ht="15" customHeight="1">
+      <c r="A242" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8am Finkenberg ▸ 8:30am Schlegeis toll €17 ▸ 9am Olpererhütte hike ▸ 10:30am Kebema bridge ▸ 11am lunch ▸ 1:30pm descent ▸ Swarovski (if rain) ▸ Achensee optional ▸ Fern Pass ▸ 7:30pm Bichlbach ▸ Heiterwanger See sunset</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="22" customHeight="1">
-      <c r="A242" s="5" t="inlineStr">
+    <row r="243" ht="22" customHeight="1">
+      <c r="A243" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Arrive dam by 8:45am — reach Kebema bridge 10:30am · beats 45min photo queue by midday  |  ☀️ Plan A (sunny): Achensee — steamboat ~€22/adult OR free Gaisalm promenade walk if kids tired  |  ️ Plan B (rain/cloudy): Swarovski Crystal Worlds — 5min off A12 · ~€22/adult · no booking needed</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="31" customHeight="1">
-      <c r="A243" s="6" t="inlineStr"/>
-      <c r="B243" s="7" t="inlineStr">
+    <row r="244" ht="31" customHeight="1">
+      <c r="A244" s="6" t="inlineStr"/>
+      <c r="B244" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C243" s="8" t="inlineStr">
+      <c r="C244" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D243" s="7" t="inlineStr"/>
-      <c r="E243" s="9" t="inlineStr">
+      <c r="D244" s="7" t="inlineStr"/>
+      <c r="E244" s="9" t="inlineStr">
         <is>
           <t>⏰ 8:00am — Depart Finkenberg — 20 min to Schlegeis · ⚠️ tunnel traffic lights = up to 15 min wait</t>
         </is>
       </c>
-      <c r="F243" s="10" t="inlineStr">
+      <c r="F244" s="10" t="inlineStr">
         <is>
           <t>20 min / 15 min</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="27" customHeight="1">
-      <c r="A244" s="16" t="inlineStr"/>
-      <c r="B244" s="17" t="inlineStr">
+    <row r="245" ht="27" customHeight="1">
+      <c r="A245" s="16" t="inlineStr"/>
+      <c r="B245" s="17" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C244" s="16" t="inlineStr">
+      <c r="C245" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D244" s="17" t="inlineStr"/>
-      <c r="E244" s="18" t="inlineStr">
+      <c r="D245" s="17" t="inlineStr"/>
+      <c r="E245" s="18" t="inlineStr">
         <is>
           <t>8:30am — Schlegeis Alpine Road toll — €17 · pay at the gate (cash or card)</t>
         </is>
       </c>
-      <c r="F244" s="19" t="inlineStr">
+      <c r="F245" s="19" t="inlineStr">
         <is>
           <t>€17</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="29" customHeight="1">
-      <c r="A245" s="20" t="inlineStr"/>
-      <c r="B245" s="21" t="inlineStr">
+    <row r="246" ht="29" customHeight="1">
+      <c r="A246" s="20" t="inlineStr"/>
+      <c r="B246" s="21" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C245" s="22" t="inlineStr">
+      <c r="C246" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D245" s="21" t="inlineStr"/>
-      <c r="E245" s="23" t="inlineStr">
+      <c r="D246" s="21" t="inlineStr"/>
+      <c r="E246" s="23" t="inlineStr">
         <is>
           <t>9:00am — Olpererhütte Hike (Trail 502) — 3km / 1.9mi each way · well-maintained trail</t>
         </is>
       </c>
-      <c r="F245" s="24" t="inlineStr">
+      <c r="F246" s="24" t="inlineStr">
         <is>
           <t>3km</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="41" customHeight="1">
-      <c r="A246" s="16" t="inlineStr"/>
-      <c r="B246" s="17" t="inlineStr">
+    <row r="247" ht="41" customHeight="1">
+      <c r="A247" s="16" t="inlineStr"/>
+      <c r="B247" s="17" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C246" s="16" t="inlineStr">
+      <c r="C247" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D246" s="17" t="inlineStr"/>
-      <c r="E246" s="18" t="inlineStr">
+      <c r="D247" s="17" t="inlineStr"/>
+      <c r="E247" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 10:30am — Kebema Suspension Bridge (Olperer Panoramabrücke) — 3–4 min past the hut · floats in mid-air above the turquoise reservoir 600m below</t>
         </is>
       </c>
-      <c r="F246" s="19" t="inlineStr">
+      <c r="F247" s="19" t="inlineStr">
         <is>
           <t>4 min</t>
         </is>
       </c>
     </row>
-    <row r="247" ht="36" customHeight="1">
-      <c r="A247" s="11" t="inlineStr"/>
-      <c r="B247" s="12" t="inlineStr">
+    <row r="248" ht="36" customHeight="1">
+      <c r="A248" s="11" t="inlineStr"/>
+      <c r="B248" s="12" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C247" s="13" t="inlineStr">
+      <c r="C248" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D247" s="12" t="inlineStr"/>
-      <c r="E247" s="14" t="inlineStr">
+      <c r="D248" s="12" t="inlineStr"/>
+      <c r="E248" s="14" t="inlineStr">
         <is>
           <t>️ 11:00am — Lunch at Olpererhütte — cash preferred (but Wi-Fi available — check your Neuschwanstein booking!) · allow 1hr</t>
         </is>
       </c>
-      <c r="F247" s="15" t="inlineStr">
+      <c r="F248" s="15" t="inlineStr">
         <is>
           <t>1hr</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="35" customHeight="1">
-      <c r="A248" s="20" t="inlineStr"/>
-      <c r="B248" s="21" t="inlineStr">
+    <row r="249" ht="35" customHeight="1">
+      <c r="A249" s="20" t="inlineStr"/>
+      <c r="B249" s="21" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C248" s="22" t="inlineStr">
+      <c r="C249" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D248" s="21" t="inlineStr"/>
-      <c r="E248" s="23" t="inlineStr">
+      <c r="D249" s="21" t="inlineStr"/>
+      <c r="E249" s="23" t="inlineStr">
         <is>
           <t>1:30pm — Descent to the dam — ~1hr back down same trail · easier on the knees than going up · back at car ~2:30pm</t>
         </is>
       </c>
-      <c r="F248" s="24" t="inlineStr">
+      <c r="F249" s="24" t="inlineStr">
         <is>
           <t>~1hr</t>
         </is>
       </c>
     </row>
-    <row r="249" ht="50" customHeight="1">
-      <c r="A249" s="6" t="inlineStr"/>
-      <c r="B249" s="7" t="inlineStr">
+    <row r="250" ht="50" customHeight="1">
+      <c r="A250" s="6" t="inlineStr"/>
+      <c r="B250" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C249" s="8" t="inlineStr">
+      <c r="C250" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D249" s="7" t="inlineStr"/>
-      <c r="E249" s="9" t="inlineStr">
+      <c r="D250" s="7" t="inlineStr"/>
+      <c r="E250" s="9" t="inlineStr">
         <is>
           <t>☀️ Plan A — Sunny: Achensee — 50 min drive north from Schlegeis · park at Pertisau · Option 1: Achensee steamboat ~€22/adult · allow 1.5hrs · Option 2 (kids tired): Gaisalm promenade walk — free · same fjord-like views ·</t>
         </is>
       </c>
-      <c r="F249" s="10" t="inlineStr">
+      <c r="F250" s="10" t="inlineStr">
         <is>
           <t>50 min / €22 / 5hr</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="50" customHeight="1">
-      <c r="A250" s="20" t="inlineStr"/>
-      <c r="B250" s="21" t="inlineStr">
+    <row r="251" ht="50" customHeight="1">
+      <c r="A251" s="20" t="inlineStr"/>
+      <c r="B251" s="21" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C250" s="22" t="inlineStr">
+      <c r="C251" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D250" s="21" t="inlineStr"/>
-      <c r="E250" s="23" t="inlineStr">
+      <c r="D251" s="21" t="inlineStr"/>
+      <c r="E251" s="23" t="inlineStr">
         <is>
           <t>️ Plan B — Rain/Cloudy: Swarovski Crystal Worlds — 5 min off A12 at Wattens · ~€22/adult · allow 1.5–2hrs · indoor immersive art installation · perfect rainy-day refuge after cold wet Olpererhütte hike · no booking neede</t>
         </is>
       </c>
-      <c r="F250" s="24" t="inlineStr">
+      <c r="F251" s="24" t="inlineStr">
         <is>
           <t>5 min / €22 / 2hr</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="29" customHeight="1">
-      <c r="A251" s="6" t="inlineStr"/>
-      <c r="B251" s="7" t="inlineStr">
+    <row r="252" ht="29" customHeight="1">
+      <c r="A252" s="6" t="inlineStr"/>
+      <c r="B252" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C251" s="8" t="inlineStr">
+      <c r="C252" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D251" s="7" t="inlineStr"/>
-      <c r="E251" s="9" t="inlineStr">
+      <c r="D252" s="7" t="inlineStr"/>
+      <c r="E252" s="9" t="inlineStr">
         <is>
           <t>⚠️ Fern Pass warning on drive to Bichlbach — village Gasthäuser are relaxed about timing</t>
         </is>
       </c>
-      <c r="F251" s="10" t="inlineStr"/>
-    </row>
-    <row r="252" ht="33" customHeight="1">
-      <c r="A252" s="25" t="inlineStr"/>
-      <c r="B252" s="26" t="inlineStr">
+      <c r="F252" s="10" t="inlineStr"/>
+    </row>
+    <row r="253" ht="33" customHeight="1">
+      <c r="A253" s="25" t="inlineStr"/>
+      <c r="B253" s="26" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C252" s="27" t="inlineStr">
+      <c r="C253" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D252" s="26" t="inlineStr"/>
-      <c r="E252" s="28" t="inlineStr">
+      <c r="D253" s="26" t="inlineStr"/>
+      <c r="E253" s="28" t="inlineStr">
         <is>
           <t>~7:30pm — Landhaus Bichlbach — $467 / €405 · Heiterwanger See lake is a 20 min evening walk from the hotel</t>
         </is>
       </c>
-      <c r="F252" s="29" t="inlineStr">
+      <c r="F253" s="29" t="inlineStr">
         <is>
           <t>$467 / €405 / 20 min</t>
         </is>
       </c>
     </row>
-    <row r="253" ht="28" customHeight="1">
-      <c r="A253" s="16" t="inlineStr"/>
-      <c r="B253" s="17" t="inlineStr">
+    <row r="254" ht="28" customHeight="1">
+      <c r="A254" s="16" t="inlineStr"/>
+      <c r="B254" s="17" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C253" s="16" t="inlineStr">
+      <c r="C254" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D253" s="17" t="inlineStr"/>
-      <c r="E253" s="18" t="inlineStr">
+      <c r="D254" s="17" t="inlineStr"/>
+      <c r="E254" s="18" t="inlineStr">
         <is>
           <t>⭐ Heiterwanger See sunset walk — easy 20 min walk from Landhaus along Panoramaweg</t>
         </is>
       </c>
-      <c r="F253" s="19" t="inlineStr">
+      <c r="F254" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="25" customHeight="1">
-      <c r="A254" s="6" t="inlineStr"/>
-      <c r="B254" s="7" t="inlineStr">
+    <row r="255" ht="25" customHeight="1">
+      <c r="A255" s="6" t="inlineStr"/>
+      <c r="B255" s="7" t="inlineStr">
         <is>
           <t>Jul 2</t>
         </is>
       </c>
-      <c r="C254" s="8" t="inlineStr">
+      <c r="C255" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D254" s="7" t="inlineStr"/>
-      <c r="E254" s="9" t="inlineStr">
+      <c r="D255" s="7" t="inlineStr"/>
+      <c r="E255" s="9" t="inlineStr">
         <is>
           <t>Dinner + pack bags — Gasthof Bichlbach · checkout 8am · alarm 7am</t>
         </is>
       </c>
-      <c r="F254" s="10" t="inlineStr"/>
-    </row>
-    <row r="255" ht="32" customHeight="1">
-      <c r="A255" s="30" t="inlineStr"/>
-      <c r="B255" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C255" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Schlegeis tunnel traffic lights — one-way sections · red light = up to 15 min wait · factor into morning timing · aim to be at the dam car park by 8:45am</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="34" customHeight="1">
+      <c r="F255" s="10" t="inlineStr"/>
+    </row>
+    <row r="256" ht="32" customHeight="1">
       <c r="A256" s="30" t="inlineStr"/>
       <c r="B256" s="31" t="inlineStr">
         <is>
@@ -5601,11 +5612,11 @@
       </c>
       <c r="C256" s="32" t="inlineStr">
         <is>
-          <t>⚠️ Fern Pass congestion 2026 — slow trucks · one of the most congested alpine roads · flexible dinner only — no reservations · Bichlbach Gasthäuser are relaxed about timing</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="32" customHeight="1">
+          <t>⚠️ Schlegeis tunnel traffic lights — one-way sections · red light = up to 15 min wait · factor into morning timing · aim to be at the dam car park by 8:45am</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="34" customHeight="1">
       <c r="A257" s="30" t="inlineStr"/>
       <c r="B257" s="31" t="inlineStr">
         <is>
@@ -5614,11 +5625,11 @@
       </c>
       <c r="C257" s="32" t="inlineStr">
         <is>
-          <t>At Olpererhütte: check Neuschwanstein booking — the hut has excellent Wi-Fi · confirm your 9:30am slot for tomorrow · cash preferred for food but cards accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="34" customHeight="1">
+          <t>⚠️ Fern Pass congestion 2026 — slow trucks · one of the most congested alpine roads · flexible dinner only — no reservations · Bichlbach Gasthäuser are relaxed about timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="32" customHeight="1">
       <c r="A258" s="30" t="inlineStr"/>
       <c r="B258" s="31" t="inlineStr">
         <is>
@@ -5627,309 +5638,309 @@
       </c>
       <c r="C258" s="32" t="inlineStr">
         <is>
+          <t>At Olpererhütte: check Neuschwanstein booking — the hut has excellent Wi-Fi · confirm your 9:30am slot for tomorrow · cash preferred for food but cards accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="34" customHeight="1">
+      <c r="A259" s="30" t="inlineStr"/>
+      <c r="B259" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C259" s="32" t="inlineStr">
+        <is>
           <t>Blindsee — 2km from Landhaus Bichlbach — one of Austria's most photogenic lakes · emerald green · often misty in the morning · short walk or 3 min drive from the hotel · many visitors prefer it over Achensee · perfect early morning walk bef</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="3" customHeight="1">
-      <c r="A259" s="33" t="n"/>
-      <c r="B259" s="33" t="n"/>
-      <c r="C259" s="33" t="n"/>
-      <c r="D259" s="33" t="n"/>
-      <c r="E259" s="33" t="n"/>
-      <c r="F259" s="33" t="n"/>
-    </row>
-    <row r="260" ht="20" customHeight="1">
-      <c r="A260" s="3" t="inlineStr">
+    <row r="260" ht="3" customHeight="1">
+      <c r="A260" s="33" t="n"/>
+      <c r="B260" s="33" t="n"/>
+      <c r="C260" s="33" t="n"/>
+      <c r="D260" s="33" t="n"/>
+      <c r="E260" s="33" t="n"/>
+      <c r="F260" s="33" t="n"/>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
         <is>
           <t>DAY 14  |  Jul 3  |  The Lakes of the Dragon — Seebensee · Drachensee · Coburger Hütte  |  ~20 km / 12 mi  ~30m · just Bichlbach ↔ Ehrwald</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="15" customHeight="1">
-      <c r="A261" s="4" t="inlineStr">
+    <row r="262" ht="15" customHeight="1">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>Timeline: Tonight: ATM Ehrwald €60–80 ▸ 7:45am Bichlbach ▸ 8:00am Ehrwalder Almbahn (first car) ▸ 8:10am hike ▸ 9:45am Seebensee mirror ▸ 10:15am Drachensee climb ▸ 11:00am Coburger Hütte Kaiserschmarrn ▸ 12:45pm descent ▸ 2:45pm back at car ▸ 3pm Bichlbach ▸ 7:30pm Heiterwanger See sunset</t>
         </is>
       </c>
     </row>
-    <row r="262" ht="22" customHeight="1">
-      <c r="A262" s="5" t="inlineStr">
+    <row r="263" ht="22" customHeight="1">
+      <c r="A263" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ ATM in Ehrwald tonight — €60–80 cash · Coburger Hütte cash only · no card reader  |  ✅ 7:45am departure — first cable car 8:00am · arrive Seebensee 9:45am · beats 10:30am winds  |  ⚠️ Seebensee mirror reflection before 10:30am — winds create ripples by midday · 9:45am arrival ✅  |  ⚠️ Drachensee path slippery if rained Jul 2 — best-grip boots · 217m steep climb · 30–45 min  |  ➕ E-bikes optional at valley station — cuts Seebensee hike from 1.5hrs to 25 min · saves legs for Drachensee</t>
         </is>
       </c>
     </row>
-    <row r="263" ht="50" customHeight="1">
-      <c r="A263" s="16" t="inlineStr"/>
-      <c r="B263" s="17" t="inlineStr">
+    <row r="264" ht="50" customHeight="1">
+      <c r="A264" s="16" t="inlineStr"/>
+      <c r="B264" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C263" s="16" t="inlineStr">
+      <c r="C264" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D263" s="17" t="inlineStr"/>
-      <c r="E263" s="18" t="inlineStr">
+      <c r="D264" s="17" t="inlineStr"/>
+      <c r="E264" s="18" t="inlineStr">
         <is>
           <t>Tonight (Jul 2 evening): ATM in Ehrwald — withdraw €60–80 cash for the family · Coburger Hütte is cash only — no card reader on the mountain · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
         </is>
       </c>
-      <c r="F263" s="19" t="inlineStr">
+      <c r="F264" s="19" t="inlineStr">
         <is>
           <t>€60 / €12 / €14</t>
         </is>
       </c>
     </row>
-    <row r="264" ht="38" customHeight="1">
-      <c r="A264" s="6" t="inlineStr"/>
-      <c r="B264" s="7" t="inlineStr">
+    <row r="265" ht="38" customHeight="1">
+      <c r="A265" s="6" t="inlineStr"/>
+      <c r="B265" s="7" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C264" s="8" t="inlineStr">
+      <c r="C265" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D264" s="7" t="inlineStr"/>
-      <c r="E264" s="9" t="inlineStr">
+      <c r="D265" s="7" t="inlineStr"/>
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>7:45am — Depart Bichlbach — 5 min drive to Ehrwalder Almbahn valley station · free parking for cable car guests · arrive ~7:55am</t>
         </is>
       </c>
-      <c r="F264" s="10" t="inlineStr">
+      <c r="F265" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="44" customHeight="1">
-      <c r="A265" s="16" t="inlineStr"/>
-      <c r="B265" s="17" t="inlineStr">
+    <row r="266" ht="44" customHeight="1">
+      <c r="A266" s="16" t="inlineStr"/>
+      <c r="B266" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C265" s="16" t="inlineStr">
+      <c r="C266" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D265" s="17" t="inlineStr"/>
-      <c r="E265" s="18" t="inlineStr">
+      <c r="D266" s="17" t="inlineStr"/>
+      <c r="E266" s="18" t="inlineStr">
         <is>
           <t>⭐ 8:00am — Ehrwalder Almbahn — first cable car of the day · ~€26/adult · free parking · 5 min at top for Zugspitze platform view · ⚠️ July high season: opens 8:00am</t>
         </is>
       </c>
-      <c r="F265" s="19" t="inlineStr">
+      <c r="F266" s="19" t="inlineStr">
         <is>
           <t>€26 / 5 min</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="50" customHeight="1">
-      <c r="A266" s="20" t="inlineStr"/>
-      <c r="B266" s="21" t="inlineStr">
+    <row r="267" ht="50" customHeight="1">
+      <c r="A267" s="20" t="inlineStr"/>
+      <c r="B267" s="21" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C266" s="22" t="inlineStr">
+      <c r="C267" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D266" s="21" t="inlineStr"/>
-      <c r="E266" s="23" t="inlineStr">
+      <c r="D267" s="21" t="inlineStr"/>
+      <c r="E267" s="23" t="inlineStr">
         <is>
           <t>8:10am — Hike to Seebensee — 5.6km from top station · wide gravel path · 152m elevation gain · easy · allow 1.5hrs · arrive ~9:45am · ➕ E-bikes available at valley station — cuts hike to 25 min if family wants to save le</t>
         </is>
       </c>
-      <c r="F266" s="24" t="inlineStr">
+      <c r="F267" s="24" t="inlineStr">
         <is>
           <t>6km / 5hr / 25 min</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="50" customHeight="1">
-      <c r="A267" s="6" t="inlineStr"/>
-      <c r="B267" s="7" t="inlineStr">
+    <row r="268" ht="50" customHeight="1">
+      <c r="A268" s="6" t="inlineStr"/>
+      <c r="B268" s="7" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C267" s="8" t="inlineStr">
+      <c r="C268" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D267" s="7" t="inlineStr"/>
-      <c r="E267" s="9" t="inlineStr">
+      <c r="D268" s="7" t="inlineStr"/>
+      <c r="E268" s="9" t="inlineStr">
         <is>
           <t>⭐ ⭐ 9:45am — Seebensee mirror reflection — crystal-clear turquoise water · Zugspitze reflected · winds pick up after 10:30am — 9:45am arrival is perfectly timed · allow 30 min · benches along the southern shore</t>
         </is>
       </c>
-      <c r="F267" s="10" t="inlineStr">
+      <c r="F268" s="10" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="44" customHeight="1">
-      <c r="A268" s="20" t="inlineStr"/>
-      <c r="B268" s="21" t="inlineStr">
+    <row r="269" ht="44" customHeight="1">
+      <c r="A269" s="20" t="inlineStr"/>
+      <c r="B269" s="21" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C268" s="22" t="inlineStr">
+      <c r="C269" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D268" s="21" t="inlineStr"/>
-      <c r="E268" s="23" t="inlineStr">
+      <c r="D269" s="21" t="inlineStr"/>
+      <c r="E269" s="23" t="inlineStr">
         <is>
           <t>10:15am — Drachensee ascent — 1.4km · 217m elevation gain · 30–45 min · ⚠️ slippery if rained Jul 2 · best-grip boots · steeper than Seebensee section but short</t>
         </is>
       </c>
-      <c r="F268" s="24" t="inlineStr">
+      <c r="F269" s="24" t="inlineStr">
         <is>
           <t>4km / 45 min</t>
         </is>
       </c>
     </row>
-    <row r="269" ht="46" customHeight="1">
-      <c r="A269" s="16" t="inlineStr"/>
-      <c r="B269" s="17" t="inlineStr">
+    <row r="270" ht="46" customHeight="1">
+      <c r="A270" s="16" t="inlineStr"/>
+      <c r="B270" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C269" s="16" t="inlineStr">
+      <c r="C270" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D269" s="17" t="inlineStr"/>
-      <c r="E269" s="18" t="inlineStr">
+      <c r="D270" s="17" t="inlineStr"/>
+      <c r="E270" s="18" t="inlineStr">
         <is>
           <t>⭐ ⭐ 11:00am — Coburger Hütte (1,917m) — legendary Kaiserschmarrn — MUST · cash only — bring €60–80 family · outdoor table facing deep blue Drachensee below · allow 1hr 45min</t>
         </is>
       </c>
-      <c r="F269" s="19" t="inlineStr">
+      <c r="F270" s="19" t="inlineStr">
         <is>
           <t>€60 / 1hr / 45min</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="40" customHeight="1">
-      <c r="A270" s="20" t="inlineStr"/>
-      <c r="B270" s="21" t="inlineStr">
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" s="20" t="inlineStr"/>
+      <c r="B271" s="21" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C270" s="22" t="inlineStr">
+      <c r="C271" s="22" t="inlineStr">
         <is>
           <t>Hike</t>
         </is>
       </c>
-      <c r="D270" s="21" t="inlineStr"/>
-      <c r="E270" s="23" t="inlineStr">
+      <c r="D271" s="21" t="inlineStr"/>
+      <c r="E271" s="23" t="inlineStr">
         <is>
           <t>12:45pm — Descent to cable car station — ~1.5hrs back down · same trail · arrive top station ~2:15pm · cable car down · back at car ~2:45pm</t>
         </is>
       </c>
-      <c r="F270" s="24" t="inlineStr">
+      <c r="F271" s="24" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="271" ht="39" customHeight="1">
-      <c r="A271" s="6" t="inlineStr"/>
-      <c r="B271" s="7" t="inlineStr">
+    <row r="272" ht="39" customHeight="1">
+      <c r="A272" s="6" t="inlineStr"/>
+      <c r="B272" s="7" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C271" s="8" t="inlineStr">
+      <c r="C272" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D271" s="7" t="inlineStr"/>
-      <c r="E271" s="9" t="inlineStr">
+      <c r="D272" s="7" t="inlineStr"/>
+      <c r="E272" s="9" t="inlineStr">
         <is>
           <t>3:00pm — Back at Landhaus Bichlbach — shower · rest legs · pack bags for tomorrow · checkout 8am — Neuschwanstein 9:30am · alarm 7:00am</t>
         </is>
       </c>
-      <c r="F271" s="10" t="inlineStr"/>
-    </row>
-    <row r="272" ht="46" customHeight="1">
-      <c r="A272" s="16" t="inlineStr"/>
-      <c r="B272" s="17" t="inlineStr">
+      <c r="F272" s="10" t="inlineStr"/>
+    </row>
+    <row r="273" ht="46" customHeight="1">
+      <c r="A273" s="16" t="inlineStr"/>
+      <c r="B273" s="17" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C272" s="16" t="inlineStr">
+      <c r="C273" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D272" s="17" t="inlineStr"/>
-      <c r="E272" s="18" t="inlineStr">
+      <c r="D273" s="17" t="inlineStr"/>
+      <c r="E273" s="18" t="inlineStr">
         <is>
           <t>⭐ 7:30pm — Heiterwanger See sunset walk — 20 min walk from Landhaus along the Panoramaweg · flat · easy · clears the lactic acid · alpenglow after sunset on the higher path</t>
         </is>
       </c>
-      <c r="F272" s="19" t="inlineStr">
+      <c r="F273" s="19" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
     </row>
-    <row r="273" ht="39" customHeight="1">
-      <c r="A273" s="11" t="inlineStr"/>
-      <c r="B273" s="12" t="inlineStr">
+    <row r="274" ht="39" customHeight="1">
+      <c r="A274" s="11" t="inlineStr"/>
+      <c r="B274" s="12" t="inlineStr">
         <is>
           <t>Jul 3</t>
         </is>
       </c>
-      <c r="C273" s="13" t="inlineStr">
+      <c r="C274" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D273" s="12" t="inlineStr"/>
-      <c r="E273" s="14" t="inlineStr">
+      <c r="D274" s="12" t="inlineStr"/>
+      <c r="E274" s="14" t="inlineStr">
         <is>
           <t>Dinner — Gasthof Bichlbach or hotel restaurant — early dinner + early bed · alarm 7:00am tomorrow · Neuschwanstein 9:30am — last big day</t>
         </is>
       </c>
-      <c r="F273" s="15" t="inlineStr"/>
-    </row>
-    <row r="274" ht="33" customHeight="1">
-      <c r="A274" s="30" t="inlineStr"/>
-      <c r="B274" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C274" s="32" t="inlineStr">
-        <is>
-          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="34" customHeight="1">
+      <c r="F274" s="15" t="inlineStr"/>
+    </row>
+    <row r="275" ht="33" customHeight="1">
       <c r="A275" s="30" t="inlineStr"/>
       <c r="B275" s="31" t="inlineStr">
         <is>
@@ -5938,7 +5949,7 @@
       </c>
       <c r="C275" s="32" t="inlineStr">
         <is>
-          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
+          <t>Coburger Hütte cash only — withdraw €60–80 at Raiffeisenbank ATM in Ehrwald village tonight · budget: Kaiserschmarrn ~€12 · Tiroler Gröstl ~€14 · drinks ~€4–6 each</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5962,7 @@
       </c>
       <c r="C276" s="32" t="inlineStr">
         <is>
-          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
+          <t>Seebensee mirror reflection — must arrive before 10:30am · mountain winds create ripples by midday · morning start from Bichlbach (8:30am) guarantees the calm water window</t>
         </is>
       </c>
     </row>
@@ -5964,180 +5975,169 @@
       </c>
       <c r="C277" s="32" t="inlineStr">
         <is>
+          <t>️ Zugspitze platform at top station — take 5 min before walking to Seebensee · look north toward Germany · see the "other side" of the Zugspitze (2,962m) — same peak visible from Garmisch-Partenkirchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="34" customHeight="1">
+      <c r="A278" s="30" t="inlineStr"/>
+      <c r="B278" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C278" s="32" t="inlineStr">
+        <is>
           <t>Panoramaweg for Heiterwanger See — take the higher Panoramaweg trail not the lakeside path · stays above the valley floor to catch alpenglow after sunset · 20 min from hotel · flat + easy</t>
         </is>
       </c>
     </row>
-    <row r="278" ht="3" customHeight="1">
-      <c r="A278" s="33" t="n"/>
-      <c r="B278" s="33" t="n"/>
-      <c r="C278" s="33" t="n"/>
-      <c r="D278" s="33" t="n"/>
-      <c r="E278" s="33" t="n"/>
-      <c r="F278" s="33" t="n"/>
-    </row>
-    <row r="279" ht="20" customHeight="1">
-      <c r="A279" s="3" t="inlineStr">
+    <row r="279" ht="3" customHeight="1">
+      <c r="A279" s="33" t="n"/>
+      <c r="B279" s="33" t="n"/>
+      <c r="C279" s="33" t="n"/>
+      <c r="D279" s="33" t="n"/>
+      <c r="E279" s="33" t="n"/>
+      <c r="F279" s="33" t="n"/>
+    </row>
+    <row r="280" ht="20" customHeight="1">
+      <c r="A280" s="3" t="inlineStr">
         <is>
           <t>DAY 15  |  Jul 4  |  Zurich Day — Old Town · Lake · Caliente Festival → ZRH  |  ~185 km / 115 mi  ~2h direct · saves 100km vs castle route</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="15" customHeight="1">
-      <c r="A280" s="4" t="inlineStr">
+    <row r="281" ht="15" customHeight="1">
+      <c r="A281" s="4" t="inlineStr">
         <is>
           <t>Timeline: 8:00am Bichlbach checkout ▸ ~10:00am Airport Hotel ZRH ▸ 10:30am return Europcar ▸ 11:00am train to Zurich HB ▸ 11:15am Lindenhof + Grossmünster + Fraumünster ▸ 1:00pm Bahnhofstrasse + Sprüngli ▸ 1:45pm Lake Zurich waterfront ▸ 2:30pm Caliente! Latin Festival ▸ 4:30pm dinner by the lake ▸ 6:00pm train back ▸ early bed</t>
         </is>
       </c>
     </row>
-    <row r="281" ht="22" customHeight="1">
-      <c r="A281" s="5" t="inlineStr">
+    <row r="282" ht="22" customHeight="1">
+      <c r="A282" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Return Europcar ZRH first thing — 10:30am · 5 min drive · done before Zurich  |  ✅ Caliente! Latin Festival Jul 4 — final day · Europe's largest Latin festival · lakefront · family-friendly  |  ✅ Confirm Hilton shuttle 5:30am at front desk tonight — CHF 7/person · NOT walk (2km)  |  ⚠️ Swiss vignette — verify on windscreen before crossing border</t>
         </is>
       </c>
     </row>
-    <row r="282" ht="44" customHeight="1">
-      <c r="A282" s="6" t="inlineStr"/>
-      <c r="B282" s="7" t="inlineStr">
+    <row r="283" ht="44" customHeight="1">
+      <c r="A283" s="6" t="inlineStr"/>
+      <c r="B283" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C282" s="8" t="inlineStr">
+      <c r="C283" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D282" s="7" t="inlineStr"/>
-      <c r="E282" s="9" t="inlineStr">
+      <c r="D283" s="7" t="inlineStr"/>
+      <c r="E283" s="9" t="inlineStr">
         <is>
           <t>8:00am — Checkout Landhaus Bichlbach + depart — ~185km direct to Zurich Airport · ~2hrs via A17/A12/A14 · no border stress · no peak Saturday mountain parking</t>
         </is>
       </c>
-      <c r="F282" s="10" t="inlineStr">
+      <c r="F283" s="10" t="inlineStr">
         <is>
           <t>~185km / ~2hr</t>
         </is>
       </c>
     </row>
-    <row r="283" ht="35" customHeight="1">
-      <c r="A283" s="16" t="inlineStr"/>
-      <c r="B283" s="17" t="inlineStr">
+    <row r="284" ht="35" customHeight="1">
+      <c r="A284" s="16" t="inlineStr"/>
+      <c r="B284" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C283" s="16" t="inlineStr">
+      <c r="C284" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D283" s="17" t="inlineStr"/>
-      <c r="E283" s="18" t="inlineStr">
+      <c r="D284" s="17" t="inlineStr"/>
+      <c r="E284" s="18" t="inlineStr">
         <is>
           <t>Swiss vignette check — cameras trigger a CHF 200 fine if missing · verify on windscreen before entering Switzerland</t>
         </is>
       </c>
-      <c r="F283" s="19" t="inlineStr">
+      <c r="F284" s="19" t="inlineStr">
         <is>
           <t>CHF 200</t>
         </is>
       </c>
     </row>
-    <row r="284" ht="41" customHeight="1">
-      <c r="A284" s="25" t="inlineStr"/>
-      <c r="B284" s="26" t="inlineStr">
+    <row r="285" ht="41" customHeight="1">
+      <c r="A285" s="25" t="inlineStr"/>
+      <c r="B285" s="26" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C284" s="27" t="inlineStr">
+      <c r="C285" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D284" s="26" t="inlineStr"/>
-      <c r="E284" s="28" t="inlineStr">
+      <c r="D285" s="26" t="inlineStr"/>
+      <c r="E285" s="28" t="inlineStr">
         <is>
           <t>~10:00am — Airport Hotel Zurich — drop bags at hotel · Lindbergh-Platz 1, 8152 Glattbrugg · check-in may not be ready — leave bags at reception</t>
         </is>
       </c>
-      <c r="F284" s="29" t="inlineStr"/>
-    </row>
-    <row r="285" ht="46" customHeight="1">
-      <c r="A285" s="6" t="inlineStr"/>
-      <c r="B285" s="7" t="inlineStr">
+      <c r="F285" s="29" t="inlineStr"/>
+    </row>
+    <row r="286" ht="46" customHeight="1">
+      <c r="A286" s="6" t="inlineStr"/>
+      <c r="B286" s="7" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C285" s="8" t="inlineStr">
+      <c r="C286" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D285" s="7" t="inlineStr"/>
-      <c r="E285" s="9" t="inlineStr">
+      <c r="D286" s="7" t="inlineStr"/>
+      <c r="E286" s="9" t="inlineStr">
         <is>
           <t>10:30am — Return Europcar ZRH — 5 min drive from hotel · confirm return closed out correctly · take Hilton shuttle back · keep boarding passes + passports in hand-carry</t>
         </is>
       </c>
-      <c r="F285" s="10" t="inlineStr">
+      <c r="F286" s="10" t="inlineStr">
         <is>
           <t>5 min</t>
         </is>
       </c>
     </row>
-    <row r="286" ht="38" customHeight="1">
-      <c r="A286" s="16" t="inlineStr"/>
-      <c r="B286" s="17" t="inlineStr">
+    <row r="287" ht="38" customHeight="1">
+      <c r="A287" s="16" t="inlineStr"/>
+      <c r="B287" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C286" s="16" t="inlineStr">
+      <c r="C287" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D286" s="17" t="inlineStr"/>
-      <c r="E286" s="18" t="inlineStr">
+      <c r="D287" s="17" t="inlineStr"/>
+      <c r="E287" s="18" t="inlineStr">
         <is>
           <t>11:00am — Train to Zurich HB — Zurich Airport → Zurich HB · 10 min · CHF 7 · runs every 10 min from the airport underground station</t>
         </is>
       </c>
-      <c r="F286" s="19" t="inlineStr">
+      <c r="F287" s="19" t="inlineStr">
         <is>
           <t>10 min / CHF 7 / 10 min</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="37" customHeight="1">
-      <c r="A287" s="20" t="inlineStr"/>
-      <c r="B287" s="21" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C287" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D287" s="21" t="inlineStr"/>
-      <c r="E287" s="23" t="inlineStr">
-        <is>
-          <t>⭐ 11:15am — Lindenhof viewpoint — hilltop square · best city panorama without climbing · Romans used it as a fort · free · 15 min</t>
-        </is>
-      </c>
-      <c r="F287" s="24" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="40" customHeight="1">
+    <row r="288" ht="37" customHeight="1">
       <c r="A288" s="20" t="inlineStr"/>
       <c r="B288" s="21" t="inlineStr">
         <is>
@@ -6152,40 +6152,40 @@
       <c r="D288" s="21" t="inlineStr"/>
       <c r="E288" s="23" t="inlineStr">
         <is>
+          <t>⭐ 11:15am — Lindenhof viewpoint — hilltop square · best city panorama without climbing · Romans used it as a fort · free · 15 min</t>
+        </is>
+      </c>
+      <c r="F288" s="24" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" s="20" t="inlineStr"/>
+      <c r="B289" s="21" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C289" s="22" t="inlineStr">
+        <is>
+          <t>Hike</t>
+        </is>
+      </c>
+      <c r="D289" s="21" t="inlineStr"/>
+      <c r="E289" s="23" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 11:30am — Grossmünster — twin-towered landmark · climb to the top for panorama of city + Lake Zurich · kids love the tower climb · ~CHF 5</t>
         </is>
       </c>
-      <c r="F288" s="24" t="inlineStr">
+      <c r="F289" s="24" t="inlineStr">
         <is>
           <t>CHF 5</t>
         </is>
       </c>
     </row>
-    <row r="289" ht="37" customHeight="1">
-      <c r="A289" s="16" t="inlineStr"/>
-      <c r="B289" s="17" t="inlineStr">
-        <is>
-          <t>Jul 4</t>
-        </is>
-      </c>
-      <c r="C289" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D289" s="17" t="inlineStr"/>
-      <c r="E289" s="18" t="inlineStr">
-        <is>
-          <t>⭐ 12:15pm — Fraumünster — Marc Chagall stained glass windows — genuinely stunning · unlike anything else on the trip · ~CHF 5</t>
-        </is>
-      </c>
-      <c r="F289" s="19" t="inlineStr">
-        <is>
-          <t>CHF 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" ht="43" customHeight="1">
+    <row r="290" ht="37" customHeight="1">
       <c r="A290" s="16" t="inlineStr"/>
       <c r="B290" s="17" t="inlineStr">
         <is>
@@ -6200,16 +6200,16 @@
       <c r="D290" s="17" t="inlineStr"/>
       <c r="E290" s="18" t="inlineStr">
         <is>
-          <t>1:00pm — Bahnhofstrasse — one of the world's great shopping streets · Confiserie Sprüngli for Swiss chocolate + Luxemburgerli macarons — MUST · 30 min stroll</t>
+          <t>⭐ 12:15pm — Fraumünster — Marc Chagall stained glass windows — genuinely stunning · unlike anything else on the trip · ~CHF 5</t>
         </is>
       </c>
       <c r="F290" s="19" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" ht="39" customHeight="1">
+          <t>CHF 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="43" customHeight="1">
       <c r="A291" s="16" t="inlineStr"/>
       <c r="B291" s="17" t="inlineStr">
         <is>
@@ -6224,16 +6224,16 @@
       <c r="D291" s="17" t="inlineStr"/>
       <c r="E291" s="18" t="inlineStr">
         <is>
-          <t>⭐ ⭐ 1:45pm — Lake Zurich waterfront — Bürkliplatz · swans · paddle boats · Alps visible in the background on a clear day · free · 45 min</t>
+          <t>1:00pm — Bahnhofstrasse — one of the world's great shopping streets · Confiserie Sprüngli for Swiss chocolate + Luxemburgerli macarons — MUST · 30 min stroll</t>
         </is>
       </c>
       <c r="F291" s="19" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="50" customHeight="1">
+          <t>30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="39" customHeight="1">
       <c r="A292" s="16" t="inlineStr"/>
       <c r="B292" s="17" t="inlineStr">
         <is>
@@ -6248,93 +6248,104 @@
       <c r="D292" s="17" t="inlineStr"/>
       <c r="E292" s="18" t="inlineStr">
         <is>
+          <t>⭐ ⭐ 1:45pm — Lake Zurich waterfront — Bürkliplatz · swans · paddle boats · Alps visible in the background on a clear day · free · 45 min</t>
+        </is>
+      </c>
+      <c r="F292" s="19" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="50" customHeight="1">
+      <c r="A293" s="16" t="inlineStr"/>
+      <c r="B293" s="17" t="inlineStr">
+        <is>
+          <t>Jul 4</t>
+        </is>
+      </c>
+      <c r="C293" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D293" s="17" t="inlineStr"/>
+      <c r="E293" s="18" t="inlineStr">
+        <is>
           <t>⭐ ⭐ 2:30pm — Caliente! Latin Festival — Jul 3–5 2026 · Europe's largest Latin festival · Kasernenareal · South American music + dancing + food stalls · Jul 4 is the final day — biggest atmosphere · family-friendly · free</t>
         </is>
       </c>
-      <c r="F292" s="19" t="inlineStr"/>
-    </row>
-    <row r="293" ht="44" customHeight="1">
-      <c r="A293" s="11" t="inlineStr"/>
-      <c r="B293" s="12" t="inlineStr">
+      <c r="F293" s="19" t="inlineStr"/>
+    </row>
+    <row r="294" ht="44" customHeight="1">
+      <c r="A294" s="11" t="inlineStr"/>
+      <c r="B294" s="12" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C293" s="13" t="inlineStr">
+      <c r="C294" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D293" s="12" t="inlineStr"/>
-      <c r="E293" s="14" t="inlineStr">
+      <c r="D294" s="12" t="inlineStr"/>
+      <c r="E294" s="14" t="inlineStr">
         <is>
           <t>4:30pm — Early dinner by Lake Zurich — Zeughauskeller (15th century armory beer hall · hearty Swiss meals) · or lakeside restaurant at Bürkliplatz · allow 1.5hrs</t>
         </is>
       </c>
-      <c r="F293" s="15" t="inlineStr">
+      <c r="F294" s="15" t="inlineStr">
         <is>
           <t>5hr</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="27" customHeight="1">
-      <c r="A294" s="16" t="inlineStr"/>
-      <c r="B294" s="17" t="inlineStr">
+    <row r="295" ht="27" customHeight="1">
+      <c r="A295" s="16" t="inlineStr"/>
+      <c r="B295" s="17" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C294" s="16" t="inlineStr">
+      <c r="C295" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D294" s="17" t="inlineStr"/>
-      <c r="E294" s="18" t="inlineStr">
+      <c r="D295" s="17" t="inlineStr"/>
+      <c r="E295" s="18" t="inlineStr">
         <is>
           <t>6:00pm — Train back to airport — Zurich HB → Zurich Airport · 10 min · CHF 7</t>
         </is>
       </c>
-      <c r="F294" s="19" t="inlineStr">
+      <c r="F295" s="19" t="inlineStr">
         <is>
           <t>10 min / CHF 7</t>
         </is>
       </c>
     </row>
-    <row r="295" ht="47" customHeight="1">
-      <c r="A295" s="25" t="inlineStr"/>
-      <c r="B295" s="26" t="inlineStr">
+    <row r="296" ht="47" customHeight="1">
+      <c r="A296" s="25" t="inlineStr"/>
+      <c r="B296" s="26" t="inlineStr">
         <is>
           <t>Jul 4</t>
         </is>
       </c>
-      <c r="C295" s="27" t="inlineStr">
+      <c r="C296" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D295" s="26" t="inlineStr"/>
-      <c r="E295" s="28" t="inlineStr">
+      <c r="D296" s="26" t="inlineStr"/>
+      <c r="E296" s="28" t="inlineStr">
         <is>
           <t>6:30pm — Airport Hotel Zurich — pack final bags · passports in hand-carry · boarding passes to phone wallet · confirm 5:30am shuttle at front desk · set two alarms · early bed</t>
         </is>
       </c>
-      <c r="F295" s="29" t="inlineStr"/>
-    </row>
-    <row r="296" ht="31" customHeight="1">
-      <c r="A296" s="30" t="inlineStr"/>
-      <c r="B296" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C296" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="34" customHeight="1">
+      <c r="F296" s="29" t="inlineStr"/>
+    </row>
+    <row r="297" ht="31" customHeight="1">
       <c r="A297" s="30" t="inlineStr"/>
       <c r="B297" s="31" t="inlineStr">
         <is>
@@ -6343,11 +6354,11 @@
       </c>
       <c r="C297" s="32" t="inlineStr">
         <is>
-          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="30" customHeight="1">
+          <t>⚠️ Castle gate 9:20am — be at the GATE not the ticket centre by 9:20am · €17.50/adult incl. booking fee · guide does not wait · strictly timed entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="34" customHeight="1">
       <c r="A298" s="30" t="inlineStr"/>
       <c r="B298" s="31" t="inlineStr">
         <is>
@@ -6356,11 +6367,11 @@
       </c>
       <c r="C298" s="32" t="inlineStr">
         <is>
-          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="34" customHeight="1">
+          <t>Aescher Swing event Jul 4 from 5pm — restaurant will be extremely crowded for the evening event · arrive 1:30–2:00pm · eat + leave before 4pm · if terrace full: Siedwurst at the kiosk + wooden bench · same views</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="30" customHeight="1">
       <c r="A299" s="30" t="inlineStr"/>
       <c r="B299" s="31" t="inlineStr">
         <is>
@@ -6369,7 +6380,7 @@
       </c>
       <c r="C299" s="32" t="inlineStr">
         <is>
-          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+          <t>Wildkirchli caves — 30°C outside · 10°C inside the caves · pack a light layer in your daypack · 5 min walk through the cave on the path to Aescher</t>
         </is>
       </c>
     </row>
@@ -6382,11 +6393,11 @@
       </c>
       <c r="C300" s="32" t="inlineStr">
         <is>
-          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="301" ht="32" customHeight="1">
+          <t>Return car tonight — drop bags at Airport Hotel Zurich · drive 5 min to Europcar ZRH car return · take Hilton shuttle back · Europcar open until midnight · eliminates 5:30am stress tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="34" customHeight="1">
       <c r="A301" s="30" t="inlineStr"/>
       <c r="B301" s="31" t="inlineStr">
         <is>
@@ -6395,148 +6406,137 @@
       </c>
       <c r="C301" s="32" t="inlineStr">
         <is>
+          <t>Aescher food — Chäs-Chnöpfli (Swiss mac and cheese with Appenzeller) · or Rösti · or Siedwurst at the kiosk if terrace full · same cliff view from the wooden benches outside</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="32" customHeight="1">
+      <c r="A302" s="30" t="inlineStr"/>
+      <c r="B302" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C302" s="32" t="inlineStr">
+        <is>
           <t>⚠️ 5:00am alarm Jul 5 — set two alarms · FI571 departs 7:55am · check-in opens 5:30am · hotel is 5 min walk to terminal · boarding passes on phone tonight</t>
         </is>
       </c>
     </row>
-    <row r="302" ht="3" customHeight="1">
-      <c r="A302" s="33" t="n"/>
-      <c r="B302" s="33" t="n"/>
-      <c r="C302" s="33" t="n"/>
-      <c r="D302" s="33" t="n"/>
-      <c r="E302" s="33" t="n"/>
-      <c r="F302" s="33" t="n"/>
-    </row>
-    <row r="303" ht="20" customHeight="1">
-      <c r="A303" s="3" t="inlineStr">
+    <row r="303" ht="3" customHeight="1">
+      <c r="A303" s="33" t="n"/>
+      <c r="B303" s="33" t="n"/>
+      <c r="C303" s="33" t="n"/>
+      <c r="D303" s="33" t="n"/>
+      <c r="E303" s="33" t="n"/>
+      <c r="F303" s="33" t="n"/>
+    </row>
+    <row r="304" ht="20" customHeight="1">
+      <c r="A304" s="3" t="inlineStr">
         <is>
           <t>DAY 16  |  Jul 5  |  Homebound — ZRH → KEF → MCO · The Final Leg  |  —  —</t>
         </is>
       </c>
     </row>
-    <row r="304" ht="15" customHeight="1">
-      <c r="A304" s="4" t="inlineStr">
+    <row r="305" ht="15" customHeight="1">
+      <c r="A305" s="4" t="inlineStr">
         <is>
           <t>Timeline: Sat night: app check-in ▸ confirm shuttle ▸ 5am wake ▸ 5:30am Hilton shuttle (NOT walk) ▸ 5:45am Terminal 2 · Check-in Row 3 ▸ 6am security + E Gate Skymetro ▸ 7:55am FI571 ZRH→KEF ▸ KEF Pylsur layover ▸ 8:50pm MCO home</t>
         </is>
       </c>
     </row>
-    <row r="305" ht="22" customHeight="1">
-      <c r="A305" s="5" t="inlineStr">
+    <row r="306" ht="22" customHeight="1">
+      <c r="A306" s="5" t="inlineStr">
         <is>
           <t>Key: ✅ Take hotel shuttle NOT walk — Hilton is 2km from terminal · not walkable with luggage · CHF 7/person  |  ✅ Icelandair app check-in Saturday night — digital boarding pass · fast bag drop at Check-in 2 Row 3  |  ✅ US Customs at MCO not KEF — do not leave transit area in Iceland</t>
         </is>
       </c>
     </row>
-    <row r="306" ht="39" customHeight="1">
-      <c r="A306" s="34" t="inlineStr"/>
-      <c r="B306" s="35" t="inlineStr">
+    <row r="307" ht="39" customHeight="1">
+      <c r="A307" s="34" t="inlineStr"/>
+      <c r="B307" s="35" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C306" s="36" t="inlineStr">
+      <c r="C307" s="36" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="D306" s="35" t="inlineStr"/>
-      <c r="E306" s="37" t="inlineStr">
+      <c r="D307" s="35" t="inlineStr"/>
+      <c r="E307" s="37" t="inlineStr">
         <is>
           <t>✅ Night before (Jul 4 Saturday evening) — final prep — (2) Check Europcar/Booking.com email — confirm car return was closed out correctly</t>
         </is>
       </c>
-      <c r="F306" s="38" t="inlineStr"/>
-    </row>
-    <row r="307" ht="40" customHeight="1">
-      <c r="A307" s="11" t="inlineStr"/>
-      <c r="B307" s="12" t="inlineStr">
+      <c r="F307" s="38" t="inlineStr"/>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" s="11" t="inlineStr"/>
+      <c r="B308" s="12" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C307" s="13" t="inlineStr">
+      <c r="C308" s="13" t="inlineStr">
         <is>
           <t>Eat</t>
         </is>
       </c>
-      <c r="D307" s="12" t="inlineStr"/>
-      <c r="E307" s="14" t="inlineStr">
+      <c r="D308" s="12" t="inlineStr"/>
+      <c r="E308" s="14" t="inlineStr">
         <is>
           <t>⏰ 5:00am — Wake up — perfect timing · do not wake earlier unless extra bags need special handling · hotel breakfast starts at 5:30am if needed</t>
         </is>
       </c>
-      <c r="F307" s="15" t="inlineStr"/>
-    </row>
-    <row r="308" ht="31" customHeight="1">
-      <c r="A308" s="16" t="inlineStr"/>
-      <c r="B308" s="17" t="inlineStr">
+      <c r="F308" s="15" t="inlineStr"/>
+    </row>
+    <row r="309" ht="31" customHeight="1">
+      <c r="A309" s="16" t="inlineStr"/>
+      <c r="B309" s="17" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C308" s="16" t="inlineStr">
+      <c r="C309" s="16" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D308" s="17" t="inlineStr"/>
-      <c r="E308" s="18" t="inlineStr">
+      <c r="D309" s="17" t="inlineStr"/>
+      <c r="E309" s="18" t="inlineStr">
         <is>
           <t>⚠️ 5:30am — Hilton shuttle — ❌ do NOT walk · 2km to terminal · CHF 7/person · confirm seat tonight</t>
         </is>
       </c>
-      <c r="F308" s="19" t="inlineStr">
+      <c r="F309" s="19" t="inlineStr">
         <is>
           <t>2km / CHF 7</t>
         </is>
       </c>
     </row>
-    <row r="309" ht="31" customHeight="1">
-      <c r="A309" s="25" t="inlineStr"/>
-      <c r="B309" s="26" t="inlineStr">
+    <row r="310" ht="31" customHeight="1">
+      <c r="A310" s="25" t="inlineStr"/>
+      <c r="B310" s="26" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C309" s="27" t="inlineStr">
+      <c r="C310" s="27" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="D309" s="26" t="inlineStr"/>
-      <c r="E309" s="28" t="inlineStr">
+      <c r="D310" s="26" t="inlineStr"/>
+      <c r="E310" s="28" t="inlineStr">
         <is>
           <t>✈️ 5:45am — Terminal 2, Check-in Row 3 — bag drop opens 5:25am · digital boarding pass on phone</t>
         </is>
       </c>
-      <c r="F309" s="29" t="inlineStr"/>
-    </row>
-    <row r="310" ht="30" customHeight="1">
-      <c r="A310" s="16" t="inlineStr"/>
-      <c r="B310" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C310" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D310" s="17" t="inlineStr"/>
-      <c r="E310" s="18" t="inlineStr">
-        <is>
-          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
-        </is>
-      </c>
-      <c r="F310" s="19" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="311" ht="38" customHeight="1">
+      <c r="F310" s="29" t="inlineStr"/>
+    </row>
+    <row r="311" ht="30" customHeight="1">
       <c r="A311" s="16" t="inlineStr"/>
       <c r="B311" s="17" t="inlineStr">
         <is>
@@ -6551,56 +6551,56 @@
       <c r="D311" s="17" t="inlineStr"/>
       <c r="E311" s="18" t="inlineStr">
         <is>
+          <t>6:00am — Security + E Gates — Skymetro train from main terminal · allow 45 min · Sunday busy</t>
+        </is>
+      </c>
+      <c r="F311" s="19" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="38" customHeight="1">
+      <c r="A312" s="16" t="inlineStr"/>
+      <c r="B312" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C312" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D312" s="17" t="inlineStr"/>
+      <c r="E312" s="18" t="inlineStr">
+        <is>
           <t>Spend remaining Swiss Francs — airport shops + cafés open by 6:00am · CHF coins and small bills are hard to exchange back in the US</t>
         </is>
       </c>
-      <c r="F311" s="19" t="inlineStr"/>
-    </row>
-    <row r="312" ht="19" customHeight="1">
-      <c r="A312" s="6" t="inlineStr"/>
-      <c r="B312" s="7" t="inlineStr">
+      <c r="F312" s="19" t="inlineStr"/>
+    </row>
+    <row r="313" ht="19" customHeight="1">
+      <c r="A313" s="6" t="inlineStr"/>
+      <c r="B313" s="7" t="inlineStr">
         <is>
           <t>Jul 5</t>
         </is>
       </c>
-      <c r="C312" s="8" t="inlineStr">
+      <c r="C313" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D312" s="7" t="inlineStr"/>
-      <c r="E312" s="9" t="inlineStr">
+      <c r="D313" s="7" t="inlineStr"/>
+      <c r="E313" s="9" t="inlineStr">
         <is>
           <t>✈️ 7:55am — FI571 departs ZRH → KEF</t>
         </is>
       </c>
-      <c r="F312" s="10" t="inlineStr"/>
-    </row>
-    <row r="313" ht="37" customHeight="1">
-      <c r="A313" s="16" t="inlineStr"/>
-      <c r="B313" s="17" t="inlineStr">
-        <is>
-          <t>Jul 5</t>
-        </is>
-      </c>
-      <c r="C313" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D313" s="17" t="inlineStr"/>
-      <c r="E313" s="18" t="inlineStr">
-        <is>
-          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
-        </is>
-      </c>
-      <c r="F313" s="19" t="inlineStr">
-        <is>
-          <t>2hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="35" customHeight="1">
+      <c r="F313" s="10" t="inlineStr"/>
+    </row>
+    <row r="314" ht="37" customHeight="1">
       <c r="A314" s="16" t="inlineStr"/>
       <c r="B314" s="17" t="inlineStr">
         <is>
@@ -6615,25 +6615,36 @@
       <c r="D314" s="17" t="inlineStr"/>
       <c r="E314" s="18" t="inlineStr">
         <is>
+          <t>KEF layover tip — 1.5–2hr layover is just enough time · grab a Pylsur — duty-free is excellent here if you missed anything</t>
+        </is>
+      </c>
+      <c r="F314" s="19" t="inlineStr">
+        <is>
+          <t>2hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="35" customHeight="1">
+      <c r="A315" s="16" t="inlineStr"/>
+      <c r="B315" s="17" t="inlineStr">
+        <is>
+          <t>Jul 5</t>
+        </is>
+      </c>
+      <c r="C315" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D315" s="17" t="inlineStr"/>
+      <c r="E315" s="18" t="inlineStr">
+        <is>
           <t>8:50pm — Arrive Orlando MCO — clear US Customs + Immigration at MCO · allow 45–60 min for customs on Sunday evening</t>
         </is>
       </c>
-      <c r="F314" s="19" t="inlineStr">
+      <c r="F315" s="19" t="inlineStr">
         <is>
           <t>60 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="34" customHeight="1">
-      <c r="A315" s="30" t="inlineStr"/>
-      <c r="B315" s="31" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="C315" s="32" t="inlineStr">
-        <is>
-          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6657,7 @@
       </c>
       <c r="C316" s="32" t="inlineStr">
         <is>
-          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
+          <t>⚠️ Do NOT walk to terminal — Hilton Zurich Airport is ~2km from Terminal 2 in Glattbrugg · take the hotel shuttle · CHF 7/person · confirm 5:30am seat at front desk on Saturday evening</t>
         </is>
       </c>
     </row>
@@ -6659,11 +6670,11 @@
       </c>
       <c r="C317" s="32" t="inlineStr">
         <is>
-          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="318" ht="31" customHeight="1">
+          <t>Saturday night app check-in — Icelandair app · download boarding passes to Apple/Google Wallet · check Europcar email for car return confirmation · passports in hand-carry bag · two alarms set</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="34" customHeight="1">
       <c r="A318" s="30" t="inlineStr"/>
       <c r="B318" s="31" t="inlineStr">
         <is>
@@ -6672,17 +6683,30 @@
       </c>
       <c r="C318" s="32" t="inlineStr">
         <is>
+          <t>ZRH Terminal 2 details — Icelandair Check-in 2, Row 3 · E Gates for US-bound flights · Skymetro train from main terminal · extra security check at E Gate is standard · allow 45 min total at airport before gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="31" customHeight="1">
+      <c r="A319" s="30" t="inlineStr"/>
+      <c r="B319" s="31" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C319" s="32" t="inlineStr">
+        <is>
           <t>KEF layover — 1.5–2hrs · Pylsur hot dog (best in the world) · Skyr yoghurt · duty-free is excellent · US customs at MCO not here · do not leave transit</t>
         </is>
       </c>
     </row>
-    <row r="319" ht="3" customHeight="1">
-      <c r="A319" s="33" t="n"/>
-      <c r="B319" s="33" t="n"/>
-      <c r="C319" s="33" t="n"/>
-      <c r="D319" s="33" t="n"/>
-      <c r="E319" s="33" t="n"/>
-      <c r="F319" s="33" t="n"/>
+    <row r="320" ht="3" customHeight="1">
+      <c r="A320" s="33" t="n"/>
+      <c r="B320" s="33" t="n"/>
+      <c r="C320" s="33" t="n"/>
+      <c r="D320" s="33" t="n"/>
+      <c r="E320" s="33" t="n"/>
+      <c r="F320" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="113">
@@ -6694,45 +6718,44 @@
     <mergeCell ref="C217:F217"/>
     <mergeCell ref="C258:F258"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A303:F303"/>
-    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A263:F263"/>
+    <mergeCell ref="A144:F144"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A280:F280"/>
-    <mergeCell ref="A161:F161"/>
     <mergeCell ref="C73:F73"/>
-    <mergeCell ref="C315:F315"/>
     <mergeCell ref="A202:F202"/>
+    <mergeCell ref="C302:F302"/>
     <mergeCell ref="C121:F121"/>
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="A186:F186"/>
     <mergeCell ref="C277:F277"/>
-    <mergeCell ref="A260:F260"/>
     <mergeCell ref="C236:F236"/>
     <mergeCell ref="C276:F276"/>
     <mergeCell ref="A241:F241"/>
     <mergeCell ref="C120:F120"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="C300:F300"/>
+    <mergeCell ref="C278:F278"/>
     <mergeCell ref="A305:F305"/>
+    <mergeCell ref="A243:F243"/>
     <mergeCell ref="A221:F221"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C158:F158"/>
     <mergeCell ref="A163:F163"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A306:F306"/>
     <mergeCell ref="C317:F317"/>
+    <mergeCell ref="C199:F199"/>
     <mergeCell ref="C96:F96"/>
-    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="C239:F239"/>
+    <mergeCell ref="C319:F319"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C235:F235"/>
     <mergeCell ref="A262:F262"/>
-    <mergeCell ref="A240:F240"/>
-    <mergeCell ref="C216:F216"/>
     <mergeCell ref="C98:F98"/>
     <mergeCell ref="A125:F125"/>
     <mergeCell ref="C218:F218"/>
-    <mergeCell ref="C274:F274"/>
-    <mergeCell ref="C137:F137"/>
     <mergeCell ref="A142:F142"/>
     <mergeCell ref="A304:F304"/>
     <mergeCell ref="A79:F79"/>
@@ -6743,23 +6766,24 @@
     <mergeCell ref="C76:F76"/>
     <mergeCell ref="C181:F181"/>
     <mergeCell ref="C119:F119"/>
+    <mergeCell ref="A282:F282"/>
+    <mergeCell ref="A164:F164"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="C155:F155"/>
     <mergeCell ref="C237:F237"/>
     <mergeCell ref="A242:F242"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C53:F53"/>
+    <mergeCell ref="A203:F203"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C179:F179"/>
     <mergeCell ref="C157:F157"/>
+    <mergeCell ref="C160:F160"/>
     <mergeCell ref="C97:F97"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="C318:F318"/>
     <mergeCell ref="C256:F256"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A279:F279"/>
-    <mergeCell ref="C255:F255"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A281:F281"/>
@@ -6767,28 +6791,27 @@
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C95:F95"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="C178:F178"/>
     <mergeCell ref="C297:F297"/>
+    <mergeCell ref="C219:F219"/>
     <mergeCell ref="C299:F299"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="C296:F296"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="C140:F140"/>
     <mergeCell ref="C298:F298"/>
     <mergeCell ref="A185:F185"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="C275:F275"/>
     <mergeCell ref="C156:F156"/>
-    <mergeCell ref="A184:F184"/>
     <mergeCell ref="C74:F74"/>
+    <mergeCell ref="C259:F259"/>
     <mergeCell ref="C197:F197"/>
     <mergeCell ref="C35:F35"/>
-    <mergeCell ref="A220:F220"/>
-    <mergeCell ref="C196:F196"/>
     <mergeCell ref="A201:F201"/>
     <mergeCell ref="C99:F99"/>
+    <mergeCell ref="C183:F183"/>
     <mergeCell ref="A261:F261"/>
     <mergeCell ref="C301:F301"/>
     <mergeCell ref="C180:F180"/>
@@ -6799,6 +6822,7 @@
     <mergeCell ref="C198:F198"/>
     <mergeCell ref="C238:F238"/>
     <mergeCell ref="C182:F182"/>
+    <mergeCell ref="A187:F187"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -157,12 +157,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="006B7280"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -338,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -542,22 +536,10 @@
     <xf numFmtId="0" fontId="23" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,13 +557,13 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -590,19 +572,19 @@
     <xf numFmtId="0" fontId="23" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4966,7 +4948,7 @@
     <row r="223" ht="22" customHeight="1">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Key: ️ Plan A: P2 Compatsch — keep checking seiseralm.it for cancellations · must arrive before 9am · €30  |   Plan B: Seis cable car → Compatsch — park in Seis · ~€30/adult RT · no booking · no 9am rule · same trailhead  |   St. Valentin gate closes 9:00am SHARP — leave Collalbo 7:45am · arrive 8:30am · no exceptions  |  ❌ Skip Rifugio Zallinger — 4hr RT or 2 extra lifts · impractical · eat at Tschötsch Alm instead  |  ⚠️ Brenner Lueg Bridge construction 2026 — 30–45 min delay · Digital Flex toll essential</t>
+          <t>Key: ✅ P2 Compatsch booked · Ticket 325F53124754 · pass St. Valentin before 09:00 · bring voucher  |   St. Valentin gate closes 9:00am SHARP — leave Collalbo 7:45am · arrive 8:30am · no exceptions  |  ❌ Skip Rifugio Zallinger — 4hr RT or 2 extra lifts · impractical · eat at Tschötsch Alm instead  |  ⚠️ Brenner Lueg Bridge construction 2026 — 30–45 min delay · Digital Flex toll essential</t>
         </is>
       </c>
     </row>
@@ -5019,26 +5001,26 @@
       </c>
     </row>
     <row r="226" ht="50" customHeight="1">
-      <c r="A226" s="20" t="inlineStr"/>
-      <c r="B226" s="21" t="inlineStr">
+      <c r="A226" s="16" t="inlineStr"/>
+      <c r="B226" s="17" t="inlineStr">
         <is>
           <t>Jul 1</t>
         </is>
       </c>
-      <c r="C226" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D226" s="21" t="inlineStr"/>
-      <c r="E226" s="23" t="inlineStr">
-        <is>
-          <t>P2 Compatsch parking — ⚠️ Currently fully booked · keep checking seiseralm.it for cancellations · slots open up to 6 days before · €30 cash · must arrive before 9am · cameras enforce the gate ·  Plan B: Seis–Compatsch ca</t>
-        </is>
-      </c>
-      <c r="F226" s="24" t="inlineStr">
-        <is>
-          <t>€30 / €30 / €65</t>
+      <c r="C226" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D226" s="17" t="inlineStr"/>
+      <c r="E226" s="18" t="inlineStr">
+        <is>
+          <t>️ P2 Compatsch parking — ✅ Booked · Ticket 325F53124754 · €30 · ⚠️ Pass St. Valentin checkpoint before 09:00 SHARP · entry allowed 05:00–09:30 · plate AI55582 auto-read at barrier · bring voucher — it is your entry ticke</t>
+        </is>
+      </c>
+      <c r="F226" s="19" t="inlineStr">
+        <is>
+          <t>€30</t>
         </is>
       </c>
     </row>
@@ -7693,28 +7675,32 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="69" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B8" s="70" t="inlineStr">
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>P2 Compatsch parking — Jul 1</t>
         </is>
       </c>
-      <c r="C8" s="71" t="inlineStr">
-        <is>
-          <t>seiseralm.it · €30/day · must arrive before 9am · QR code scan at barrier above Hotel Zorzi · booking system opens end of June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="71" t="inlineStr">
-        <is>
-          <t>Booking NOT open yet — system opens ~Jun 25 · check seiseralm.it daily from Jun 25 · book immediately when live · within 6-day window from Collalbo · Plan B: Seis cable car (no booking needed)</t>
-        </is>
-      </c>
-      <c r="E8" s="72" t="inlineStr"/>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>Ticket 325F53124754 · Order P039-60627-41931420C6 · €30 · Jul 1 05:00–23:00 · entry 05:00–09:30 · plate AI55582 · seieralmbahn.it</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Booked ✅ · Pass St. Valentin checkpoint before 09:00 · bring voucher as entry ticket · no cancellation</t>
+        </is>
+      </c>
+      <c r="E8" s="70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7730,14 +7716,14 @@
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="74" t="inlineStr">
+      <c r="E9" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="73" t="inlineStr">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7753,14 +7739,14 @@
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr"/>
-      <c r="E10" s="74" t="inlineStr">
+      <c r="E10" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="73" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7776,14 +7762,14 @@
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr"/>
-      <c r="E11" s="74" t="inlineStr">
+      <c r="E11" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="73" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7799,14 +7785,14 @@
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr"/>
-      <c r="E12" s="74" t="inlineStr">
+      <c r="E12" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7822,14 +7808,14 @@
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr"/>
-      <c r="E13" s="74" t="inlineStr">
+      <c r="E13" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="73" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7845,14 +7831,14 @@
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr"/>
-      <c r="E14" s="74" t="inlineStr">
+      <c r="E14" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="73" t="inlineStr">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7872,14 +7858,14 @@
           <t>Booked ✅ — print tickets before departure</t>
         </is>
       </c>
-      <c r="E15" s="74" t="inlineStr">
+      <c r="E15" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7895,14 +7881,14 @@
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr"/>
-      <c r="E16" s="74" t="inlineStr">
+      <c r="E16" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
+      <c r="A17" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7922,14 +7908,14 @@
           <t>Booked ✅ · Arrive Seelände dock by 8:55am (20 min before) · Keep return tickets separately</t>
         </is>
       </c>
-      <c r="E17" s="74" t="inlineStr">
+      <c r="E17" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="73" t="inlineStr">
+      <c r="A18" s="69" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7949,7 +7935,7 @@
           <t>Booked ✅ · update licence plate night before (Jun 28 in Sillian)</t>
         </is>
       </c>
-      <c r="E18" s="74" t="inlineStr">
+      <c r="E18" s="70" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -8014,17 +8000,17 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="76" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>Jun 20–21</t>
         </is>
       </c>
-      <c r="C3" s="76" t="inlineStr">
+      <c r="C3" s="72" t="inlineStr">
         <is>
           <t>Farmhouse Lodge, Vík</t>
         </is>
@@ -8041,17 +8027,17 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="78" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>Jun 21–22</t>
         </is>
       </c>
-      <c r="C4" s="78" t="inlineStr">
+      <c r="C4" s="74" t="inlineStr">
         <is>
           <t>BergOne</t>
         </is>
@@ -8068,17 +8054,17 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>3–4</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Jun 22–24</t>
         </is>
       </c>
-      <c r="C5" s="76" t="inlineStr">
+      <c r="C5" s="72" t="inlineStr">
         <is>
           <t>Camping Jungfrau</t>
         </is>
@@ -8095,17 +8081,17 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="73" t="inlineStr">
         <is>
           <t>5–6</t>
         </is>
       </c>
-      <c r="B6" s="78" t="inlineStr">
+      <c r="B6" s="74" t="inlineStr">
         <is>
           <t>Jun 24–26</t>
         </is>
       </c>
-      <c r="C6" s="78" t="inlineStr">
+      <c r="C6" s="74" t="inlineStr">
         <is>
           <t>One-Bedroom Apartment, Berchtesgaden</t>
         </is>
@@ -8122,17 +8108,17 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="76" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Jun 26–28</t>
         </is>
       </c>
-      <c r="C7" s="76" t="inlineStr">
+      <c r="C7" s="72" t="inlineStr">
         <is>
           <t>Kaiserblick Goisern</t>
         </is>
@@ -8149,17 +8135,17 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="73" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B8" s="78" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>Jun 28–29</t>
         </is>
       </c>
-      <c r="C8" s="78" t="inlineStr">
+      <c r="C8" s="74" t="inlineStr">
         <is>
           <t>Hotel Schwarzer Adler Sillian</t>
         </is>
@@ -8176,17 +8162,17 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>10–11</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>Jun 29–Jul 1</t>
         </is>
       </c>
-      <c r="C9" s="76" t="inlineStr">
+      <c r="C9" s="72" t="inlineStr">
         <is>
           <t>Kaiserau 1907, Collalbo</t>
         </is>
@@ -8203,17 +8189,17 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="73" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B10" s="78" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>Jul 1–2</t>
         </is>
       </c>
-      <c r="C10" s="78" t="inlineStr">
+      <c r="C10" s="74" t="inlineStr">
         <is>
           <t>Keyone Rooms Finkenberg</t>
         </is>
@@ -8230,17 +8216,17 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="75" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>13-14-15</t>
         </is>
       </c>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>Jul 2–4</t>
         </is>
       </c>
-      <c r="C11" s="76" t="inlineStr">
+      <c r="C11" s="72" t="inlineStr">
         <is>
           <t>Landhaus Bichlbach</t>
         </is>
@@ -8257,17 +8243,17 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="73" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B12" s="78" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>Jul 4–5</t>
         </is>
       </c>
-      <c r="C12" s="78" t="inlineStr">
+      <c r="C12" s="74" t="inlineStr">
         <is>
           <t>Airport Hotel Zurich</t>
         </is>
@@ -8336,17 +8322,17 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="76" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>Flights x4 (confirmed)</t>
         </is>
       </c>
-      <c r="B3" s="79" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>$4,088</t>
         </is>
       </c>
-      <c r="C3" s="80" t="inlineStr">
+      <c r="C3" s="76" t="inlineStr">
         <is>
           <t>$4,088</t>
         </is>
@@ -8358,17 +8344,17 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="76" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>Accommodation 15 nights (confirmed)</t>
         </is>
       </c>
-      <c r="B4" s="79" t="inlineStr">
+      <c r="B4" s="75" t="inlineStr">
         <is>
           <t>$3,032</t>
         </is>
       </c>
-      <c r="C4" s="80" t="inlineStr">
+      <c r="C4" s="76" t="inlineStr">
         <is>
           <t>$3,032</t>
         </is>
@@ -8380,17 +8366,17 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="76" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>Car Rental ZRH + KEF (confirmed)</t>
         </is>
       </c>
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>$1,182</t>
         </is>
       </c>
-      <c r="C5" s="80" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>$1,182</t>
         </is>
@@ -8407,12 +8393,12 @@
           <t>Food &amp; Drinks</t>
         </is>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>$1,850</t>
         </is>
       </c>
-      <c r="C6" s="82" t="inlineStr"/>
+      <c r="C6" s="78" t="inlineStr"/>
       <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Update daily</t>
@@ -8420,18 +8406,18 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="83" t="inlineStr">
+      <c r="A7" s="79" t="inlineStr">
         <is>
           <t>Activities &amp; Entry Fees</t>
         </is>
       </c>
-      <c r="B7" s="84" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>$1,100</t>
         </is>
       </c>
-      <c r="C7" s="85" t="inlineStr"/>
-      <c r="D7" s="86" t="inlineStr">
+      <c r="C7" s="81" t="inlineStr"/>
+      <c r="D7" s="82" t="inlineStr">
         <is>
           <t>Cable cars, castle entries</t>
         </is>
@@ -8443,12 +8429,12 @@
           <t>Fuel &amp; Tolls</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>$1,000</t>
         </is>
       </c>
-      <c r="C8" s="82" t="inlineStr"/>
+      <c r="C8" s="78" t="inlineStr"/>
       <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Grossglockner 46.50 EUR, Schlegeis 17 EUR, Auronzo 40 EUR</t>
@@ -8456,32 +8442,32 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="83" t="inlineStr">
+      <c r="A9" s="79" t="inlineStr">
         <is>
           <t>Shopping &amp; Misc</t>
         </is>
       </c>
-      <c r="B9" s="84" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>$400</t>
         </is>
       </c>
-      <c r="C9" s="85" t="inlineStr"/>
-      <c r="D9" s="86" t="inlineStr"/>
+      <c r="C9" s="81" t="inlineStr"/>
+      <c r="D9" s="82" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="87" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>TOTAL CONFIRMED</t>
         </is>
       </c>
-      <c r="B10" s="88" t="inlineStr">
+      <c r="B10" s="84" t="inlineStr">
         <is>
           <t>$8,302</t>
         </is>
       </c>
-      <c r="C10" s="88" t="inlineStr"/>
-      <c r="D10" s="89" t="inlineStr">
+      <c r="C10" s="84" t="inlineStr"/>
+      <c r="D10" s="85" t="inlineStr">
         <is>
           <t>vs est. ~$11,600-$12,900</t>
         </is>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -4308,7 +4308,7 @@
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>Key: ✅ 8am departure — relaxed start · Braies 8:45am · still beautiful · P3 no reservation  |  ❌ Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |  ✅ Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |  ⚠️ Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |  ⚠️ Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
+          <t>Key: ✅ Braies Jun 29 — NO reservation needed · reservation system only starts Jul 1 · drive straight to P3 · pay €12 cash on arrival · 8:45am arrival perfect  |  ❌ Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |  ✅ Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |  ⚠️ Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |  ⚠️ Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
         </is>
       </c>
     </row>
@@ -4336,25 +4336,25 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="49" customHeight="1">
-      <c r="A189" s="16" t="inlineStr"/>
-      <c r="B189" s="17" t="inlineStr">
+    <row r="189" ht="50" customHeight="1">
+      <c r="A189" s="6" t="inlineStr"/>
+      <c r="B189" s="7" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C189" s="16" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D189" s="17" t="inlineStr"/>
-      <c r="E189" s="18" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 · no reservation needed · walk the best half of the lakeside circuit · famous stilt boathouse · morning views · allow 1.5hrs · leave by 10:15am</t>
-        </is>
-      </c>
-      <c r="F189" s="19" t="inlineStr">
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr"/>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 cash · 500m walk to lake · ✅ No reservation needed — Jun 29 is before Jul 1 · Reservation system only activates Jul 1–Sep 15 · drive straight in · pay cash at P3 on arrival · wa</t>
+        </is>
+      </c>
+      <c r="F189" s="10" t="inlineStr">
         <is>
           <t>€12 / 5hr</t>
         </is>

--- a/Europe-2026-VRFamilyTravels-Final.xlsx
+++ b/Europe-2026-VRFamilyTravels-Final.xlsx
@@ -4301,138 +4301,138 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Timeline: 8am Sillian ▸ 8:45am Braies P3 ▸ 10:15am depart ▸ Misurina coffee ▸ 11:15am Auronzo gate ▸ 11:45am Cadini Trail 117 ▸ 1:30pm lunch ▸ 2:30pm Tre Cime walk ▸ 3:45pm Gardena Pass ▸ 5pm Collalbo</t>
+          <t>Timeline: 7:00am Sillian ▸ 8:00am Braies P3 ▸ 8:05am full lake circuit 3.5km ▸ 9:05am rowboat optional ▸ 9:30am depart ▸ 10:15am Misurina coffee ▸ 11:15am Auronzo gate ▸ 11:45am Cadini Trail 117 ▸ 1:30pm lunch ▸ 2:30pm Tre Cime walk ▸ 3:45pm Gardena Pass ▸ 5:00pm Collalbo</t>
         </is>
       </c>
     </row>
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>Key: ✅ Braies Jun 29 — NO reservation needed · reservation system only starts Jul 1 · drive straight to P3 · pay €12 cash on arrival · 8:45am arrival perfect  |  ❌ Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |  ✅ Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |  ⚠️ Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |  ⚠️ Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="48" customHeight="1">
-      <c r="A188" s="6" t="inlineStr"/>
-      <c r="B188" s="7" t="inlineStr">
+          <t>Key: ✅ Braies 8:00am — NO reservation needed · reservation system only starts Jul 1 · drive straight to P3 · pay €12 cash · full 3.5km circuit + rowboat at 8am  |   Rowboat rental at Braies — €20/30min · fits 4 · opens 8am · first in queue · iconic birthday photo for Veena  |  ❌ Prato Piazza dropped — already have Alpe di Siusi Day 12 · same alpine meadow experience  |  ✅ Auronzo gate 11:15am — well within 9am–8:59pm slot · plate auto-read · no queue  |  ⚠️ Cadini final 50m narrow ridge — secondary viewpoint 20m back is 95% as good  |  ⚠️ Update Auronzo licence plate Jun 28 evening at pass.auronzo.info before Sillian dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="50" customHeight="1">
+      <c r="A188" s="16" t="inlineStr"/>
+      <c r="B188" s="17" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D188" s="7" t="inlineStr"/>
-      <c r="E188" s="9" t="inlineStr">
-        <is>
-          <t>8:00am — Depart Sillian — 45 min straight across the Italian border · download offline Dolomites maps tonight if not done · update Auronzo plate at pass.auronzo.info tonight (Jun 28)</t>
-        </is>
-      </c>
-      <c r="F188" s="10" t="inlineStr">
-        <is>
-          <t>45 min</t>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D188" s="17" t="inlineStr"/>
+      <c r="E188" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⭐ ⭐ 8:00am — Lago di Braies — park P3 ~€12 cash · 500m walk to lake · ✅ No reservation needed — Jun 29 is before Jul 1 · reservation system only activates Jul 1–Sep 15 · ⭐ Full 3.5km lake circuit — ~1hr · golden morning </t>
+        </is>
+      </c>
+      <c r="F188" s="19" t="inlineStr">
+        <is>
+          <t>€12 / 5km / ~1hr</t>
         </is>
       </c>
     </row>
     <row r="189" ht="50" customHeight="1">
-      <c r="A189" s="6" t="inlineStr"/>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="A189" s="16" t="inlineStr"/>
+      <c r="B189" s="17" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C189" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D189" s="7" t="inlineStr"/>
-      <c r="E189" s="9" t="inlineStr">
-        <is>
-          <t>⭐ ⭐ 8:45am — Lago di Braies — park P3 ~€12 cash · 500m walk to lake · ✅ No reservation needed — Jun 29 is before Jul 1 · Reservation system only activates Jul 1–Sep 15 · drive straight in · pay cash at P3 on arrival · wa</t>
-        </is>
-      </c>
-      <c r="F189" s="10" t="inlineStr">
-        <is>
-          <t>€12 / 5hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="44" customHeight="1">
-      <c r="A190" s="6" t="inlineStr"/>
-      <c r="B190" s="7" t="inlineStr">
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D189" s="17" t="inlineStr"/>
+      <c r="E189" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⭐ ⭐ 8:00am — Lago di Braies — park P3 ~€12 cash · 500m walk to lake · ✅ No reservation needed — Jun 29 is before Jul 1 · reservation system only activates Jul 1–Sep 15 · ⭐ Full 3.5km lake circuit — ~1hr · golden morning </t>
+        </is>
+      </c>
+      <c r="F189" s="19" t="inlineStr">
+        <is>
+          <t>€12 / 5km / ~1hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="42" customHeight="1">
+      <c r="A190" s="11" t="inlineStr"/>
+      <c r="B190" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D190" s="7" t="inlineStr"/>
-      <c r="E190" s="9" t="inlineStr">
-        <is>
-          <t>☕ 10:15am — Drive via Lago di Misurina — 1hr drive down the valley · stop at Rifugio Misurina café · 15 min coffee + mirror-reflection photo of Tre Cime in the lake</t>
-        </is>
-      </c>
-      <c r="F190" s="10" t="inlineStr">
-        <is>
-          <t>1hr / 15 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="45" customHeight="1">
-      <c r="A191" s="6" t="inlineStr"/>
-      <c r="B191" s="7" t="inlineStr">
+      <c r="C190" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D190" s="12" t="inlineStr"/>
+      <c r="E190" s="14" t="inlineStr">
+        <is>
+          <t>☕ 10:00am — Lago di Misurina coffee stop — mirror lake reflection · Rifugio Misurina terrace · 15 min · Tre Cime visible from the terrace on clear days</t>
+        </is>
+      </c>
+      <c r="F190" s="15" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="48" customHeight="1">
+      <c r="A191" s="11" t="inlineStr"/>
+      <c r="B191" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C191" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D191" s="7" t="inlineStr"/>
-      <c r="E191" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ 11:15am — Auronzo gate — ✅ Pre-booked · PASS3CIME_26017885 · Ticket P26134547 · 9am–8:59pm slot · plate reads automatically · drive straight up · €40 paid · no queue</t>
-        </is>
-      </c>
-      <c r="F191" s="10" t="inlineStr">
-        <is>
-          <t>€40</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="50" customHeight="1">
-      <c r="A192" s="20" t="inlineStr"/>
-      <c r="B192" s="21" t="inlineStr">
+      <c r="C191" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D191" s="12" t="inlineStr"/>
+      <c r="E191" s="14" t="inlineStr">
+        <is>
+          <t>⚠️ 10:45am — Auronzo gate — ✅ Pre-booked · PASS3CIME_26017885 · Ticket P26134547 · 9am–8:59pm slot · plate AI55582 auto-read · no queue · 7km toll road to Rifugio Auronzo at 2,333m</t>
+        </is>
+      </c>
+      <c r="F191" s="15" t="inlineStr">
+        <is>
+          <t>7km</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="42" customHeight="1">
+      <c r="A192" s="11" t="inlineStr"/>
+      <c r="B192" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C192" s="22" t="inlineStr">
-        <is>
-          <t>Hike</t>
-        </is>
-      </c>
-      <c r="D192" s="21" t="inlineStr"/>
-      <c r="E192" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⭐ ⭐ 11:45am — Cadini di Misurina Trail 117 — hike out to the iconic jagged peak viewpoint · 45 min RT at normal pace · ⚠️ final 50m is a narrow ridge · secondary viewpoint 20m back is 95% as good · allow 1hr 45min total </t>
-        </is>
-      </c>
-      <c r="F192" s="24" t="inlineStr">
-        <is>
-          <t>45 min / 1hr / 45min</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="29" customHeight="1">
+      <c r="C192" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr"/>
+      <c r="E192" s="14" t="inlineStr">
+        <is>
+          <t>☕ 10:00am — Lago di Misurina coffee stop — mirror lake reflection · Rifugio Misurina terrace · 15 min · Tre Cime visible from the terrace on clear days</t>
+        </is>
+      </c>
+      <c r="F192" s="15" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="35" customHeight="1">
       <c r="A193" s="11" t="inlineStr"/>
       <c r="B193" s="12" t="inlineStr">
         <is>
@@ -4447,16 +4447,16 @@
       <c r="D193" s="12" t="inlineStr"/>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>1:30pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr</t>
+          <t>1:00pm — Lunch at Rifugio Auronzo — cash is faster · hearty mountain lunch · allow 1hr · budget €40–50 family cash</t>
         </is>
       </c>
       <c r="F193" s="15" t="inlineStr">
         <is>
-          <t>1hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="40" customHeight="1">
+          <t>1hr / €40</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="50" customHeight="1">
       <c r="A194" s="11" t="inlineStr"/>
       <c r="B194" s="12" t="inlineStr">
         <is>
@@ -4471,16 +4471,16 @@
       <c r="D194" s="12" t="inlineStr"/>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>2:30pm — Tre Cime Highlights Walk — flat path to Rifugio Lavaredo (20 min each way) · see the towering north faces up close · allow 1hr 15min</t>
+          <t>2:00pm — Tre Cime highlights walk — 4km RT · 1hr · flat gravel path · walk to Rifugio Lavaredo (20 min each way) · best views of the Three Peaks · easy for kids · loose stones · hiking shoes recommended</t>
         </is>
       </c>
       <c r="F194" s="15" t="inlineStr">
         <is>
-          <t>20 min / 1hr / 15min</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="50" customHeight="1">
+          <t>4km / 1hr / 20 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="48" customHeight="1">
       <c r="A195" s="6" t="inlineStr"/>
       <c r="B195" s="7" t="inlineStr">
         <is>
@@ -4495,34 +4495,34 @@
       <c r="D195" s="7" t="inlineStr"/>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>3:45pm — Passo Gardena scenic drive — drive back down toll road · SS243 Gardena Pass (2,121m) · hairpin turns · low gear descent · ➕ Lagazuoi cable car optional if energy · ~1hr 15min drive</t>
-        </is>
-      </c>
-      <c r="F195" s="10" t="inlineStr">
-        <is>
-          <t>~1hr / 15min</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="43" customHeight="1">
-      <c r="A196" s="25" t="inlineStr"/>
-      <c r="B196" s="26" t="inlineStr">
+          <t>3:15pm — Passo Gardena scenic drive — drive back down toll road · SS243 Gardena Pass 2,121m · stunning Sella Group + Sassolungo views · pull over at any viewpoint on the way down</t>
+        </is>
+      </c>
+      <c r="F195" s="10" t="inlineStr"/>
+    </row>
+    <row r="196" ht="50" customHeight="1">
+      <c r="A196" s="11" t="inlineStr"/>
+      <c r="B196" s="12" t="inlineStr">
         <is>
           <t>Jun 29</t>
         </is>
       </c>
-      <c r="C196" s="27" t="inlineStr">
-        <is>
-          <t>Stay</t>
-        </is>
-      </c>
-      <c r="D196" s="26" t="inlineStr"/>
-      <c r="E196" s="28" t="inlineStr">
-        <is>
-          <t>5:00pm — Kaiserau 1907, Collalbo — ✅ Check in · Via Peter Mayr 65, 39054 Collalbo · check-in 15:00–22:00 · unpack · rest · open a bottle of Italian wine</t>
-        </is>
-      </c>
-      <c r="F196" s="29" t="inlineStr"/>
+      <c r="C196" s="13" t="inlineStr">
+        <is>
+          <t>Eat</t>
+        </is>
+      </c>
+      <c r="D196" s="12" t="inlineStr"/>
+      <c r="E196" s="14" t="inlineStr">
+        <is>
+          <t>4:30pm — Kaiserau 1907, Collalbo — ✅ Check in · Via Peter Mayr 65, 39054 Collalbo · check-in from 3pm ·  Veena’s birthday dinner — book restaurant table tonight · Renon Earth Pyramids 5 min walk — evening light is magica</t>
+        </is>
+      </c>
+      <c r="F196" s="15" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="34" customHeight="1">
       <c r="A197" s="30" t="inlineStr"/>
